--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
@@ -1009,7 +1009,7 @@
         <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
       </c>
       <c r="B17" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>3:21</v>
@@ -1997,7 +1997,7 @@
         <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G43" t="str">
         <v>4:30</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B2" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:09</v>
@@ -477,7 +477,7 @@
         <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:08</v>
@@ -971,7 +971,7 @@
         <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G16" t="str">
         <v>2:56</v>
@@ -1579,7 +1579,7 @@
         <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G32" t="str">
         <v>2:44</v>
@@ -1769,7 +1769,7 @@
         <v>Kiana Ledé - Jury [Official Visualizer]</v>
       </c>
       <c r="B37" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G37" t="str">
         <v>2:31</v>
@@ -1807,7 +1807,7 @@
         <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
       </c>
       <c r="B38" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G38" t="str">
         <v>2:43</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
@@ -591,7 +591,7 @@
         <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B6" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G6" t="str">
         <v>4:12</v>
@@ -629,7 +629,7 @@
         <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
       </c>
       <c r="B7" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:57</v>
@@ -705,7 +705,7 @@
         <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G9" t="str">
         <v>3:48</v>
@@ -857,7 +857,7 @@
         <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
       </c>
       <c r="B13" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G13" t="str">
         <v>4:56</v>
@@ -895,7 +895,7 @@
         <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
       </c>
       <c r="B14" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=366CV87TguE</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G14" t="str">
         <v>2:54</v>
@@ -933,7 +933,7 @@
         <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G15" t="str">
         <v>2:46</v>
@@ -1655,7 +1655,7 @@
         <v>Cannons - These Nights (Live at The Fonda)</v>
       </c>
       <c r="B34" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G34" t="str">
         <v>4:52</v>
@@ -1693,7 +1693,7 @@
         <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
       </c>
       <c r="B35" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>2:13</v>
@@ -1731,7 +1731,7 @@
         <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
       </c>
       <c r="B36" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>3:19</v>
@@ -1883,7 +1883,7 @@
         <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B40" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>3:55</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
@@ -553,7 +553,7 @@
         <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B5" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:13</v>
@@ -743,7 +743,7 @@
         <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G10" t="str">
         <v>4:58</v>
@@ -781,7 +781,7 @@
         <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G11" t="str">
         <v>2:33</v>
@@ -819,7 +819,7 @@
         <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B12" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G12" t="str">
         <v>5:01</v>
@@ -1503,7 +1503,7 @@
         <v>Bazzi - moment (Official Music Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G30" t="str">
         <v>2:43</v>
@@ -1541,7 +1541,7 @@
         <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
       </c>
       <c r="B31" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>4:43</v>
@@ -1617,7 +1617,7 @@
         <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G33" t="str">
         <v>4:37</v>
@@ -1921,7 +1921,7 @@
         <v>Demi Lovato - Really Don't Care (Live)</v>
       </c>
       <c r="B41" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G41" t="str">
         <v>3:52</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -515,19 +515,19 @@
         <v>Natalie Jane - sabotage (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G4" t="str">
         <v>2:57</v>
@@ -559,7 +559,7 @@
         <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -667,19 +667,19 @@
         <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
       </c>
       <c r="B8" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:34</v>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=366CV87TguE</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1845,19 +1845,19 @@
         <v>Maya Hawke - Devil You Know (Official Audio)</v>
       </c>
       <c r="B39" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G39" t="str">
         <v>3:10</v>
@@ -1889,7 +1889,7 @@
         <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/porch-light/1872239892</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/dry-spell/1883177258</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/the-visitor/1882146993</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/i-aint-no-cowboy/1862634799</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/cant-sit-still/1878782917</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245797</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/blow-my-mind/1852752616</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/sata/1874015489</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/una-aventura/1882069505</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/home-feat-hikaru-utada/1845190340</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/dirty-wedding-dress/1872842320</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/fastest-gun-alive/1874700373</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/imposible/1880775726</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/trade-places/1878823464</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/motion-party/1882152039</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/woman/1882549709</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/sunburn/1880836041</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/que-te-cost%C3%B3/1882108997</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/oooshxt/1879612533</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/cruel-world/1859630041</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/star/1876633306</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/get-go/1862570884</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/thunderwave/1861531685</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/club-song/1882478246</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/better-man/1880496044</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/sabotage/1882209853</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/2000s-pop-punk-rnb/1878820143</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/naked/1883802157</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/catharina/1880130477</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/through-the-pain-feat-pozer/1877868063</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/trying-times/1862353792</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/595/1880470541</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/when-did-you-stop-loving-me/1879593803</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/call-me/1882521075</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/mi-amor/1872454951</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/boba/1880372256</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/video-shoot/1882892621</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/talk-to-me-nuh/1882510363</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/just-believe/1884083105</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/knife-in-the-heart/1857952500</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/the-way-we-touch/1875315428</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/dangerous/1867202642</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/when-i-wake-up/1878237800</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/breathe/1882808152</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/minty/1870867418</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/earth/1870867498</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/drink-the-water/1883172887</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/a-rainy-night-in-soho/1878459216</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/if-i-dont-leave-im-gonna-stay/1880111466</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/muchacho-alegre/1880256976</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/real-slow/1869618394</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/mountain-girl/1870722299</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/like-a-spark/1876952751</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/cheesecake/1882526540</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/always-let-you-down/1871578121</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/freakin-out/1879596115</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/name-in-vein/1880069474</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/st-catherines-wheel/1868804170</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/undefeated-champion/1840517120</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/pull-up/1854381591</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/ranjha/1882965642</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/zombies-in-love/1880178176</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/days-of-us/1868438268</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/life-of-a-man/1882845328</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/ya-no/1882115676</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/do-you-really-love-her/1879639011</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/relieve-you/1879589717</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/safety/1878181748</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/starlet/1873450846</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/physical/1883210753</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/im-dying-to-feel-alive-again/1880883509</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/regalito/1880846653</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/cruel-streak/1858689493</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/die-young/1870715300</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/island-girl/1884461360</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/girly-things/1876032954</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/looking-lovely-feat-robin-thicke/1878437828</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/tommys-song/1876670040</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/rainbows/1882790536</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/butterflies/1878228436</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/youre-right/1874975857</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/bible-belt/1821125622</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/daze/1862607801</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/passionfruit/1878215125</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/madan/1879822223</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/bad-bitch/1882818210</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/shame/1874080307</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/teach-you-to-love-me/1883146005</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/the-fix/1882082897</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/hanging-on-hope/1881749452</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/i-know-what-to-say-now/1879440545</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/feel-something/1876008375</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/you-or-me/1869085528</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -7779,7 +7779,7 @@
         <v>https://music.apple.com/us/song/mortercheyn/1862521946</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -7817,7 +7817,7 @@
         <v>https://music.apple.com/us/song/rip-the-god/1866957697</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -7855,7 +7855,7 @@
         <v>https://music.apple.com/us/song/who-we-are/1879626950</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -7893,7 +7893,7 @@
         <v>https://music.apple.com/us/song/reels-in-360/1867998408</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E198" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
@@ -1009,7 +1009,7 @@
         <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
       </c>
       <c r="B17" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>3:21</v>
@@ -1047,7 +1047,7 @@
         <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G18" t="str">
         <v>3:16</v>
@@ -1085,7 +1085,7 @@
         <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
       </c>
       <c r="B19" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G19" t="str">
         <v>2:41</v>
@@ -1123,7 +1123,7 @@
         <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>2:29</v>
@@ -1161,7 +1161,7 @@
         <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
       </c>
       <c r="B21" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G21" t="str">
         <v>2:43</v>
@@ -1199,7 +1199,7 @@
         <v>Matt Hansen - SAME TIME (Official Live Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G22" t="str">
         <v>3:46</v>
@@ -1237,7 +1237,7 @@
         <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>4:01</v>
@@ -1275,7 +1275,7 @@
         <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G24" t="str">
         <v>3:23</v>
@@ -1313,7 +1313,7 @@
         <v>almost monday - leaving is easy (official video)</v>
       </c>
       <c r="B25" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G25" t="str">
         <v>3:39</v>
@@ -1351,7 +1351,7 @@
         <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>3:04</v>
@@ -1389,7 +1389,7 @@
         <v>vaultboy - DELETED (Official Lyric Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G27" t="str">
         <v>3:25</v>
@@ -1427,7 +1427,7 @@
         <v>The Warning - Kerosene (Official Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G28" t="str">
         <v>3:49</v>
@@ -1465,7 +1465,7 @@
         <v>aron! - Wonderful Thing (City View Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G29" t="str">
         <v>2:14</v>
@@ -1959,7 +1959,7 @@
         <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
       </c>
       <c r="B42" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G42" t="str">
         <v>2:53</v>
@@ -4201,7 +4201,7 @@
         <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B101" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v>4:39</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
@@ -4163,7 +4163,7 @@
         <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
       </c>
       <c r="B100" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v>5:32</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B2" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:09</v>
@@ -477,7 +477,7 @@
         <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:08</v>
@@ -1579,7 +1579,7 @@
         <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G32" t="str">
         <v>2:44</v>
@@ -1807,7 +1807,7 @@
         <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
       </c>
       <c r="B38" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G38" t="str">
         <v>2:43</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L198"/>
+  <dimension ref="A1:L199"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -553,7 +553,7 @@
         <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B5" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:13</v>
@@ -591,7 +591,7 @@
         <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B6" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G6" t="str">
         <v>4:12</v>
@@ -629,7 +629,7 @@
         <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
       </c>
       <c r="B7" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:57</v>
@@ -705,7 +705,7 @@
         <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G9" t="str">
         <v>3:48</v>
@@ -857,7 +857,7 @@
         <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
       </c>
       <c r="B13" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G13" t="str">
         <v>4:56</v>
@@ -895,7 +895,7 @@
         <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
       </c>
       <c r="B14" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=366CV87TguE</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G14" t="str">
         <v>2:54</v>
@@ -933,7 +933,7 @@
         <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G15" t="str">
         <v>2:46</v>
@@ -971,7 +971,7 @@
         <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G16" t="str">
         <v>2:56</v>
@@ -1541,7 +1541,7 @@
         <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
       </c>
       <c r="B31" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>4:43</v>
@@ -1617,7 +1617,7 @@
         <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G33" t="str">
         <v>4:37</v>
@@ -1655,7 +1655,7 @@
         <v>Cannons - These Nights (Live at The Fonda)</v>
       </c>
       <c r="B34" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G34" t="str">
         <v>4:52</v>
@@ -1693,7 +1693,7 @@
         <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
       </c>
       <c r="B35" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>2:13</v>
@@ -1731,7 +1731,7 @@
         <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
       </c>
       <c r="B36" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>3:19</v>
@@ -1769,7 +1769,7 @@
         <v>Kiana Ledé - Jury [Official Visualizer]</v>
       </c>
       <c r="B37" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G37" t="str">
         <v>2:31</v>
@@ -1883,7 +1883,7 @@
         <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B40" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G40" t="str">
         <v>3:55</v>
@@ -1921,7 +1921,7 @@
         <v>Demi Lovato - Really Don't Care (Live)</v>
       </c>
       <c r="B41" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G41" t="str">
         <v>3:52</v>
@@ -3973,7 +3973,7 @@
         <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
       </c>
       <c r="B95" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G95" t="str">
         <v>3:35</v>
@@ -4049,7 +4049,7 @@
         <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
       </c>
       <c r="B97" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
         <v>4:38</v>
@@ -4087,7 +4087,7 @@
         <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
       </c>
       <c r="B98" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v>3:46</v>
@@ -4125,7 +4125,7 @@
         <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
         <v>3:08</v>
@@ -4236,13 +4236,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Porch Light</v>
+        <v>Riptides</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/porch-light/1872239892</v>
+        <v>https://music.apple.com/us/song/riptides/1878362645</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-16</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>The Great Divide</v>
+        <v>I Built You a Tower</v>
       </c>
       <c r="G102" t="str">
-        <v>4:22</v>
+        <v>3:17</v>
       </c>
       <c r="H102" t="str">
-        <v>Noah Kahan</v>
+        <v>Death Cab for Cutie</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
+        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/porch-light/1872239868</v>
+        <v>https://music.apple.com/us/album/riptides/1878362451</v>
       </c>
       <c r="L102" t="str">
-        <v>Porch Light - Noah Kahan</v>
+        <v>Riptides - Death Cab for Cutie</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Dry Spell</v>
+        <v>Porch Light</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/dry-spell/1883177258</v>
+        <v>https://music.apple.com/us/song/porch-light/1872239892</v>
       </c>
       <c r="D103" t="str">
         <v>2026-03-16</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Middle of Nowhere</v>
+        <v>The Great Divide</v>
       </c>
       <c r="G103" t="str">
-        <v>3:17</v>
+        <v>4:22</v>
       </c>
       <c r="H103" t="str">
-        <v>Kacey Musgraves</v>
+        <v>Noah Kahan</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
+        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/dry-spell/1883176984</v>
+        <v>https://music.apple.com/us/album/porch-light/1872239868</v>
       </c>
       <c r="L103" t="str">
-        <v>Dry Spell - Kacey Musgraves</v>
+        <v>Porch Light - Noah Kahan</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>The Visitor</v>
+        <v>Dry Spell</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/the-visitor/1882146993</v>
+        <v>https://music.apple.com/us/song/dry-spell/1883177258</v>
       </c>
       <c r="D104" t="str">
         <v>2026-03-16</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>The Visitor - Single</v>
+        <v>Middle of Nowhere</v>
       </c>
       <c r="G104" t="str">
-        <v>3:48</v>
+        <v>3:17</v>
       </c>
       <c r="H104" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Kacey Musgraves</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
+        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/the-visitor/1882146992</v>
+        <v>https://music.apple.com/us/album/dry-spell/1883176984</v>
       </c>
       <c r="L104" t="str">
-        <v>The Visitor - SIENNA SPIRO</v>
+        <v>Dry Spell - Kacey Musgraves</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>I Ain't No Cowboy</v>
+        <v>The Visitor</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/i-aint-no-cowboy/1862634799</v>
+        <v>https://music.apple.com/us/song/the-visitor/1882146993</v>
       </c>
       <c r="D105" t="str">
         <v>2026-03-16</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>The Way I Am</v>
+        <v>The Visitor - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>3:13</v>
+        <v>3:48</v>
       </c>
       <c r="H105" t="str">
-        <v>Luke Combs</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
+        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/i-aint-no-cowboy/1862634688</v>
+        <v>https://music.apple.com/us/album/the-visitor/1882146992</v>
       </c>
       <c r="L105" t="str">
-        <v>I Ain't No Cowboy - Luke Combs</v>
+        <v>The Visitor - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Can't Sit Still</v>
+        <v>I Ain't No Cowboy</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/cant-sit-still/1878782917</v>
+        <v>https://music.apple.com/us/song/i-aint-no-cowboy/1862634799</v>
       </c>
       <c r="D106" t="str">
         <v>2026-03-16</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Can't Sit Still - Single</v>
+        <v>The Way I Am</v>
       </c>
       <c r="G106" t="str">
-        <v>3:35</v>
+        <v>3:13</v>
       </c>
       <c r="H106" t="str">
-        <v>Lainey Wilson</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
+        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/cant-sit-still/1878782913</v>
+        <v>https://music.apple.com/us/album/i-aint-no-cowboy/1862634688</v>
       </c>
       <c r="L106" t="str">
-        <v>Can't Sit Still - Lainey Wilson</v>
+        <v>I Ain't No Cowboy - Luke Combs</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>All I Did Was Dream of You (feat. The Marías)</v>
+        <v>Can't Sit Still</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245797</v>
+        <v>https://music.apple.com/us/song/cant-sit-still/1878782917</v>
       </c>
       <c r="D107" t="str">
         <v>2026-03-16</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>All I Did Was Dream of You (feat. The Marías) - Single</v>
+        <v>Can't Sit Still - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>3:43</v>
+        <v>3:35</v>
       </c>
       <c r="H107" t="str">
-        <v>beabadoobee</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/beabadoobee/1307650474</v>
+        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245651</v>
+        <v>https://music.apple.com/us/album/cant-sit-still/1878782913</v>
       </c>
       <c r="L107" t="str">
-        <v>All I Did Was Dream of You (feat. The Marías) - beabadoobee</v>
+        <v>Can't Sit Still - Lainey Wilson</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Blow My Mind</v>
+        <v>All I Did Was Dream of You (feat. The Marías)</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/blow-my-mind/1852752616</v>
+        <v>https://music.apple.com/us/song/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245797</v>
       </c>
       <c r="D108" t="str">
         <v>2026-03-16</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Sexistential</v>
+        <v>All I Did Was Dream of You (feat. The Marías) - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>2:57</v>
+        <v>3:43</v>
       </c>
       <c r="H108" t="str">
-        <v>Robyn</v>
+        <v>beabadoobee</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v>https://music.apple.com/us/artist/beabadoobee/1307650474</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/blow-my-mind/1852752613</v>
+        <v>https://music.apple.com/us/album/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245651</v>
       </c>
       <c r="L108" t="str">
-        <v>Blow My Mind - Robyn</v>
+        <v>All I Did Was Dream of You (feat. The Marías) - beabadoobee</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>SATA</v>
+        <v>Blow My Mind</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/sata/1874015489</v>
+        <v>https://music.apple.com/us/song/blow-my-mind/1852752616</v>
       </c>
       <c r="D109" t="str">
         <v>2026-03-16</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>CTRL ESCAPE</v>
+        <v>Sexistential</v>
       </c>
       <c r="G109" t="str">
-        <v>3:02</v>
+        <v>2:57</v>
       </c>
       <c r="H109" t="str">
-        <v>John Summit</v>
+        <v>Robyn</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/sata/1874015470</v>
+        <v>https://music.apple.com/us/album/blow-my-mind/1852752613</v>
       </c>
       <c r="L109" t="str">
-        <v>SATA - John Summit</v>
+        <v>Blow My Mind - Robyn</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Una Aventura</v>
+        <v>SATA</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/una-aventura/1882069505</v>
+        <v>https://music.apple.com/us/song/sata/1874015489</v>
       </c>
       <c r="D110" t="str">
         <v>2026-03-16</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Una Aventura - Single</v>
+        <v>CTRL ESCAPE</v>
       </c>
       <c r="G110" t="str">
-        <v>3:00</v>
+        <v>3:02</v>
       </c>
       <c r="H110" t="str">
-        <v>Ozuna</v>
+        <v>John Summit</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/ozuna/283578837</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/una-aventura/1882068957</v>
+        <v>https://music.apple.com/us/album/sata/1874015470</v>
       </c>
       <c r="L110" t="str">
-        <v>Una Aventura - Ozuna</v>
+        <v>SATA - John Summit</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Home (feat. Hikaru Utada)</v>
+        <v>Una Aventura</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/home-feat-hikaru-utada/1845190340</v>
+        <v>https://music.apple.com/us/song/una-aventura/1882069505</v>
       </c>
       <c r="D111" t="str">
         <v>2026-03-16</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Whatever's Clever!</v>
+        <v>Una Aventura - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>3:44</v>
+        <v>3:00</v>
       </c>
       <c r="H111" t="str">
-        <v>Charlie Puth</v>
+        <v>Ozuna</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v>https://music.apple.com/us/artist/ozuna/283578837</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/home-feat-hikaru-utada/1845189970</v>
+        <v>https://music.apple.com/us/album/una-aventura/1882068957</v>
       </c>
       <c r="L111" t="str">
-        <v>Home (feat. Hikaru Utada) - Charlie Puth</v>
+        <v>Una Aventura - Ozuna</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>dirty wedding dress</v>
+        <v>Home (feat. Hikaru Utada)</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/dirty-wedding-dress/1872842320</v>
+        <v>https://music.apple.com/us/song/home-feat-hikaru-utada/1845190340</v>
       </c>
       <c r="D112" t="str">
         <v>2026-03-16</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>everyone for ten minutes</v>
+        <v>Whatever's Clever!</v>
       </c>
       <c r="G112" t="str">
-        <v>4:49</v>
+        <v>3:44</v>
       </c>
       <c r="H112" t="str">
-        <v>Bleachers</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/dirty-wedding-dress/1872842313</v>
+        <v>https://music.apple.com/us/album/home-feat-hikaru-utada/1845189970</v>
       </c>
       <c r="L112" t="str">
-        <v>dirty wedding dress - Bleachers</v>
+        <v>Home (feat. Hikaru Utada) - Charlie Puth</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Fastest Gun Alive</v>
+        <v>dirty wedding dress</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/fastest-gun-alive/1874700373</v>
+        <v>https://music.apple.com/us/song/dirty-wedding-dress/1872842320</v>
       </c>
       <c r="D113" t="str">
         <v>2026-03-16</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Age of the Ram</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G113" t="str">
-        <v>3:07</v>
+        <v>4:49</v>
       </c>
       <c r="H113" t="str">
-        <v>Charley Crockett</v>
+        <v>Bleachers</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/fastest-gun-alive/1874700242</v>
+        <v>https://music.apple.com/us/album/dirty-wedding-dress/1872842313</v>
       </c>
       <c r="L113" t="str">
-        <v>Fastest Gun Alive - Charley Crockett</v>
+        <v>dirty wedding dress - Bleachers</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>IMPOSIBLE</v>
+        <v>Fastest Gun Alive</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/imposible/1880775726</v>
+        <v>https://music.apple.com/us/song/fastest-gun-alive/1874700373</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-16</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>IMPOSIBLE - Single</v>
+        <v>Age of the Ram</v>
       </c>
       <c r="G114" t="str">
-        <v>3:13</v>
+        <v>3:07</v>
       </c>
       <c r="H114" t="str">
-        <v>Grupo Frontera</v>
+        <v>Charley Crockett</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
+        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/imposible/1880775721</v>
+        <v>https://music.apple.com/us/album/fastest-gun-alive/1874700242</v>
       </c>
       <c r="L114" t="str">
-        <v>IMPOSIBLE - Grupo Frontera</v>
+        <v>Fastest Gun Alive - Charley Crockett</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Trade Places</v>
+        <v>IMPOSIBLE</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/trade-places/1878823464</v>
+        <v>https://music.apple.com/us/song/imposible/1880775726</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-16</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Monica</v>
+        <v>IMPOSIBLE - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:02</v>
+        <v>3:13</v>
       </c>
       <c r="H115" t="str">
-        <v>Jack Harlow</v>
+        <v>Grupo Frontera</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/jack-harlow/1047679432</v>
+        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/trade-places/1878823462</v>
+        <v>https://music.apple.com/us/album/imposible/1880775721</v>
       </c>
       <c r="L115" t="str">
-        <v>Trade Places - Jack Harlow</v>
+        <v>IMPOSIBLE - Grupo Frontera</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Motion Party</v>
+        <v>Trade Places</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/motion-party/1882152039</v>
+        <v>https://music.apple.com/us/song/trade-places/1878823464</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-16</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Motion Party - Single</v>
+        <v>Monica</v>
       </c>
       <c r="G116" t="str">
-        <v>1:35</v>
+        <v>3:02</v>
       </c>
       <c r="H116" t="str">
-        <v>Bossman Dlow</v>
+        <v>Jack Harlow</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
+        <v>https://music.apple.com/us/artist/jack-harlow/1047679432</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/motion-party/1882151996</v>
+        <v>https://music.apple.com/us/album/trade-places/1878823462</v>
       </c>
       <c r="L116" t="str">
-        <v>Motion Party - Bossman Dlow</v>
+        <v>Trade Places - Jack Harlow</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Woman</v>
+        <v>Motion Party</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/woman/1882549709</v>
+        <v>https://music.apple.com/us/song/motion-party/1882152039</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-16</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Woman - Single</v>
+        <v>Motion Party - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>2:46</v>
+        <v>1:35</v>
       </c>
       <c r="H117" t="str">
-        <v>Kane Brown</v>
+        <v>Bossman Dlow</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/kane-brown/930928857</v>
+        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/woman/1882549705</v>
+        <v>https://music.apple.com/us/album/motion-party/1882151996</v>
       </c>
       <c r="L117" t="str">
-        <v>Woman - Kane Brown</v>
+        <v>Motion Party - Bossman Dlow</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Sunburn</v>
+        <v>Woman</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/sunburn/1880836041</v>
+        <v>https://music.apple.com/us/song/woman/1882549709</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-16</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Sunburn - Single</v>
+        <v>Woman - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>3:05</v>
+        <v>2:46</v>
       </c>
       <c r="H118" t="str">
-        <v>Tucker Wetmore</v>
+        <v>Kane Brown</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/tucker-wetmore/1486724646</v>
+        <v>https://music.apple.com/us/artist/kane-brown/930928857</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/sunburn/1880835818</v>
+        <v>https://music.apple.com/us/album/woman/1882549705</v>
       </c>
       <c r="L118" t="str">
-        <v>Sunburn - Tucker Wetmore</v>
+        <v>Woman - Kane Brown</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Que Te Costó</v>
+        <v>Sunburn</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/que-te-cost%C3%B3/1882108997</v>
+        <v>https://music.apple.com/us/song/sunburn/1880836041</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-16</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Metamorfosis</v>
+        <v>Sunburn - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>2:54</v>
+        <v>3:05</v>
       </c>
       <c r="H119" t="str">
-        <v>Yahritza Y Su Esencia</v>
+        <v>Tucker Wetmore</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
+        <v>https://music.apple.com/us/artist/tucker-wetmore/1486724646</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/que-te-cost%C3%B3/1882108989</v>
+        <v>https://music.apple.com/us/album/sunburn/1880835818</v>
       </c>
       <c r="L119" t="str">
-        <v>Que Te Costó - Yahritza Y Su Esencia</v>
+        <v>Sunburn - Tucker Wetmore</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>oooshxt!</v>
+        <v>Que Te Costó</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/oooshxt/1879612533</v>
+        <v>https://music.apple.com/us/song/que-te-cost%C3%B3/1882108997</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-16</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>oooshxt! - Single</v>
+        <v>Metamorfosis</v>
       </c>
       <c r="G120" t="str">
-        <v>2:15</v>
+        <v>2:54</v>
       </c>
       <c r="H120" t="str">
-        <v>Samara Cyn</v>
+        <v>Yahritza Y Su Esencia</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
+        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/oooshxt/1879612532</v>
+        <v>https://music.apple.com/us/album/que-te-cost%C3%B3/1882108989</v>
       </c>
       <c r="L120" t="str">
-        <v>oooshxt! - Samara Cyn</v>
+        <v>Que Te Costó - Yahritza Y Su Esencia</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Cruel World</v>
+        <v>oooshxt!</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/cruel-world/1859630041</v>
+        <v>https://music.apple.com/us/song/oooshxt/1879612533</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-16</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Cruel World</v>
+        <v>oooshxt! - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:26</v>
+        <v>2:15</v>
       </c>
       <c r="H121" t="str">
-        <v>Holly Humberstone</v>
+        <v>Samara Cyn</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/cruel-world/1859629846</v>
+        <v>https://music.apple.com/us/album/oooshxt/1879612532</v>
       </c>
       <c r="L121" t="str">
-        <v>Cruel World - Holly Humberstone</v>
+        <v>oooshxt! - Samara Cyn</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Star</v>
+        <v>Cruel World</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/star/1876633306</v>
+        <v>https://music.apple.com/us/song/cruel-world/1859630041</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-16</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Star - Single</v>
+        <v>Cruel World</v>
       </c>
       <c r="G122" t="str">
-        <v>3:25</v>
+        <v>3:26</v>
       </c>
       <c r="H122" t="str">
-        <v>Iceage</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/star/1876633303</v>
+        <v>https://music.apple.com/us/album/cruel-world/1859629846</v>
       </c>
       <c r="L122" t="str">
-        <v>Star - Iceage</v>
+        <v>Cruel World - Holly Humberstone</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Get Go</v>
+        <v>Star</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/get-go/1862570884</v>
+        <v>https://music.apple.com/us/song/star/1876633306</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-16</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Ambiguous Desire</v>
+        <v>Star - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>3:22</v>
+        <v>3:25</v>
       </c>
       <c r="H123" t="str">
-        <v>Arlo Parks</v>
+        <v>Iceage</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
+        <v>https://music.apple.com/us/artist/iceage/406846711</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/get-go/1862570378</v>
+        <v>https://music.apple.com/us/album/star/1876633303</v>
       </c>
       <c r="L123" t="str">
-        <v>Get Go - Arlo Parks</v>
+        <v>Star - Iceage</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>ThunderWave</v>
+        <v>Get Go</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/thunderwave/1861531685</v>
+        <v>https://music.apple.com/us/song/get-go/1862570884</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-16</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Distracted</v>
+        <v>Ambiguous Desire</v>
       </c>
       <c r="G124" t="str">
-        <v>3:14</v>
+        <v>3:22</v>
       </c>
       <c r="H124" t="str">
-        <v>Thundercat</v>
+        <v>Arlo Parks</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
+        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/thunderwave/1861531667</v>
+        <v>https://music.apple.com/us/album/get-go/1862570378</v>
       </c>
       <c r="L124" t="str">
-        <v>ThunderWave - Thundercat</v>
+        <v>Get Go - Arlo Parks</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Club Song</v>
+        <v>ThunderWave</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/club-song/1882478246</v>
+        <v>https://music.apple.com/us/song/thunderwave/1861531685</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-16</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Club Song - Single</v>
+        <v>Distracted</v>
       </c>
       <c r="G125" t="str">
-        <v>2:27</v>
+        <v>3:14</v>
       </c>
       <c r="H125" t="str">
-        <v>The Pussycat Dolls</v>
+        <v>Thundercat</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/the-pussycat-dolls/23331509</v>
+        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/club-song/1882478243</v>
+        <v>https://music.apple.com/us/album/thunderwave/1861531667</v>
       </c>
       <c r="L125" t="str">
-        <v>Club Song - The Pussycat Dolls</v>
+        <v>ThunderWave - Thundercat</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Better Man</v>
+        <v>Club Song</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/better-man/1880496044</v>
+        <v>https://music.apple.com/us/song/club-song/1882478246</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-16</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Better Man - Single</v>
+        <v>Club Song - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>2:53</v>
+        <v>2:27</v>
       </c>
       <c r="H126" t="str">
-        <v>jxdn</v>
+        <v>The Pussycat Dolls</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/jxdn/1513237359</v>
+        <v>https://music.apple.com/us/artist/the-pussycat-dolls/23331509</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/better-man/1880496042</v>
+        <v>https://music.apple.com/us/album/club-song/1882478243</v>
       </c>
       <c r="L126" t="str">
-        <v>Better Man - jxdn</v>
+        <v>Club Song - The Pussycat Dolls</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>sabotage</v>
+        <v>Better Man</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/sabotage/1882209853</v>
+        <v>https://music.apple.com/us/song/better-man/1880496044</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-16</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>sabotage - Single</v>
+        <v>Better Man - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>2:58</v>
+        <v>2:53</v>
       </c>
       <c r="H127" t="str">
-        <v>Natalie Jane</v>
+        <v>jxdn</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/natalie-jane/1504380197</v>
+        <v>https://music.apple.com/us/artist/jxdn/1513237359</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/sabotage/1882209670</v>
+        <v>https://music.apple.com/us/album/better-man/1880496042</v>
       </c>
       <c r="L127" t="str">
-        <v>sabotage - Natalie Jane</v>
+        <v>Better Man - jxdn</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>2000s Pop Punk Rnb</v>
+        <v>sabotage</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/2000s-pop-punk-rnb/1878820143</v>
+        <v>https://music.apple.com/us/song/sabotage/1882209853</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-16</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Still Loiteringgg / 2000s Pop Punk Rnb - Single</v>
+        <v>sabotage - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>2:56</v>
+        <v>2:58</v>
       </c>
       <c r="H128" t="str">
-        <v>WHATMORE</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/whatmore/1797119133</v>
+        <v>https://music.apple.com/us/artist/natalie-jane/1504380197</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/2000s-pop-punk-rnb/1878820131</v>
+        <v>https://music.apple.com/us/album/sabotage/1882209670</v>
       </c>
       <c r="L128" t="str">
-        <v>2000s Pop Punk Rnb - WHATMORE</v>
+        <v>sabotage - Natalie Jane</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Naked</v>
+        <v>2000s Pop Punk Rnb</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/naked/1883802157</v>
+        <v>https://music.apple.com/us/song/2000s-pop-punk-rnb/1878820143</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-16</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Naked - Single</v>
+        <v>Still Loiteringgg / 2000s Pop Punk Rnb - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:39</v>
+        <v>2:56</v>
       </c>
       <c r="H129" t="str">
-        <v>Kenya Grace</v>
+        <v>WHATMORE</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
+        <v>https://music.apple.com/us/artist/whatmore/1797119133</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/naked/1883801913</v>
+        <v>https://music.apple.com/us/album/2000s-pop-punk-rnb/1878820131</v>
       </c>
       <c r="L129" t="str">
-        <v>Naked - Kenya Grace</v>
+        <v>2000s Pop Punk Rnb - WHATMORE</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Catharina</v>
+        <v>Naked</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/catharina/1880130477</v>
+        <v>https://music.apple.com/us/song/naked/1883802157</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-16</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Catharina - Single</v>
+        <v>Naked - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>3:27</v>
+        <v>3:39</v>
       </c>
       <c r="H130" t="str">
-        <v>Martin Garrix</v>
+        <v>Kenya Grace</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
+        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/catharina/1880130476</v>
+        <v>https://music.apple.com/us/album/naked/1883801913</v>
       </c>
       <c r="L130" t="str">
-        <v>Catharina - Martin Garrix</v>
+        <v>Naked - Kenya Grace</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Through The Pain (feat. Pozer)</v>
+        <v>Catharina</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/through-the-pain-feat-pozer/1877868063</v>
+        <v>https://music.apple.com/us/song/catharina/1880130477</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-16</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Through The Pain (feat. Pozer) - Single</v>
+        <v>Catharina - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>3:00</v>
+        <v>3:27</v>
       </c>
       <c r="H131" t="str">
-        <v>Chase &amp; Status</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/chase-status/121546679</v>
+        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/through-the-pain-feat-pozer/1877868059</v>
+        <v>https://music.apple.com/us/album/catharina/1880130476</v>
       </c>
       <c r="L131" t="str">
-        <v>Through The Pain (feat. Pozer) - Chase &amp; Status</v>
+        <v>Catharina - Martin Garrix</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Trying Times</v>
+        <v>Through The Pain (feat. Pozer)</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/trying-times/1862353792</v>
+        <v>https://music.apple.com/us/song/through-the-pain-feat-pozer/1877868063</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-16</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Trying Times</v>
+        <v>Through The Pain (feat. Pozer) - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>4:33</v>
+        <v>3:00</v>
       </c>
       <c r="H132" t="str">
-        <v>James Blake</v>
+        <v>Chase &amp; Status</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/chase-status/121546679</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/trying-times/1862353780</v>
+        <v>https://music.apple.com/us/album/through-the-pain-feat-pozer/1877868059</v>
       </c>
       <c r="L132" t="str">
-        <v>Trying Times - James Blake</v>
+        <v>Through The Pain (feat. Pozer) - Chase &amp; Status</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>595</v>
+        <v>Trying Times</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/595/1880470541</v>
+        <v>https://music.apple.com/us/song/trying-times/1862353792</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-16</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Be Sweet To Me</v>
+        <v>Trying Times</v>
       </c>
       <c r="G133" t="str">
-        <v>2:29</v>
+        <v>4:33</v>
       </c>
       <c r="H133" t="str">
-        <v>Violet Grohl</v>
+        <v>James Blake</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/595/1880470537</v>
+        <v>https://music.apple.com/us/album/trying-times/1862353780</v>
       </c>
       <c r="L133" t="str">
-        <v>595 - Violet Grohl</v>
+        <v>Trying Times - James Blake</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>When Did You Stop Loving Me?</v>
+        <v>595</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/when-did-you-stop-loving-me/1879593803</v>
+        <v>https://music.apple.com/us/song/595/1880470541</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-16</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Soft 2</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G134" t="str">
-        <v>3:50</v>
+        <v>2:29</v>
       </c>
       <c r="H134" t="str">
-        <v>LANY</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/lany/867853783</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/when-did-you-stop-loving-me/1879593289</v>
+        <v>https://music.apple.com/us/album/595/1880470537</v>
       </c>
       <c r="L134" t="str">
-        <v>When Did You Stop Loving Me? - LANY</v>
+        <v>595 - Violet Grohl</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>CALL ME</v>
+        <v>When Did You Stop Loving Me?</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/call-me/1882521075</v>
+        <v>https://music.apple.com/us/song/when-did-you-stop-loving-me/1879593803</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-16</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>CALL ME - Single</v>
+        <v>Soft 2</v>
       </c>
       <c r="G135" t="str">
-        <v>2:10</v>
+        <v>3:50</v>
       </c>
       <c r="H135" t="str">
-        <v>ALTÉGO</v>
+        <v>LANY</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/alt%C3%A9go/1606418899</v>
+        <v>https://music.apple.com/us/artist/lany/867853783</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/call-me/1882521073</v>
+        <v>https://music.apple.com/us/album/when-did-you-stop-loving-me/1879593289</v>
       </c>
       <c r="L135" t="str">
-        <v>CALL ME - ALTÉGO</v>
+        <v>When Did You Stop Loving Me? - LANY</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Mi Amor</v>
+        <v>CALL ME</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/mi-amor/1872454951</v>
+        <v>https://music.apple.com/us/song/call-me/1882521075</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-16</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Free (Deluxe)</v>
+        <v>CALL ME - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>2:00</v>
+        <v>2:10</v>
       </c>
       <c r="H136" t="str">
-        <v>Nasty C</v>
+        <v>ALTÉGO</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
+        <v>https://music.apple.com/us/artist/alt%C3%A9go/1606418899</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/mi-amor/1872454582</v>
+        <v>https://music.apple.com/us/album/call-me/1882521073</v>
       </c>
       <c r="L136" t="str">
-        <v>Mi Amor - Nasty C</v>
+        <v>CALL ME - ALTÉGO</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>BOBA</v>
+        <v>Mi Amor</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/boba/1880372256</v>
+        <v>https://music.apple.com/us/song/mi-amor/1872454951</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-16</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>BOBA - Single</v>
+        <v>Free (Deluxe)</v>
       </c>
       <c r="G137" t="str">
-        <v>3:00</v>
+        <v>2:00</v>
       </c>
       <c r="H137" t="str">
-        <v>SOFI TUKKER</v>
+        <v>Nasty C</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
+        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/boba/1880372250</v>
+        <v>https://music.apple.com/us/album/mi-amor/1872454582</v>
       </c>
       <c r="L137" t="str">
-        <v>BOBA - SOFI TUKKER</v>
+        <v>Mi Amor - Nasty C</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Video Shoot</v>
+        <v>BOBA</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/video-shoot/1882892621</v>
+        <v>https://music.apple.com/us/song/boba/1880372256</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-16</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Skeletor</v>
+        <v>BOBA - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>2:38</v>
+        <v>3:00</v>
       </c>
       <c r="H138" t="str">
-        <v>Chief Keef</v>
+        <v>SOFI TUKKER</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
+        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/video-shoot/1882892614</v>
+        <v>https://music.apple.com/us/album/boba/1880372250</v>
       </c>
       <c r="L138" t="str">
-        <v>Video Shoot - Chief Keef</v>
+        <v>BOBA - SOFI TUKKER</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Talk To Me Nuh</v>
+        <v>Video Shoot</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/talk-to-me-nuh/1882510363</v>
+        <v>https://music.apple.com/us/song/video-shoot/1882892621</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-16</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Talk To Me Nuh - Single</v>
+        <v>Skeletor</v>
       </c>
       <c r="G139" t="str">
-        <v>2:06</v>
+        <v>2:38</v>
       </c>
       <c r="H139" t="str">
-        <v>Shenseea</v>
+        <v>Chief Keef</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/shenseea/1132311326</v>
+        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/talk-to-me-nuh/1882510361</v>
+        <v>https://music.apple.com/us/album/video-shoot/1882892614</v>
       </c>
       <c r="L139" t="str">
-        <v>Talk To Me Nuh - Shenseea</v>
+        <v>Video Shoot - Chief Keef</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Just Believe</v>
+        <v>Talk To Me Nuh</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/just-believe/1884083105</v>
+        <v>https://music.apple.com/us/song/talk-to-me-nuh/1882510363</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-16</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Just Believe - Single</v>
+        <v>Talk To Me Nuh - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>2:41</v>
+        <v>2:06</v>
       </c>
       <c r="H140" t="str">
-        <v>Bailey Zimmerman</v>
+        <v>Shenseea</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
+        <v>https://music.apple.com/us/artist/shenseea/1132311326</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/just-believe/1884083104</v>
+        <v>https://music.apple.com/us/album/talk-to-me-nuh/1882510361</v>
       </c>
       <c r="L140" t="str">
-        <v>Just Believe - Bailey Zimmerman</v>
+        <v>Talk To Me Nuh - Shenseea</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Knife In The Heart</v>
+        <v>Just Believe</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/knife-in-the-heart/1857952500</v>
+        <v>https://music.apple.com/us/song/just-believe/1884083105</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-16</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>The Afterparty</v>
+        <v>Just Believe - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>2:57</v>
+        <v>2:41</v>
       </c>
       <c r="H141" t="str">
-        <v>Lykke Li</v>
+        <v>Bailey Zimmerman</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
+        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/knife-in-the-heart/1857952252</v>
+        <v>https://music.apple.com/us/album/just-believe/1884083104</v>
       </c>
       <c r="L141" t="str">
-        <v>Knife In The Heart - Lykke Li</v>
+        <v>Just Believe - Bailey Zimmerman</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>The Way We Touch</v>
+        <v>Knife In The Heart</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/the-way-we-touch/1875315428</v>
+        <v>https://music.apple.com/us/song/knife-in-the-heart/1857952500</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-16</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>The Way We Touch - Single</v>
+        <v>The Afterparty</v>
       </c>
       <c r="G142" t="str">
-        <v>3:09</v>
+        <v>2:57</v>
       </c>
       <c r="H142" t="str">
-        <v>Charlotte Cardin</v>
+        <v>Lykke Li</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-cardin/784665014</v>
+        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/the-way-we-touch/1875315210</v>
+        <v>https://music.apple.com/us/album/knife-in-the-heart/1857952252</v>
       </c>
       <c r="L142" t="str">
-        <v>The Way We Touch - Charlotte Cardin</v>
+        <v>Knife In The Heart - Lykke Li</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>DANGEROUS</v>
+        <v>The Way We Touch</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/dangerous/1867202642</v>
+        <v>https://music.apple.com/us/song/the-way-we-touch/1875315428</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-16</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>NIGHTS AFTER VAMP</v>
+        <v>The Way We Touch - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>4:06</v>
+        <v>3:09</v>
       </c>
       <c r="H143" t="str">
-        <v>Magnolia Park</v>
+        <v>Charlotte Cardin</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
+        <v>https://music.apple.com/us/artist/charlotte-cardin/784665014</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/dangerous/1867202638</v>
+        <v>https://music.apple.com/us/album/the-way-we-touch/1875315210</v>
       </c>
       <c r="L143" t="str">
-        <v>DANGEROUS - Magnolia Park</v>
+        <v>The Way We Touch - Charlotte Cardin</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>When I Wake Up</v>
+        <v>DANGEROUS</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/when-i-wake-up/1878237800</v>
+        <v>https://music.apple.com/us/song/dangerous/1867202642</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-16</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Dear God</v>
+        <v>NIGHTS AFTER VAMP</v>
       </c>
       <c r="G144" t="str">
-        <v>3:33</v>
+        <v>4:06</v>
       </c>
       <c r="H144" t="str">
-        <v>The Pretty Reckless</v>
+        <v>Magnolia Park</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
+        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/when-i-wake-up/1878237662</v>
+        <v>https://music.apple.com/us/album/dangerous/1867202638</v>
       </c>
       <c r="L144" t="str">
-        <v>When I Wake Up - The Pretty Reckless</v>
+        <v>DANGEROUS - Magnolia Park</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Breathe</v>
+        <v>When I Wake Up</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/breathe/1882808152</v>
+        <v>https://music.apple.com/us/song/when-i-wake-up/1878237800</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-16</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Breathe - Single</v>
+        <v>Dear God</v>
       </c>
       <c r="G145" t="str">
-        <v>2:56</v>
+        <v>3:33</v>
       </c>
       <c r="H145" t="str">
-        <v>Malcolm Todd</v>
+        <v>The Pretty Reckless</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
+        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/breathe/1882807987</v>
+        <v>https://music.apple.com/us/album/when-i-wake-up/1878237662</v>
       </c>
       <c r="L145" t="str">
-        <v>Breathe - Malcolm Todd</v>
+        <v>When I Wake Up - The Pretty Reckless</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Minty</v>
+        <v>Breathe</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/minty/1870867418</v>
+        <v>https://music.apple.com/us/song/breathe/1882808152</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-16</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>Breathe - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>1:47</v>
+        <v>2:56</v>
       </c>
       <c r="H146" t="str">
-        <v>MIKE</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/mike/1253023714</v>
+        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/minty/1870867411</v>
+        <v>https://music.apple.com/us/album/breathe/1882807987</v>
       </c>
       <c r="L146" t="str">
-        <v>Minty - MIKE</v>
+        <v>Breathe - Malcolm Todd</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Earth</v>
+        <v>Minty</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/earth/1870867498</v>
+        <v>https://music.apple.com/us/song/minty/1870867418</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-16</v>
@@ -5964,33 +5964,33 @@
         <v>POMPEII // UTILITY</v>
       </c>
       <c r="G147" t="str">
-        <v>1:37</v>
+        <v>1:47</v>
       </c>
       <c r="H147" t="str">
-        <v>Earl Sweatshirt</v>
+        <v>MIKE</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
+        <v>https://music.apple.com/us/artist/mike/1253023714</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/earth/1870867411</v>
+        <v>https://music.apple.com/us/album/minty/1870867411</v>
       </c>
       <c r="L147" t="str">
-        <v>Earth - Earl Sweatshirt</v>
+        <v>Minty - MIKE</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Drink The Water</v>
+        <v>Earth</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/drink-the-water/1883172887</v>
+        <v>https://music.apple.com/us/song/earth/1870867498</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-16</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G148" t="str">
-        <v>3:42</v>
+        <v>1:37</v>
       </c>
       <c r="H148" t="str">
-        <v>Jack Johnson</v>
+        <v>Earl Sweatshirt</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
+        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/drink-the-water/1883172879</v>
+        <v>https://music.apple.com/us/album/earth/1870867411</v>
       </c>
       <c r="L148" t="str">
-        <v>Drink The Water - Jack Johnson</v>
+        <v>Earth - Earl Sweatshirt</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>A Rainy Night in Soho</v>
+        <v>Drink The Water</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/a-rainy-night-in-soho/1878459216</v>
+        <v>https://music.apple.com/us/song/drink-the-water/1883172887</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-16</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>A Rainy Night in Soho - Single</v>
+        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
       </c>
       <c r="G149" t="str">
-        <v>4:32</v>
+        <v>3:42</v>
       </c>
       <c r="H149" t="str">
-        <v>Bruce Springsteen</v>
+        <v>Jack Johnson</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/bruce-springsteen/178834</v>
+        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/a-rainy-night-in-soho/1878459215</v>
+        <v>https://music.apple.com/us/album/drink-the-water/1883172879</v>
       </c>
       <c r="L149" t="str">
-        <v>A Rainy Night in Soho - Bruce Springsteen</v>
+        <v>Drink The Water - Jack Johnson</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>If I Don't Leave I'm Gonna Stay</v>
+        <v>A Rainy Night in Soho</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/if-i-dont-leave-im-gonna-stay/1880111466</v>
+        <v>https://music.apple.com/us/song/a-rainy-night-in-soho/1878459216</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-16</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>If I Don't Leave I'm Gonna Stay - Single</v>
+        <v>A Rainy Night in Soho - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:32</v>
+        <v>4:32</v>
       </c>
       <c r="H150" t="str">
-        <v>Carly Pearce</v>
+        <v>Bruce Springsteen</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/bruce-springsteen/178834</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/if-i-dont-leave-im-gonna-stay/1880111464</v>
+        <v>https://music.apple.com/us/album/a-rainy-night-in-soho/1878459215</v>
       </c>
       <c r="L150" t="str">
-        <v>If I Don't Leave I'm Gonna Stay - Carly Pearce</v>
+        <v>A Rainy Night in Soho - Bruce Springsteen</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Muchacho Alegre</v>
+        <v>If I Don't Leave I'm Gonna Stay</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/muchacho-alegre/1880256976</v>
+        <v>https://music.apple.com/us/song/if-i-dont-leave-im-gonna-stay/1880111466</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-16</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Muchacho Alegre - Single</v>
+        <v>If I Don't Leave I'm Gonna Stay - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:08</v>
+        <v>3:32</v>
       </c>
       <c r="H151" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/muchacho-alegre/1880256973</v>
+        <v>https://music.apple.com/us/album/if-i-dont-leave-im-gonna-stay/1880111464</v>
       </c>
       <c r="L151" t="str">
-        <v>Muchacho Alegre - Luis R Conriquez</v>
+        <v>If I Don't Leave I'm Gonna Stay - Carly Pearce</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Real Slow</v>
+        <v>Muchacho Alegre</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/real-slow/1869618394</v>
+        <v>https://music.apple.com/us/song/muchacho-alegre/1880256976</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-16</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Work of Heart</v>
+        <v>Muchacho Alegre - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>3:22</v>
+        <v>3:08</v>
       </c>
       <c r="H152" t="str">
-        <v>Flatland Cavalry</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/real-slow/1869617637</v>
+        <v>https://music.apple.com/us/album/muchacho-alegre/1880256973</v>
       </c>
       <c r="L152" t="str">
-        <v>Real Slow - Flatland Cavalry</v>
+        <v>Muchacho Alegre - Luis R Conriquez</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Mountain Girl</v>
+        <v>Real Slow</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/mountain-girl/1870722299</v>
+        <v>https://music.apple.com/us/song/real-slow/1869618394</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-16</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>As Is</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G153" t="str">
-        <v>2:42</v>
+        <v>3:22</v>
       </c>
       <c r="H153" t="str">
-        <v>Josiah and the Bonnevilles</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/josiah-and-the-bonnevilles/1101954493</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/mountain-girl/1870722288</v>
+        <v>https://music.apple.com/us/album/real-slow/1869617637</v>
       </c>
       <c r="L153" t="str">
-        <v>Mountain Girl - Josiah and the Bonnevilles</v>
+        <v>Real Slow - Flatland Cavalry</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Like a Spark</v>
+        <v>Mountain Girl</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/like-a-spark/1876952751</v>
+        <v>https://music.apple.com/us/song/mountain-girl/1870722299</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-16</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>American Stories</v>
+        <v>As Is</v>
       </c>
       <c r="G154" t="str">
-        <v>3:31</v>
+        <v>2:42</v>
       </c>
       <c r="H154" t="str">
-        <v>Rostam</v>
+        <v>Josiah and the Bonnevilles</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
+        <v>https://music.apple.com/us/artist/josiah-and-the-bonnevilles/1101954493</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/like-a-spark/1876952750</v>
+        <v>https://music.apple.com/us/album/mountain-girl/1870722288</v>
       </c>
       <c r="L154" t="str">
-        <v>Like a Spark - Rostam</v>
+        <v>Mountain Girl - Josiah and the Bonnevilles</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Cheesecake</v>
+        <v>Like a Spark</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/cheesecake/1882526540</v>
+        <v>https://music.apple.com/us/song/like-a-spark/1876952751</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-16</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>So Much To Tell You (Deluxe)</v>
+        <v>American Stories</v>
       </c>
       <c r="G155" t="str">
-        <v>3:29</v>
+        <v>3:31</v>
       </c>
       <c r="H155" t="str">
-        <v>Ax and the Hatchetmen</v>
+        <v>Rostam</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/ax-and-the-hatchetmen/1471855465</v>
+        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/cheesecake/1882525852</v>
+        <v>https://music.apple.com/us/album/like-a-spark/1876952750</v>
       </c>
       <c r="L155" t="str">
-        <v>Cheesecake - Ax and the Hatchetmen</v>
+        <v>Like a Spark - Rostam</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>ALWAYS LET YOU DOWN</v>
+        <v>Cheesecake</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/always-let-you-down/1871578121</v>
+        <v>https://music.apple.com/us/song/cheesecake/1882526540</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-16</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>KINDA HARD</v>
+        <v>So Much To Tell You (Deluxe)</v>
       </c>
       <c r="G156" t="str">
-        <v>3:04</v>
+        <v>3:29</v>
       </c>
       <c r="H156" t="str">
-        <v>Bilmuri</v>
+        <v>Ax and the Hatchetmen</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
+        <v>https://music.apple.com/us/artist/ax-and-the-hatchetmen/1471855465</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/always-let-you-down/1871578103</v>
+        <v>https://music.apple.com/us/album/cheesecake/1882525852</v>
       </c>
       <c r="L156" t="str">
-        <v>ALWAYS LET YOU DOWN - Bilmuri</v>
+        <v>Cheesecake - Ax and the Hatchetmen</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Freakin’ Out</v>
+        <v>ALWAYS LET YOU DOWN</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/freakin-out/1879596115</v>
+        <v>https://music.apple.com/us/song/always-let-you-down/1871578121</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-16</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Freakin’ Out - Single</v>
+        <v>KINDA HARD</v>
       </c>
       <c r="G157" t="str">
-        <v>3:37</v>
+        <v>3:04</v>
       </c>
       <c r="H157" t="str">
-        <v>Dexter and The Moonrocks</v>
+        <v>Bilmuri</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
+        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/freakin-out/1879596114</v>
+        <v>https://music.apple.com/us/album/always-let-you-down/1871578103</v>
       </c>
       <c r="L157" t="str">
-        <v>Freakin’ Out - Dexter and The Moonrocks</v>
+        <v>ALWAYS LET YOU DOWN - Bilmuri</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Name in Vein</v>
+        <v>Freakin’ Out</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/name-in-vein/1880069474</v>
+        <v>https://music.apple.com/us/song/freakin-out/1879596115</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-16</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Name in Vein - Single</v>
+        <v>Freakin’ Out - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:03</v>
+        <v>3:37</v>
       </c>
       <c r="H158" t="str">
-        <v>VOILÀ</v>
+        <v>Dexter and The Moonrocks</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/name-in-vein/1880069473</v>
+        <v>https://music.apple.com/us/album/freakin-out/1879596114</v>
       </c>
       <c r="L158" t="str">
-        <v>Name in Vein - VOILÀ</v>
+        <v>Freakin’ Out - Dexter and The Moonrocks</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>St. Catherine's Wheel</v>
+        <v>Name in Vein</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/st-catherines-wheel/1868804170</v>
+        <v>https://music.apple.com/us/song/name-in-vein/1880069474</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-16</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Into Oblivion</v>
+        <v>Name in Vein - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>4:05</v>
+        <v>3:03</v>
       </c>
       <c r="H159" t="str">
-        <v>Lamb of God</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
+        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/st-catherines-wheel/1868804163</v>
+        <v>https://music.apple.com/us/album/name-in-vein/1880069473</v>
       </c>
       <c r="L159" t="str">
-        <v>St. Catherine's Wheel - Lamb of God</v>
+        <v>Name in Vein - VOILÀ</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Undefeated Champion</v>
+        <v>St. Catherine's Wheel</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/undefeated-champion/1840517120</v>
+        <v>https://music.apple.com/us/song/st-catherines-wheel/1868804170</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-16</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Sweat</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G160" t="str">
-        <v>3:34</v>
+        <v>4:05</v>
       </c>
       <c r="H160" t="str">
-        <v>Melanie C</v>
+        <v>Lamb of God</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
+        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/undefeated-champion/1840516706</v>
+        <v>https://music.apple.com/us/album/st-catherines-wheel/1868804163</v>
       </c>
       <c r="L160" t="str">
-        <v>Undefeated Champion - Melanie C</v>
+        <v>St. Catherine's Wheel - Lamb of God</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Pull Up</v>
+        <v>Undefeated Champion</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/pull-up/1854381591</v>
+        <v>https://music.apple.com/us/song/undefeated-champion/1840517120</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-16</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Pull Up - Single</v>
+        <v>Sweat</v>
       </c>
       <c r="G161" t="str">
-        <v>2:35</v>
+        <v>3:34</v>
       </c>
       <c r="H161" t="str">
-        <v>Collect 200</v>
+        <v>Melanie C</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/collect-200/1804375505</v>
+        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/pull-up/1854381590</v>
+        <v>https://music.apple.com/us/album/undefeated-champion/1840516706</v>
       </c>
       <c r="L161" t="str">
-        <v>Pull Up - Collect 200</v>
+        <v>Undefeated Champion - Melanie C</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Ranjha</v>
+        <v>Pull Up</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/ranjha/1882965642</v>
+        <v>https://music.apple.com/us/song/pull-up/1854381591</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-16</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Ranjha - Single</v>
+        <v>Pull Up - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:04</v>
+        <v>2:35</v>
       </c>
       <c r="H162" t="str">
-        <v>Diljit Dosanjh</v>
+        <v>Collect 200</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/diljit-dosanjh/423087540</v>
+        <v>https://music.apple.com/us/artist/collect-200/1804375505</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/ranjha/1882965641</v>
+        <v>https://music.apple.com/us/album/pull-up/1854381590</v>
       </c>
       <c r="L162" t="str">
-        <v>Ranjha - Diljit Dosanjh</v>
+        <v>Pull Up - Collect 200</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>zombies in love</v>
+        <v>Ranjha</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/zombies-in-love/1880178176</v>
+        <v>https://music.apple.com/us/song/ranjha/1882965642</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-16</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>zombies in love - Single</v>
+        <v>Ranjha - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>2:53</v>
+        <v>3:04</v>
       </c>
       <c r="H163" t="str">
-        <v>paris jackson</v>
+        <v>Diljit Dosanjh</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
+        <v>https://music.apple.com/us/artist/diljit-dosanjh/423087540</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/zombies-in-love/1880178173</v>
+        <v>https://music.apple.com/us/album/ranjha/1882965641</v>
       </c>
       <c r="L163" t="str">
-        <v>zombies in love - paris jackson</v>
+        <v>Ranjha - Diljit Dosanjh</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Days Of Us</v>
+        <v>zombies in love</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/days-of-us/1868438268</v>
+        <v>https://music.apple.com/us/song/zombies-in-love/1880178176</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-16</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Full Circle</v>
+        <v>zombies in love - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>4:39</v>
+        <v>2:53</v>
       </c>
       <c r="H164" t="str">
-        <v>Tom Misch</v>
+        <v>paris jackson</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
+        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/days-of-us/1868437787</v>
+        <v>https://music.apple.com/us/album/zombies-in-love/1880178173</v>
       </c>
       <c r="L164" t="str">
-        <v>Days Of Us - Tom Misch</v>
+        <v>zombies in love - paris jackson</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Life Of A Man</v>
+        <v>Days Of Us</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/life-of-a-man/1882845328</v>
+        <v>https://music.apple.com/us/song/days-of-us/1868438268</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-16</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Life Of A Man - Single</v>
+        <v>Full Circle</v>
       </c>
       <c r="G165" t="str">
-        <v>3:15</v>
+        <v>4:39</v>
       </c>
       <c r="H165" t="str">
-        <v>1Ski OG</v>
+        <v>Tom Misch</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/life-of-a-man/1882845327</v>
+        <v>https://music.apple.com/us/album/days-of-us/1868437787</v>
       </c>
       <c r="L165" t="str">
-        <v>Life Of A Man - 1Ski OG</v>
+        <v>Days Of Us - Tom Misch</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Ya No</v>
+        <v>Life Of A Man</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/ya-no/1882115676</v>
+        <v>https://music.apple.com/us/song/life-of-a-man/1882845328</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-16</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Ya No - Single</v>
+        <v>Life Of A Man - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:40</v>
+        <v>3:15</v>
       </c>
       <c r="H166" t="str">
-        <v>Marca MP</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/ya-no/1882115675</v>
+        <v>https://music.apple.com/us/album/life-of-a-man/1882845327</v>
       </c>
       <c r="L166" t="str">
-        <v>Ya No - Marca MP</v>
+        <v>Life Of A Man - 1Ski OG</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Do You Really Love Her</v>
+        <v>Ya No</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/do-you-really-love-her/1879639011</v>
+        <v>https://music.apple.com/us/song/ya-no/1882115676</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-16</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Do You Really Love Her - Single</v>
+        <v>Ya No - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:48</v>
+        <v>3:40</v>
       </c>
       <c r="H167" t="str">
-        <v>Spacey Jane</v>
+        <v>Marca MP</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
+        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/do-you-really-love-her/1879639009</v>
+        <v>https://music.apple.com/us/album/ya-no/1882115675</v>
       </c>
       <c r="L167" t="str">
-        <v>Do You Really Love Her - Spacey Jane</v>
+        <v>Ya No - Marca MP</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Relieve You</v>
+        <v>Do You Really Love Her</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/relieve-you/1879589717</v>
+        <v>https://music.apple.com/us/song/do-you-really-love-her/1879639011</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-16</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Relieve You - Single</v>
+        <v>Do You Really Love Her - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>2:19</v>
+        <v>3:48</v>
       </c>
       <c r="H168" t="str">
-        <v>4Fargo</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/4fargo/1381605295</v>
+        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/relieve-you/1879589716</v>
+        <v>https://music.apple.com/us/album/do-you-really-love-her/1879639009</v>
       </c>
       <c r="L168" t="str">
-        <v>Relieve You - 4Fargo</v>
+        <v>Do You Really Love Her - Spacey Jane</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Safety</v>
+        <v>Relieve You</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/safety/1878181748</v>
+        <v>https://music.apple.com/us/song/relieve-you/1879589717</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-16</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Safety - Single</v>
+        <v>Relieve You - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:18</v>
+        <v>2:19</v>
       </c>
       <c r="H169" t="str">
-        <v>Lekan</v>
+        <v>4Fargo</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/lekan/1540259198</v>
+        <v>https://music.apple.com/us/artist/4fargo/1381605295</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/safety/1878181738</v>
+        <v>https://music.apple.com/us/album/relieve-you/1879589716</v>
       </c>
       <c r="L169" t="str">
-        <v>Safety - Lekan</v>
+        <v>Relieve You - 4Fargo</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Starlet</v>
+        <v>Safety</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/starlet/1873450846</v>
+        <v>https://music.apple.com/us/song/safety/1878181748</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-16</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>LK99</v>
+        <v>Safety - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>2:56</v>
+        <v>3:18</v>
       </c>
       <c r="H170" t="str">
-        <v>Leven Kali</v>
+        <v>Lekan</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/leven-kali/1166360470</v>
+        <v>https://music.apple.com/us/artist/lekan/1540259198</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/starlet/1873450570</v>
+        <v>https://music.apple.com/us/album/safety/1878181738</v>
       </c>
       <c r="L170" t="str">
-        <v>Starlet - Leven Kali</v>
+        <v>Safety - Lekan</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Physical</v>
+        <v>Starlet</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/physical/1883210753</v>
+        <v>https://music.apple.com/us/song/starlet/1873450846</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-16</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Physical - Single</v>
+        <v>LK99</v>
       </c>
       <c r="G171" t="str">
-        <v>3:52</v>
+        <v>2:56</v>
       </c>
       <c r="H171" t="str">
-        <v>Jacquees</v>
+        <v>Leven Kali</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/jacquees/386779763</v>
+        <v>https://music.apple.com/us/artist/leven-kali/1166360470</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/physical/1883210752</v>
+        <v>https://music.apple.com/us/album/starlet/1873450570</v>
       </c>
       <c r="L171" t="str">
-        <v>Physical - Jacquees</v>
+        <v>Starlet - Leven Kali</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>i'm dying to feel alive again</v>
+        <v>Physical</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/im-dying-to-feel-alive-again/1880883509</v>
+        <v>https://music.apple.com/us/song/physical/1883210753</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-16</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>i'm dying to feel alive again - Single</v>
+        <v>Physical - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>4:29</v>
+        <v>3:52</v>
       </c>
       <c r="H172" t="str">
-        <v>Casper Sage</v>
+        <v>Jacquees</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
+        <v>https://music.apple.com/us/artist/jacquees/386779763</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/im-dying-to-feel-alive-again/1880883507</v>
+        <v>https://music.apple.com/us/album/physical/1883210752</v>
       </c>
       <c r="L172" t="str">
-        <v>i'm dying to feel alive again - Casper Sage</v>
+        <v>Physical - Jacquees</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Regalito</v>
+        <v>i'm dying to feel alive again</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/regalito/1880846653</v>
+        <v>https://music.apple.com/us/song/im-dying-to-feel-alive-again/1880883509</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-16</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>TRESCENDER</v>
+        <v>i'm dying to feel alive again - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:41</v>
+        <v>4:29</v>
       </c>
       <c r="H173" t="str">
-        <v>Piso 21</v>
+        <v>Casper Sage</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/piso-21/403121923</v>
+        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/regalito/1880845994</v>
+        <v>https://music.apple.com/us/album/im-dying-to-feel-alive-again/1880883507</v>
       </c>
       <c r="L173" t="str">
-        <v>Regalito - Piso 21</v>
+        <v>i'm dying to feel alive again - Casper Sage</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Cruel Streak</v>
+        <v>Regalito</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/cruel-streak/1858689493</v>
+        <v>https://music.apple.com/us/song/regalito/1880846653</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-16</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>A Pound of Feathers</v>
+        <v>TRESCENDER</v>
       </c>
       <c r="G174" t="str">
-        <v>4:09</v>
+        <v>2:41</v>
       </c>
       <c r="H174" t="str">
-        <v>The Black Crowes</v>
+        <v>Piso 21</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
+        <v>https://music.apple.com/us/artist/piso-21/403121923</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/cruel-streak/1858689485</v>
+        <v>https://music.apple.com/us/album/regalito/1880845994</v>
       </c>
       <c r="L174" t="str">
-        <v>Cruel Streak - The Black Crowes</v>
+        <v>Regalito - Piso 21</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Die Young</v>
+        <v>Cruel Streak</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/die-young/1870715300</v>
+        <v>https://music.apple.com/us/song/cruel-streak/1858689493</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-16</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Little Wide Open</v>
+        <v>A Pound of Feathers</v>
       </c>
       <c r="G175" t="str">
-        <v>3:52</v>
+        <v>4:09</v>
       </c>
       <c r="H175" t="str">
-        <v>Kevin Morby</v>
+        <v>The Black Crowes</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/kevin-morby/708517315</v>
+        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/die-young/1870715298</v>
+        <v>https://music.apple.com/us/album/cruel-streak/1858689485</v>
       </c>
       <c r="L175" t="str">
-        <v>Die Young - Kevin Morby</v>
+        <v>Cruel Streak - The Black Crowes</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Island Girl</v>
+        <v>Die Young</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/island-girl/1884461360</v>
+        <v>https://music.apple.com/us/song/die-young/1870715300</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-16</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Island Girl - Single</v>
+        <v>Little Wide Open</v>
       </c>
       <c r="G176" t="str">
-        <v>3:27</v>
+        <v>3:52</v>
       </c>
       <c r="H176" t="str">
-        <v>Pia Mia</v>
+        <v>Kevin Morby</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/pia-mia/483071062</v>
+        <v>https://music.apple.com/us/artist/kevin-morby/708517315</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/island-girl/1884461354</v>
+        <v>https://music.apple.com/us/album/die-young/1870715298</v>
       </c>
       <c r="L176" t="str">
-        <v>Island Girl - Pia Mia</v>
+        <v>Die Young - Kevin Morby</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>GIRLY THINGS</v>
+        <v>Island Girl</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/girly-things/1876032954</v>
+        <v>https://music.apple.com/us/song/island-girl/1884461360</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-16</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>GIRLY THINGS - Single</v>
+        <v>Island Girl - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:20</v>
+        <v>3:27</v>
       </c>
       <c r="H177" t="str">
-        <v>Claudia Valentina</v>
+        <v>Pia Mia</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/claudia-valentina/1434841711</v>
+        <v>https://music.apple.com/us/artist/pia-mia/483071062</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/girly-things/1876032953</v>
+        <v>https://music.apple.com/us/album/island-girl/1884461354</v>
       </c>
       <c r="L177" t="str">
-        <v>GIRLY THINGS - Claudia Valentina</v>
+        <v>Island Girl - Pia Mia</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Looking Lovely (feat. Robin Thicke)</v>
+        <v>GIRLY THINGS</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/looking-lovely-feat-robin-thicke/1878437828</v>
+        <v>https://music.apple.com/us/song/girly-things/1876032954</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-16</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Looking Lovely (feat. Robin Thicke) - Single</v>
+        <v>GIRLY THINGS - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:22</v>
+        <v>2:20</v>
       </c>
       <c r="H178" t="str">
-        <v>Shaggy</v>
+        <v>Claudia Valentina</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/shaggy/68616</v>
+        <v>https://music.apple.com/us/artist/claudia-valentina/1434841711</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/looking-lovely-feat-robin-thicke/1878437504</v>
+        <v>https://music.apple.com/us/album/girly-things/1876032953</v>
       </c>
       <c r="L178" t="str">
-        <v>Looking Lovely (feat. Robin Thicke) - Shaggy</v>
+        <v>GIRLY THINGS - Claudia Valentina</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Tommy’s Song</v>
+        <v>Looking Lovely (feat. Robin Thicke)</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/tommys-song/1876670040</v>
+        <v>https://music.apple.com/us/song/looking-lovely-feat-robin-thicke/1878437828</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-16</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Lovers - Single</v>
+        <v>Looking Lovely (feat. Robin Thicke) - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:44</v>
+        <v>3:22</v>
       </c>
       <c r="H179" t="str">
-        <v>Nathaniel Rateliff</v>
+        <v>Shaggy</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/nathaniel-rateliff/362131302</v>
+        <v>https://music.apple.com/us/artist/shaggy/68616</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/tommys-song/1876670038</v>
+        <v>https://music.apple.com/us/album/looking-lovely-feat-robin-thicke/1878437504</v>
       </c>
       <c r="L179" t="str">
-        <v>Tommy’s Song - Nathaniel Rateliff</v>
+        <v>Looking Lovely (feat. Robin Thicke) - Shaggy</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Rainbows</v>
+        <v>Tommy’s Song</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/rainbows/1882790536</v>
+        <v>https://music.apple.com/us/song/tommys-song/1876670040</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-16</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Rainbows - Single</v>
+        <v>Lovers - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:25</v>
+        <v>3:44</v>
       </c>
       <c r="H180" t="str">
-        <v>Allison Russell</v>
+        <v>Nathaniel Rateliff</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/allison-russell/451740458</v>
+        <v>https://music.apple.com/us/artist/nathaniel-rateliff/362131302</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/rainbows/1882790535</v>
+        <v>https://music.apple.com/us/album/tommys-song/1876670038</v>
       </c>
       <c r="L180" t="str">
-        <v>Rainbows - Allison Russell</v>
+        <v>Tommy’s Song - Nathaniel Rateliff</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>butterflies</v>
+        <v>Rainbows</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/butterflies/1878228436</v>
+        <v>https://music.apple.com/us/song/rainbows/1882790536</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-16</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Bloom Again - EP</v>
+        <v>Rainbows - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:48</v>
+        <v>3:25</v>
       </c>
       <c r="H181" t="str">
-        <v>runo plum</v>
+        <v>Allison Russell</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
+        <v>https://music.apple.com/us/artist/allison-russell/451740458</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/butterflies/1878228434</v>
+        <v>https://music.apple.com/us/album/rainbows/1882790535</v>
       </c>
       <c r="L181" t="str">
-        <v>butterflies - runo plum</v>
+        <v>Rainbows - Allison Russell</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>You're Right</v>
+        <v>butterflies</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/youre-right/1874975857</v>
+        <v>https://music.apple.com/us/song/butterflies/1878228436</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-16</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>You're Right - Single</v>
+        <v>Bloom Again - EP</v>
       </c>
       <c r="G182" t="str">
-        <v>3:00</v>
+        <v>2:48</v>
       </c>
       <c r="H182" t="str">
-        <v>Emma Harner</v>
+        <v>runo plum</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/emma-harner/1543609198</v>
+        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/youre-right/1874975856</v>
+        <v>https://music.apple.com/us/album/butterflies/1878228434</v>
       </c>
       <c r="L182" t="str">
-        <v>You're Right - Emma Harner</v>
+        <v>butterflies - runo plum</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Bible Belt</v>
+        <v>You're Right</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/bible-belt/1821125622</v>
+        <v>https://music.apple.com/us/song/youre-right/1874975857</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-16</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Bible Belt - Single</v>
+        <v>You're Right - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:34</v>
+        <v>3:00</v>
       </c>
       <c r="H183" t="str">
-        <v>Baby Bugs</v>
+        <v>Emma Harner</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/baby-bugs/1551794879</v>
+        <v>https://music.apple.com/us/artist/emma-harner/1543609198</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/bible-belt/1821125621</v>
+        <v>https://music.apple.com/us/album/youre-right/1874975856</v>
       </c>
       <c r="L183" t="str">
-        <v>Bible Belt - Baby Bugs</v>
+        <v>You're Right - Emma Harner</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Daze</v>
+        <v>Bible Belt</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/daze/1862607801</v>
+        <v>https://music.apple.com/us/song/bible-belt/1821125622</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-16</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Daze - Single</v>
+        <v>Bible Belt - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:22</v>
+        <v>3:34</v>
       </c>
       <c r="H184" t="str">
-        <v>Olympia Vitalis</v>
+        <v>Baby Bugs</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
+        <v>https://music.apple.com/us/artist/baby-bugs/1551794879</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/daze/1862607800</v>
+        <v>https://music.apple.com/us/album/bible-belt/1821125621</v>
       </c>
       <c r="L184" t="str">
-        <v>Daze - Olympia Vitalis</v>
+        <v>Bible Belt - Baby Bugs</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Passionfruit</v>
+        <v>Daze</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/passionfruit/1878215125</v>
+        <v>https://music.apple.com/us/song/daze/1862607801</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-16</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Passionfruit - Single</v>
+        <v>Daze - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:57</v>
+        <v>3:22</v>
       </c>
       <c r="H185" t="str">
-        <v>Anish Kumar</v>
+        <v>Olympia Vitalis</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/passionfruit/1878215124</v>
+        <v>https://music.apple.com/us/album/daze/1862607800</v>
       </c>
       <c r="L185" t="str">
-        <v>Passionfruit - Anish Kumar</v>
+        <v>Daze - Olympia Vitalis</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Madan</v>
+        <v>Passionfruit</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/madan/1879822223</v>
+        <v>https://music.apple.com/us/song/passionfruit/1878215125</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-16</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Madan - Single</v>
+        <v>Passionfruit - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>2:56</v>
+        <v>3:57</v>
       </c>
       <c r="H186" t="str">
-        <v>Jonas Blue</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/jonas-blue/405728790</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/madan/1879822222</v>
+        <v>https://music.apple.com/us/album/passionfruit/1878215124</v>
       </c>
       <c r="L186" t="str">
-        <v>Madan - Jonas Blue</v>
+        <v>Passionfruit - Anish Kumar</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Bad Bitch</v>
+        <v>Madan</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/bad-bitch/1882818210</v>
+        <v>https://music.apple.com/us/song/madan/1879822223</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-16</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Bad Bitch - Single</v>
+        <v>Madan - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>2:28</v>
+        <v>2:56</v>
       </c>
       <c r="H187" t="str">
-        <v>41</v>
+        <v>Jonas Blue</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/41/1688992229</v>
+        <v>https://music.apple.com/us/artist/jonas-blue/405728790</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/bad-bitch/1882818208</v>
+        <v>https://music.apple.com/us/album/madan/1879822222</v>
       </c>
       <c r="L187" t="str">
-        <v>Bad Bitch - 41</v>
+        <v>Madan - Jonas Blue</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Shame</v>
+        <v>Bad Bitch</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/shame/1874080307</v>
+        <v>https://music.apple.com/us/song/bad-bitch/1882818210</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-16</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Devotion [Deluxe]</v>
+        <v>Bad Bitch - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:36</v>
+        <v>2:28</v>
       </c>
       <c r="H188" t="str">
-        <v>Sunday (1994)</v>
+        <v>41</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/sunday-1994/1728938785</v>
+        <v>https://music.apple.com/us/artist/41/1688992229</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/shame/1874080202</v>
+        <v>https://music.apple.com/us/album/bad-bitch/1882818208</v>
       </c>
       <c r="L188" t="str">
-        <v>Shame - Sunday (1994)</v>
+        <v>Bad Bitch - 41</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>teach you to love me</v>
+        <v>Shame</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/teach-you-to-love-me/1883146005</v>
+        <v>https://music.apple.com/us/song/shame/1874080307</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-16</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>teach you to love me - Single</v>
+        <v>Devotion [Deluxe]</v>
       </c>
       <c r="G189" t="str">
-        <v>3:09</v>
+        <v>3:36</v>
       </c>
       <c r="H189" t="str">
-        <v>Hailey Picardi</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/sunday-1994/1728938785</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/teach-you-to-love-me/1883146002</v>
+        <v>https://music.apple.com/us/album/shame/1874080202</v>
       </c>
       <c r="L189" t="str">
-        <v>teach you to love me - Hailey Picardi</v>
+        <v>Shame - Sunday (1994)</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>The Fix</v>
+        <v>teach you to love me</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/the-fix/1882082897</v>
+        <v>https://music.apple.com/us/song/teach-you-to-love-me/1883146005</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-16</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>The Fix - Single</v>
+        <v>teach you to love me - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>2:42</v>
+        <v>3:09</v>
       </c>
       <c r="H190" t="str">
-        <v>Baby J</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/the-fix/1882082895</v>
+        <v>https://music.apple.com/us/album/teach-you-to-love-me/1883146002</v>
       </c>
       <c r="L190" t="str">
-        <v>The Fix - Baby J</v>
+        <v>teach you to love me - Hailey Picardi</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Hanging on Hope</v>
+        <v>The Fix</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/hanging-on-hope/1881749452</v>
+        <v>https://music.apple.com/us/song/the-fix/1882082897</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-16</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Hanging on Hope - Single</v>
+        <v>The Fix - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>3:43</v>
+        <v>2:42</v>
       </c>
       <c r="H191" t="str">
-        <v>Buffalo Traffic Jam</v>
+        <v>Baby J</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
+        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/hanging-on-hope/1881749451</v>
+        <v>https://music.apple.com/us/album/the-fix/1882082895</v>
       </c>
       <c r="L191" t="str">
-        <v>Hanging on Hope - Buffalo Traffic Jam</v>
+        <v>The Fix - Baby J</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>I Know What to Say Now</v>
+        <v>Hanging on Hope</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/i-know-what-to-say-now/1879440545</v>
+        <v>https://music.apple.com/us/song/hanging-on-hope/1881749452</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-16</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>I Know What to Say Now - Single</v>
+        <v>Hanging on Hope - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>3:18</v>
+        <v>3:43</v>
       </c>
       <c r="H192" t="str">
-        <v>Active Child</v>
+        <v>Buffalo Traffic Jam</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/active-child/355288617</v>
+        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/i-know-what-to-say-now/1879440351</v>
+        <v>https://music.apple.com/us/album/hanging-on-hope/1881749451</v>
       </c>
       <c r="L192" t="str">
-        <v>I Know What to Say Now - Active Child</v>
+        <v>Hanging on Hope - Buffalo Traffic Jam</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Feel Something</v>
+        <v>I Know What to Say Now</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/feel-something/1876008375</v>
+        <v>https://music.apple.com/us/song/i-know-what-to-say-now/1879440545</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-16</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Feel Something - Single</v>
+        <v>I Know What to Say Now - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:09</v>
+        <v>3:18</v>
       </c>
       <c r="H193" t="str">
-        <v>Baby Queen</v>
+        <v>Active Child</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
+        <v>https://music.apple.com/us/artist/active-child/355288617</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/feel-something/1876008371</v>
+        <v>https://music.apple.com/us/album/i-know-what-to-say-now/1879440351</v>
       </c>
       <c r="L193" t="str">
-        <v>Feel Something - Baby Queen</v>
+        <v>I Know What to Say Now - Active Child</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>You Or Me</v>
+        <v>Feel Something</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/you-or-me/1869085528</v>
+        <v>https://music.apple.com/us/song/feel-something/1876008375</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-16</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Good God / Baad Man</v>
+        <v>Feel Something - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>5:28</v>
+        <v>3:09</v>
       </c>
       <c r="H194" t="str">
-        <v>Corrosion of Conformity</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
+        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/you-or-me/1869085524</v>
+        <v>https://music.apple.com/us/album/feel-something/1876008371</v>
       </c>
       <c r="L194" t="str">
-        <v>You Or Me - Corrosion of Conformity</v>
+        <v>Feel Something - Baby Queen</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Mortercheyn</v>
+        <v>You Or Me</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/mortercheyn/1862521946</v>
+        <v>https://music.apple.com/us/song/you-or-me/1869085528</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-16</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Coronach</v>
+        <v>Good God / Baad Man</v>
       </c>
       <c r="G195" t="str">
-        <v>4:18</v>
+        <v>5:28</v>
       </c>
       <c r="H195" t="str">
-        <v>Hellripper</v>
+        <v>Corrosion of Conformity</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/hellripper/1229248568</v>
+        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/mortercheyn/1862521937</v>
+        <v>https://music.apple.com/us/album/you-or-me/1869085524</v>
       </c>
       <c r="L195" t="str">
-        <v>Mortercheyn - Hellripper</v>
+        <v>You Or Me - Corrosion of Conformity</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Rip The God</v>
+        <v>Mortercheyn</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/rip-the-god/1866957697</v>
+        <v>https://music.apple.com/us/song/mortercheyn/1862521946</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-16</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Savage Imperial Death March</v>
+        <v>Coronach</v>
       </c>
       <c r="G196" t="str">
-        <v>5:20</v>
+        <v>4:18</v>
       </c>
       <c r="H196" t="str">
-        <v>Melvins</v>
+        <v>Hellripper</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/melvins/737433</v>
+        <v>https://music.apple.com/us/artist/hellripper/1229248568</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/rip-the-god/1866957685</v>
+        <v>https://music.apple.com/us/album/mortercheyn/1862521937</v>
       </c>
       <c r="L196" t="str">
-        <v>Rip The God - Melvins</v>
+        <v>Mortercheyn - Hellripper</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Who We Are</v>
+        <v>Rip The God</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/who-we-are/1879626950</v>
+        <v>https://music.apple.com/us/song/rip-the-god/1866957697</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-16</v>
@@ -7861,68 +7861,106 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Who We Are - Single</v>
+        <v>Savage Imperial Death March</v>
       </c>
       <c r="G197" t="str">
-        <v>2:10</v>
+        <v>5:20</v>
       </c>
       <c r="H197" t="str">
-        <v>Kaleena Zanders</v>
+        <v>Melvins</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+        <v>https://music.apple.com/us/artist/melvins/737433</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/who-we-are/1879626949</v>
+        <v>https://music.apple.com/us/album/rip-the-god/1866957685</v>
       </c>
       <c r="L197" t="str">
-        <v>Who We Are - Kaleena Zanders</v>
+        <v>Rip The God - Melvins</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
+        <v>Who We Are</v>
+      </c>
+      <c r="B198" t="str">
+        <v/>
+      </c>
+      <c r="C198" t="str">
+        <v>https://music.apple.com/us/song/who-we-are/1879626950</v>
+      </c>
+      <c r="D198" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E198" t="str">
+        <v/>
+      </c>
+      <c r="F198" t="str">
+        <v>Who We Are - Single</v>
+      </c>
+      <c r="G198" t="str">
+        <v>2:10</v>
+      </c>
+      <c r="H198" t="str">
+        <v>Kaleena Zanders</v>
+      </c>
+      <c r="I198" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J198" t="str">
+        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+      </c>
+      <c r="K198" t="str">
+        <v>https://music.apple.com/us/album/who-we-are/1879626949</v>
+      </c>
+      <c r="L198" t="str">
+        <v>Who We Are - Kaleena Zanders</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
         <v>Reels in 360</v>
       </c>
-      <c r="B198" t="str">
-        <v/>
-      </c>
-      <c r="C198" t="str">
+      <c r="B199" t="str">
+        <v/>
+      </c>
+      <c r="C199" t="str">
         <v>https://music.apple.com/us/song/reels-in-360/1867998408</v>
       </c>
-      <c r="D198" t="str">
-        <v>2026-03-16</v>
-      </c>
-      <c r="E198" t="str">
-        <v/>
-      </c>
-      <c r="F198" t="str">
+      <c r="D199" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E199" t="str">
+        <v/>
+      </c>
+      <c r="F199" t="str">
         <v>Dying Is The Internet</v>
       </c>
-      <c r="G198" t="str">
+      <c r="G199" t="str">
         <v>4:37</v>
       </c>
-      <c r="H198" t="str">
+      <c r="H199" t="str">
         <v>Simo Cell</v>
       </c>
-      <c r="I198" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J198" t="str">
+      <c r="I199" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J199" t="str">
         <v>https://music.apple.com/us/artist/simo-cell/1001568130</v>
       </c>
-      <c r="K198" t="str">
+      <c r="K199" t="str">
         <v>https://music.apple.com/us/album/reels-in-360/1867998295</v>
       </c>
-      <c r="L198" t="str">
+      <c r="L199" t="str">
         <v>Reels in 360 - Simo Cell</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L198"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L199"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
@@ -819,7 +819,7 @@
         <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B12" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G12" t="str">
         <v>5:01</v>
@@ -1503,7 +1503,7 @@
         <v>Bazzi - moment (Official Music Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G30" t="str">
         <v>2:43</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
@@ -781,7 +781,7 @@
         <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G11" t="str">
         <v>2:33</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
@@ -743,7 +743,7 @@
         <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G10" t="str">
         <v>4:58</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -515,19 +515,19 @@
         <v>Natalie Jane - sabotage (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G4" t="str">
         <v>2:57</v>
@@ -559,7 +559,7 @@
         <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -667,19 +667,19 @@
         <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
       </c>
       <c r="B8" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:34</v>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=366CV87TguE</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1009,19 +1009,19 @@
         <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
       </c>
       <c r="B17" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>3:21</v>
@@ -1047,19 +1047,19 @@
         <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G18" t="str">
         <v>3:16</v>
@@ -1085,19 +1085,19 @@
         <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
       </c>
       <c r="B19" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G19" t="str">
         <v>2:41</v>
@@ -1123,19 +1123,19 @@
         <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>2:29</v>
@@ -1161,19 +1161,19 @@
         <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
       </c>
       <c r="B21" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G21" t="str">
         <v>2:43</v>
@@ -1199,19 +1199,19 @@
         <v>Matt Hansen - SAME TIME (Official Live Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G22" t="str">
         <v>3:46</v>
@@ -1237,19 +1237,19 @@
         <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>4:01</v>
@@ -1275,19 +1275,19 @@
         <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G24" t="str">
         <v>3:23</v>
@@ -1313,19 +1313,19 @@
         <v>almost monday - leaving is easy (official video)</v>
       </c>
       <c r="B25" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G25" t="str">
         <v>3:39</v>
@@ -1351,19 +1351,19 @@
         <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>3:04</v>
@@ -1389,19 +1389,19 @@
         <v>vaultboy - DELETED (Official Lyric Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G27" t="str">
         <v>3:25</v>
@@ -1427,19 +1427,19 @@
         <v>The Warning - Kerosene (Official Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G28" t="str">
         <v>3:49</v>
@@ -1465,19 +1465,19 @@
         <v>aron! - Wonderful Thing (City View Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G29" t="str">
         <v>2:14</v>
@@ -1509,7 +1509,7 @@
         <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1845,19 +1845,19 @@
         <v>Maya Hawke - Devil You Know (Official Audio)</v>
       </c>
       <c r="B39" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G39" t="str">
         <v>3:10</v>
@@ -1889,7 +1889,7 @@
         <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1959,19 +1959,19 @@
         <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
       </c>
       <c r="B42" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G42" t="str">
         <v>2:53</v>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3935,19 +3935,19 @@
         <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
       </c>
       <c r="B94" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G94" t="str">
         <v>4:49</v>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/riptides/1878362645</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/porch-light/1872239892</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/dry-spell/1883177258</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/the-visitor/1882146993</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/i-aint-no-cowboy/1862634799</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/cant-sit-still/1878782917</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245797</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/blow-my-mind/1852752616</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/sata/1874015489</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/una-aventura/1882069505</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/home-feat-hikaru-utada/1845190340</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/dirty-wedding-dress/1872842320</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/fastest-gun-alive/1874700373</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/imposible/1880775726</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/trade-places/1878823464</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/motion-party/1882152039</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/woman/1882549709</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/sunburn/1880836041</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/que-te-cost%C3%B3/1882108997</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/oooshxt/1879612533</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/cruel-world/1859630041</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/star/1876633306</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/get-go/1862570884</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/thunderwave/1861531685</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/club-song/1882478246</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/better-man/1880496044</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/sabotage/1882209853</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/2000s-pop-punk-rnb/1878820143</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/naked/1883802157</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/catharina/1880130477</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/through-the-pain-feat-pozer/1877868063</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/trying-times/1862353792</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/595/1880470541</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/when-did-you-stop-loving-me/1879593803</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/call-me/1882521075</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/mi-amor/1872454951</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/boba/1880372256</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/video-shoot/1882892621</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/talk-to-me-nuh/1882510363</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/just-believe/1884083105</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/knife-in-the-heart/1857952500</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/the-way-we-touch/1875315428</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/dangerous/1867202642</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/when-i-wake-up/1878237800</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/breathe/1882808152</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/minty/1870867418</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/earth/1870867498</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/drink-the-water/1883172887</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/a-rainy-night-in-soho/1878459216</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/if-i-dont-leave-im-gonna-stay/1880111466</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/muchacho-alegre/1880256976</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/real-slow/1869618394</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/mountain-girl/1870722299</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/like-a-spark/1876952751</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/cheesecake/1882526540</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/always-let-you-down/1871578121</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/freakin-out/1879596115</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/name-in-vein/1880069474</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/st-catherines-wheel/1868804170</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/undefeated-champion/1840517120</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/pull-up/1854381591</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/ranjha/1882965642</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/zombies-in-love/1880178176</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/days-of-us/1868438268</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/life-of-a-man/1882845328</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/ya-no/1882115676</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/do-you-really-love-her/1879639011</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/relieve-you/1879589717</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/safety/1878181748</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/starlet/1873450846</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/physical/1883210753</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/im-dying-to-feel-alive-again/1880883509</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/regalito/1880846653</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/cruel-streak/1858689493</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/die-young/1870715300</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/island-girl/1884461360</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/girly-things/1876032954</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/looking-lovely-feat-robin-thicke/1878437828</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/tommys-song/1876670040</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/rainbows/1882790536</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/butterflies/1878228436</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/youre-right/1874975857</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/bible-belt/1821125622</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/daze/1862607801</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/passionfruit/1878215125</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/madan/1879822223</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/bad-bitch/1882818210</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/shame/1874080307</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/teach-you-to-love-me/1883146005</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/the-fix/1882082897</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/hanging-on-hope/1881749452</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/i-know-what-to-say-now/1879440545</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/feel-something/1876008375</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -7779,7 +7779,7 @@
         <v>https://music.apple.com/us/song/you-or-me/1869085528</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -7817,7 +7817,7 @@
         <v>https://music.apple.com/us/song/mortercheyn/1862521946</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -7855,7 +7855,7 @@
         <v>https://music.apple.com/us/song/rip-the-god/1866957697</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -7893,7 +7893,7 @@
         <v>https://music.apple.com/us/song/who-we-are/1879626950</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E198" t="str">
         <v/>
@@ -7931,7 +7931,7 @@
         <v>https://music.apple.com/us/song/reels-in-360/1867998408</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E199" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
       </c>
       <c r="B2" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
+        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-17</v>
@@ -451,13 +451,13 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G2" t="str">
-        <v>4:09</v>
+        <v>2:31</v>
       </c>
       <c r="H2" t="str">
-        <v>Mei Semones</v>
+        <v>Chris Janson</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
+        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-17</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G3" t="str">
-        <v>2:08</v>
+        <v>3:14</v>
       </c>
       <c r="H3" t="str">
-        <v>The Lemon Twigs</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video)</v>
+        <v>Allison Russell - Rainbows (Official Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
+        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-17</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G4" t="str">
-        <v>2:57</v>
+        <v>3:22</v>
       </c>
       <c r="H4" t="str">
-        <v>Natalie Jane</v>
+        <v>Allison Russell</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
+        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
+        <v>We Three - Love Who You Love (Official Audio)</v>
       </c>
       <c r="B5" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
+        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-17</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G5" t="str">
-        <v>3:13</v>
+        <v>3:43</v>
       </c>
       <c r="H5" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>We Three</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
+        <v>paris jackson - zombies in love</v>
       </c>
       <c r="B6" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
+        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-17</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G6" t="str">
-        <v>4:12</v>
+        <v>2:54</v>
       </c>
       <c r="H6" t="str">
-        <v>David Gilmour</v>
+        <v>paris jackson</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>paris jackson - zombies in love - paris jackson</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
+        <v>Kane Brown - Woman (Official Music Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
+        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-17</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v>3:57</v>
+        <v>2:46</v>
       </c>
       <c r="H7" t="str">
-        <v>Far Caspian</v>
+        <v>Kane Brown</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
+        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
+        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-17</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>3:34</v>
+        <v>3:37</v>
       </c>
       <c r="H8" t="str">
-        <v>Celine Dion</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Harry Styles - American Girls (Official Video)</v>
+        <v>Malcolm Todd - Breathe (Official Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
+        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
       </c>
       <c r="D9" t="str">
         <v>2026-03-17</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>3:48</v>
+        <v>2:57</v>
       </c>
       <c r="H9" t="str">
-        <v>Harry Styles</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
+        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay</v>
       </c>
       <c r="B10" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
+        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
       </c>
       <c r="D10" t="str">
         <v>2026-03-17</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>4:58</v>
+        <v>3:38</v>
       </c>
       <c r="H10" t="str">
-        <v>Warner Records and Morrissey</v>
+        <v>Carly Pearce and Riley Green</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay - Carly Pearce and Riley Green</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Ellise - Littlepill (Official Music Video)</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
       </c>
       <c r="B11" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
+        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
       </c>
       <c r="D11" t="str">
         <v>2026-03-17</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>2:33</v>
+        <v>4:29</v>
       </c>
       <c r="H11" t="str">
-        <v>Ellise</v>
+        <v>Kungs</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
       </c>
       <c r="B12" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
+        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
       </c>
       <c r="D12" t="str">
         <v>2026-03-17</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>5:01</v>
+        <v>4:28</v>
       </c>
       <c r="H12" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
+        <v>aron! - Wonderful Thing (Piano)</v>
       </c>
       <c r="B13" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
+        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-17</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>4:56</v>
+        <v>3:26</v>
       </c>
       <c r="H13" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>aron!</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>aron! - Wonderful Thing (Piano) - aron!</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
       </c>
       <c r="B14" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
+        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
       </c>
       <c r="D14" t="str">
         <v>2026-03-17</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>2:54</v>
+        <v>3:51</v>
       </c>
       <c r="H14" t="str">
-        <v>Bebe Rexha</v>
+        <v>Colinstoughmusic</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
+        <v>Sunday (1994) - The Fairground</v>
       </c>
       <c r="B15" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
+        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
       </c>
       <c r="D15" t="str">
         <v>2026-03-17</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>2:46</v>
+        <v>2:49</v>
       </c>
       <c r="H15" t="str">
-        <v>NathanEvanss</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
+        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
+        <v>Owen Riegling - In The Feeling (Visualizer)</v>
       </c>
       <c r="B16" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
+        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-17</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>2:56</v>
+        <v>4:16</v>
       </c>
       <c r="H16" t="str">
-        <v>R3HAB</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
+        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>11 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
+        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-17</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>11 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:21</v>
+        <v>4:16</v>
       </c>
       <c r="H17" t="str">
-        <v>War Child UK and Depeche Mode</v>
+        <v>LANY</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
+        <v>Maverick Sabre - 8 Stages</v>
       </c>
       <c r="B18" t="str">
-        <v>11 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
+        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-17</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>11 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:16</v>
+        <v>3:25</v>
       </c>
       <c r="H18" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Maverick Sabre</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
+        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
+        <v>Amanda Jordan - What Else Is New</v>
       </c>
       <c r="B19" t="str">
-        <v>11 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
+        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-17</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>11 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>2:41</v>
+        <v>2:50</v>
       </c>
       <c r="H19" t="str">
-        <v>Johnny Orlando</v>
+        <v>Amanda Jordan</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
+        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
       </c>
       <c r="B20" t="str">
-        <v>11 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
+        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-17</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>11 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>2:29</v>
+        <v>3:57</v>
       </c>
       <c r="H20" t="str">
-        <v>Russell Dickerson</v>
+        <v>Beabadoobee</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>11 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
+        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-17</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>11 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>2:43</v>
+        <v>3:58</v>
       </c>
       <c r="H21" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
       </c>
       <c r="B22" t="str">
-        <v>11 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
+        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-17</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>11 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:46</v>
+        <v>3:25</v>
       </c>
       <c r="H22" t="str">
-        <v>Matt Hansen</v>
+        <v>Spotify and Zara Larsson</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
       </c>
       <c r="B23" t="str">
-        <v>11 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
+        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-17</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>11 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>4:01</v>
+        <v>3:05</v>
       </c>
       <c r="H23" t="str">
-        <v>Mike Posner</v>
+        <v>Tucker Wetmore</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B24" t="str">
-        <v>11 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
+        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-17</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>11 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:23</v>
+        <v>4:09</v>
       </c>
       <c r="H24" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>almost monday - leaving is easy (official video)</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>11 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
+        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-17</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>11 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:39</v>
+        <v>2:08</v>
       </c>
       <c r="H25" t="str">
-        <v>almost monday</v>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>almost monday - leaving is easy (official video) - almost monday</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
+        <v>Natalie Jane - sabotage (Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>11 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
+        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-17</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>11 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:04</v>
+        <v>2:57</v>
       </c>
       <c r="H26" t="str">
-        <v>Anne Wilson and Cole Swindell</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
+        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video)</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B27" t="str">
-        <v>11 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
+        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-17</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>11 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:25</v>
+        <v>3:13</v>
       </c>
       <c r="H27" t="str">
-        <v>vaultboy</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>The Warning - Kerosene (Official Video)</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B28" t="str">
-        <v>11 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
+        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-17</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>11 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:49</v>
+        <v>4:12</v>
       </c>
       <c r="H28" t="str">
-        <v>The Warning</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>The Warning - Kerosene (Official Video) - The Warning</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>aron! - Wonderful Thing (City View Video)</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
       </c>
       <c r="B29" t="str">
-        <v>11 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
+        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-17</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>11 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>2:14</v>
+        <v>3:57</v>
       </c>
       <c r="H29" t="str">
-        <v>aron!</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Bazzi - moment (Official Music Video)</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
       </c>
       <c r="B30" t="str">
-        <v>11 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
+        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-17</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>11 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:43</v>
+        <v>3:34</v>
       </c>
       <c r="H30" t="str">
-        <v>Bazzi</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
+        <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
+        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-17</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>4:43</v>
+        <v>3:48</v>
       </c>
       <c r="H31" t="str">
-        <v>Sting</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
+        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
+        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-17</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>2:44</v>
+        <v>4:58</v>
       </c>
       <c r="H32" t="str">
-        <v>Dean Lewis</v>
+        <v>Warner Records and Morrissey</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Jessie Ware - Ride (Official Video)</v>
+        <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
+        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-17</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>4:37</v>
+        <v>2:33</v>
       </c>
       <c r="H33" t="str">
-        <v>Jessie Ware</v>
+        <v>Ellise</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
+        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Cannons - These Nights (Live at The Fonda)</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B34" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
+        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-17</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>4:52</v>
+        <v>5:01</v>
       </c>
       <c r="H34" t="str">
-        <v>Cannons</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
       </c>
       <c r="B35" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
+        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-17</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>2:13</v>
+        <v>4:56</v>
       </c>
       <c r="H35" t="str">
-        <v>Kim Petras</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
       </c>
       <c r="B36" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
+        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-17</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:19</v>
+        <v>2:54</v>
       </c>
       <c r="H36" t="str">
-        <v>Vanessa Carlton</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer]</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
+        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-17</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>2:31</v>
+        <v>2:46</v>
       </c>
       <c r="H37" t="str">
-        <v>Kiana Ledé</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
+        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-17</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:43</v>
+        <v>2:56</v>
       </c>
       <c r="H38" t="str">
-        <v>Ringo Starr</v>
+        <v>R3HAB</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio)</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
       </c>
       <c r="B39" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
+        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-17</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:10</v>
+        <v>3:21</v>
       </c>
       <c r="H39" t="str">
-        <v>Maya Hawke</v>
+        <v>War Child UK and Depeche Mode</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
+        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-17</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:55</v>
+        <v>3:16</v>
       </c>
       <c r="H40" t="str">
-        <v>Armin van Buuren</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Demi Lovato - Really Don't Care (Live)</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
       </c>
       <c r="B41" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
+        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-17</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:52</v>
+        <v>2:41</v>
       </c>
       <c r="H41" t="str">
-        <v>Demi Lovato</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
+        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-17</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>2:53</v>
+        <v>2:29</v>
       </c>
       <c r="H42" t="str">
-        <v>Peter Gabriel</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video)</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
       </c>
       <c r="B43" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
+        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-17</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>4:30</v>
+        <v>2:43</v>
       </c>
       <c r="H43" t="str">
-        <v>Jessie J</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
+        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-17</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>5:18</v>
+        <v>3:46</v>
       </c>
       <c r="H44" t="str">
-        <v>Harry Styles</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
+        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-17</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>7:20</v>
+        <v>4:01</v>
       </c>
       <c r="H45" t="str">
-        <v>Mark Ronson and BRITs</v>
+        <v>Mike Posner</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
+        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-17</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:01</v>
+        <v>3:23</v>
       </c>
       <c r="H46" t="str">
-        <v>BRITs</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
+        <v>almost monday - leaving is easy (official video)</v>
       </c>
       <c r="B47" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
+        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-17</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:31</v>
+        <v>3:39</v>
       </c>
       <c r="H47" t="str">
-        <v>Olivia Dean and BRITs</v>
+        <v>almost monday</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
+        <v>almost monday - leaving is easy (official video) - almost monday</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
+        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-17</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:00</v>
+        <v>3:04</v>
       </c>
       <c r="H48" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Anne Wilson and Cole Swindell</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
+        <v>vaultboy - DELETED (Official Lyric Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
+        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-17</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:11</v>
+        <v>3:25</v>
       </c>
       <c r="H49" t="str">
-        <v>The Kiffness</v>
+        <v>vaultboy</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
+        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Lauv - “insecure” (Official Audio)</v>
+        <v>The Warning - Kerosene (Official Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
+        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-17</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:32</v>
+        <v>3:49</v>
       </c>
       <c r="H50" t="str">
-        <v>Lauv</v>
+        <v>The Warning</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
+        <v>The Warning - Kerosene (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
+        <v>aron! - Wonderful Thing (City View Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
+        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-17</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>5:03</v>
+        <v>2:14</v>
       </c>
       <c r="H51" t="str">
-        <v>RAYE</v>
+        <v>aron!</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
+        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>Bazzi - moment (Official Music Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
+        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-17</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>4:50</v>
+        <v>2:43</v>
       </c>
       <c r="H52" t="str">
-        <v>Armik</v>
+        <v>Bazzi</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
       </c>
       <c r="B53" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
+        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-17</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>4:53</v>
+        <v>4:43</v>
       </c>
       <c r="H53" t="str">
-        <v>Scorpions</v>
+        <v>Sting</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
+        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-17</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:04</v>
+        <v>2:44</v>
       </c>
       <c r="H54" t="str">
-        <v>Cat Music and 3 more</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
+        <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
+        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-17</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>4:32</v>
+        <v>4:37</v>
       </c>
       <c r="H55" t="str">
-        <v>MercyMe and 3 more</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
+        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video)</v>
+        <v>Cannons - These Nights (Live at The Fonda)</v>
       </c>
       <c r="B56" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
+        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-17</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:47</v>
+        <v>4:52</v>
       </c>
       <c r="H56" t="str">
-        <v>Girl Tones</v>
+        <v>Cannons</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
+        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
       </c>
       <c r="B57" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
+        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-17</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:40</v>
+        <v>2:13</v>
       </c>
       <c r="H57" t="str">
-        <v>Jessie Ware and empik</v>
+        <v>Kim Petras</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
       </c>
       <c r="B58" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
+        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-17</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>4:05</v>
+        <v>3:19</v>
       </c>
       <c r="H58" t="str">
-        <v>HAUSER</v>
+        <v>Vanessa Carlton</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
+        <v>Kiana Ledé - Jury [Official Visualizer]</v>
       </c>
       <c r="B59" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
+        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-17</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>2:59</v>
+        <v>2:31</v>
       </c>
       <c r="H59" t="str">
-        <v>Queen Official</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
+        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
       </c>
       <c r="B60" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
+        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-17</v>
@@ -2658,10 +2658,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:55</v>
+        <v>2:43</v>
       </c>
       <c r="H60" t="str">
-        <v>Tenille Townes</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
+        <v>Maya Hawke - Devil You Know (Official Audio)</v>
       </c>
       <c r="B61" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
+        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-17</v>
@@ -2696,10 +2696,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
-        <v>5:12</v>
+        <v>3:10</v>
       </c>
       <c r="H61" t="str">
-        <v>Self Esteem</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
+        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B62" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
+        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-17</v>
@@ -2734,10 +2734,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:47</v>
+        <v>3:55</v>
       </c>
       <c r="H62" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
+        <v>Demi Lovato - Really Don't Care (Live)</v>
       </c>
       <c r="B63" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
+        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-17</v>
@@ -2772,10 +2772,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:18</v>
+        <v>3:52</v>
       </c>
       <c r="H63" t="str">
-        <v>Em Beihold</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
+        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Michael Bublé - That's All (Live)</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
       </c>
       <c r="B64" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
+        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-17</v>
@@ -2810,10 +2810,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:50</v>
+        <v>2:53</v>
       </c>
       <c r="H64" t="str">
-        <v>Michael Bublé</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>MyKey - Ride With Me</v>
+        <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B65" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
+        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-17</v>
@@ -2848,10 +2848,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:24</v>
+        <v>4:30</v>
       </c>
       <c r="H65" t="str">
-        <v>MyKey</v>
+        <v>Jessie J</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>MyKey - Ride With Me - MyKey</v>
+        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Max McNown - Done For (Official Lyric Video)</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B66" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
+        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-17</v>
@@ -2886,10 +2886,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
-        <v>2:36</v>
+        <v>5:18</v>
       </c>
       <c r="H66" t="str">
-        <v>Max McNown</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
       </c>
       <c r="B67" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
+        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-17</v>
@@ -2924,10 +2924,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:34</v>
+        <v>7:20</v>
       </c>
       <c r="H67" t="str">
-        <v>Megan Moroney</v>
+        <v>Mark Ronson and BRITs</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer)</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
+        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-17</v>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>4:03</v>
+        <v>3:01</v>
       </c>
       <c r="H68" t="str">
-        <v>ERNEST</v>
+        <v>BRITs</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video]</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
+        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-17</v>
@@ -3003,7 +3003,7 @@
         <v>3:31</v>
       </c>
       <c r="H69" t="str">
-        <v>Bruno Mars</v>
+        <v>Olivia Dean and BRITs</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>BLACKPINK - ‘GO’ M/V</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
+        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-17</v>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:22</v>
+        <v>3:00</v>
       </c>
       <c r="H70" t="str">
-        <v>BLACKPINK</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
+        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-17</v>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>5:49</v>
+        <v>3:11</v>
       </c>
       <c r="H71" t="str">
-        <v>Andrew Bird and Nu Deco Ensemble</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
+        <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
+        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-17</v>
@@ -3114,10 +3114,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:47</v>
+        <v>3:32</v>
       </c>
       <c r="H72" t="str">
-        <v>Nessa Barrett</v>
+        <v>Lauv</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
+        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video)</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
+        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-17</v>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>2:20</v>
+        <v>5:03</v>
       </c>
       <c r="H73" t="str">
-        <v>Towa Bird</v>
+        <v>RAYE</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Ty Myers - Morning Comes (Official Video)</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
+        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-17</v>
@@ -3190,10 +3190,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>4:18</v>
+        <v>4:50</v>
       </c>
       <c r="H74" t="str">
-        <v>Ty Myers</v>
+        <v>Armik</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video)</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
+        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-17</v>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>2:39</v>
+        <v>4:53</v>
       </c>
       <c r="H75" t="str">
-        <v>kenzie</v>
+        <v>Scorpions</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
+        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-17</v>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:52</v>
+        <v>3:04</v>
       </c>
       <c r="H76" t="str">
-        <v>Leanna Crawford</v>
+        <v>Cat Music and 3 more</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
+        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-17</v>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>4:01</v>
+        <v>4:32</v>
       </c>
       <c r="H77" t="str">
-        <v>Bryan Adams</v>
+        <v>MercyMe and 3 more</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>CHESCA - 3AM visualizer )</v>
+        <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
+        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-17</v>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>2:54</v>
+        <v>3:47</v>
       </c>
       <c r="H78" t="str">
-        <v>CHESCA</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
+        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
+        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-17</v>
@@ -3380,10 +3380,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>4:03</v>
+        <v>3:40</v>
       </c>
       <c r="H79" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Jessie Ware and empik</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
+        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-17</v>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>4:50</v>
+        <v>4:05</v>
       </c>
       <c r="H80" t="str">
-        <v>earMUSIC</v>
+        <v>HAUSER</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
+        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-17</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:06</v>
+        <v>2:59</v>
       </c>
       <c r="H81" t="str">
-        <v>Y2K</v>
+        <v>Queen Official</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
+        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-17</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>2:43</v>
+        <v>3:55</v>
       </c>
       <c r="H82" t="str">
-        <v>Lainey Wilson</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
+        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-17</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>6:21</v>
+        <v>5:12</v>
       </c>
       <c r="H83" t="str">
-        <v>Aly &amp; AJ</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
+        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-17</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>2:46</v>
+        <v>3:47</v>
       </c>
       <c r="H84" t="str">
-        <v>Bryan Ferry</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Saint Harison - glass houses (Live Session)</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
+        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-17</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>2:42</v>
+        <v>3:18</v>
       </c>
       <c r="H85" t="str">
-        <v>Saint Harison</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
+        <v>Michael Bublé - That's All (Live)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
+        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-17</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:04</v>
+        <v>3:50</v>
       </c>
       <c r="H86" t="str">
-        <v>John Summit and JULIA WOLF</v>
+        <v>Michael Bublé</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
+        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
+        <v>MyKey - Ride With Me</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
+        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-17</v>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:59</v>
+        <v>3:24</v>
       </c>
       <c r="H87" t="str">
-        <v>Catie Turner</v>
+        <v>MyKey</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
+        <v>MyKey - Ride With Me - MyKey</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE (Lyric Video)</v>
+        <v>Max McNown - Done For (Official Lyric Video)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
+        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-17</v>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>2:22</v>
+        <v>2:36</v>
       </c>
       <c r="H88" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Max McNown</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE (Lyric Video) - Lauren Sanderson</v>
+        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
+        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-17</v>
@@ -3760,10 +3760,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:53</v>
+        <v>3:34</v>
       </c>
       <c r="H89" t="str">
-        <v>Roxette</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>To The Greatest Guitarist Of All Time</v>
+        <v>ERNEST - Boat Named After You (Visualizer)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
+        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-17</v>
@@ -3798,10 +3798,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>2:28</v>
+        <v>4:03</v>
       </c>
       <c r="H90" t="str">
-        <v>Marcin</v>
+        <v>ERNEST</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>To The Greatest Guitarist Of All Time - Marcin</v>
+        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
+        <v>Bruno Mars - Risk It All [Official Music Video]</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
+        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-17</v>
@@ -3836,10 +3836,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>2:47</v>
+        <v>3:31</v>
       </c>
       <c r="H91" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
+        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
+        <v>BLACKPINK - ‘GO’ M/V</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
+        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-17</v>
@@ -3874,10 +3874,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:40</v>
+        <v>3:22</v>
       </c>
       <c r="H92" t="str">
-        <v>Laufey</v>
+        <v>BLACKPINK</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
+        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
+        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-17</v>
@@ -3912,10 +3912,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>2:49</v>
+        <v>5:49</v>
       </c>
       <c r="H93" t="str">
-        <v>Ava Max</v>
+        <v>Andrew Bird and Nu Deco Ensemble</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
       </c>
       <c r="B94" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
+        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-17</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>4:49</v>
+        <v>3:47</v>
       </c>
       <c r="H94" t="str">
-        <v>U2</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
+        <v>Towa Bird - Gentleman (Official Music Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
+        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-17</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:35</v>
+        <v>2:20</v>
       </c>
       <c r="H95" t="str">
-        <v>Taylor Swift</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
+        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
+        <v>Ty Myers - Morning Comes (Official Video)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
+        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-17</v>
@@ -4026,10 +4026,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>2:59</v>
+        <v>4:18</v>
       </c>
       <c r="H96" t="str">
-        <v>Kiana Ledé</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
+        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
+        <v>kenzie - mutual destruction (Visualizer Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
+        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-17</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>4:38</v>
+        <v>2:39</v>
       </c>
       <c r="H97" t="str">
-        <v>Jessie Ware</v>
+        <v>kenzie</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
+        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
       </c>
       <c r="B98" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
+        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-17</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:46</v>
+        <v>3:52</v>
       </c>
       <c r="H98" t="str">
-        <v>Madison Beer</v>
+        <v>Leanna Crawford</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
       </c>
       <c r="B99" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
+        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
       </c>
       <c r="D99" t="str">
         <v>2026-03-17</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:08</v>
+        <v>4:01</v>
       </c>
       <c r="H99" t="str">
-        <v>Sean Stemaly</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
+        <v>CHESCA - 3AM visualizer )</v>
       </c>
       <c r="B100" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
+        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
       </c>
       <c r="D100" t="str">
         <v>2026-03-17</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>5:32</v>
+        <v>2:54</v>
       </c>
       <c r="H100" t="str">
-        <v>earMUSIC</v>
+        <v>CHESCA</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
+        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
       </c>
       <c r="B101" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
+        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
       </c>
       <c r="D101" t="str">
         <v>2026-03-17</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>4:39</v>
+        <v>4:03</v>
       </c>
       <c r="H101" t="str">
-        <v>georgemichael</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="102">

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L199"/>
+  <dimension ref="A1:L200"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>4 days ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
+        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-17</v>
@@ -451,13 +451,13 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>4 days ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="G2" t="str">
-        <v>2:31</v>
+        <v>3:17</v>
       </c>
       <c r="H2" t="str">
-        <v>Chris Janson</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
+        <v>Nick Carter - Love Life Tragedy</v>
       </c>
       <c r="B3" t="str">
-        <v>4 days ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
+        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-17</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>4 days ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>3:14</v>
+        <v>3:31</v>
       </c>
       <c r="H3" t="str">
-        <v>Luke Combs</v>
+        <v>Nick Carter</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
+        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Allison Russell - Rainbows (Official Video)</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>4 days ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
+        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-17</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>4 days ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G4" t="str">
-        <v>3:22</v>
+        <v>3:38</v>
       </c>
       <c r="H4" t="str">
-        <v>Allison Russell</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>We Three - Love Who You Love (Official Audio)</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
       </c>
       <c r="B5" t="str">
-        <v>4 days ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
+        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-17</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>4 days ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G5" t="str">
-        <v>3:43</v>
+        <v>4:11</v>
       </c>
       <c r="H5" t="str">
-        <v>We Three</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>paris jackson - zombies in love</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
       </c>
       <c r="B6" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
+        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-17</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
-        <v>2:54</v>
+        <v>2:57</v>
       </c>
       <c r="H6" t="str">
-        <v>paris jackson</v>
+        <v>Jonas Blue and The Real Salif Keita</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>paris jackson - zombies in love - paris jackson</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Kane Brown - Woman (Official Music Video)</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B7" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
+        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-17</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
-        <v>2:46</v>
+        <v>3:47</v>
       </c>
       <c r="H7" t="str">
-        <v>Kane Brown</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B8" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
+        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-17</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>3:37</v>
+        <v>7:10</v>
       </c>
       <c r="H8" t="str">
-        <v>Lainey Wilson</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Malcolm Todd - Breathe (Official Video)</v>
+        <v>Grace Enger - Give A Little (Live Performance)</v>
       </c>
       <c r="B9" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
+        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
       </c>
       <c r="D9" t="str">
         <v>2026-03-17</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>2:57</v>
+        <v>3:06</v>
       </c>
       <c r="H9" t="str">
-        <v>Malcolm Todd</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
+        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
       </c>
       <c r="B10" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
+        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
       </c>
       <c r="D10" t="str">
         <v>2026-03-17</v>
@@ -758,10 +758,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:38</v>
+        <v>3:05</v>
       </c>
       <c r="H10" t="str">
-        <v>Carly Pearce and Riley Green</v>
+        <v>Tucker Wetmore</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay - Carly Pearce and Riley Green</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
+        <v>Nathan Evans x Saint PHNX - Happy Place (Official Acoustic Video)</v>
       </c>
       <c r="B11" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
+        <v>https://www.youtube.com/watch?v=lyuE94W1WIc</v>
       </c>
       <c r="D11" t="str">
         <v>2026-03-17</v>
@@ -796,10 +796,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>4:29</v>
+        <v>3:03</v>
       </c>
       <c r="H11" t="str">
-        <v>Kungs</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
+        <v>Nathan Evans x Saint PHNX - Happy Place (Official Acoustic Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
       </c>
       <c r="B12" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
+        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
       </c>
       <c r="D12" t="str">
         <v>2026-03-17</v>
@@ -834,10 +834,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>4:28</v>
+        <v>3:12</v>
       </c>
       <c r="H12" t="str">
-        <v>Sunday (1994)</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>aron! - Wonderful Thing (Piano)</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B13" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
+        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-17</v>
@@ -872,10 +872,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:26</v>
+        <v>9:11</v>
       </c>
       <c r="H13" t="str">
-        <v>aron!</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>aron! - Wonderful Thing (Piano) - aron!</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
+        <v>SIENNA SPIRO - The Visitor</v>
       </c>
       <c r="B14" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
+        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
       </c>
       <c r="D14" t="str">
         <v>2026-03-17</v>
@@ -910,10 +910,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:51</v>
+        <v>3:49</v>
       </c>
       <c r="H14" t="str">
-        <v>Colinstoughmusic</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
+        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Sunday (1994) - The Fairground</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
       </c>
       <c r="B15" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
+        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
       </c>
       <c r="D15" t="str">
         <v>2026-03-17</v>
@@ -948,10 +948,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>2:49</v>
+        <v>3:28</v>
       </c>
       <c r="H15" t="str">
-        <v>Sunday (1994)</v>
+        <v>Jonas Brothers and Demi Lovato</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer)</v>
+        <v>Martin Garrix - Catharina (Official Video)</v>
       </c>
       <c r="B16" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
+        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-17</v>
@@ -986,10 +986,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>4:16</v>
+        <v>3:31</v>
       </c>
       <c r="H16" t="str">
-        <v>Owen Riegling</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
+        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
+        <v>Baby Queen - Feel Something (Official Visualiser)</v>
       </c>
       <c r="B17" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
+        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-17</v>
@@ -1024,10 +1024,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>4:16</v>
+        <v>3:11</v>
       </c>
       <c r="H17" t="str">
-        <v>LANY</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
+        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Maverick Sabre - 8 Stages</v>
+        <v>HAUSER - Hungarian Dance No. 5</v>
       </c>
       <c r="B18" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
+        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-17</v>
@@ -1062,10 +1062,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:25</v>
+        <v>2:27</v>
       </c>
       <c r="H18" t="str">
-        <v>Maverick Sabre</v>
+        <v>HAUSER</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
+        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Amanda Jordan - What Else Is New</v>
+        <v>Holly Humberstone - Cruel World</v>
       </c>
       <c r="B19" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
+        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-17</v>
@@ -1100,10 +1100,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>2:50</v>
+        <v>3:34</v>
       </c>
       <c r="H19" t="str">
-        <v>Amanda Jordan</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
+        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
       </c>
       <c r="B20" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
+        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-17</v>
@@ -1138,10 +1138,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:57</v>
+        <v>2:50</v>
       </c>
       <c r="H20" t="str">
-        <v>Beabadoobee</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
+        <v>Rick Astley - Waiting On You (Official Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
+        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-17</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:58</v>
+        <v>3:51</v>
       </c>
       <c r="H21" t="str">
-        <v>Spacey Jane</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
+        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
+        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-17</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:25</v>
+        <v>2:39</v>
       </c>
       <c r="H22" t="str">
-        <v>Spotify and Zara Larsson</v>
+        <v>Alan Walker and Emyrson Flora</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
       </c>
       <c r="B23" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
+        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-17</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:05</v>
+        <v>5:08</v>
       </c>
       <c r="H23" t="str">
-        <v>Tucker Wetmore</v>
+        <v>Jessie J</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
+        <v>Bishop Briggs - River (10 Years Later)</v>
       </c>
       <c r="B24" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
+        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-17</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>4:09</v>
+        <v>3:46</v>
       </c>
       <c r="H24" t="str">
-        <v>Mei Semones</v>
+        <v>Bishop Briggs</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
+        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
+        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-17</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>2:08</v>
+        <v>2:42</v>
       </c>
       <c r="H25" t="str">
-        <v>The Lemon Twigs</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video)</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
       </c>
       <c r="B26" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
+        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-17</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>2:57</v>
+        <v>2:31</v>
       </c>
       <c r="H26" t="str">
-        <v>Natalie Jane</v>
+        <v>Chris Janson</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
+        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-17</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:13</v>
+        <v>3:14</v>
       </c>
       <c r="H27" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
+        <v>Allison Russell - Rainbows (Official Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
+        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-17</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>4:12</v>
+        <v>3:22</v>
       </c>
       <c r="H28" t="str">
-        <v>David Gilmour</v>
+        <v>Allison Russell</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
+        <v>We Three - Love Who You Love (Official Audio)</v>
       </c>
       <c r="B29" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
+        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-17</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:57</v>
+        <v>3:43</v>
       </c>
       <c r="H29" t="str">
-        <v>Far Caspian</v>
+        <v>We Three</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
+        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
+        <v>paris jackson - zombies in love</v>
       </c>
       <c r="B30" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
+        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-17</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:34</v>
+        <v>2:54</v>
       </c>
       <c r="H30" t="str">
-        <v>Celine Dion</v>
+        <v>paris jackson</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
+        <v>paris jackson - zombies in love - paris jackson</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Harry Styles - American Girls (Official Video)</v>
+        <v>Kane Brown - Woman (Official Music Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
+        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-17</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:48</v>
+        <v>2:46</v>
       </c>
       <c r="H31" t="str">
-        <v>Harry Styles</v>
+        <v>Kane Brown</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
+        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
+        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-17</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>4:58</v>
+        <v>3:37</v>
       </c>
       <c r="H32" t="str">
-        <v>Warner Records and Morrissey</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Ellise - Littlepill (Official Music Video)</v>
+        <v>Malcolm Todd - Breathe (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
+        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-17</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>2:33</v>
+        <v>2:57</v>
       </c>
       <c r="H33" t="str">
-        <v>Ellise</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
+        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay</v>
       </c>
       <c r="B34" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
+        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-17</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>5:01</v>
+        <v>3:38</v>
       </c>
       <c r="H34" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Carly Pearce and Riley Green</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay - Carly Pearce and Riley Green</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
       </c>
       <c r="B35" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
+        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-17</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>4:56</v>
+        <v>4:29</v>
       </c>
       <c r="H35" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Kungs</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
       </c>
       <c r="B36" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
+        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-17</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>2:54</v>
+        <v>4:28</v>
       </c>
       <c r="H36" t="str">
-        <v>Bebe Rexha</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
+        <v>aron! - Wonderful Thing (Piano)</v>
       </c>
       <c r="B37" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
+        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-17</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>2:46</v>
+        <v>3:26</v>
       </c>
       <c r="H37" t="str">
-        <v>NathanEvanss</v>
+        <v>aron!</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
+        <v>aron! - Wonderful Thing (Piano) - aron!</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
       </c>
       <c r="B38" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
+        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-17</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:56</v>
+        <v>3:51</v>
       </c>
       <c r="H38" t="str">
-        <v>R3HAB</v>
+        <v>Colinstoughmusic</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
+        <v>Sunday (1994) - The Fairground</v>
       </c>
       <c r="B39" t="str">
-        <v>11 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
+        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-17</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>11 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:21</v>
+        <v>2:49</v>
       </c>
       <c r="H39" t="str">
-        <v>War Child UK and Depeche Mode</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
+        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
+        <v>Owen Riegling - In The Feeling (Visualizer)</v>
       </c>
       <c r="B40" t="str">
-        <v>11 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
+        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-17</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>11 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:16</v>
+        <v>4:16</v>
       </c>
       <c r="H40" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
+        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>11 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
+        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-17</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>11 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>2:41</v>
+        <v>4:16</v>
       </c>
       <c r="H41" t="str">
-        <v>Johnny Orlando</v>
+        <v>LANY</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
+        <v>Maverick Sabre - 8 Stages</v>
       </c>
       <c r="B42" t="str">
-        <v>11 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
+        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-17</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>11 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>2:29</v>
+        <v>3:25</v>
       </c>
       <c r="H42" t="str">
-        <v>Russell Dickerson</v>
+        <v>Maverick Sabre</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
+        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
+        <v>Amanda Jordan - What Else Is New</v>
       </c>
       <c r="B43" t="str">
-        <v>11 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
+        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-17</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>11 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>2:43</v>
+        <v>2:50</v>
       </c>
       <c r="H43" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Amanda Jordan</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
       </c>
       <c r="B44" t="str">
-        <v>11 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
+        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-17</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>11 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:46</v>
+        <v>3:57</v>
       </c>
       <c r="H44" t="str">
-        <v>Matt Hansen</v>
+        <v>Beabadoobee</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>11 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
+        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-17</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>11 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>4:01</v>
+        <v>3:58</v>
       </c>
       <c r="H45" t="str">
-        <v>Mike Posner</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
       </c>
       <c r="B46" t="str">
-        <v>11 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
+        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-17</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>11 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:23</v>
+        <v>3:25</v>
       </c>
       <c r="H46" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Spotify and Zara Larsson</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>almost monday - leaving is easy (official video)</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B47" t="str">
-        <v>11 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
+        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-17</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>11 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:39</v>
+        <v>4:09</v>
       </c>
       <c r="H47" t="str">
-        <v>almost monday</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>almost monday - leaving is easy (official video) - almost monday</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>11 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
+        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-17</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>11 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:04</v>
+        <v>2:08</v>
       </c>
       <c r="H48" t="str">
-        <v>Anne Wilson and Cole Swindell</v>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video)</v>
+        <v>Natalie Jane - sabotage (Lyric Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>11 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
+        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-17</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>11 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:25</v>
+        <v>2:57</v>
       </c>
       <c r="H49" t="str">
-        <v>vaultboy</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
+        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>The Warning - Kerosene (Official Video)</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B50" t="str">
-        <v>11 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
+        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-17</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>11 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:49</v>
+        <v>3:13</v>
       </c>
       <c r="H50" t="str">
-        <v>The Warning</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>The Warning - Kerosene (Official Video) - The Warning</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>aron! - Wonderful Thing (City View Video)</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B51" t="str">
-        <v>11 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
+        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-17</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>11 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>2:14</v>
+        <v>4:12</v>
       </c>
       <c r="H51" t="str">
-        <v>aron!</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Bazzi - moment (Official Music Video)</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
       </c>
       <c r="B52" t="str">
-        <v>11 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
+        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-17</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>11 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>2:43</v>
+        <v>3:57</v>
       </c>
       <c r="H52" t="str">
-        <v>Bazzi</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
       </c>
       <c r="B53" t="str">
-        <v>11 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
+        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-17</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>11 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>4:43</v>
+        <v>3:34</v>
       </c>
       <c r="H53" t="str">
-        <v>Sting</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
+        <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
+        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-17</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>2:44</v>
+        <v>3:48</v>
       </c>
       <c r="H54" t="str">
-        <v>Dean Lewis</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
+        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Jessie Ware - Ride (Official Video)</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
+        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-17</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>4:37</v>
+        <v>4:58</v>
       </c>
       <c r="H55" t="str">
-        <v>Jessie Ware</v>
+        <v>Warner Records and Morrissey</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Cannons - These Nights (Live at The Fonda)</v>
+        <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
+        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-17</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>4:52</v>
+        <v>2:33</v>
       </c>
       <c r="H56" t="str">
-        <v>Cannons</v>
+        <v>Ellise</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
+        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B57" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
+        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-17</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>2:13</v>
+        <v>5:01</v>
       </c>
       <c r="H57" t="str">
-        <v>Kim Petras</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
       </c>
       <c r="B58" t="str">
-        <v>13 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
+        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-17</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>13 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:19</v>
+        <v>4:56</v>
       </c>
       <c r="H58" t="str">
-        <v>Vanessa Carlton</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer]</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
       </c>
       <c r="B59" t="str">
-        <v>13 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
+        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-17</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>13 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>2:31</v>
+        <v>2:54</v>
       </c>
       <c r="H59" t="str">
-        <v>Kiana Ledé</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
+        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-17</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>2:43</v>
+        <v>2:46</v>
       </c>
       <c r="H60" t="str">
-        <v>Ringo Starr</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio)</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
+        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-17</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:10</v>
+        <v>2:56</v>
       </c>
       <c r="H61" t="str">
-        <v>Maya Hawke</v>
+        <v>R3HAB</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
       </c>
       <c r="B62" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
+        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-17</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:55</v>
+        <v>3:21</v>
       </c>
       <c r="H62" t="str">
-        <v>Armin van Buuren</v>
+        <v>War Child UK and Depeche Mode</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Demi Lovato - Really Don't Care (Live)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
+        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-17</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:52</v>
+        <v>3:16</v>
       </c>
       <c r="H63" t="str">
-        <v>Demi Lovato</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
       </c>
       <c r="B64" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
+        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-17</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:53</v>
+        <v>2:41</v>
       </c>
       <c r="H64" t="str">
-        <v>Peter Gabriel</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video)</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
+        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-17</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>4:30</v>
+        <v>2:29</v>
       </c>
       <c r="H65" t="str">
-        <v>Jessie J</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
       </c>
       <c r="B66" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
+        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-17</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>5:18</v>
+        <v>2:43</v>
       </c>
       <c r="H66" t="str">
-        <v>Harry Styles</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
+        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-17</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>7:20</v>
+        <v>3:46</v>
       </c>
       <c r="H67" t="str">
-        <v>Mark Ronson and BRITs</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
+        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-17</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:01</v>
+        <v>4:01</v>
       </c>
       <c r="H68" t="str">
-        <v>BRITs</v>
+        <v>Mike Posner</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
+        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-17</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:31</v>
+        <v>3:23</v>
       </c>
       <c r="H69" t="str">
-        <v>Olivia Dean and BRITs</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026</v>
+        <v>almost monday - leaving is easy (official video)</v>
       </c>
       <c r="B70" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
+        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-17</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:00</v>
+        <v>3:39</v>
       </c>
       <c r="H70" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>almost monday</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>almost monday - leaving is easy (official video) - almost monday</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
+        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-17</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:11</v>
+        <v>3:04</v>
       </c>
       <c r="H71" t="str">
-        <v>The Kiffness</v>
+        <v>Anne Wilson and Cole Swindell</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Lauv - “insecure” (Official Audio)</v>
+        <v>vaultboy - DELETED (Official Lyric Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
+        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-17</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:32</v>
+        <v>3:25</v>
       </c>
       <c r="H72" t="str">
-        <v>Lauv</v>
+        <v>vaultboy</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
+        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
+        <v>The Warning - Kerosene (Official Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
+        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-17</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>5:03</v>
+        <v>3:49</v>
       </c>
       <c r="H73" t="str">
-        <v>RAYE</v>
+        <v>The Warning</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
+        <v>The Warning - Kerosene (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>aron! - Wonderful Thing (City View Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
+        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-17</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>4:50</v>
+        <v>2:14</v>
       </c>
       <c r="H74" t="str">
-        <v>Armik</v>
+        <v>aron!</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
+        <v>Bazzi - moment (Official Music Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
+        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-17</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>4:53</v>
+        <v>2:43</v>
       </c>
       <c r="H75" t="str">
-        <v>Scorpions</v>
+        <v>Bazzi</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
+        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
       </c>
       <c r="B76" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
+        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-17</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:04</v>
+        <v>4:43</v>
       </c>
       <c r="H76" t="str">
-        <v>Cat Music and 3 more</v>
+        <v>Sting</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
+        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-17</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>4:32</v>
+        <v>2:44</v>
       </c>
       <c r="H77" t="str">
-        <v>MercyMe and 3 more</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video)</v>
+        <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
+        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-17</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:47</v>
+        <v>4:37</v>
       </c>
       <c r="H78" t="str">
-        <v>Girl Tones</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
+        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
+        <v>Cannons - These Nights (Live at The Fonda)</v>
       </c>
       <c r="B79" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
+        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-17</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:40</v>
+        <v>4:52</v>
       </c>
       <c r="H79" t="str">
-        <v>Jessie Ware and empik</v>
+        <v>Cannons</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
+        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
+        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-17</v>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>4:05</v>
+        <v>2:13</v>
       </c>
       <c r="H80" t="str">
-        <v>HAUSER</v>
+        <v>Kim Petras</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
+        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-17</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>2:59</v>
+        <v>3:19</v>
       </c>
       <c r="H81" t="str">
-        <v>Queen Official</v>
+        <v>Vanessa Carlton</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
+        <v>Kiana Ledé - Jury [Official Visualizer]</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
+        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-17</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:55</v>
+        <v>2:31</v>
       </c>
       <c r="H82" t="str">
-        <v>Tenille Townes</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
+        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
+        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-17</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>5:12</v>
+        <v>2:43</v>
       </c>
       <c r="H83" t="str">
-        <v>Self Esteem</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
+        <v>Maya Hawke - Devil You Know (Official Audio)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
+        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-17</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:47</v>
+        <v>3:10</v>
       </c>
       <c r="H84" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
+        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
+        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-17</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:18</v>
+        <v>3:55</v>
       </c>
       <c r="H85" t="str">
-        <v>Em Beihold</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Michael Bublé - That's All (Live)</v>
+        <v>Demi Lovato - Really Don't Care (Live)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
+        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-17</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:50</v>
+        <v>3:52</v>
       </c>
       <c r="H86" t="str">
-        <v>Michael Bublé</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
+        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>MyKey - Ride With Me</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
+        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-17</v>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:24</v>
+        <v>2:53</v>
       </c>
       <c r="H87" t="str">
-        <v>MyKey</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>MyKey - Ride With Me - MyKey</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Max McNown - Done For (Official Lyric Video)</v>
+        <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
+        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-17</v>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>2:36</v>
+        <v>4:30</v>
       </c>
       <c r="H88" t="str">
-        <v>Max McNown</v>
+        <v>Jessie J</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
+        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
+        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-17</v>
@@ -3760,10 +3760,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:34</v>
+        <v>5:18</v>
       </c>
       <c r="H89" t="str">
-        <v>Megan Moroney</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer)</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
+        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-17</v>
@@ -3798,10 +3798,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>4:03</v>
+        <v>7:20</v>
       </c>
       <c r="H90" t="str">
-        <v>ERNEST</v>
+        <v>Mark Ronson and BRITs</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video]</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
+        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-17</v>
@@ -3836,10 +3836,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:31</v>
+        <v>3:01</v>
       </c>
       <c r="H91" t="str">
-        <v>Bruno Mars</v>
+        <v>BRITs</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>BLACKPINK - ‘GO’ M/V</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
+        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-17</v>
@@ -3874,10 +3874,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:22</v>
+        <v>3:31</v>
       </c>
       <c r="H92" t="str">
-        <v>BLACKPINK</v>
+        <v>Olivia Dean and BRITs</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
+        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-17</v>
@@ -3912,10 +3912,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>5:49</v>
+        <v>3:00</v>
       </c>
       <c r="H93" t="str">
-        <v>Andrew Bird and Nu Deco Ensemble</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
+        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-17</v>
@@ -3950,10 +3950,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:47</v>
+        <v>3:11</v>
       </c>
       <c r="H94" t="str">
-        <v>Nessa Barrett</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video)</v>
+        <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
+        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-17</v>
@@ -3988,10 +3988,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>2:20</v>
+        <v>3:32</v>
       </c>
       <c r="H95" t="str">
-        <v>Towa Bird</v>
+        <v>Lauv</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
+        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Ty Myers - Morning Comes (Official Video)</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
+        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-17</v>
@@ -4026,10 +4026,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>4:18</v>
+        <v>5:03</v>
       </c>
       <c r="H96" t="str">
-        <v>Ty Myers</v>
+        <v>RAYE</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video)</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
+        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-17</v>
@@ -4064,10 +4064,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>2:39</v>
+        <v>4:50</v>
       </c>
       <c r="H97" t="str">
-        <v>kenzie</v>
+        <v>Armik</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
+        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-17</v>
@@ -4102,10 +4102,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:52</v>
+        <v>4:53</v>
       </c>
       <c r="H98" t="str">
-        <v>Leanna Crawford</v>
+        <v>Scorpions</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
+        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D99" t="str">
         <v>2026-03-17</v>
@@ -4140,10 +4140,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>4:01</v>
+        <v>3:04</v>
       </c>
       <c r="H99" t="str">
-        <v>Bryan Adams</v>
+        <v>Cat Music and 3 more</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>CHESCA - 3AM visualizer )</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
+        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D100" t="str">
         <v>2026-03-17</v>
@@ -4178,10 +4178,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>2:54</v>
+        <v>4:32</v>
       </c>
       <c r="H100" t="str">
-        <v>CHESCA</v>
+        <v>MercyMe and 3 more</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
+        <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
+        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D101" t="str">
         <v>2026-03-17</v>
@@ -4216,10 +4216,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>4:03</v>
+        <v>3:47</v>
       </c>
       <c r="H101" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
+        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Riptides</v>
+        <v>Ocean In The Desert</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/riptides/1878362645</v>
+        <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-17</v>
@@ -4251,25 +4251,25 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>I Built You a Tower</v>
+        <v>Ocean In The Desert - Single</v>
       </c>
       <c r="G102" t="str">
-        <v>3:17</v>
+        <v>3:44</v>
       </c>
       <c r="H102" t="str">
-        <v>Death Cab for Cutie</v>
+        <v>Dionne Warwick</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
+        <v>https://music.apple.com/us/artist/dionne-warwick/16198</v>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/riptides/1878362451</v>
+        <v>https://music.apple.com/us/album/ocean-in-the-desert/1878421568</v>
       </c>
       <c r="L102" t="str">
-        <v>Riptides - Death Cab for Cutie</v>
+        <v>Ocean In The Desert - Dionne Warwick</v>
       </c>
     </row>
     <row r="103">
@@ -4350,13 +4350,13 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>The Visitor</v>
+        <v>Riptides</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/the-visitor/1882146993</v>
+        <v>https://music.apple.com/us/song/riptides/1878362645</v>
       </c>
       <c r="D105" t="str">
         <v>2026-03-17</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>The Visitor - Single</v>
+        <v>I Built You a Tower</v>
       </c>
       <c r="G105" t="str">
-        <v>3:48</v>
+        <v>3:17</v>
       </c>
       <c r="H105" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Death Cab for Cutie</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
+        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/the-visitor/1882146992</v>
+        <v>https://music.apple.com/us/album/riptides/1878362451</v>
       </c>
       <c r="L105" t="str">
-        <v>The Visitor - SIENNA SPIRO</v>
+        <v>Riptides - Death Cab for Cutie</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>I Ain't No Cowboy</v>
+        <v>The Visitor</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/i-aint-no-cowboy/1862634799</v>
+        <v>https://music.apple.com/us/song/the-visitor/1882146993</v>
       </c>
       <c r="D106" t="str">
         <v>2026-03-17</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>The Way I Am</v>
+        <v>The Visitor - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>3:13</v>
+        <v>3:48</v>
       </c>
       <c r="H106" t="str">
-        <v>Luke Combs</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
+        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/i-aint-no-cowboy/1862634688</v>
+        <v>https://music.apple.com/us/album/the-visitor/1882146992</v>
       </c>
       <c r="L106" t="str">
-        <v>I Ain't No Cowboy - Luke Combs</v>
+        <v>The Visitor - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Can't Sit Still</v>
+        <v>I Ain't No Cowboy</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/cant-sit-still/1878782917</v>
+        <v>https://music.apple.com/us/song/i-aint-no-cowboy/1862634799</v>
       </c>
       <c r="D107" t="str">
         <v>2026-03-17</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Can't Sit Still - Single</v>
+        <v>The Way I Am</v>
       </c>
       <c r="G107" t="str">
-        <v>3:35</v>
+        <v>3:13</v>
       </c>
       <c r="H107" t="str">
-        <v>Lainey Wilson</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
+        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/cant-sit-still/1878782913</v>
+        <v>https://music.apple.com/us/album/i-aint-no-cowboy/1862634688</v>
       </c>
       <c r="L107" t="str">
-        <v>Can't Sit Still - Lainey Wilson</v>
+        <v>I Ain't No Cowboy - Luke Combs</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>All I Did Was Dream of You (feat. The Marías)</v>
+        <v>Can't Sit Still</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245797</v>
+        <v>https://music.apple.com/us/song/cant-sit-still/1878782917</v>
       </c>
       <c r="D108" t="str">
         <v>2026-03-17</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>All I Did Was Dream of You (feat. The Marías) - Single</v>
+        <v>Can't Sit Still - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>3:43</v>
+        <v>3:35</v>
       </c>
       <c r="H108" t="str">
-        <v>beabadoobee</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/beabadoobee/1307650474</v>
+        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245651</v>
+        <v>https://music.apple.com/us/album/cant-sit-still/1878782913</v>
       </c>
       <c r="L108" t="str">
-        <v>All I Did Was Dream of You (feat. The Marías) - beabadoobee</v>
+        <v>Can't Sit Still - Lainey Wilson</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Blow My Mind</v>
+        <v>All I Did Was Dream of You (feat. The Marías)</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/blow-my-mind/1852752616</v>
+        <v>https://music.apple.com/us/song/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245797</v>
       </c>
       <c r="D109" t="str">
         <v>2026-03-17</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Sexistential</v>
+        <v>All I Did Was Dream of You (feat. The Marías) - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>2:57</v>
+        <v>3:43</v>
       </c>
       <c r="H109" t="str">
-        <v>Robyn</v>
+        <v>beabadoobee</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v>https://music.apple.com/us/artist/beabadoobee/1307650474</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/blow-my-mind/1852752613</v>
+        <v>https://music.apple.com/us/album/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245651</v>
       </c>
       <c r="L109" t="str">
-        <v>Blow My Mind - Robyn</v>
+        <v>All I Did Was Dream of You (feat. The Marías) - beabadoobee</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>SATA</v>
+        <v>Blow My Mind</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/sata/1874015489</v>
+        <v>https://music.apple.com/us/song/blow-my-mind/1852752616</v>
       </c>
       <c r="D110" t="str">
         <v>2026-03-17</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>CTRL ESCAPE</v>
+        <v>Sexistential</v>
       </c>
       <c r="G110" t="str">
-        <v>3:02</v>
+        <v>2:57</v>
       </c>
       <c r="H110" t="str">
-        <v>John Summit</v>
+        <v>Robyn</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/sata/1874015470</v>
+        <v>https://music.apple.com/us/album/blow-my-mind/1852752613</v>
       </c>
       <c r="L110" t="str">
-        <v>SATA - John Summit</v>
+        <v>Blow My Mind - Robyn</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Una Aventura</v>
+        <v>SATA</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/una-aventura/1882069505</v>
+        <v>https://music.apple.com/us/song/sata/1874015489</v>
       </c>
       <c r="D111" t="str">
         <v>2026-03-17</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Una Aventura - Single</v>
+        <v>CTRL ESCAPE</v>
       </c>
       <c r="G111" t="str">
-        <v>3:00</v>
+        <v>3:02</v>
       </c>
       <c r="H111" t="str">
-        <v>Ozuna</v>
+        <v>John Summit</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/ozuna/283578837</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/una-aventura/1882068957</v>
+        <v>https://music.apple.com/us/album/sata/1874015470</v>
       </c>
       <c r="L111" t="str">
-        <v>Una Aventura - Ozuna</v>
+        <v>SATA - John Summit</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Home (feat. Hikaru Utada)</v>
+        <v>Una Aventura</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/home-feat-hikaru-utada/1845190340</v>
+        <v>https://music.apple.com/us/song/una-aventura/1882069505</v>
       </c>
       <c r="D112" t="str">
         <v>2026-03-17</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Whatever's Clever!</v>
+        <v>Una Aventura - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>3:44</v>
+        <v>3:00</v>
       </c>
       <c r="H112" t="str">
-        <v>Charlie Puth</v>
+        <v>Ozuna</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v>https://music.apple.com/us/artist/ozuna/283578837</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/home-feat-hikaru-utada/1845189970</v>
+        <v>https://music.apple.com/us/album/una-aventura/1882068957</v>
       </c>
       <c r="L112" t="str">
-        <v>Home (feat. Hikaru Utada) - Charlie Puth</v>
+        <v>Una Aventura - Ozuna</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>dirty wedding dress</v>
+        <v>Home (feat. Hikaru Utada)</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/dirty-wedding-dress/1872842320</v>
+        <v>https://music.apple.com/us/song/home-feat-hikaru-utada/1845190340</v>
       </c>
       <c r="D113" t="str">
         <v>2026-03-17</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>everyone for ten minutes</v>
+        <v>Whatever's Clever!</v>
       </c>
       <c r="G113" t="str">
-        <v>4:49</v>
+        <v>3:44</v>
       </c>
       <c r="H113" t="str">
-        <v>Bleachers</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/dirty-wedding-dress/1872842313</v>
+        <v>https://music.apple.com/us/album/home-feat-hikaru-utada/1845189970</v>
       </c>
       <c r="L113" t="str">
-        <v>dirty wedding dress - Bleachers</v>
+        <v>Home (feat. Hikaru Utada) - Charlie Puth</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Fastest Gun Alive</v>
+        <v>dirty wedding dress</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/fastest-gun-alive/1874700373</v>
+        <v>https://music.apple.com/us/song/dirty-wedding-dress/1872842320</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-17</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Age of the Ram</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G114" t="str">
-        <v>3:07</v>
+        <v>4:49</v>
       </c>
       <c r="H114" t="str">
-        <v>Charley Crockett</v>
+        <v>Bleachers</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/fastest-gun-alive/1874700242</v>
+        <v>https://music.apple.com/us/album/dirty-wedding-dress/1872842313</v>
       </c>
       <c r="L114" t="str">
-        <v>Fastest Gun Alive - Charley Crockett</v>
+        <v>dirty wedding dress - Bleachers</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>IMPOSIBLE</v>
+        <v>Fastest Gun Alive</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/imposible/1880775726</v>
+        <v>https://music.apple.com/us/song/fastest-gun-alive/1874700373</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-17</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>IMPOSIBLE - Single</v>
+        <v>Age of the Ram</v>
       </c>
       <c r="G115" t="str">
-        <v>3:13</v>
+        <v>3:07</v>
       </c>
       <c r="H115" t="str">
-        <v>Grupo Frontera</v>
+        <v>Charley Crockett</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
+        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/imposible/1880775721</v>
+        <v>https://music.apple.com/us/album/fastest-gun-alive/1874700242</v>
       </c>
       <c r="L115" t="str">
-        <v>IMPOSIBLE - Grupo Frontera</v>
+        <v>Fastest Gun Alive - Charley Crockett</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Trade Places</v>
+        <v>IMPOSIBLE</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/trade-places/1878823464</v>
+        <v>https://music.apple.com/us/song/imposible/1880775726</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-17</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Monica</v>
+        <v>IMPOSIBLE - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:02</v>
+        <v>3:13</v>
       </c>
       <c r="H116" t="str">
-        <v>Jack Harlow</v>
+        <v>Grupo Frontera</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/jack-harlow/1047679432</v>
+        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/trade-places/1878823462</v>
+        <v>https://music.apple.com/us/album/imposible/1880775721</v>
       </c>
       <c r="L116" t="str">
-        <v>Trade Places - Jack Harlow</v>
+        <v>IMPOSIBLE - Grupo Frontera</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Motion Party</v>
+        <v>Trade Places</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/motion-party/1882152039</v>
+        <v>https://music.apple.com/us/song/trade-places/1878823464</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-17</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Motion Party - Single</v>
+        <v>Monica</v>
       </c>
       <c r="G117" t="str">
-        <v>1:35</v>
+        <v>3:02</v>
       </c>
       <c r="H117" t="str">
-        <v>Bossman Dlow</v>
+        <v>Jack Harlow</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
+        <v>https://music.apple.com/us/artist/jack-harlow/1047679432</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/motion-party/1882151996</v>
+        <v>https://music.apple.com/us/album/trade-places/1878823462</v>
       </c>
       <c r="L117" t="str">
-        <v>Motion Party - Bossman Dlow</v>
+        <v>Trade Places - Jack Harlow</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Woman</v>
+        <v>Motion Party</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/woman/1882549709</v>
+        <v>https://music.apple.com/us/song/motion-party/1882152039</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-17</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Woman - Single</v>
+        <v>Motion Party - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>2:46</v>
+        <v>1:35</v>
       </c>
       <c r="H118" t="str">
-        <v>Kane Brown</v>
+        <v>Bossman Dlow</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/kane-brown/930928857</v>
+        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/woman/1882549705</v>
+        <v>https://music.apple.com/us/album/motion-party/1882151996</v>
       </c>
       <c r="L118" t="str">
-        <v>Woman - Kane Brown</v>
+        <v>Motion Party - Bossman Dlow</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Sunburn</v>
+        <v>Woman</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/sunburn/1880836041</v>
+        <v>https://music.apple.com/us/song/woman/1882549709</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-17</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Sunburn - Single</v>
+        <v>Woman - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:05</v>
+        <v>2:46</v>
       </c>
       <c r="H119" t="str">
-        <v>Tucker Wetmore</v>
+        <v>Kane Brown</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/tucker-wetmore/1486724646</v>
+        <v>https://music.apple.com/us/artist/kane-brown/930928857</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/sunburn/1880835818</v>
+        <v>https://music.apple.com/us/album/woman/1882549705</v>
       </c>
       <c r="L119" t="str">
-        <v>Sunburn - Tucker Wetmore</v>
+        <v>Woman - Kane Brown</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Que Te Costó</v>
+        <v>Sunburn</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/que-te-cost%C3%B3/1882108997</v>
+        <v>https://music.apple.com/us/song/sunburn/1880836041</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-17</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Metamorfosis</v>
+        <v>Sunburn - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>2:54</v>
+        <v>3:05</v>
       </c>
       <c r="H120" t="str">
-        <v>Yahritza Y Su Esencia</v>
+        <v>Tucker Wetmore</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
+        <v>https://music.apple.com/us/artist/tucker-wetmore/1486724646</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/que-te-cost%C3%B3/1882108989</v>
+        <v>https://music.apple.com/us/album/sunburn/1880835818</v>
       </c>
       <c r="L120" t="str">
-        <v>Que Te Costó - Yahritza Y Su Esencia</v>
+        <v>Sunburn - Tucker Wetmore</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>oooshxt!</v>
+        <v>Que Te Costó</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/oooshxt/1879612533</v>
+        <v>https://music.apple.com/us/song/que-te-cost%C3%B3/1882108997</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-17</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>oooshxt! - Single</v>
+        <v>Metamorfosis</v>
       </c>
       <c r="G121" t="str">
-        <v>2:15</v>
+        <v>2:54</v>
       </c>
       <c r="H121" t="str">
-        <v>Samara Cyn</v>
+        <v>Yahritza Y Su Esencia</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
+        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/oooshxt/1879612532</v>
+        <v>https://music.apple.com/us/album/que-te-cost%C3%B3/1882108989</v>
       </c>
       <c r="L121" t="str">
-        <v>oooshxt! - Samara Cyn</v>
+        <v>Que Te Costó - Yahritza Y Su Esencia</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Cruel World</v>
+        <v>oooshxt!</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/cruel-world/1859630041</v>
+        <v>https://music.apple.com/us/song/oooshxt/1879612533</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-17</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Cruel World</v>
+        <v>oooshxt! - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:26</v>
+        <v>2:15</v>
       </c>
       <c r="H122" t="str">
-        <v>Holly Humberstone</v>
+        <v>Samara Cyn</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/cruel-world/1859629846</v>
+        <v>https://music.apple.com/us/album/oooshxt/1879612532</v>
       </c>
       <c r="L122" t="str">
-        <v>Cruel World - Holly Humberstone</v>
+        <v>oooshxt! - Samara Cyn</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Star</v>
+        <v>Cruel World</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/star/1876633306</v>
+        <v>https://music.apple.com/us/song/cruel-world/1859630041</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-17</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Star - Single</v>
+        <v>Cruel World</v>
       </c>
       <c r="G123" t="str">
-        <v>3:25</v>
+        <v>3:26</v>
       </c>
       <c r="H123" t="str">
-        <v>Iceage</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/star/1876633303</v>
+        <v>https://music.apple.com/us/album/cruel-world/1859629846</v>
       </c>
       <c r="L123" t="str">
-        <v>Star - Iceage</v>
+        <v>Cruel World - Holly Humberstone</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Get Go</v>
+        <v>Star</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/get-go/1862570884</v>
+        <v>https://music.apple.com/us/song/star/1876633306</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-17</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Ambiguous Desire</v>
+        <v>Star - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>3:22</v>
+        <v>3:25</v>
       </c>
       <c r="H124" t="str">
-        <v>Arlo Parks</v>
+        <v>Iceage</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
+        <v>https://music.apple.com/us/artist/iceage/406846711</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/get-go/1862570378</v>
+        <v>https://music.apple.com/us/album/star/1876633303</v>
       </c>
       <c r="L124" t="str">
-        <v>Get Go - Arlo Parks</v>
+        <v>Star - Iceage</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>ThunderWave</v>
+        <v>Get Go</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/thunderwave/1861531685</v>
+        <v>https://music.apple.com/us/song/get-go/1862570884</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-17</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Distracted</v>
+        <v>Ambiguous Desire</v>
       </c>
       <c r="G125" t="str">
-        <v>3:14</v>
+        <v>3:22</v>
       </c>
       <c r="H125" t="str">
-        <v>Thundercat</v>
+        <v>Arlo Parks</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
+        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/thunderwave/1861531667</v>
+        <v>https://music.apple.com/us/album/get-go/1862570378</v>
       </c>
       <c r="L125" t="str">
-        <v>ThunderWave - Thundercat</v>
+        <v>Get Go - Arlo Parks</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Club Song</v>
+        <v>ThunderWave</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/club-song/1882478246</v>
+        <v>https://music.apple.com/us/song/thunderwave/1861531685</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-17</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Club Song - Single</v>
+        <v>Distracted</v>
       </c>
       <c r="G126" t="str">
-        <v>2:27</v>
+        <v>3:14</v>
       </c>
       <c r="H126" t="str">
-        <v>The Pussycat Dolls</v>
+        <v>Thundercat</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/the-pussycat-dolls/23331509</v>
+        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/club-song/1882478243</v>
+        <v>https://music.apple.com/us/album/thunderwave/1861531667</v>
       </c>
       <c r="L126" t="str">
-        <v>Club Song - The Pussycat Dolls</v>
+        <v>ThunderWave - Thundercat</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Better Man</v>
+        <v>Club Song</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/better-man/1880496044</v>
+        <v>https://music.apple.com/us/song/club-song/1882478246</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-17</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Better Man - Single</v>
+        <v>Club Song - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>2:53</v>
+        <v>2:27</v>
       </c>
       <c r="H127" t="str">
-        <v>jxdn</v>
+        <v>The Pussycat Dolls</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/jxdn/1513237359</v>
+        <v>https://music.apple.com/us/artist/the-pussycat-dolls/23331509</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/better-man/1880496042</v>
+        <v>https://music.apple.com/us/album/club-song/1882478243</v>
       </c>
       <c r="L127" t="str">
-        <v>Better Man - jxdn</v>
+        <v>Club Song - The Pussycat Dolls</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>sabotage</v>
+        <v>Better Man</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/sabotage/1882209853</v>
+        <v>https://music.apple.com/us/song/better-man/1880496044</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-17</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>sabotage - Single</v>
+        <v>Better Man - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>2:58</v>
+        <v>2:53</v>
       </c>
       <c r="H128" t="str">
-        <v>Natalie Jane</v>
+        <v>jxdn</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/natalie-jane/1504380197</v>
+        <v>https://music.apple.com/us/artist/jxdn/1513237359</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/sabotage/1882209670</v>
+        <v>https://music.apple.com/us/album/better-man/1880496042</v>
       </c>
       <c r="L128" t="str">
-        <v>sabotage - Natalie Jane</v>
+        <v>Better Man - jxdn</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>2000s Pop Punk Rnb</v>
+        <v>sabotage</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/2000s-pop-punk-rnb/1878820143</v>
+        <v>https://music.apple.com/us/song/sabotage/1882209853</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-17</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Still Loiteringgg / 2000s Pop Punk Rnb - Single</v>
+        <v>sabotage - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>2:56</v>
+        <v>2:58</v>
       </c>
       <c r="H129" t="str">
-        <v>WHATMORE</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/whatmore/1797119133</v>
+        <v>https://music.apple.com/us/artist/natalie-jane/1504380197</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/2000s-pop-punk-rnb/1878820131</v>
+        <v>https://music.apple.com/us/album/sabotage/1882209670</v>
       </c>
       <c r="L129" t="str">
-        <v>2000s Pop Punk Rnb - WHATMORE</v>
+        <v>sabotage - Natalie Jane</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Naked</v>
+        <v>2000s Pop Punk Rnb</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/naked/1883802157</v>
+        <v>https://music.apple.com/us/song/2000s-pop-punk-rnb/1878820143</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-17</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Naked - Single</v>
+        <v>Still Loiteringgg / 2000s Pop Punk Rnb - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>3:39</v>
+        <v>2:56</v>
       </c>
       <c r="H130" t="str">
-        <v>Kenya Grace</v>
+        <v>WHATMORE</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
+        <v>https://music.apple.com/us/artist/whatmore/1797119133</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/naked/1883801913</v>
+        <v>https://music.apple.com/us/album/2000s-pop-punk-rnb/1878820131</v>
       </c>
       <c r="L130" t="str">
-        <v>Naked - Kenya Grace</v>
+        <v>2000s Pop Punk Rnb - WHATMORE</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Catharina</v>
+        <v>Naked</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/catharina/1880130477</v>
+        <v>https://music.apple.com/us/song/naked/1883802157</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-17</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Catharina - Single</v>
+        <v>Naked - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>3:27</v>
+        <v>3:39</v>
       </c>
       <c r="H131" t="str">
-        <v>Martin Garrix</v>
+        <v>Kenya Grace</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
+        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/catharina/1880130476</v>
+        <v>https://music.apple.com/us/album/naked/1883801913</v>
       </c>
       <c r="L131" t="str">
-        <v>Catharina - Martin Garrix</v>
+        <v>Naked - Kenya Grace</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Through The Pain (feat. Pozer)</v>
+        <v>Catharina</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/through-the-pain-feat-pozer/1877868063</v>
+        <v>https://music.apple.com/us/song/catharina/1880130477</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-17</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Through The Pain (feat. Pozer) - Single</v>
+        <v>Catharina - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>3:00</v>
+        <v>3:27</v>
       </c>
       <c r="H132" t="str">
-        <v>Chase &amp; Status</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/chase-status/121546679</v>
+        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/through-the-pain-feat-pozer/1877868059</v>
+        <v>https://music.apple.com/us/album/catharina/1880130476</v>
       </c>
       <c r="L132" t="str">
-        <v>Through The Pain (feat. Pozer) - Chase &amp; Status</v>
+        <v>Catharina - Martin Garrix</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Trying Times</v>
+        <v>Through The Pain (feat. Pozer)</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/trying-times/1862353792</v>
+        <v>https://music.apple.com/us/song/through-the-pain-feat-pozer/1877868063</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-17</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Trying Times</v>
+        <v>Through The Pain (feat. Pozer) - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>4:33</v>
+        <v>3:00</v>
       </c>
       <c r="H133" t="str">
-        <v>James Blake</v>
+        <v>Chase &amp; Status</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/chase-status/121546679</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/trying-times/1862353780</v>
+        <v>https://music.apple.com/us/album/through-the-pain-feat-pozer/1877868059</v>
       </c>
       <c r="L133" t="str">
-        <v>Trying Times - James Blake</v>
+        <v>Through The Pain (feat. Pozer) - Chase &amp; Status</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>595</v>
+        <v>Trying Times</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/595/1880470541</v>
+        <v>https://music.apple.com/us/song/trying-times/1862353792</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-17</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Be Sweet To Me</v>
+        <v>Trying Times</v>
       </c>
       <c r="G134" t="str">
-        <v>2:29</v>
+        <v>4:33</v>
       </c>
       <c r="H134" t="str">
-        <v>Violet Grohl</v>
+        <v>James Blake</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/595/1880470537</v>
+        <v>https://music.apple.com/us/album/trying-times/1862353780</v>
       </c>
       <c r="L134" t="str">
-        <v>595 - Violet Grohl</v>
+        <v>Trying Times - James Blake</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>When Did You Stop Loving Me?</v>
+        <v>595</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/when-did-you-stop-loving-me/1879593803</v>
+        <v>https://music.apple.com/us/song/595/1880470541</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-17</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Soft 2</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G135" t="str">
-        <v>3:50</v>
+        <v>2:29</v>
       </c>
       <c r="H135" t="str">
-        <v>LANY</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/lany/867853783</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/when-did-you-stop-loving-me/1879593289</v>
+        <v>https://music.apple.com/us/album/595/1880470537</v>
       </c>
       <c r="L135" t="str">
-        <v>When Did You Stop Loving Me? - LANY</v>
+        <v>595 - Violet Grohl</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>CALL ME</v>
+        <v>When Did You Stop Loving Me?</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/call-me/1882521075</v>
+        <v>https://music.apple.com/us/song/when-did-you-stop-loving-me/1879593803</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-17</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>CALL ME - Single</v>
+        <v>Soft 2</v>
       </c>
       <c r="G136" t="str">
-        <v>2:10</v>
+        <v>3:50</v>
       </c>
       <c r="H136" t="str">
-        <v>ALTÉGO</v>
+        <v>LANY</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/alt%C3%A9go/1606418899</v>
+        <v>https://music.apple.com/us/artist/lany/867853783</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/call-me/1882521073</v>
+        <v>https://music.apple.com/us/album/when-did-you-stop-loving-me/1879593289</v>
       </c>
       <c r="L136" t="str">
-        <v>CALL ME - ALTÉGO</v>
+        <v>When Did You Stop Loving Me? - LANY</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Mi Amor</v>
+        <v>CALL ME</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/mi-amor/1872454951</v>
+        <v>https://music.apple.com/us/song/call-me/1882521075</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-17</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Free (Deluxe)</v>
+        <v>CALL ME - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>2:00</v>
+        <v>2:10</v>
       </c>
       <c r="H137" t="str">
-        <v>Nasty C</v>
+        <v>ALTÉGO</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
+        <v>https://music.apple.com/us/artist/alt%C3%A9go/1606418899</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/mi-amor/1872454582</v>
+        <v>https://music.apple.com/us/album/call-me/1882521073</v>
       </c>
       <c r="L137" t="str">
-        <v>Mi Amor - Nasty C</v>
+        <v>CALL ME - ALTÉGO</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>BOBA</v>
+        <v>Mi Amor</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/boba/1880372256</v>
+        <v>https://music.apple.com/us/song/mi-amor/1872454951</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-17</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>BOBA - Single</v>
+        <v>Free (Deluxe)</v>
       </c>
       <c r="G138" t="str">
-        <v>3:00</v>
+        <v>2:00</v>
       </c>
       <c r="H138" t="str">
-        <v>SOFI TUKKER</v>
+        <v>Nasty C</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
+        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/boba/1880372250</v>
+        <v>https://music.apple.com/us/album/mi-amor/1872454582</v>
       </c>
       <c r="L138" t="str">
-        <v>BOBA - SOFI TUKKER</v>
+        <v>Mi Amor - Nasty C</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Video Shoot</v>
+        <v>BOBA</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/video-shoot/1882892621</v>
+        <v>https://music.apple.com/us/song/boba/1880372256</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-17</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Skeletor</v>
+        <v>BOBA - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>2:38</v>
+        <v>3:00</v>
       </c>
       <c r="H139" t="str">
-        <v>Chief Keef</v>
+        <v>SOFI TUKKER</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
+        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/video-shoot/1882892614</v>
+        <v>https://music.apple.com/us/album/boba/1880372250</v>
       </c>
       <c r="L139" t="str">
-        <v>Video Shoot - Chief Keef</v>
+        <v>BOBA - SOFI TUKKER</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Talk To Me Nuh</v>
+        <v>Video Shoot</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/talk-to-me-nuh/1882510363</v>
+        <v>https://music.apple.com/us/song/video-shoot/1882892621</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-17</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Talk To Me Nuh - Single</v>
+        <v>Skeletor</v>
       </c>
       <c r="G140" t="str">
-        <v>2:06</v>
+        <v>2:38</v>
       </c>
       <c r="H140" t="str">
-        <v>Shenseea</v>
+        <v>Chief Keef</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/shenseea/1132311326</v>
+        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/talk-to-me-nuh/1882510361</v>
+        <v>https://music.apple.com/us/album/video-shoot/1882892614</v>
       </c>
       <c r="L140" t="str">
-        <v>Talk To Me Nuh - Shenseea</v>
+        <v>Video Shoot - Chief Keef</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Just Believe</v>
+        <v>Talk To Me Nuh</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/just-believe/1884083105</v>
+        <v>https://music.apple.com/us/song/talk-to-me-nuh/1882510363</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-17</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Just Believe - Single</v>
+        <v>Talk To Me Nuh - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>2:41</v>
+        <v>2:06</v>
       </c>
       <c r="H141" t="str">
-        <v>Bailey Zimmerman</v>
+        <v>Shenseea</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
+        <v>https://music.apple.com/us/artist/shenseea/1132311326</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/just-believe/1884083104</v>
+        <v>https://music.apple.com/us/album/talk-to-me-nuh/1882510361</v>
       </c>
       <c r="L141" t="str">
-        <v>Just Believe - Bailey Zimmerman</v>
+        <v>Talk To Me Nuh - Shenseea</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Knife In The Heart</v>
+        <v>Just Believe</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/knife-in-the-heart/1857952500</v>
+        <v>https://music.apple.com/us/song/just-believe/1884083105</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-17</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>The Afterparty</v>
+        <v>Just Believe - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>2:57</v>
+        <v>2:41</v>
       </c>
       <c r="H142" t="str">
-        <v>Lykke Li</v>
+        <v>Bailey Zimmerman</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
+        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/knife-in-the-heart/1857952252</v>
+        <v>https://music.apple.com/us/album/just-believe/1884083104</v>
       </c>
       <c r="L142" t="str">
-        <v>Knife In The Heart - Lykke Li</v>
+        <v>Just Believe - Bailey Zimmerman</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>The Way We Touch</v>
+        <v>Knife In The Heart</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/the-way-we-touch/1875315428</v>
+        <v>https://music.apple.com/us/song/knife-in-the-heart/1857952500</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-17</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>The Way We Touch - Single</v>
+        <v>The Afterparty</v>
       </c>
       <c r="G143" t="str">
-        <v>3:09</v>
+        <v>2:57</v>
       </c>
       <c r="H143" t="str">
-        <v>Charlotte Cardin</v>
+        <v>Lykke Li</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-cardin/784665014</v>
+        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/the-way-we-touch/1875315210</v>
+        <v>https://music.apple.com/us/album/knife-in-the-heart/1857952252</v>
       </c>
       <c r="L143" t="str">
-        <v>The Way We Touch - Charlotte Cardin</v>
+        <v>Knife In The Heart - Lykke Li</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>DANGEROUS</v>
+        <v>The Way We Touch</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/dangerous/1867202642</v>
+        <v>https://music.apple.com/us/song/the-way-we-touch/1875315428</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-17</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>NIGHTS AFTER VAMP</v>
+        <v>The Way We Touch - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>4:06</v>
+        <v>3:09</v>
       </c>
       <c r="H144" t="str">
-        <v>Magnolia Park</v>
+        <v>Charlotte Cardin</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
+        <v>https://music.apple.com/us/artist/charlotte-cardin/784665014</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/dangerous/1867202638</v>
+        <v>https://music.apple.com/us/album/the-way-we-touch/1875315210</v>
       </c>
       <c r="L144" t="str">
-        <v>DANGEROUS - Magnolia Park</v>
+        <v>The Way We Touch - Charlotte Cardin</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>When I Wake Up</v>
+        <v>DANGEROUS</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/when-i-wake-up/1878237800</v>
+        <v>https://music.apple.com/us/song/dangerous/1867202642</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-17</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Dear God</v>
+        <v>NIGHTS AFTER VAMP</v>
       </c>
       <c r="G145" t="str">
-        <v>3:33</v>
+        <v>4:06</v>
       </c>
       <c r="H145" t="str">
-        <v>The Pretty Reckless</v>
+        <v>Magnolia Park</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
+        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/when-i-wake-up/1878237662</v>
+        <v>https://music.apple.com/us/album/dangerous/1867202638</v>
       </c>
       <c r="L145" t="str">
-        <v>When I Wake Up - The Pretty Reckless</v>
+        <v>DANGEROUS - Magnolia Park</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Breathe</v>
+        <v>When I Wake Up</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/breathe/1882808152</v>
+        <v>https://music.apple.com/us/song/when-i-wake-up/1878237800</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-17</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Breathe - Single</v>
+        <v>Dear God</v>
       </c>
       <c r="G146" t="str">
-        <v>2:56</v>
+        <v>3:33</v>
       </c>
       <c r="H146" t="str">
-        <v>Malcolm Todd</v>
+        <v>The Pretty Reckless</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
+        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/breathe/1882807987</v>
+        <v>https://music.apple.com/us/album/when-i-wake-up/1878237662</v>
       </c>
       <c r="L146" t="str">
-        <v>Breathe - Malcolm Todd</v>
+        <v>When I Wake Up - The Pretty Reckless</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Minty</v>
+        <v>Breathe</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/minty/1870867418</v>
+        <v>https://music.apple.com/us/song/breathe/1882808152</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-17</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>Breathe - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>1:47</v>
+        <v>2:56</v>
       </c>
       <c r="H147" t="str">
-        <v>MIKE</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/mike/1253023714</v>
+        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/minty/1870867411</v>
+        <v>https://music.apple.com/us/album/breathe/1882807987</v>
       </c>
       <c r="L147" t="str">
-        <v>Minty - MIKE</v>
+        <v>Breathe - Malcolm Todd</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Earth</v>
+        <v>Minty</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/earth/1870867498</v>
+        <v>https://music.apple.com/us/song/minty/1870867418</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-17</v>
@@ -6002,33 +6002,33 @@
         <v>POMPEII // UTILITY</v>
       </c>
       <c r="G148" t="str">
-        <v>1:37</v>
+        <v>1:47</v>
       </c>
       <c r="H148" t="str">
-        <v>Earl Sweatshirt</v>
+        <v>MIKE</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
+        <v>https://music.apple.com/us/artist/mike/1253023714</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/earth/1870867411</v>
+        <v>https://music.apple.com/us/album/minty/1870867411</v>
       </c>
       <c r="L148" t="str">
-        <v>Earth - Earl Sweatshirt</v>
+        <v>Minty - MIKE</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Drink The Water</v>
+        <v>Earth</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/drink-the-water/1883172887</v>
+        <v>https://music.apple.com/us/song/earth/1870867498</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-17</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G149" t="str">
-        <v>3:42</v>
+        <v>1:37</v>
       </c>
       <c r="H149" t="str">
-        <v>Jack Johnson</v>
+        <v>Earl Sweatshirt</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
+        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/drink-the-water/1883172879</v>
+        <v>https://music.apple.com/us/album/earth/1870867411</v>
       </c>
       <c r="L149" t="str">
-        <v>Drink The Water - Jack Johnson</v>
+        <v>Earth - Earl Sweatshirt</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>A Rainy Night in Soho</v>
+        <v>Drink The Water</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/a-rainy-night-in-soho/1878459216</v>
+        <v>https://music.apple.com/us/song/drink-the-water/1883172887</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-17</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>A Rainy Night in Soho - Single</v>
+        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
       </c>
       <c r="G150" t="str">
-        <v>4:32</v>
+        <v>3:42</v>
       </c>
       <c r="H150" t="str">
-        <v>Bruce Springsteen</v>
+        <v>Jack Johnson</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/bruce-springsteen/178834</v>
+        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/a-rainy-night-in-soho/1878459215</v>
+        <v>https://music.apple.com/us/album/drink-the-water/1883172879</v>
       </c>
       <c r="L150" t="str">
-        <v>A Rainy Night in Soho - Bruce Springsteen</v>
+        <v>Drink The Water - Jack Johnson</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>If I Don't Leave I'm Gonna Stay</v>
+        <v>A Rainy Night in Soho</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/if-i-dont-leave-im-gonna-stay/1880111466</v>
+        <v>https://music.apple.com/us/song/a-rainy-night-in-soho/1878459216</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-17</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>If I Don't Leave I'm Gonna Stay - Single</v>
+        <v>A Rainy Night in Soho - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:32</v>
+        <v>4:32</v>
       </c>
       <c r="H151" t="str">
-        <v>Carly Pearce</v>
+        <v>Bruce Springsteen</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/bruce-springsteen/178834</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/if-i-dont-leave-im-gonna-stay/1880111464</v>
+        <v>https://music.apple.com/us/album/a-rainy-night-in-soho/1878459215</v>
       </c>
       <c r="L151" t="str">
-        <v>If I Don't Leave I'm Gonna Stay - Carly Pearce</v>
+        <v>A Rainy Night in Soho - Bruce Springsteen</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Muchacho Alegre</v>
+        <v>If I Don't Leave I'm Gonna Stay</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/muchacho-alegre/1880256976</v>
+        <v>https://music.apple.com/us/song/if-i-dont-leave-im-gonna-stay/1880111466</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-17</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Muchacho Alegre - Single</v>
+        <v>If I Don't Leave I'm Gonna Stay - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>3:08</v>
+        <v>3:32</v>
       </c>
       <c r="H152" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/muchacho-alegre/1880256973</v>
+        <v>https://music.apple.com/us/album/if-i-dont-leave-im-gonna-stay/1880111464</v>
       </c>
       <c r="L152" t="str">
-        <v>Muchacho Alegre - Luis R Conriquez</v>
+        <v>If I Don't Leave I'm Gonna Stay - Carly Pearce</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Real Slow</v>
+        <v>Muchacho Alegre</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/real-slow/1869618394</v>
+        <v>https://music.apple.com/us/song/muchacho-alegre/1880256976</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-17</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Work of Heart</v>
+        <v>Muchacho Alegre - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>3:22</v>
+        <v>3:08</v>
       </c>
       <c r="H153" t="str">
-        <v>Flatland Cavalry</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/real-slow/1869617637</v>
+        <v>https://music.apple.com/us/album/muchacho-alegre/1880256973</v>
       </c>
       <c r="L153" t="str">
-        <v>Real Slow - Flatland Cavalry</v>
+        <v>Muchacho Alegre - Luis R Conriquez</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Mountain Girl</v>
+        <v>Real Slow</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/mountain-girl/1870722299</v>
+        <v>https://music.apple.com/us/song/real-slow/1869618394</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-17</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>As Is</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G154" t="str">
-        <v>2:42</v>
+        <v>3:22</v>
       </c>
       <c r="H154" t="str">
-        <v>Josiah and the Bonnevilles</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/josiah-and-the-bonnevilles/1101954493</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/mountain-girl/1870722288</v>
+        <v>https://music.apple.com/us/album/real-slow/1869617637</v>
       </c>
       <c r="L154" t="str">
-        <v>Mountain Girl - Josiah and the Bonnevilles</v>
+        <v>Real Slow - Flatland Cavalry</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Like a Spark</v>
+        <v>Mountain Girl</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/like-a-spark/1876952751</v>
+        <v>https://music.apple.com/us/song/mountain-girl/1870722299</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-17</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>American Stories</v>
+        <v>As Is</v>
       </c>
       <c r="G155" t="str">
-        <v>3:31</v>
+        <v>2:42</v>
       </c>
       <c r="H155" t="str">
-        <v>Rostam</v>
+        <v>Josiah and the Bonnevilles</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
+        <v>https://music.apple.com/us/artist/josiah-and-the-bonnevilles/1101954493</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/like-a-spark/1876952750</v>
+        <v>https://music.apple.com/us/album/mountain-girl/1870722288</v>
       </c>
       <c r="L155" t="str">
-        <v>Like a Spark - Rostam</v>
+        <v>Mountain Girl - Josiah and the Bonnevilles</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Cheesecake</v>
+        <v>Like a Spark</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/cheesecake/1882526540</v>
+        <v>https://music.apple.com/us/song/like-a-spark/1876952751</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-17</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>So Much To Tell You (Deluxe)</v>
+        <v>American Stories</v>
       </c>
       <c r="G156" t="str">
-        <v>3:29</v>
+        <v>3:31</v>
       </c>
       <c r="H156" t="str">
-        <v>Ax and the Hatchetmen</v>
+        <v>Rostam</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/ax-and-the-hatchetmen/1471855465</v>
+        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/cheesecake/1882525852</v>
+        <v>https://music.apple.com/us/album/like-a-spark/1876952750</v>
       </c>
       <c r="L156" t="str">
-        <v>Cheesecake - Ax and the Hatchetmen</v>
+        <v>Like a Spark - Rostam</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>ALWAYS LET YOU DOWN</v>
+        <v>Cheesecake</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/always-let-you-down/1871578121</v>
+        <v>https://music.apple.com/us/song/cheesecake/1882526540</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-17</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>KINDA HARD</v>
+        <v>So Much To Tell You (Deluxe)</v>
       </c>
       <c r="G157" t="str">
-        <v>3:04</v>
+        <v>3:29</v>
       </c>
       <c r="H157" t="str">
-        <v>Bilmuri</v>
+        <v>Ax and the Hatchetmen</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
+        <v>https://music.apple.com/us/artist/ax-and-the-hatchetmen/1471855465</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/always-let-you-down/1871578103</v>
+        <v>https://music.apple.com/us/album/cheesecake/1882525852</v>
       </c>
       <c r="L157" t="str">
-        <v>ALWAYS LET YOU DOWN - Bilmuri</v>
+        <v>Cheesecake - Ax and the Hatchetmen</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Freakin’ Out</v>
+        <v>ALWAYS LET YOU DOWN</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/freakin-out/1879596115</v>
+        <v>https://music.apple.com/us/song/always-let-you-down/1871578121</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-17</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Freakin’ Out - Single</v>
+        <v>KINDA HARD</v>
       </c>
       <c r="G158" t="str">
-        <v>3:37</v>
+        <v>3:04</v>
       </c>
       <c r="H158" t="str">
-        <v>Dexter and The Moonrocks</v>
+        <v>Bilmuri</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
+        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/freakin-out/1879596114</v>
+        <v>https://music.apple.com/us/album/always-let-you-down/1871578103</v>
       </c>
       <c r="L158" t="str">
-        <v>Freakin’ Out - Dexter and The Moonrocks</v>
+        <v>ALWAYS LET YOU DOWN - Bilmuri</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Name in Vein</v>
+        <v>Freakin’ Out</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/name-in-vein/1880069474</v>
+        <v>https://music.apple.com/us/song/freakin-out/1879596115</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-17</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Name in Vein - Single</v>
+        <v>Freakin’ Out - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:03</v>
+        <v>3:37</v>
       </c>
       <c r="H159" t="str">
-        <v>VOILÀ</v>
+        <v>Dexter and The Moonrocks</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/name-in-vein/1880069473</v>
+        <v>https://music.apple.com/us/album/freakin-out/1879596114</v>
       </c>
       <c r="L159" t="str">
-        <v>Name in Vein - VOILÀ</v>
+        <v>Freakin’ Out - Dexter and The Moonrocks</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>St. Catherine's Wheel</v>
+        <v>Name in Vein</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/st-catherines-wheel/1868804170</v>
+        <v>https://music.apple.com/us/song/name-in-vein/1880069474</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-17</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Into Oblivion</v>
+        <v>Name in Vein - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>4:05</v>
+        <v>3:03</v>
       </c>
       <c r="H160" t="str">
-        <v>Lamb of God</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
+        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/st-catherines-wheel/1868804163</v>
+        <v>https://music.apple.com/us/album/name-in-vein/1880069473</v>
       </c>
       <c r="L160" t="str">
-        <v>St. Catherine's Wheel - Lamb of God</v>
+        <v>Name in Vein - VOILÀ</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Undefeated Champion</v>
+        <v>St. Catherine's Wheel</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/undefeated-champion/1840517120</v>
+        <v>https://music.apple.com/us/song/st-catherines-wheel/1868804170</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-17</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Sweat</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G161" t="str">
-        <v>3:34</v>
+        <v>4:05</v>
       </c>
       <c r="H161" t="str">
-        <v>Melanie C</v>
+        <v>Lamb of God</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
+        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/undefeated-champion/1840516706</v>
+        <v>https://music.apple.com/us/album/st-catherines-wheel/1868804163</v>
       </c>
       <c r="L161" t="str">
-        <v>Undefeated Champion - Melanie C</v>
+        <v>St. Catherine's Wheel - Lamb of God</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Pull Up</v>
+        <v>Undefeated Champion</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/pull-up/1854381591</v>
+        <v>https://music.apple.com/us/song/undefeated-champion/1840517120</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-17</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Pull Up - Single</v>
+        <v>Sweat</v>
       </c>
       <c r="G162" t="str">
-        <v>2:35</v>
+        <v>3:34</v>
       </c>
       <c r="H162" t="str">
-        <v>Collect 200</v>
+        <v>Melanie C</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/collect-200/1804375505</v>
+        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/pull-up/1854381590</v>
+        <v>https://music.apple.com/us/album/undefeated-champion/1840516706</v>
       </c>
       <c r="L162" t="str">
-        <v>Pull Up - Collect 200</v>
+        <v>Undefeated Champion - Melanie C</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Ranjha</v>
+        <v>Pull Up</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/ranjha/1882965642</v>
+        <v>https://music.apple.com/us/song/pull-up/1854381591</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-17</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Ranjha - Single</v>
+        <v>Pull Up - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>3:04</v>
+        <v>2:35</v>
       </c>
       <c r="H163" t="str">
-        <v>Diljit Dosanjh</v>
+        <v>Collect 200</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/diljit-dosanjh/423087540</v>
+        <v>https://music.apple.com/us/artist/collect-200/1804375505</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/ranjha/1882965641</v>
+        <v>https://music.apple.com/us/album/pull-up/1854381590</v>
       </c>
       <c r="L163" t="str">
-        <v>Ranjha - Diljit Dosanjh</v>
+        <v>Pull Up - Collect 200</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>zombies in love</v>
+        <v>Ranjha</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/zombies-in-love/1880178176</v>
+        <v>https://music.apple.com/us/song/ranjha/1882965642</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-17</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>zombies in love - Single</v>
+        <v>Ranjha - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>2:53</v>
+        <v>3:04</v>
       </c>
       <c r="H164" t="str">
-        <v>paris jackson</v>
+        <v>Diljit Dosanjh</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
+        <v>https://music.apple.com/us/artist/diljit-dosanjh/423087540</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/zombies-in-love/1880178173</v>
+        <v>https://music.apple.com/us/album/ranjha/1882965641</v>
       </c>
       <c r="L164" t="str">
-        <v>zombies in love - paris jackson</v>
+        <v>Ranjha - Diljit Dosanjh</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Days Of Us</v>
+        <v>zombies in love</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/days-of-us/1868438268</v>
+        <v>https://music.apple.com/us/song/zombies-in-love/1880178176</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-17</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Full Circle</v>
+        <v>zombies in love - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>4:39</v>
+        <v>2:53</v>
       </c>
       <c r="H165" t="str">
-        <v>Tom Misch</v>
+        <v>paris jackson</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
+        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/days-of-us/1868437787</v>
+        <v>https://music.apple.com/us/album/zombies-in-love/1880178173</v>
       </c>
       <c r="L165" t="str">
-        <v>Days Of Us - Tom Misch</v>
+        <v>zombies in love - paris jackson</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Life Of A Man</v>
+        <v>Days Of Us</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/life-of-a-man/1882845328</v>
+        <v>https://music.apple.com/us/song/days-of-us/1868438268</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-17</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Life Of A Man - Single</v>
+        <v>Full Circle</v>
       </c>
       <c r="G166" t="str">
-        <v>3:15</v>
+        <v>4:39</v>
       </c>
       <c r="H166" t="str">
-        <v>1Ski OG</v>
+        <v>Tom Misch</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/life-of-a-man/1882845327</v>
+        <v>https://music.apple.com/us/album/days-of-us/1868437787</v>
       </c>
       <c r="L166" t="str">
-        <v>Life Of A Man - 1Ski OG</v>
+        <v>Days Of Us - Tom Misch</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Ya No</v>
+        <v>Life Of A Man</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/ya-no/1882115676</v>
+        <v>https://music.apple.com/us/song/life-of-a-man/1882845328</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-17</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Ya No - Single</v>
+        <v>Life Of A Man - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:40</v>
+        <v>3:15</v>
       </c>
       <c r="H167" t="str">
-        <v>Marca MP</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/ya-no/1882115675</v>
+        <v>https://music.apple.com/us/album/life-of-a-man/1882845327</v>
       </c>
       <c r="L167" t="str">
-        <v>Ya No - Marca MP</v>
+        <v>Life Of A Man - 1Ski OG</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Do You Really Love Her</v>
+        <v>Ya No</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/do-you-really-love-her/1879639011</v>
+        <v>https://music.apple.com/us/song/ya-no/1882115676</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-17</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Do You Really Love Her - Single</v>
+        <v>Ya No - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:48</v>
+        <v>3:40</v>
       </c>
       <c r="H168" t="str">
-        <v>Spacey Jane</v>
+        <v>Marca MP</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
+        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/do-you-really-love-her/1879639009</v>
+        <v>https://music.apple.com/us/album/ya-no/1882115675</v>
       </c>
       <c r="L168" t="str">
-        <v>Do You Really Love Her - Spacey Jane</v>
+        <v>Ya No - Marca MP</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Relieve You</v>
+        <v>Do You Really Love Her</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/relieve-you/1879589717</v>
+        <v>https://music.apple.com/us/song/do-you-really-love-her/1879639011</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-17</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Relieve You - Single</v>
+        <v>Do You Really Love Her - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>2:19</v>
+        <v>3:48</v>
       </c>
       <c r="H169" t="str">
-        <v>4Fargo</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/4fargo/1381605295</v>
+        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/relieve-you/1879589716</v>
+        <v>https://music.apple.com/us/album/do-you-really-love-her/1879639009</v>
       </c>
       <c r="L169" t="str">
-        <v>Relieve You - 4Fargo</v>
+        <v>Do You Really Love Her - Spacey Jane</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Safety</v>
+        <v>Relieve You</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/safety/1878181748</v>
+        <v>https://music.apple.com/us/song/relieve-you/1879589717</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-17</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Safety - Single</v>
+        <v>Relieve You - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:18</v>
+        <v>2:19</v>
       </c>
       <c r="H170" t="str">
-        <v>Lekan</v>
+        <v>4Fargo</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/lekan/1540259198</v>
+        <v>https://music.apple.com/us/artist/4fargo/1381605295</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/safety/1878181738</v>
+        <v>https://music.apple.com/us/album/relieve-you/1879589716</v>
       </c>
       <c r="L170" t="str">
-        <v>Safety - Lekan</v>
+        <v>Relieve You - 4Fargo</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Starlet</v>
+        <v>Safety</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/starlet/1873450846</v>
+        <v>https://music.apple.com/us/song/safety/1878181748</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-17</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>LK99</v>
+        <v>Safety - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:56</v>
+        <v>3:18</v>
       </c>
       <c r="H171" t="str">
-        <v>Leven Kali</v>
+        <v>Lekan</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/leven-kali/1166360470</v>
+        <v>https://music.apple.com/us/artist/lekan/1540259198</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/starlet/1873450570</v>
+        <v>https://music.apple.com/us/album/safety/1878181738</v>
       </c>
       <c r="L171" t="str">
-        <v>Starlet - Leven Kali</v>
+        <v>Safety - Lekan</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Physical</v>
+        <v>Starlet</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/physical/1883210753</v>
+        <v>https://music.apple.com/us/song/starlet/1873450846</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-17</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Physical - Single</v>
+        <v>LK99</v>
       </c>
       <c r="G172" t="str">
-        <v>3:52</v>
+        <v>2:56</v>
       </c>
       <c r="H172" t="str">
-        <v>Jacquees</v>
+        <v>Leven Kali</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/jacquees/386779763</v>
+        <v>https://music.apple.com/us/artist/leven-kali/1166360470</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/physical/1883210752</v>
+        <v>https://music.apple.com/us/album/starlet/1873450570</v>
       </c>
       <c r="L172" t="str">
-        <v>Physical - Jacquees</v>
+        <v>Starlet - Leven Kali</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>i'm dying to feel alive again</v>
+        <v>Physical</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/im-dying-to-feel-alive-again/1880883509</v>
+        <v>https://music.apple.com/us/song/physical/1883210753</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-17</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>i'm dying to feel alive again - Single</v>
+        <v>Physical - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>4:29</v>
+        <v>3:52</v>
       </c>
       <c r="H173" t="str">
-        <v>Casper Sage</v>
+        <v>Jacquees</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
+        <v>https://music.apple.com/us/artist/jacquees/386779763</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/im-dying-to-feel-alive-again/1880883507</v>
+        <v>https://music.apple.com/us/album/physical/1883210752</v>
       </c>
       <c r="L173" t="str">
-        <v>i'm dying to feel alive again - Casper Sage</v>
+        <v>Physical - Jacquees</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Regalito</v>
+        <v>i'm dying to feel alive again</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/regalito/1880846653</v>
+        <v>https://music.apple.com/us/song/im-dying-to-feel-alive-again/1880883509</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-17</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>TRESCENDER</v>
+        <v>i'm dying to feel alive again - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:41</v>
+        <v>4:29</v>
       </c>
       <c r="H174" t="str">
-        <v>Piso 21</v>
+        <v>Casper Sage</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/piso-21/403121923</v>
+        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/regalito/1880845994</v>
+        <v>https://music.apple.com/us/album/im-dying-to-feel-alive-again/1880883507</v>
       </c>
       <c r="L174" t="str">
-        <v>Regalito - Piso 21</v>
+        <v>i'm dying to feel alive again - Casper Sage</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Cruel Streak</v>
+        <v>Regalito</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/cruel-streak/1858689493</v>
+        <v>https://music.apple.com/us/song/regalito/1880846653</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-17</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>A Pound of Feathers</v>
+        <v>TRESCENDER</v>
       </c>
       <c r="G175" t="str">
-        <v>4:09</v>
+        <v>2:41</v>
       </c>
       <c r="H175" t="str">
-        <v>The Black Crowes</v>
+        <v>Piso 21</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
+        <v>https://music.apple.com/us/artist/piso-21/403121923</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/cruel-streak/1858689485</v>
+        <v>https://music.apple.com/us/album/regalito/1880845994</v>
       </c>
       <c r="L175" t="str">
-        <v>Cruel Streak - The Black Crowes</v>
+        <v>Regalito - Piso 21</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Die Young</v>
+        <v>Cruel Streak</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/die-young/1870715300</v>
+        <v>https://music.apple.com/us/song/cruel-streak/1858689493</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-17</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Little Wide Open</v>
+        <v>A Pound of Feathers</v>
       </c>
       <c r="G176" t="str">
-        <v>3:52</v>
+        <v>4:09</v>
       </c>
       <c r="H176" t="str">
-        <v>Kevin Morby</v>
+        <v>The Black Crowes</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/kevin-morby/708517315</v>
+        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/die-young/1870715298</v>
+        <v>https://music.apple.com/us/album/cruel-streak/1858689485</v>
       </c>
       <c r="L176" t="str">
-        <v>Die Young - Kevin Morby</v>
+        <v>Cruel Streak - The Black Crowes</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Island Girl</v>
+        <v>Die Young</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/island-girl/1884461360</v>
+        <v>https://music.apple.com/us/song/die-young/1870715300</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-17</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Island Girl - Single</v>
+        <v>Little Wide Open</v>
       </c>
       <c r="G177" t="str">
-        <v>3:27</v>
+        <v>3:52</v>
       </c>
       <c r="H177" t="str">
-        <v>Pia Mia</v>
+        <v>Kevin Morby</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/pia-mia/483071062</v>
+        <v>https://music.apple.com/us/artist/kevin-morby/708517315</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/island-girl/1884461354</v>
+        <v>https://music.apple.com/us/album/die-young/1870715298</v>
       </c>
       <c r="L177" t="str">
-        <v>Island Girl - Pia Mia</v>
+        <v>Die Young - Kevin Morby</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>GIRLY THINGS</v>
+        <v>Island Girl</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/girly-things/1876032954</v>
+        <v>https://music.apple.com/us/song/island-girl/1884461360</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-17</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>GIRLY THINGS - Single</v>
+        <v>Island Girl - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:20</v>
+        <v>3:27</v>
       </c>
       <c r="H178" t="str">
-        <v>Claudia Valentina</v>
+        <v>Pia Mia</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/claudia-valentina/1434841711</v>
+        <v>https://music.apple.com/us/artist/pia-mia/483071062</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/girly-things/1876032953</v>
+        <v>https://music.apple.com/us/album/island-girl/1884461354</v>
       </c>
       <c r="L178" t="str">
-        <v>GIRLY THINGS - Claudia Valentina</v>
+        <v>Island Girl - Pia Mia</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Looking Lovely (feat. Robin Thicke)</v>
+        <v>GIRLY THINGS</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/looking-lovely-feat-robin-thicke/1878437828</v>
+        <v>https://music.apple.com/us/song/girly-things/1876032954</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-17</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Looking Lovely (feat. Robin Thicke) - Single</v>
+        <v>GIRLY THINGS - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:22</v>
+        <v>2:20</v>
       </c>
       <c r="H179" t="str">
-        <v>Shaggy</v>
+        <v>Claudia Valentina</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/shaggy/68616</v>
+        <v>https://music.apple.com/us/artist/claudia-valentina/1434841711</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/looking-lovely-feat-robin-thicke/1878437504</v>
+        <v>https://music.apple.com/us/album/girly-things/1876032953</v>
       </c>
       <c r="L179" t="str">
-        <v>Looking Lovely (feat. Robin Thicke) - Shaggy</v>
+        <v>GIRLY THINGS - Claudia Valentina</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Tommy’s Song</v>
+        <v>Looking Lovely (feat. Robin Thicke)</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/tommys-song/1876670040</v>
+        <v>https://music.apple.com/us/song/looking-lovely-feat-robin-thicke/1878437828</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-17</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Lovers - Single</v>
+        <v>Looking Lovely (feat. Robin Thicke) - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:44</v>
+        <v>3:22</v>
       </c>
       <c r="H180" t="str">
-        <v>Nathaniel Rateliff</v>
+        <v>Shaggy</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/nathaniel-rateliff/362131302</v>
+        <v>https://music.apple.com/us/artist/shaggy/68616</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/tommys-song/1876670038</v>
+        <v>https://music.apple.com/us/album/looking-lovely-feat-robin-thicke/1878437504</v>
       </c>
       <c r="L180" t="str">
-        <v>Tommy’s Song - Nathaniel Rateliff</v>
+        <v>Looking Lovely (feat. Robin Thicke) - Shaggy</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Rainbows</v>
+        <v>Tommy’s Song</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/rainbows/1882790536</v>
+        <v>https://music.apple.com/us/song/tommys-song/1876670040</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-17</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Rainbows - Single</v>
+        <v>Lovers - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:25</v>
+        <v>3:44</v>
       </c>
       <c r="H181" t="str">
-        <v>Allison Russell</v>
+        <v>Nathaniel Rateliff</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/allison-russell/451740458</v>
+        <v>https://music.apple.com/us/artist/nathaniel-rateliff/362131302</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/rainbows/1882790535</v>
+        <v>https://music.apple.com/us/album/tommys-song/1876670038</v>
       </c>
       <c r="L181" t="str">
-        <v>Rainbows - Allison Russell</v>
+        <v>Tommy’s Song - Nathaniel Rateliff</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>butterflies</v>
+        <v>Rainbows</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/butterflies/1878228436</v>
+        <v>https://music.apple.com/us/song/rainbows/1882790536</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-17</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Bloom Again - EP</v>
+        <v>Rainbows - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:48</v>
+        <v>3:25</v>
       </c>
       <c r="H182" t="str">
-        <v>runo plum</v>
+        <v>Allison Russell</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
+        <v>https://music.apple.com/us/artist/allison-russell/451740458</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/butterflies/1878228434</v>
+        <v>https://music.apple.com/us/album/rainbows/1882790535</v>
       </c>
       <c r="L182" t="str">
-        <v>butterflies - runo plum</v>
+        <v>Rainbows - Allison Russell</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>You're Right</v>
+        <v>butterflies</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/youre-right/1874975857</v>
+        <v>https://music.apple.com/us/song/butterflies/1878228436</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-17</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>You're Right - Single</v>
+        <v>Bloom Again - EP</v>
       </c>
       <c r="G183" t="str">
-        <v>3:00</v>
+        <v>2:48</v>
       </c>
       <c r="H183" t="str">
-        <v>Emma Harner</v>
+        <v>runo plum</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/emma-harner/1543609198</v>
+        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/youre-right/1874975856</v>
+        <v>https://music.apple.com/us/album/butterflies/1878228434</v>
       </c>
       <c r="L183" t="str">
-        <v>You're Right - Emma Harner</v>
+        <v>butterflies - runo plum</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Bible Belt</v>
+        <v>You're Right</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/bible-belt/1821125622</v>
+        <v>https://music.apple.com/us/song/youre-right/1874975857</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-17</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Bible Belt - Single</v>
+        <v>You're Right - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:34</v>
+        <v>3:00</v>
       </c>
       <c r="H184" t="str">
-        <v>Baby Bugs</v>
+        <v>Emma Harner</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/baby-bugs/1551794879</v>
+        <v>https://music.apple.com/us/artist/emma-harner/1543609198</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/bible-belt/1821125621</v>
+        <v>https://music.apple.com/us/album/youre-right/1874975856</v>
       </c>
       <c r="L184" t="str">
-        <v>Bible Belt - Baby Bugs</v>
+        <v>You're Right - Emma Harner</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Daze</v>
+        <v>Bible Belt</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/daze/1862607801</v>
+        <v>https://music.apple.com/us/song/bible-belt/1821125622</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-17</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Daze - Single</v>
+        <v>Bible Belt - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:22</v>
+        <v>3:34</v>
       </c>
       <c r="H185" t="str">
-        <v>Olympia Vitalis</v>
+        <v>Baby Bugs</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
+        <v>https://music.apple.com/us/artist/baby-bugs/1551794879</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/daze/1862607800</v>
+        <v>https://music.apple.com/us/album/bible-belt/1821125621</v>
       </c>
       <c r="L185" t="str">
-        <v>Daze - Olympia Vitalis</v>
+        <v>Bible Belt - Baby Bugs</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Passionfruit</v>
+        <v>Daze</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/passionfruit/1878215125</v>
+        <v>https://music.apple.com/us/song/daze/1862607801</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-17</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Passionfruit - Single</v>
+        <v>Daze - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:57</v>
+        <v>3:22</v>
       </c>
       <c r="H186" t="str">
-        <v>Anish Kumar</v>
+        <v>Olympia Vitalis</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/passionfruit/1878215124</v>
+        <v>https://music.apple.com/us/album/daze/1862607800</v>
       </c>
       <c r="L186" t="str">
-        <v>Passionfruit - Anish Kumar</v>
+        <v>Daze - Olympia Vitalis</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Madan</v>
+        <v>Passionfruit</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/madan/1879822223</v>
+        <v>https://music.apple.com/us/song/passionfruit/1878215125</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-17</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Madan - Single</v>
+        <v>Passionfruit - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>2:56</v>
+        <v>3:57</v>
       </c>
       <c r="H187" t="str">
-        <v>Jonas Blue</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/jonas-blue/405728790</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/madan/1879822222</v>
+        <v>https://music.apple.com/us/album/passionfruit/1878215124</v>
       </c>
       <c r="L187" t="str">
-        <v>Madan - Jonas Blue</v>
+        <v>Passionfruit - Anish Kumar</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Bad Bitch</v>
+        <v>Madan</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/bad-bitch/1882818210</v>
+        <v>https://music.apple.com/us/song/madan/1879822223</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-17</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Bad Bitch - Single</v>
+        <v>Madan - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>2:28</v>
+        <v>2:56</v>
       </c>
       <c r="H188" t="str">
-        <v>41</v>
+        <v>Jonas Blue</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/41/1688992229</v>
+        <v>https://music.apple.com/us/artist/jonas-blue/405728790</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/bad-bitch/1882818208</v>
+        <v>https://music.apple.com/us/album/madan/1879822222</v>
       </c>
       <c r="L188" t="str">
-        <v>Bad Bitch - 41</v>
+        <v>Madan - Jonas Blue</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Shame</v>
+        <v>Bad Bitch</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/shame/1874080307</v>
+        <v>https://music.apple.com/us/song/bad-bitch/1882818210</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-17</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Devotion [Deluxe]</v>
+        <v>Bad Bitch - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:36</v>
+        <v>2:28</v>
       </c>
       <c r="H189" t="str">
-        <v>Sunday (1994)</v>
+        <v>41</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/sunday-1994/1728938785</v>
+        <v>https://music.apple.com/us/artist/41/1688992229</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/shame/1874080202</v>
+        <v>https://music.apple.com/us/album/bad-bitch/1882818208</v>
       </c>
       <c r="L189" t="str">
-        <v>Shame - Sunday (1994)</v>
+        <v>Bad Bitch - 41</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>teach you to love me</v>
+        <v>Shame</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/teach-you-to-love-me/1883146005</v>
+        <v>https://music.apple.com/us/song/shame/1874080307</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-17</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>teach you to love me - Single</v>
+        <v>Devotion [Deluxe]</v>
       </c>
       <c r="G190" t="str">
-        <v>3:09</v>
+        <v>3:36</v>
       </c>
       <c r="H190" t="str">
-        <v>Hailey Picardi</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/sunday-1994/1728938785</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/teach-you-to-love-me/1883146002</v>
+        <v>https://music.apple.com/us/album/shame/1874080202</v>
       </c>
       <c r="L190" t="str">
-        <v>teach you to love me - Hailey Picardi</v>
+        <v>Shame - Sunday (1994)</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>The Fix</v>
+        <v>teach you to love me</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/the-fix/1882082897</v>
+        <v>https://music.apple.com/us/song/teach-you-to-love-me/1883146005</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-17</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>The Fix - Single</v>
+        <v>teach you to love me - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>2:42</v>
+        <v>3:09</v>
       </c>
       <c r="H191" t="str">
-        <v>Baby J</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/the-fix/1882082895</v>
+        <v>https://music.apple.com/us/album/teach-you-to-love-me/1883146002</v>
       </c>
       <c r="L191" t="str">
-        <v>The Fix - Baby J</v>
+        <v>teach you to love me - Hailey Picardi</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Hanging on Hope</v>
+        <v>The Fix</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/hanging-on-hope/1881749452</v>
+        <v>https://music.apple.com/us/song/the-fix/1882082897</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-17</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Hanging on Hope - Single</v>
+        <v>The Fix - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>3:43</v>
+        <v>2:42</v>
       </c>
       <c r="H192" t="str">
-        <v>Buffalo Traffic Jam</v>
+        <v>Baby J</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
+        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/hanging-on-hope/1881749451</v>
+        <v>https://music.apple.com/us/album/the-fix/1882082895</v>
       </c>
       <c r="L192" t="str">
-        <v>Hanging on Hope - Buffalo Traffic Jam</v>
+        <v>The Fix - Baby J</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>I Know What to Say Now</v>
+        <v>Hanging on Hope</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/i-know-what-to-say-now/1879440545</v>
+        <v>https://music.apple.com/us/song/hanging-on-hope/1881749452</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-17</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>I Know What to Say Now - Single</v>
+        <v>Hanging on Hope - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:18</v>
+        <v>3:43</v>
       </c>
       <c r="H193" t="str">
-        <v>Active Child</v>
+        <v>Buffalo Traffic Jam</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/active-child/355288617</v>
+        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/i-know-what-to-say-now/1879440351</v>
+        <v>https://music.apple.com/us/album/hanging-on-hope/1881749451</v>
       </c>
       <c r="L193" t="str">
-        <v>I Know What to Say Now - Active Child</v>
+        <v>Hanging on Hope - Buffalo Traffic Jam</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Feel Something</v>
+        <v>I Know What to Say Now</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/feel-something/1876008375</v>
+        <v>https://music.apple.com/us/song/i-know-what-to-say-now/1879440545</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-17</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Feel Something - Single</v>
+        <v>I Know What to Say Now - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:09</v>
+        <v>3:18</v>
       </c>
       <c r="H194" t="str">
-        <v>Baby Queen</v>
+        <v>Active Child</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
+        <v>https://music.apple.com/us/artist/active-child/355288617</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/feel-something/1876008371</v>
+        <v>https://music.apple.com/us/album/i-know-what-to-say-now/1879440351</v>
       </c>
       <c r="L194" t="str">
-        <v>Feel Something - Baby Queen</v>
+        <v>I Know What to Say Now - Active Child</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>You Or Me</v>
+        <v>Feel Something</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/you-or-me/1869085528</v>
+        <v>https://music.apple.com/us/song/feel-something/1876008375</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-17</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Good God / Baad Man</v>
+        <v>Feel Something - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>5:28</v>
+        <v>3:09</v>
       </c>
       <c r="H195" t="str">
-        <v>Corrosion of Conformity</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
+        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/you-or-me/1869085524</v>
+        <v>https://music.apple.com/us/album/feel-something/1876008371</v>
       </c>
       <c r="L195" t="str">
-        <v>You Or Me - Corrosion of Conformity</v>
+        <v>Feel Something - Baby Queen</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Mortercheyn</v>
+        <v>You Or Me</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/mortercheyn/1862521946</v>
+        <v>https://music.apple.com/us/song/you-or-me/1869085528</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-17</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Coronach</v>
+        <v>Good God / Baad Man</v>
       </c>
       <c r="G196" t="str">
-        <v>4:18</v>
+        <v>5:28</v>
       </c>
       <c r="H196" t="str">
-        <v>Hellripper</v>
+        <v>Corrosion of Conformity</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/hellripper/1229248568</v>
+        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/mortercheyn/1862521937</v>
+        <v>https://music.apple.com/us/album/you-or-me/1869085524</v>
       </c>
       <c r="L196" t="str">
-        <v>Mortercheyn - Hellripper</v>
+        <v>You Or Me - Corrosion of Conformity</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Rip The God</v>
+        <v>Mortercheyn</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/rip-the-god/1866957697</v>
+        <v>https://music.apple.com/us/song/mortercheyn/1862521946</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-17</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Savage Imperial Death March</v>
+        <v>Coronach</v>
       </c>
       <c r="G197" t="str">
-        <v>5:20</v>
+        <v>4:18</v>
       </c>
       <c r="H197" t="str">
-        <v>Melvins</v>
+        <v>Hellripper</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/melvins/737433</v>
+        <v>https://music.apple.com/us/artist/hellripper/1229248568</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/rip-the-god/1866957685</v>
+        <v>https://music.apple.com/us/album/mortercheyn/1862521937</v>
       </c>
       <c r="L197" t="str">
-        <v>Rip The God - Melvins</v>
+        <v>Mortercheyn - Hellripper</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Who We Are</v>
+        <v>Rip The God</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/who-we-are/1879626950</v>
+        <v>https://music.apple.com/us/song/rip-the-god/1866957697</v>
       </c>
       <c r="D198" t="str">
         <v>2026-03-17</v>
@@ -7899,68 +7899,106 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Who We Are - Single</v>
+        <v>Savage Imperial Death March</v>
       </c>
       <c r="G198" t="str">
-        <v>2:10</v>
+        <v>5:20</v>
       </c>
       <c r="H198" t="str">
-        <v>Kaleena Zanders</v>
+        <v>Melvins</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+        <v>https://music.apple.com/us/artist/melvins/737433</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/who-we-are/1879626949</v>
+        <v>https://music.apple.com/us/album/rip-the-god/1866957685</v>
       </c>
       <c r="L198" t="str">
-        <v>Who We Are - Kaleena Zanders</v>
+        <v>Rip The God - Melvins</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
+        <v>Who We Are</v>
+      </c>
+      <c r="B199" t="str">
+        <v/>
+      </c>
+      <c r="C199" t="str">
+        <v>https://music.apple.com/us/song/who-we-are/1879626950</v>
+      </c>
+      <c r="D199" t="str">
+        <v>2026-03-17</v>
+      </c>
+      <c r="E199" t="str">
+        <v/>
+      </c>
+      <c r="F199" t="str">
+        <v>Who We Are - Single</v>
+      </c>
+      <c r="G199" t="str">
+        <v>2:10</v>
+      </c>
+      <c r="H199" t="str">
+        <v>Kaleena Zanders</v>
+      </c>
+      <c r="I199" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J199" t="str">
+        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+      </c>
+      <c r="K199" t="str">
+        <v>https://music.apple.com/us/album/who-we-are/1879626949</v>
+      </c>
+      <c r="L199" t="str">
+        <v>Who We Are - Kaleena Zanders</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
         <v>Reels in 360</v>
       </c>
-      <c r="B199" t="str">
-        <v/>
-      </c>
-      <c r="C199" t="str">
+      <c r="B200" t="str">
+        <v/>
+      </c>
+      <c r="C200" t="str">
         <v>https://music.apple.com/us/song/reels-in-360/1867998408</v>
       </c>
-      <c r="D199" t="str">
-        <v>2026-03-17</v>
-      </c>
-      <c r="E199" t="str">
-        <v/>
-      </c>
-      <c r="F199" t="str">
+      <c r="D200" t="str">
+        <v>2026-03-17</v>
+      </c>
+      <c r="E200" t="str">
+        <v/>
+      </c>
+      <c r="F200" t="str">
         <v>Dying Is The Internet</v>
       </c>
-      <c r="G199" t="str">
+      <c r="G200" t="str">
         <v>4:37</v>
       </c>
-      <c r="H199" t="str">
+      <c r="H200" t="str">
         <v>Simo Cell</v>
       </c>
-      <c r="I199" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J199" t="str">
+      <c r="I200" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J200" t="str">
         <v>https://music.apple.com/us/artist/simo-cell/1001568130</v>
       </c>
-      <c r="K199" t="str">
+      <c r="K200" t="str">
         <v>https://music.apple.com/us/album/reels-in-360/1867998295</v>
       </c>
-      <c r="L199" t="str">
+      <c r="L200" t="str">
         <v>Reels in 360 - Simo Cell</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L199"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L200"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
@@ -439,19 +439,19 @@
         <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>4 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>4 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:17</v>
@@ -477,19 +477,19 @@
         <v>Nick Carter - Love Life Tragedy</v>
       </c>
       <c r="B3" t="str">
-        <v>12 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>12 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:31</v>
@@ -515,19 +515,19 @@
         <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>13 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=033viNHogN4</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>13 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:38</v>
@@ -553,19 +553,19 @@
         <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
       </c>
       <c r="B5" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
         <v>4:11</v>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -705,19 +705,19 @@
         <v>Grace Enger - Give A Little (Live Performance)</v>
       </c>
       <c r="B9" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G9" t="str">
         <v>3:06</v>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=lyuE94W1WIc</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1313,19 +1313,19 @@
         <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G25" t="str">
         <v>2:42</v>
@@ -1351,19 +1351,19 @@
         <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
       </c>
       <c r="B26" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>2:31</v>
@@ -1389,19 +1389,19 @@
         <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G27" t="str">
         <v>3:14</v>
@@ -1427,19 +1427,19 @@
         <v>Allison Russell - Rainbows (Official Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G28" t="str">
         <v>3:22</v>
@@ -1465,19 +1465,19 @@
         <v>We Three - Love Who You Love (Official Audio)</v>
       </c>
       <c r="B29" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G29" t="str">
         <v>3:43</v>
@@ -1503,19 +1503,19 @@
         <v>paris jackson - zombies in love</v>
       </c>
       <c r="B30" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G30" t="str">
         <v>2:54</v>
@@ -1541,19 +1541,19 @@
         <v>Kane Brown - Woman (Official Music Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>2:46</v>
@@ -1579,19 +1579,19 @@
         <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G32" t="str">
         <v>3:37</v>
@@ -1617,19 +1617,19 @@
         <v>Malcolm Todd - Breathe (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G33" t="str">
         <v>2:57</v>
@@ -1655,19 +1655,19 @@
         <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay</v>
       </c>
       <c r="B34" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G34" t="str">
         <v>3:38</v>
@@ -1693,19 +1693,19 @@
         <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
       </c>
       <c r="B35" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>4:29</v>
@@ -1731,19 +1731,19 @@
         <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
       </c>
       <c r="B36" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>4:28</v>
@@ -1769,19 +1769,19 @@
         <v>aron! - Wonderful Thing (Piano)</v>
       </c>
       <c r="B37" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G37" t="str">
         <v>3:26</v>
@@ -1807,19 +1807,19 @@
         <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
       </c>
       <c r="B38" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G38" t="str">
         <v>3:51</v>
@@ -1845,19 +1845,19 @@
         <v>Sunday (1994) - The Fairground</v>
       </c>
       <c r="B39" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G39" t="str">
         <v>2:49</v>
@@ -1883,19 +1883,19 @@
         <v>Owen Riegling - In The Feeling (Visualizer)</v>
       </c>
       <c r="B40" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>4:16</v>
@@ -1921,19 +1921,19 @@
         <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G41" t="str">
         <v>4:16</v>
@@ -1959,19 +1959,19 @@
         <v>Maverick Sabre - 8 Stages</v>
       </c>
       <c r="B42" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G42" t="str">
         <v>3:25</v>
@@ -1997,19 +1997,19 @@
         <v>Amanda Jordan - What Else Is New</v>
       </c>
       <c r="B43" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G43" t="str">
         <v>2:50</v>
@@ -2035,19 +2035,19 @@
         <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
       </c>
       <c r="B44" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E44" t="str">
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G44" t="str">
         <v>3:57</v>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2225,19 +2225,19 @@
         <v>Natalie Jane - sabotage (Lyric Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G49" t="str">
         <v>2:57</v>
@@ -2263,19 +2263,19 @@
         <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B50" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E50" t="str">
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G50" t="str">
         <v>3:13</v>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2377,19 +2377,19 @@
         <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
       </c>
       <c r="B53" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
         <v>3:34</v>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2453,19 +2453,19 @@
         <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E55" t="str">
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G55" t="str">
         <v>4:58</v>
@@ -2491,19 +2491,19 @@
         <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E56" t="str">
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G56" t="str">
         <v>2:33</v>
@@ -2529,19 +2529,19 @@
         <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B57" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E57" t="str">
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G57" t="str">
         <v>5:01</v>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=366CV87TguE</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3213,19 +3213,19 @@
         <v>Bazzi - moment (Official Music Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G75" t="str">
         <v>2:43</v>
@@ -3251,19 +3251,19 @@
         <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
       </c>
       <c r="B76" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G76" t="str">
         <v>4:43</v>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3327,19 +3327,19 @@
         <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G78" t="str">
         <v>4:37</v>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/porch-light/1872239892</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/dry-spell/1883177258</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/riptides/1878362645</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/the-visitor/1882146993</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/i-aint-no-cowboy/1862634799</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/cant-sit-still/1878782917</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245797</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/blow-my-mind/1852752616</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/sata/1874015489</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/una-aventura/1882069505</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/home-feat-hikaru-utada/1845190340</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/dirty-wedding-dress/1872842320</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/fastest-gun-alive/1874700373</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/imposible/1880775726</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/trade-places/1878823464</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/motion-party/1882152039</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/woman/1882549709</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/sunburn/1880836041</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/que-te-cost%C3%B3/1882108997</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/oooshxt/1879612533</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/cruel-world/1859630041</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/star/1876633306</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/get-go/1862570884</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/thunderwave/1861531685</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/club-song/1882478246</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/better-man/1880496044</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/sabotage/1882209853</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/2000s-pop-punk-rnb/1878820143</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/naked/1883802157</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/catharina/1880130477</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/through-the-pain-feat-pozer/1877868063</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/trying-times/1862353792</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/595/1880470541</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/when-did-you-stop-loving-me/1879593803</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/call-me/1882521075</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/mi-amor/1872454951</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/boba/1880372256</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/video-shoot/1882892621</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/talk-to-me-nuh/1882510363</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/just-believe/1884083105</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/knife-in-the-heart/1857952500</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/the-way-we-touch/1875315428</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/dangerous/1867202642</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/when-i-wake-up/1878237800</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/breathe/1882808152</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/minty/1870867418</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/earth/1870867498</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/drink-the-water/1883172887</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/a-rainy-night-in-soho/1878459216</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/if-i-dont-leave-im-gonna-stay/1880111466</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/muchacho-alegre/1880256976</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/real-slow/1869618394</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/mountain-girl/1870722299</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/like-a-spark/1876952751</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/cheesecake/1882526540</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/always-let-you-down/1871578121</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/freakin-out/1879596115</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/name-in-vein/1880069474</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/st-catherines-wheel/1868804170</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/undefeated-champion/1840517120</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/pull-up/1854381591</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/ranjha/1882965642</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/zombies-in-love/1880178176</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/days-of-us/1868438268</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/life-of-a-man/1882845328</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/ya-no/1882115676</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/do-you-really-love-her/1879639011</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/relieve-you/1879589717</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/safety/1878181748</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/starlet/1873450846</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/physical/1883210753</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/im-dying-to-feel-alive-again/1880883509</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/regalito/1880846653</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/cruel-streak/1858689493</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/die-young/1870715300</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/island-girl/1884461360</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/girly-things/1876032954</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/looking-lovely-feat-robin-thicke/1878437828</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/tommys-song/1876670040</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/rainbows/1882790536</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/butterflies/1878228436</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/youre-right/1874975857</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/bible-belt/1821125622</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/daze/1862607801</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/passionfruit/1878215125</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/madan/1879822223</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/bad-bitch/1882818210</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/shame/1874080307</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/teach-you-to-love-me/1883146005</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/the-fix/1882082897</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/hanging-on-hope/1881749452</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/i-know-what-to-say-now/1879440545</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -7779,7 +7779,7 @@
         <v>https://music.apple.com/us/song/feel-something/1876008375</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -7817,7 +7817,7 @@
         <v>https://music.apple.com/us/song/you-or-me/1869085528</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -7855,7 +7855,7 @@
         <v>https://music.apple.com/us/song/mortercheyn/1862521946</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -7893,7 +7893,7 @@
         <v>https://music.apple.com/us/song/rip-the-god/1866957697</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E198" t="str">
         <v/>
@@ -7931,7 +7931,7 @@
         <v>https://music.apple.com/us/song/who-we-are/1879626950</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E199" t="str">
         <v/>
@@ -7969,7 +7969,7 @@
         <v>https://music.apple.com/us/song/reels-in-360/1867998408</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E200" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:17</v>
@@ -477,7 +477,7 @@
         <v>Nick Carter - Love Life Tragedy</v>
       </c>
       <c r="B3" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:31</v>
@@ -1275,7 +1275,7 @@
         <v>Bishop Briggs - River (10 Years Later)</v>
       </c>
       <c r="B24" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G24" t="str">
         <v>3:46</v>
@@ -2795,7 +2795,7 @@
         <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
       </c>
       <c r="B64" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G64" t="str">
         <v>2:41</v>
@@ -2833,7 +2833,7 @@
         <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G65" t="str">
         <v>2:29</v>
@@ -2871,7 +2871,7 @@
         <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
       </c>
       <c r="B66" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G66" t="str">
         <v>2:43</v>
@@ -2909,7 +2909,7 @@
         <v>Matt Hansen - SAME TIME (Official Live Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G67" t="str">
         <v>3:46</v>
@@ -2947,7 +2947,7 @@
         <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G68" t="str">
         <v>4:01</v>
@@ -2985,7 +2985,7 @@
         <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G69" t="str">
         <v>3:23</v>
@@ -3023,7 +3023,7 @@
         <v>almost monday - leaving is easy (official video)</v>
       </c>
       <c r="B70" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G70" t="str">
         <v>3:39</v>
@@ -3061,7 +3061,7 @@
         <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G71" t="str">
         <v>3:04</v>
@@ -3099,7 +3099,7 @@
         <v>vaultboy - DELETED (Official Lyric Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G72" t="str">
         <v>3:25</v>
@@ -3137,7 +3137,7 @@
         <v>The Warning - Kerosene (Official Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G73" t="str">
         <v>3:49</v>
@@ -3175,7 +3175,7 @@
         <v>aron! - Wonderful Thing (City View Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G74" t="str">
         <v>2:14</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L200"/>
+  <dimension ref="A1:L201"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -439,7 +439,7 @@
         <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>17 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>17 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:17</v>
@@ -629,7 +629,7 @@
         <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:47</v>
@@ -971,7 +971,7 @@
         <v>Martin Garrix - Catharina (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G16" t="str">
         <v>3:31</v>
@@ -1009,7 +1009,7 @@
         <v>Baby Queen - Feel Something (Official Visualiser)</v>
       </c>
       <c r="B17" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>3:11</v>
@@ -1047,7 +1047,7 @@
         <v>HAUSER - Hungarian Dance No. 5</v>
       </c>
       <c r="B18" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G18" t="str">
         <v>2:27</v>
@@ -1085,7 +1085,7 @@
         <v>Holly Humberstone - Cruel World</v>
       </c>
       <c r="B19" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G19" t="str">
         <v>3:34</v>
@@ -1123,7 +1123,7 @@
         <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>2:50</v>
@@ -1161,7 +1161,7 @@
         <v>Rick Astley - Waiting On You (Official Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G21" t="str">
         <v>3:51</v>
@@ -1199,7 +1199,7 @@
         <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G22" t="str">
         <v>2:39</v>
@@ -1237,7 +1237,7 @@
         <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
       </c>
       <c r="B23" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>5:08</v>
@@ -2073,7 +2073,7 @@
         <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G45" t="str">
         <v>3:58</v>
@@ -2111,7 +2111,7 @@
         <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
       </c>
       <c r="B46" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G46" t="str">
         <v>3:25</v>
@@ -2149,7 +2149,7 @@
         <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B47" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G47" t="str">
         <v>4:09</v>
@@ -2187,7 +2187,7 @@
         <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G48" t="str">
         <v>2:08</v>
@@ -2339,7 +2339,7 @@
         <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
       </c>
       <c r="B52" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G52" t="str">
         <v>3:57</v>
@@ -2681,7 +2681,7 @@
         <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G61" t="str">
         <v>2:56</v>
@@ -2719,7 +2719,7 @@
         <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
       </c>
       <c r="B62" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G62" t="str">
         <v>3:21</v>
@@ -2757,7 +2757,7 @@
         <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G63" t="str">
         <v>3:16</v>
@@ -3289,7 +3289,7 @@
         <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G77" t="str">
         <v>2:44</v>
@@ -4236,13 +4236,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Ocean In The Desert</v>
+        <v>Distance</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
+        <v>https://music.apple.com/us/song/distance/1882713727</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-18</v>
@@ -4251,25 +4251,25 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Ocean In The Desert - Single</v>
+        <v>Distance - Single</v>
       </c>
       <c r="G102" t="str">
-        <v>3:44</v>
+        <v>3:14</v>
       </c>
       <c r="H102" t="str">
-        <v>Dionne Warwick</v>
+        <v>Finn Askew</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/dionne-warwick/16198</v>
+        <v>https://music.apple.com/us/artist/finn-askew/1292169978</v>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/ocean-in-the-desert/1878421568</v>
+        <v>https://music.apple.com/us/album/distance/1882713721</v>
       </c>
       <c r="L102" t="str">
-        <v>Ocean In The Desert - Dionne Warwick</v>
+        <v>Distance - Finn Askew</v>
       </c>
     </row>
     <row r="103">
@@ -4350,13 +4350,13 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Riptides</v>
+        <v>Ocean In The Desert</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/riptides/1878362645</v>
+        <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
       </c>
       <c r="D105" t="str">
         <v>2026-03-18</v>
@@ -4365,25 +4365,25 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>I Built You a Tower</v>
+        <v>Ocean In The Desert - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>3:17</v>
+        <v>3:44</v>
       </c>
       <c r="H105" t="str">
-        <v>Death Cab for Cutie</v>
+        <v>Dionne Warwick</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
+        <v>https://music.apple.com/us/artist/dionne-warwick/16198</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/riptides/1878362451</v>
+        <v>https://music.apple.com/us/album/ocean-in-the-desert/1878421568</v>
       </c>
       <c r="L105" t="str">
-        <v>Riptides - Death Cab for Cutie</v>
+        <v>Ocean In The Desert - Dionne Warwick</v>
       </c>
     </row>
     <row r="106">
@@ -4654,13 +4654,13 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Home (feat. Hikaru Utada)</v>
+        <v>Riptides</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/home-feat-hikaru-utada/1845190340</v>
+        <v>https://music.apple.com/us/song/riptides/1878362645</v>
       </c>
       <c r="D113" t="str">
         <v>2026-03-18</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Whatever's Clever!</v>
+        <v>I Built You a Tower</v>
       </c>
       <c r="G113" t="str">
-        <v>3:44</v>
+        <v>3:17</v>
       </c>
       <c r="H113" t="str">
-        <v>Charlie Puth</v>
+        <v>Death Cab for Cutie</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/home-feat-hikaru-utada/1845189970</v>
+        <v>https://music.apple.com/us/album/riptides/1878362451</v>
       </c>
       <c r="L113" t="str">
-        <v>Home (feat. Hikaru Utada) - Charlie Puth</v>
+        <v>Riptides - Death Cab for Cutie</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>dirty wedding dress</v>
+        <v>Home (feat. Hikaru Utada)</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/dirty-wedding-dress/1872842320</v>
+        <v>https://music.apple.com/us/song/home-feat-hikaru-utada/1845190340</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-18</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>everyone for ten minutes</v>
+        <v>Whatever's Clever!</v>
       </c>
       <c r="G114" t="str">
-        <v>4:49</v>
+        <v>3:44</v>
       </c>
       <c r="H114" t="str">
-        <v>Bleachers</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/dirty-wedding-dress/1872842313</v>
+        <v>https://music.apple.com/us/album/home-feat-hikaru-utada/1845189970</v>
       </c>
       <c r="L114" t="str">
-        <v>dirty wedding dress - Bleachers</v>
+        <v>Home (feat. Hikaru Utada) - Charlie Puth</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Fastest Gun Alive</v>
+        <v>dirty wedding dress</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/fastest-gun-alive/1874700373</v>
+        <v>https://music.apple.com/us/song/dirty-wedding-dress/1872842320</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-18</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Age of the Ram</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G115" t="str">
-        <v>3:07</v>
+        <v>4:49</v>
       </c>
       <c r="H115" t="str">
-        <v>Charley Crockett</v>
+        <v>Bleachers</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/fastest-gun-alive/1874700242</v>
+        <v>https://music.apple.com/us/album/dirty-wedding-dress/1872842313</v>
       </c>
       <c r="L115" t="str">
-        <v>Fastest Gun Alive - Charley Crockett</v>
+        <v>dirty wedding dress - Bleachers</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>IMPOSIBLE</v>
+        <v>Fastest Gun Alive</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/imposible/1880775726</v>
+        <v>https://music.apple.com/us/song/fastest-gun-alive/1874700373</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-18</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>IMPOSIBLE - Single</v>
+        <v>Age of the Ram</v>
       </c>
       <c r="G116" t="str">
-        <v>3:13</v>
+        <v>3:07</v>
       </c>
       <c r="H116" t="str">
-        <v>Grupo Frontera</v>
+        <v>Charley Crockett</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
+        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/imposible/1880775721</v>
+        <v>https://music.apple.com/us/album/fastest-gun-alive/1874700242</v>
       </c>
       <c r="L116" t="str">
-        <v>IMPOSIBLE - Grupo Frontera</v>
+        <v>Fastest Gun Alive - Charley Crockett</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Trade Places</v>
+        <v>IMPOSIBLE</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/trade-places/1878823464</v>
+        <v>https://music.apple.com/us/song/imposible/1880775726</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-18</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Monica</v>
+        <v>IMPOSIBLE - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:02</v>
+        <v>3:13</v>
       </c>
       <c r="H117" t="str">
-        <v>Jack Harlow</v>
+        <v>Grupo Frontera</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/jack-harlow/1047679432</v>
+        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/trade-places/1878823462</v>
+        <v>https://music.apple.com/us/album/imposible/1880775721</v>
       </c>
       <c r="L117" t="str">
-        <v>Trade Places - Jack Harlow</v>
+        <v>IMPOSIBLE - Grupo Frontera</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Motion Party</v>
+        <v>Trade Places</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/motion-party/1882152039</v>
+        <v>https://music.apple.com/us/song/trade-places/1878823464</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-18</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Motion Party - Single</v>
+        <v>Monica</v>
       </c>
       <c r="G118" t="str">
-        <v>1:35</v>
+        <v>3:02</v>
       </c>
       <c r="H118" t="str">
-        <v>Bossman Dlow</v>
+        <v>Jack Harlow</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
+        <v>https://music.apple.com/us/artist/jack-harlow/1047679432</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/motion-party/1882151996</v>
+        <v>https://music.apple.com/us/album/trade-places/1878823462</v>
       </c>
       <c r="L118" t="str">
-        <v>Motion Party - Bossman Dlow</v>
+        <v>Trade Places - Jack Harlow</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Woman</v>
+        <v>Motion Party</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/woman/1882549709</v>
+        <v>https://music.apple.com/us/song/motion-party/1882152039</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-18</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Woman - Single</v>
+        <v>Motion Party - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>2:46</v>
+        <v>1:35</v>
       </c>
       <c r="H119" t="str">
-        <v>Kane Brown</v>
+        <v>Bossman Dlow</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/kane-brown/930928857</v>
+        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/woman/1882549705</v>
+        <v>https://music.apple.com/us/album/motion-party/1882151996</v>
       </c>
       <c r="L119" t="str">
-        <v>Woman - Kane Brown</v>
+        <v>Motion Party - Bossman Dlow</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Sunburn</v>
+        <v>Woman</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/sunburn/1880836041</v>
+        <v>https://music.apple.com/us/song/woman/1882549709</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-18</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Sunburn - Single</v>
+        <v>Woman - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:05</v>
+        <v>2:46</v>
       </c>
       <c r="H120" t="str">
-        <v>Tucker Wetmore</v>
+        <v>Kane Brown</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/tucker-wetmore/1486724646</v>
+        <v>https://music.apple.com/us/artist/kane-brown/930928857</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/sunburn/1880835818</v>
+        <v>https://music.apple.com/us/album/woman/1882549705</v>
       </c>
       <c r="L120" t="str">
-        <v>Sunburn - Tucker Wetmore</v>
+        <v>Woman - Kane Brown</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Que Te Costó</v>
+        <v>Sunburn</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/que-te-cost%C3%B3/1882108997</v>
+        <v>https://music.apple.com/us/song/sunburn/1880836041</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-18</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Metamorfosis</v>
+        <v>Sunburn - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>2:54</v>
+        <v>3:05</v>
       </c>
       <c r="H121" t="str">
-        <v>Yahritza Y Su Esencia</v>
+        <v>Tucker Wetmore</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
+        <v>https://music.apple.com/us/artist/tucker-wetmore/1486724646</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/que-te-cost%C3%B3/1882108989</v>
+        <v>https://music.apple.com/us/album/sunburn/1880835818</v>
       </c>
       <c r="L121" t="str">
-        <v>Que Te Costó - Yahritza Y Su Esencia</v>
+        <v>Sunburn - Tucker Wetmore</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>oooshxt!</v>
+        <v>Que Te Costó</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/oooshxt/1879612533</v>
+        <v>https://music.apple.com/us/song/que-te-cost%C3%B3/1882108997</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-18</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>oooshxt! - Single</v>
+        <v>Metamorfosis</v>
       </c>
       <c r="G122" t="str">
-        <v>2:15</v>
+        <v>2:54</v>
       </c>
       <c r="H122" t="str">
-        <v>Samara Cyn</v>
+        <v>Yahritza Y Su Esencia</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
+        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/oooshxt/1879612532</v>
+        <v>https://music.apple.com/us/album/que-te-cost%C3%B3/1882108989</v>
       </c>
       <c r="L122" t="str">
-        <v>oooshxt! - Samara Cyn</v>
+        <v>Que Te Costó - Yahritza Y Su Esencia</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Cruel World</v>
+        <v>oooshxt!</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/cruel-world/1859630041</v>
+        <v>https://music.apple.com/us/song/oooshxt/1879612533</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-18</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Cruel World</v>
+        <v>oooshxt! - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>3:26</v>
+        <v>2:15</v>
       </c>
       <c r="H123" t="str">
-        <v>Holly Humberstone</v>
+        <v>Samara Cyn</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/cruel-world/1859629846</v>
+        <v>https://music.apple.com/us/album/oooshxt/1879612532</v>
       </c>
       <c r="L123" t="str">
-        <v>Cruel World - Holly Humberstone</v>
+        <v>oooshxt! - Samara Cyn</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Star</v>
+        <v>Cruel World</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/star/1876633306</v>
+        <v>https://music.apple.com/us/song/cruel-world/1859630041</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-18</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Star - Single</v>
+        <v>Cruel World</v>
       </c>
       <c r="G124" t="str">
-        <v>3:25</v>
+        <v>3:26</v>
       </c>
       <c r="H124" t="str">
-        <v>Iceage</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/star/1876633303</v>
+        <v>https://music.apple.com/us/album/cruel-world/1859629846</v>
       </c>
       <c r="L124" t="str">
-        <v>Star - Iceage</v>
+        <v>Cruel World - Holly Humberstone</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Get Go</v>
+        <v>Star</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/get-go/1862570884</v>
+        <v>https://music.apple.com/us/song/star/1876633306</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-18</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Ambiguous Desire</v>
+        <v>Star - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>3:22</v>
+        <v>3:25</v>
       </c>
       <c r="H125" t="str">
-        <v>Arlo Parks</v>
+        <v>Iceage</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
+        <v>https://music.apple.com/us/artist/iceage/406846711</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/get-go/1862570378</v>
+        <v>https://music.apple.com/us/album/star/1876633303</v>
       </c>
       <c r="L125" t="str">
-        <v>Get Go - Arlo Parks</v>
+        <v>Star - Iceage</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>ThunderWave</v>
+        <v>Get Go</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/thunderwave/1861531685</v>
+        <v>https://music.apple.com/us/song/get-go/1862570884</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-18</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Distracted</v>
+        <v>Ambiguous Desire</v>
       </c>
       <c r="G126" t="str">
-        <v>3:14</v>
+        <v>3:22</v>
       </c>
       <c r="H126" t="str">
-        <v>Thundercat</v>
+        <v>Arlo Parks</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
+        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/thunderwave/1861531667</v>
+        <v>https://music.apple.com/us/album/get-go/1862570378</v>
       </c>
       <c r="L126" t="str">
-        <v>ThunderWave - Thundercat</v>
+        <v>Get Go - Arlo Parks</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Club Song</v>
+        <v>ThunderWave</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/club-song/1882478246</v>
+        <v>https://music.apple.com/us/song/thunderwave/1861531685</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-18</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Club Song - Single</v>
+        <v>Distracted</v>
       </c>
       <c r="G127" t="str">
-        <v>2:27</v>
+        <v>3:14</v>
       </c>
       <c r="H127" t="str">
-        <v>The Pussycat Dolls</v>
+        <v>Thundercat</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/the-pussycat-dolls/23331509</v>
+        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/club-song/1882478243</v>
+        <v>https://music.apple.com/us/album/thunderwave/1861531667</v>
       </c>
       <c r="L127" t="str">
-        <v>Club Song - The Pussycat Dolls</v>
+        <v>ThunderWave - Thundercat</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Better Man</v>
+        <v>Club Song</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/better-man/1880496044</v>
+        <v>https://music.apple.com/us/song/club-song/1882478246</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-18</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Better Man - Single</v>
+        <v>Club Song - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>2:53</v>
+        <v>2:27</v>
       </c>
       <c r="H128" t="str">
-        <v>jxdn</v>
+        <v>The Pussycat Dolls</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/jxdn/1513237359</v>
+        <v>https://music.apple.com/us/artist/the-pussycat-dolls/23331509</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/better-man/1880496042</v>
+        <v>https://music.apple.com/us/album/club-song/1882478243</v>
       </c>
       <c r="L128" t="str">
-        <v>Better Man - jxdn</v>
+        <v>Club Song - The Pussycat Dolls</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>sabotage</v>
+        <v>Better Man</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/sabotage/1882209853</v>
+        <v>https://music.apple.com/us/song/better-man/1880496044</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-18</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>sabotage - Single</v>
+        <v>Better Man - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>2:58</v>
+        <v>2:53</v>
       </c>
       <c r="H129" t="str">
-        <v>Natalie Jane</v>
+        <v>jxdn</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/natalie-jane/1504380197</v>
+        <v>https://music.apple.com/us/artist/jxdn/1513237359</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/sabotage/1882209670</v>
+        <v>https://music.apple.com/us/album/better-man/1880496042</v>
       </c>
       <c r="L129" t="str">
-        <v>sabotage - Natalie Jane</v>
+        <v>Better Man - jxdn</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>2000s Pop Punk Rnb</v>
+        <v>sabotage</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/2000s-pop-punk-rnb/1878820143</v>
+        <v>https://music.apple.com/us/song/sabotage/1882209853</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-18</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Still Loiteringgg / 2000s Pop Punk Rnb - Single</v>
+        <v>sabotage - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>2:56</v>
+        <v>2:58</v>
       </c>
       <c r="H130" t="str">
-        <v>WHATMORE</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/whatmore/1797119133</v>
+        <v>https://music.apple.com/us/artist/natalie-jane/1504380197</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/2000s-pop-punk-rnb/1878820131</v>
+        <v>https://music.apple.com/us/album/sabotage/1882209670</v>
       </c>
       <c r="L130" t="str">
-        <v>2000s Pop Punk Rnb - WHATMORE</v>
+        <v>sabotage - Natalie Jane</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Naked</v>
+        <v>2000s Pop Punk Rnb</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/naked/1883802157</v>
+        <v>https://music.apple.com/us/song/2000s-pop-punk-rnb/1878820143</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-18</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Naked - Single</v>
+        <v>Still Loiteringgg / 2000s Pop Punk Rnb - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>3:39</v>
+        <v>2:56</v>
       </c>
       <c r="H131" t="str">
-        <v>Kenya Grace</v>
+        <v>WHATMORE</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
+        <v>https://music.apple.com/us/artist/whatmore/1797119133</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/naked/1883801913</v>
+        <v>https://music.apple.com/us/album/2000s-pop-punk-rnb/1878820131</v>
       </c>
       <c r="L131" t="str">
-        <v>Naked - Kenya Grace</v>
+        <v>2000s Pop Punk Rnb - WHATMORE</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Catharina</v>
+        <v>Naked</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/catharina/1880130477</v>
+        <v>https://music.apple.com/us/song/naked/1883802157</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-18</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Catharina - Single</v>
+        <v>Naked - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>3:27</v>
+        <v>3:39</v>
       </c>
       <c r="H132" t="str">
-        <v>Martin Garrix</v>
+        <v>Kenya Grace</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
+        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/catharina/1880130476</v>
+        <v>https://music.apple.com/us/album/naked/1883801913</v>
       </c>
       <c r="L132" t="str">
-        <v>Catharina - Martin Garrix</v>
+        <v>Naked - Kenya Grace</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Through The Pain (feat. Pozer)</v>
+        <v>Catharina</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/through-the-pain-feat-pozer/1877868063</v>
+        <v>https://music.apple.com/us/song/catharina/1880130477</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-18</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Through The Pain (feat. Pozer) - Single</v>
+        <v>Catharina - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>3:00</v>
+        <v>3:27</v>
       </c>
       <c r="H133" t="str">
-        <v>Chase &amp; Status</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/chase-status/121546679</v>
+        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/through-the-pain-feat-pozer/1877868059</v>
+        <v>https://music.apple.com/us/album/catharina/1880130476</v>
       </c>
       <c r="L133" t="str">
-        <v>Through The Pain (feat. Pozer) - Chase &amp; Status</v>
+        <v>Catharina - Martin Garrix</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Trying Times</v>
+        <v>Through The Pain (feat. Pozer)</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/trying-times/1862353792</v>
+        <v>https://music.apple.com/us/song/through-the-pain-feat-pozer/1877868063</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-18</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Trying Times</v>
+        <v>Through The Pain (feat. Pozer) - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>4:33</v>
+        <v>3:00</v>
       </c>
       <c r="H134" t="str">
-        <v>James Blake</v>
+        <v>Chase &amp; Status</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/chase-status/121546679</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/trying-times/1862353780</v>
+        <v>https://music.apple.com/us/album/through-the-pain-feat-pozer/1877868059</v>
       </c>
       <c r="L134" t="str">
-        <v>Trying Times - James Blake</v>
+        <v>Through The Pain (feat. Pozer) - Chase &amp; Status</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>595</v>
+        <v>Trying Times</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/595/1880470541</v>
+        <v>https://music.apple.com/us/song/trying-times/1862353792</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-18</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Be Sweet To Me</v>
+        <v>Trying Times</v>
       </c>
       <c r="G135" t="str">
-        <v>2:29</v>
+        <v>4:33</v>
       </c>
       <c r="H135" t="str">
-        <v>Violet Grohl</v>
+        <v>James Blake</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/595/1880470537</v>
+        <v>https://music.apple.com/us/album/trying-times/1862353780</v>
       </c>
       <c r="L135" t="str">
-        <v>595 - Violet Grohl</v>
+        <v>Trying Times - James Blake</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>When Did You Stop Loving Me?</v>
+        <v>595</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/when-did-you-stop-loving-me/1879593803</v>
+        <v>https://music.apple.com/us/song/595/1880470541</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-18</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Soft 2</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G136" t="str">
-        <v>3:50</v>
+        <v>2:29</v>
       </c>
       <c r="H136" t="str">
-        <v>LANY</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/lany/867853783</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/when-did-you-stop-loving-me/1879593289</v>
+        <v>https://music.apple.com/us/album/595/1880470537</v>
       </c>
       <c r="L136" t="str">
-        <v>When Did You Stop Loving Me? - LANY</v>
+        <v>595 - Violet Grohl</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>CALL ME</v>
+        <v>When Did You Stop Loving Me?</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/call-me/1882521075</v>
+        <v>https://music.apple.com/us/song/when-did-you-stop-loving-me/1879593803</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-18</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>CALL ME - Single</v>
+        <v>Soft 2</v>
       </c>
       <c r="G137" t="str">
-        <v>2:10</v>
+        <v>3:50</v>
       </c>
       <c r="H137" t="str">
-        <v>ALTÉGO</v>
+        <v>LANY</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/alt%C3%A9go/1606418899</v>
+        <v>https://music.apple.com/us/artist/lany/867853783</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/call-me/1882521073</v>
+        <v>https://music.apple.com/us/album/when-did-you-stop-loving-me/1879593289</v>
       </c>
       <c r="L137" t="str">
-        <v>CALL ME - ALTÉGO</v>
+        <v>When Did You Stop Loving Me? - LANY</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Mi Amor</v>
+        <v>CALL ME</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/mi-amor/1872454951</v>
+        <v>https://music.apple.com/us/song/call-me/1882521075</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-18</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Free (Deluxe)</v>
+        <v>CALL ME - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>2:00</v>
+        <v>2:10</v>
       </c>
       <c r="H138" t="str">
-        <v>Nasty C</v>
+        <v>ALTÉGO</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
+        <v>https://music.apple.com/us/artist/alt%C3%A9go/1606418899</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/mi-amor/1872454582</v>
+        <v>https://music.apple.com/us/album/call-me/1882521073</v>
       </c>
       <c r="L138" t="str">
-        <v>Mi Amor - Nasty C</v>
+        <v>CALL ME - ALTÉGO</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>BOBA</v>
+        <v>Mi Amor</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/boba/1880372256</v>
+        <v>https://music.apple.com/us/song/mi-amor/1872454951</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-18</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>BOBA - Single</v>
+        <v>Free (Deluxe)</v>
       </c>
       <c r="G139" t="str">
-        <v>3:00</v>
+        <v>2:00</v>
       </c>
       <c r="H139" t="str">
-        <v>SOFI TUKKER</v>
+        <v>Nasty C</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
+        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/boba/1880372250</v>
+        <v>https://music.apple.com/us/album/mi-amor/1872454582</v>
       </c>
       <c r="L139" t="str">
-        <v>BOBA - SOFI TUKKER</v>
+        <v>Mi Amor - Nasty C</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Video Shoot</v>
+        <v>BOBA</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/video-shoot/1882892621</v>
+        <v>https://music.apple.com/us/song/boba/1880372256</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-18</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Skeletor</v>
+        <v>BOBA - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>2:38</v>
+        <v>3:00</v>
       </c>
       <c r="H140" t="str">
-        <v>Chief Keef</v>
+        <v>SOFI TUKKER</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
+        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/video-shoot/1882892614</v>
+        <v>https://music.apple.com/us/album/boba/1880372250</v>
       </c>
       <c r="L140" t="str">
-        <v>Video Shoot - Chief Keef</v>
+        <v>BOBA - SOFI TUKKER</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Talk To Me Nuh</v>
+        <v>Video Shoot</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/talk-to-me-nuh/1882510363</v>
+        <v>https://music.apple.com/us/song/video-shoot/1882892621</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-18</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Talk To Me Nuh - Single</v>
+        <v>Skeletor</v>
       </c>
       <c r="G141" t="str">
-        <v>2:06</v>
+        <v>2:38</v>
       </c>
       <c r="H141" t="str">
-        <v>Shenseea</v>
+        <v>Chief Keef</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/shenseea/1132311326</v>
+        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/talk-to-me-nuh/1882510361</v>
+        <v>https://music.apple.com/us/album/video-shoot/1882892614</v>
       </c>
       <c r="L141" t="str">
-        <v>Talk To Me Nuh - Shenseea</v>
+        <v>Video Shoot - Chief Keef</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Just Believe</v>
+        <v>Talk To Me Nuh</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/just-believe/1884083105</v>
+        <v>https://music.apple.com/us/song/talk-to-me-nuh/1882510363</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-18</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Just Believe - Single</v>
+        <v>Talk To Me Nuh - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>2:41</v>
+        <v>2:06</v>
       </c>
       <c r="H142" t="str">
-        <v>Bailey Zimmerman</v>
+        <v>Shenseea</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
+        <v>https://music.apple.com/us/artist/shenseea/1132311326</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/just-believe/1884083104</v>
+        <v>https://music.apple.com/us/album/talk-to-me-nuh/1882510361</v>
       </c>
       <c r="L142" t="str">
-        <v>Just Believe - Bailey Zimmerman</v>
+        <v>Talk To Me Nuh - Shenseea</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Knife In The Heart</v>
+        <v>Just Believe</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/knife-in-the-heart/1857952500</v>
+        <v>https://music.apple.com/us/song/just-believe/1884083105</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-18</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>The Afterparty</v>
+        <v>Just Believe - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>2:57</v>
+        <v>2:41</v>
       </c>
       <c r="H143" t="str">
-        <v>Lykke Li</v>
+        <v>Bailey Zimmerman</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
+        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/knife-in-the-heart/1857952252</v>
+        <v>https://music.apple.com/us/album/just-believe/1884083104</v>
       </c>
       <c r="L143" t="str">
-        <v>Knife In The Heart - Lykke Li</v>
+        <v>Just Believe - Bailey Zimmerman</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>The Way We Touch</v>
+        <v>Knife In The Heart</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/the-way-we-touch/1875315428</v>
+        <v>https://music.apple.com/us/song/knife-in-the-heart/1857952500</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-18</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>The Way We Touch - Single</v>
+        <v>The Afterparty</v>
       </c>
       <c r="G144" t="str">
-        <v>3:09</v>
+        <v>2:57</v>
       </c>
       <c r="H144" t="str">
-        <v>Charlotte Cardin</v>
+        <v>Lykke Li</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-cardin/784665014</v>
+        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/the-way-we-touch/1875315210</v>
+        <v>https://music.apple.com/us/album/knife-in-the-heart/1857952252</v>
       </c>
       <c r="L144" t="str">
-        <v>The Way We Touch - Charlotte Cardin</v>
+        <v>Knife In The Heart - Lykke Li</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>DANGEROUS</v>
+        <v>The Way We Touch</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/dangerous/1867202642</v>
+        <v>https://music.apple.com/us/song/the-way-we-touch/1875315428</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-18</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>NIGHTS AFTER VAMP</v>
+        <v>The Way We Touch - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>4:06</v>
+        <v>3:09</v>
       </c>
       <c r="H145" t="str">
-        <v>Magnolia Park</v>
+        <v>Charlotte Cardin</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
+        <v>https://music.apple.com/us/artist/charlotte-cardin/784665014</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/dangerous/1867202638</v>
+        <v>https://music.apple.com/us/album/the-way-we-touch/1875315210</v>
       </c>
       <c r="L145" t="str">
-        <v>DANGEROUS - Magnolia Park</v>
+        <v>The Way We Touch - Charlotte Cardin</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>When I Wake Up</v>
+        <v>DANGEROUS</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/when-i-wake-up/1878237800</v>
+        <v>https://music.apple.com/us/song/dangerous/1867202642</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-18</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Dear God</v>
+        <v>NIGHTS AFTER VAMP</v>
       </c>
       <c r="G146" t="str">
-        <v>3:33</v>
+        <v>4:06</v>
       </c>
       <c r="H146" t="str">
-        <v>The Pretty Reckless</v>
+        <v>Magnolia Park</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
+        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/when-i-wake-up/1878237662</v>
+        <v>https://music.apple.com/us/album/dangerous/1867202638</v>
       </c>
       <c r="L146" t="str">
-        <v>When I Wake Up - The Pretty Reckless</v>
+        <v>DANGEROUS - Magnolia Park</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Breathe</v>
+        <v>When I Wake Up</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/breathe/1882808152</v>
+        <v>https://music.apple.com/us/song/when-i-wake-up/1878237800</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-18</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Breathe - Single</v>
+        <v>Dear God</v>
       </c>
       <c r="G147" t="str">
-        <v>2:56</v>
+        <v>3:33</v>
       </c>
       <c r="H147" t="str">
-        <v>Malcolm Todd</v>
+        <v>The Pretty Reckless</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
+        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/breathe/1882807987</v>
+        <v>https://music.apple.com/us/album/when-i-wake-up/1878237662</v>
       </c>
       <c r="L147" t="str">
-        <v>Breathe - Malcolm Todd</v>
+        <v>When I Wake Up - The Pretty Reckless</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Minty</v>
+        <v>Breathe</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/minty/1870867418</v>
+        <v>https://music.apple.com/us/song/breathe/1882808152</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-18</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>Breathe - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>1:47</v>
+        <v>2:56</v>
       </c>
       <c r="H148" t="str">
-        <v>MIKE</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/mike/1253023714</v>
+        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/minty/1870867411</v>
+        <v>https://music.apple.com/us/album/breathe/1882807987</v>
       </c>
       <c r="L148" t="str">
-        <v>Minty - MIKE</v>
+        <v>Breathe - Malcolm Todd</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Earth</v>
+        <v>Minty</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/earth/1870867498</v>
+        <v>https://music.apple.com/us/song/minty/1870867418</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-18</v>
@@ -6040,33 +6040,33 @@
         <v>POMPEII // UTILITY</v>
       </c>
       <c r="G149" t="str">
-        <v>1:37</v>
+        <v>1:47</v>
       </c>
       <c r="H149" t="str">
-        <v>Earl Sweatshirt</v>
+        <v>MIKE</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
+        <v>https://music.apple.com/us/artist/mike/1253023714</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/earth/1870867411</v>
+        <v>https://music.apple.com/us/album/minty/1870867411</v>
       </c>
       <c r="L149" t="str">
-        <v>Earth - Earl Sweatshirt</v>
+        <v>Minty - MIKE</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Drink The Water</v>
+        <v>Earth</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/drink-the-water/1883172887</v>
+        <v>https://music.apple.com/us/song/earth/1870867498</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-18</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G150" t="str">
-        <v>3:42</v>
+        <v>1:37</v>
       </c>
       <c r="H150" t="str">
-        <v>Jack Johnson</v>
+        <v>Earl Sweatshirt</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
+        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/drink-the-water/1883172879</v>
+        <v>https://music.apple.com/us/album/earth/1870867411</v>
       </c>
       <c r="L150" t="str">
-        <v>Drink The Water - Jack Johnson</v>
+        <v>Earth - Earl Sweatshirt</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>A Rainy Night in Soho</v>
+        <v>Drink The Water</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/a-rainy-night-in-soho/1878459216</v>
+        <v>https://music.apple.com/us/song/drink-the-water/1883172887</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-18</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>A Rainy Night in Soho - Single</v>
+        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
       </c>
       <c r="G151" t="str">
-        <v>4:32</v>
+        <v>3:42</v>
       </c>
       <c r="H151" t="str">
-        <v>Bruce Springsteen</v>
+        <v>Jack Johnson</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/bruce-springsteen/178834</v>
+        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/a-rainy-night-in-soho/1878459215</v>
+        <v>https://music.apple.com/us/album/drink-the-water/1883172879</v>
       </c>
       <c r="L151" t="str">
-        <v>A Rainy Night in Soho - Bruce Springsteen</v>
+        <v>Drink The Water - Jack Johnson</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>If I Don't Leave I'm Gonna Stay</v>
+        <v>A Rainy Night in Soho</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/if-i-dont-leave-im-gonna-stay/1880111466</v>
+        <v>https://music.apple.com/us/song/a-rainy-night-in-soho/1878459216</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-18</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>If I Don't Leave I'm Gonna Stay - Single</v>
+        <v>A Rainy Night in Soho - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>3:32</v>
+        <v>4:32</v>
       </c>
       <c r="H152" t="str">
-        <v>Carly Pearce</v>
+        <v>Bruce Springsteen</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/bruce-springsteen/178834</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/if-i-dont-leave-im-gonna-stay/1880111464</v>
+        <v>https://music.apple.com/us/album/a-rainy-night-in-soho/1878459215</v>
       </c>
       <c r="L152" t="str">
-        <v>If I Don't Leave I'm Gonna Stay - Carly Pearce</v>
+        <v>A Rainy Night in Soho - Bruce Springsteen</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Muchacho Alegre</v>
+        <v>If I Don't Leave I'm Gonna Stay</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/muchacho-alegre/1880256976</v>
+        <v>https://music.apple.com/us/song/if-i-dont-leave-im-gonna-stay/1880111466</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-18</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Muchacho Alegre - Single</v>
+        <v>If I Don't Leave I'm Gonna Stay - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>3:08</v>
+        <v>3:32</v>
       </c>
       <c r="H153" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/muchacho-alegre/1880256973</v>
+        <v>https://music.apple.com/us/album/if-i-dont-leave-im-gonna-stay/1880111464</v>
       </c>
       <c r="L153" t="str">
-        <v>Muchacho Alegre - Luis R Conriquez</v>
+        <v>If I Don't Leave I'm Gonna Stay - Carly Pearce</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Real Slow</v>
+        <v>Muchacho Alegre</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/real-slow/1869618394</v>
+        <v>https://music.apple.com/us/song/muchacho-alegre/1880256976</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-18</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Work of Heart</v>
+        <v>Muchacho Alegre - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>3:22</v>
+        <v>3:08</v>
       </c>
       <c r="H154" t="str">
-        <v>Flatland Cavalry</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/real-slow/1869617637</v>
+        <v>https://music.apple.com/us/album/muchacho-alegre/1880256973</v>
       </c>
       <c r="L154" t="str">
-        <v>Real Slow - Flatland Cavalry</v>
+        <v>Muchacho Alegre - Luis R Conriquez</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Mountain Girl</v>
+        <v>Real Slow</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/mountain-girl/1870722299</v>
+        <v>https://music.apple.com/us/song/real-slow/1869618394</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-18</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>As Is</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G155" t="str">
-        <v>2:42</v>
+        <v>3:22</v>
       </c>
       <c r="H155" t="str">
-        <v>Josiah and the Bonnevilles</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/josiah-and-the-bonnevilles/1101954493</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/mountain-girl/1870722288</v>
+        <v>https://music.apple.com/us/album/real-slow/1869617637</v>
       </c>
       <c r="L155" t="str">
-        <v>Mountain Girl - Josiah and the Bonnevilles</v>
+        <v>Real Slow - Flatland Cavalry</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Like a Spark</v>
+        <v>Mountain Girl</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/like-a-spark/1876952751</v>
+        <v>https://music.apple.com/us/song/mountain-girl/1870722299</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-18</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>American Stories</v>
+        <v>As Is</v>
       </c>
       <c r="G156" t="str">
-        <v>3:31</v>
+        <v>2:42</v>
       </c>
       <c r="H156" t="str">
-        <v>Rostam</v>
+        <v>Josiah and the Bonnevilles</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
+        <v>https://music.apple.com/us/artist/josiah-and-the-bonnevilles/1101954493</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/like-a-spark/1876952750</v>
+        <v>https://music.apple.com/us/album/mountain-girl/1870722288</v>
       </c>
       <c r="L156" t="str">
-        <v>Like a Spark - Rostam</v>
+        <v>Mountain Girl - Josiah and the Bonnevilles</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Cheesecake</v>
+        <v>Like a Spark</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/cheesecake/1882526540</v>
+        <v>https://music.apple.com/us/song/like-a-spark/1876952751</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-18</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>So Much To Tell You (Deluxe)</v>
+        <v>American Stories</v>
       </c>
       <c r="G157" t="str">
-        <v>3:29</v>
+        <v>3:31</v>
       </c>
       <c r="H157" t="str">
-        <v>Ax and the Hatchetmen</v>
+        <v>Rostam</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/ax-and-the-hatchetmen/1471855465</v>
+        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/cheesecake/1882525852</v>
+        <v>https://music.apple.com/us/album/like-a-spark/1876952750</v>
       </c>
       <c r="L157" t="str">
-        <v>Cheesecake - Ax and the Hatchetmen</v>
+        <v>Like a Spark - Rostam</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>ALWAYS LET YOU DOWN</v>
+        <v>Cheesecake</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/always-let-you-down/1871578121</v>
+        <v>https://music.apple.com/us/song/cheesecake/1882526540</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-18</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>KINDA HARD</v>
+        <v>So Much To Tell You (Deluxe)</v>
       </c>
       <c r="G158" t="str">
-        <v>3:04</v>
+        <v>3:29</v>
       </c>
       <c r="H158" t="str">
-        <v>Bilmuri</v>
+        <v>Ax and the Hatchetmen</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
+        <v>https://music.apple.com/us/artist/ax-and-the-hatchetmen/1471855465</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/always-let-you-down/1871578103</v>
+        <v>https://music.apple.com/us/album/cheesecake/1882525852</v>
       </c>
       <c r="L158" t="str">
-        <v>ALWAYS LET YOU DOWN - Bilmuri</v>
+        <v>Cheesecake - Ax and the Hatchetmen</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Freakin’ Out</v>
+        <v>ALWAYS LET YOU DOWN</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/freakin-out/1879596115</v>
+        <v>https://music.apple.com/us/song/always-let-you-down/1871578121</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-18</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Freakin’ Out - Single</v>
+        <v>KINDA HARD</v>
       </c>
       <c r="G159" t="str">
-        <v>3:37</v>
+        <v>3:04</v>
       </c>
       <c r="H159" t="str">
-        <v>Dexter and The Moonrocks</v>
+        <v>Bilmuri</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
+        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/freakin-out/1879596114</v>
+        <v>https://music.apple.com/us/album/always-let-you-down/1871578103</v>
       </c>
       <c r="L159" t="str">
-        <v>Freakin’ Out - Dexter and The Moonrocks</v>
+        <v>ALWAYS LET YOU DOWN - Bilmuri</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Name in Vein</v>
+        <v>Freakin’ Out</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/name-in-vein/1880069474</v>
+        <v>https://music.apple.com/us/song/freakin-out/1879596115</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-18</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Name in Vein - Single</v>
+        <v>Freakin’ Out - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:03</v>
+        <v>3:37</v>
       </c>
       <c r="H160" t="str">
-        <v>VOILÀ</v>
+        <v>Dexter and The Moonrocks</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/name-in-vein/1880069473</v>
+        <v>https://music.apple.com/us/album/freakin-out/1879596114</v>
       </c>
       <c r="L160" t="str">
-        <v>Name in Vein - VOILÀ</v>
+        <v>Freakin’ Out - Dexter and The Moonrocks</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>St. Catherine's Wheel</v>
+        <v>Name in Vein</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/st-catherines-wheel/1868804170</v>
+        <v>https://music.apple.com/us/song/name-in-vein/1880069474</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-18</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Into Oblivion</v>
+        <v>Name in Vein - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>4:05</v>
+        <v>3:03</v>
       </c>
       <c r="H161" t="str">
-        <v>Lamb of God</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
+        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/st-catherines-wheel/1868804163</v>
+        <v>https://music.apple.com/us/album/name-in-vein/1880069473</v>
       </c>
       <c r="L161" t="str">
-        <v>St. Catherine's Wheel - Lamb of God</v>
+        <v>Name in Vein - VOILÀ</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Undefeated Champion</v>
+        <v>St. Catherine's Wheel</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/undefeated-champion/1840517120</v>
+        <v>https://music.apple.com/us/song/st-catherines-wheel/1868804170</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-18</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Sweat</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G162" t="str">
-        <v>3:34</v>
+        <v>4:05</v>
       </c>
       <c r="H162" t="str">
-        <v>Melanie C</v>
+        <v>Lamb of God</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
+        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/undefeated-champion/1840516706</v>
+        <v>https://music.apple.com/us/album/st-catherines-wheel/1868804163</v>
       </c>
       <c r="L162" t="str">
-        <v>Undefeated Champion - Melanie C</v>
+        <v>St. Catherine's Wheel - Lamb of God</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Pull Up</v>
+        <v>Undefeated Champion</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/pull-up/1854381591</v>
+        <v>https://music.apple.com/us/song/undefeated-champion/1840517120</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-18</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Pull Up - Single</v>
+        <v>Sweat</v>
       </c>
       <c r="G163" t="str">
-        <v>2:35</v>
+        <v>3:34</v>
       </c>
       <c r="H163" t="str">
-        <v>Collect 200</v>
+        <v>Melanie C</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/collect-200/1804375505</v>
+        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/pull-up/1854381590</v>
+        <v>https://music.apple.com/us/album/undefeated-champion/1840516706</v>
       </c>
       <c r="L163" t="str">
-        <v>Pull Up - Collect 200</v>
+        <v>Undefeated Champion - Melanie C</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Ranjha</v>
+        <v>Pull Up</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/ranjha/1882965642</v>
+        <v>https://music.apple.com/us/song/pull-up/1854381591</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-18</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Ranjha - Single</v>
+        <v>Pull Up - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>3:04</v>
+        <v>2:35</v>
       </c>
       <c r="H164" t="str">
-        <v>Diljit Dosanjh</v>
+        <v>Collect 200</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/diljit-dosanjh/423087540</v>
+        <v>https://music.apple.com/us/artist/collect-200/1804375505</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/ranjha/1882965641</v>
+        <v>https://music.apple.com/us/album/pull-up/1854381590</v>
       </c>
       <c r="L164" t="str">
-        <v>Ranjha - Diljit Dosanjh</v>
+        <v>Pull Up - Collect 200</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>zombies in love</v>
+        <v>Ranjha</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/zombies-in-love/1880178176</v>
+        <v>https://music.apple.com/us/song/ranjha/1882965642</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-18</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>zombies in love - Single</v>
+        <v>Ranjha - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>2:53</v>
+        <v>3:04</v>
       </c>
       <c r="H165" t="str">
-        <v>paris jackson</v>
+        <v>Diljit Dosanjh</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
+        <v>https://music.apple.com/us/artist/diljit-dosanjh/423087540</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/zombies-in-love/1880178173</v>
+        <v>https://music.apple.com/us/album/ranjha/1882965641</v>
       </c>
       <c r="L165" t="str">
-        <v>zombies in love - paris jackson</v>
+        <v>Ranjha - Diljit Dosanjh</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Days Of Us</v>
+        <v>zombies in love</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/days-of-us/1868438268</v>
+        <v>https://music.apple.com/us/song/zombies-in-love/1880178176</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-18</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Full Circle</v>
+        <v>zombies in love - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>4:39</v>
+        <v>2:53</v>
       </c>
       <c r="H166" t="str">
-        <v>Tom Misch</v>
+        <v>paris jackson</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
+        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/days-of-us/1868437787</v>
+        <v>https://music.apple.com/us/album/zombies-in-love/1880178173</v>
       </c>
       <c r="L166" t="str">
-        <v>Days Of Us - Tom Misch</v>
+        <v>zombies in love - paris jackson</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Life Of A Man</v>
+        <v>Days Of Us</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/life-of-a-man/1882845328</v>
+        <v>https://music.apple.com/us/song/days-of-us/1868438268</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-18</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Life Of A Man - Single</v>
+        <v>Full Circle</v>
       </c>
       <c r="G167" t="str">
-        <v>3:15</v>
+        <v>4:39</v>
       </c>
       <c r="H167" t="str">
-        <v>1Ski OG</v>
+        <v>Tom Misch</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/life-of-a-man/1882845327</v>
+        <v>https://music.apple.com/us/album/days-of-us/1868437787</v>
       </c>
       <c r="L167" t="str">
-        <v>Life Of A Man - 1Ski OG</v>
+        <v>Days Of Us - Tom Misch</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Ya No</v>
+        <v>Life Of A Man</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/ya-no/1882115676</v>
+        <v>https://music.apple.com/us/song/life-of-a-man/1882845328</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-18</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Ya No - Single</v>
+        <v>Life Of A Man - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:40</v>
+        <v>3:15</v>
       </c>
       <c r="H168" t="str">
-        <v>Marca MP</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/ya-no/1882115675</v>
+        <v>https://music.apple.com/us/album/life-of-a-man/1882845327</v>
       </c>
       <c r="L168" t="str">
-        <v>Ya No - Marca MP</v>
+        <v>Life Of A Man - 1Ski OG</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Do You Really Love Her</v>
+        <v>Ya No</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/do-you-really-love-her/1879639011</v>
+        <v>https://music.apple.com/us/song/ya-no/1882115676</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-18</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Do You Really Love Her - Single</v>
+        <v>Ya No - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:48</v>
+        <v>3:40</v>
       </c>
       <c r="H169" t="str">
-        <v>Spacey Jane</v>
+        <v>Marca MP</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
+        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/do-you-really-love-her/1879639009</v>
+        <v>https://music.apple.com/us/album/ya-no/1882115675</v>
       </c>
       <c r="L169" t="str">
-        <v>Do You Really Love Her - Spacey Jane</v>
+        <v>Ya No - Marca MP</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Relieve You</v>
+        <v>Do You Really Love Her</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/relieve-you/1879589717</v>
+        <v>https://music.apple.com/us/song/do-you-really-love-her/1879639011</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-18</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Relieve You - Single</v>
+        <v>Do You Really Love Her - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>2:19</v>
+        <v>3:48</v>
       </c>
       <c r="H170" t="str">
-        <v>4Fargo</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/4fargo/1381605295</v>
+        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/relieve-you/1879589716</v>
+        <v>https://music.apple.com/us/album/do-you-really-love-her/1879639009</v>
       </c>
       <c r="L170" t="str">
-        <v>Relieve You - 4Fargo</v>
+        <v>Do You Really Love Her - Spacey Jane</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Safety</v>
+        <v>Relieve You</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/safety/1878181748</v>
+        <v>https://music.apple.com/us/song/relieve-you/1879589717</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-18</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Safety - Single</v>
+        <v>Relieve You - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>3:18</v>
+        <v>2:19</v>
       </c>
       <c r="H171" t="str">
-        <v>Lekan</v>
+        <v>4Fargo</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/lekan/1540259198</v>
+        <v>https://music.apple.com/us/artist/4fargo/1381605295</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/safety/1878181738</v>
+        <v>https://music.apple.com/us/album/relieve-you/1879589716</v>
       </c>
       <c r="L171" t="str">
-        <v>Safety - Lekan</v>
+        <v>Relieve You - 4Fargo</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Starlet</v>
+        <v>Safety</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/starlet/1873450846</v>
+        <v>https://music.apple.com/us/song/safety/1878181748</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-18</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>LK99</v>
+        <v>Safety - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>2:56</v>
+        <v>3:18</v>
       </c>
       <c r="H172" t="str">
-        <v>Leven Kali</v>
+        <v>Lekan</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/leven-kali/1166360470</v>
+        <v>https://music.apple.com/us/artist/lekan/1540259198</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/starlet/1873450570</v>
+        <v>https://music.apple.com/us/album/safety/1878181738</v>
       </c>
       <c r="L172" t="str">
-        <v>Starlet - Leven Kali</v>
+        <v>Safety - Lekan</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Physical</v>
+        <v>Starlet</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/physical/1883210753</v>
+        <v>https://music.apple.com/us/song/starlet/1873450846</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-18</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Physical - Single</v>
+        <v>LK99</v>
       </c>
       <c r="G173" t="str">
-        <v>3:52</v>
+        <v>2:56</v>
       </c>
       <c r="H173" t="str">
-        <v>Jacquees</v>
+        <v>Leven Kali</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/jacquees/386779763</v>
+        <v>https://music.apple.com/us/artist/leven-kali/1166360470</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/physical/1883210752</v>
+        <v>https://music.apple.com/us/album/starlet/1873450570</v>
       </c>
       <c r="L173" t="str">
-        <v>Physical - Jacquees</v>
+        <v>Starlet - Leven Kali</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>i'm dying to feel alive again</v>
+        <v>Physical</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/im-dying-to-feel-alive-again/1880883509</v>
+        <v>https://music.apple.com/us/song/physical/1883210753</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-18</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>i'm dying to feel alive again - Single</v>
+        <v>Physical - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>4:29</v>
+        <v>3:52</v>
       </c>
       <c r="H174" t="str">
-        <v>Casper Sage</v>
+        <v>Jacquees</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
+        <v>https://music.apple.com/us/artist/jacquees/386779763</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/im-dying-to-feel-alive-again/1880883507</v>
+        <v>https://music.apple.com/us/album/physical/1883210752</v>
       </c>
       <c r="L174" t="str">
-        <v>i'm dying to feel alive again - Casper Sage</v>
+        <v>Physical - Jacquees</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Regalito</v>
+        <v>i'm dying to feel alive again</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/regalito/1880846653</v>
+        <v>https://music.apple.com/us/song/im-dying-to-feel-alive-again/1880883509</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-18</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>TRESCENDER</v>
+        <v>i'm dying to feel alive again - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:41</v>
+        <v>4:29</v>
       </c>
       <c r="H175" t="str">
-        <v>Piso 21</v>
+        <v>Casper Sage</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/piso-21/403121923</v>
+        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/regalito/1880845994</v>
+        <v>https://music.apple.com/us/album/im-dying-to-feel-alive-again/1880883507</v>
       </c>
       <c r="L175" t="str">
-        <v>Regalito - Piso 21</v>
+        <v>i'm dying to feel alive again - Casper Sage</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Cruel Streak</v>
+        <v>Regalito</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/cruel-streak/1858689493</v>
+        <v>https://music.apple.com/us/song/regalito/1880846653</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-18</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>A Pound of Feathers</v>
+        <v>TRESCENDER</v>
       </c>
       <c r="G176" t="str">
-        <v>4:09</v>
+        <v>2:41</v>
       </c>
       <c r="H176" t="str">
-        <v>The Black Crowes</v>
+        <v>Piso 21</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
+        <v>https://music.apple.com/us/artist/piso-21/403121923</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/cruel-streak/1858689485</v>
+        <v>https://music.apple.com/us/album/regalito/1880845994</v>
       </c>
       <c r="L176" t="str">
-        <v>Cruel Streak - The Black Crowes</v>
+        <v>Regalito - Piso 21</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Die Young</v>
+        <v>Cruel Streak</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/die-young/1870715300</v>
+        <v>https://music.apple.com/us/song/cruel-streak/1858689493</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-18</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Little Wide Open</v>
+        <v>A Pound of Feathers</v>
       </c>
       <c r="G177" t="str">
-        <v>3:52</v>
+        <v>4:09</v>
       </c>
       <c r="H177" t="str">
-        <v>Kevin Morby</v>
+        <v>The Black Crowes</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/kevin-morby/708517315</v>
+        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/die-young/1870715298</v>
+        <v>https://music.apple.com/us/album/cruel-streak/1858689485</v>
       </c>
       <c r="L177" t="str">
-        <v>Die Young - Kevin Morby</v>
+        <v>Cruel Streak - The Black Crowes</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Island Girl</v>
+        <v>Die Young</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/island-girl/1884461360</v>
+        <v>https://music.apple.com/us/song/die-young/1870715300</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-18</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Island Girl - Single</v>
+        <v>Little Wide Open</v>
       </c>
       <c r="G178" t="str">
-        <v>3:27</v>
+        <v>3:52</v>
       </c>
       <c r="H178" t="str">
-        <v>Pia Mia</v>
+        <v>Kevin Morby</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/pia-mia/483071062</v>
+        <v>https://music.apple.com/us/artist/kevin-morby/708517315</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/island-girl/1884461354</v>
+        <v>https://music.apple.com/us/album/die-young/1870715298</v>
       </c>
       <c r="L178" t="str">
-        <v>Island Girl - Pia Mia</v>
+        <v>Die Young - Kevin Morby</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>GIRLY THINGS</v>
+        <v>Island Girl</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/girly-things/1876032954</v>
+        <v>https://music.apple.com/us/song/island-girl/1884461360</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-18</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>GIRLY THINGS - Single</v>
+        <v>Island Girl - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>2:20</v>
+        <v>3:27</v>
       </c>
       <c r="H179" t="str">
-        <v>Claudia Valentina</v>
+        <v>Pia Mia</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/claudia-valentina/1434841711</v>
+        <v>https://music.apple.com/us/artist/pia-mia/483071062</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/girly-things/1876032953</v>
+        <v>https://music.apple.com/us/album/island-girl/1884461354</v>
       </c>
       <c r="L179" t="str">
-        <v>GIRLY THINGS - Claudia Valentina</v>
+        <v>Island Girl - Pia Mia</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Looking Lovely (feat. Robin Thicke)</v>
+        <v>GIRLY THINGS</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/looking-lovely-feat-robin-thicke/1878437828</v>
+        <v>https://music.apple.com/us/song/girly-things/1876032954</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-18</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Looking Lovely (feat. Robin Thicke) - Single</v>
+        <v>GIRLY THINGS - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:22</v>
+        <v>2:20</v>
       </c>
       <c r="H180" t="str">
-        <v>Shaggy</v>
+        <v>Claudia Valentina</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/shaggy/68616</v>
+        <v>https://music.apple.com/us/artist/claudia-valentina/1434841711</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/looking-lovely-feat-robin-thicke/1878437504</v>
+        <v>https://music.apple.com/us/album/girly-things/1876032953</v>
       </c>
       <c r="L180" t="str">
-        <v>Looking Lovely (feat. Robin Thicke) - Shaggy</v>
+        <v>GIRLY THINGS - Claudia Valentina</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Tommy’s Song</v>
+        <v>Looking Lovely (feat. Robin Thicke)</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/tommys-song/1876670040</v>
+        <v>https://music.apple.com/us/song/looking-lovely-feat-robin-thicke/1878437828</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-18</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Lovers - Single</v>
+        <v>Looking Lovely (feat. Robin Thicke) - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:44</v>
+        <v>3:22</v>
       </c>
       <c r="H181" t="str">
-        <v>Nathaniel Rateliff</v>
+        <v>Shaggy</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/nathaniel-rateliff/362131302</v>
+        <v>https://music.apple.com/us/artist/shaggy/68616</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/tommys-song/1876670038</v>
+        <v>https://music.apple.com/us/album/looking-lovely-feat-robin-thicke/1878437504</v>
       </c>
       <c r="L181" t="str">
-        <v>Tommy’s Song - Nathaniel Rateliff</v>
+        <v>Looking Lovely (feat. Robin Thicke) - Shaggy</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Rainbows</v>
+        <v>Tommy’s Song</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/rainbows/1882790536</v>
+        <v>https://music.apple.com/us/song/tommys-song/1876670040</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-18</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Rainbows - Single</v>
+        <v>Lovers - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:25</v>
+        <v>3:44</v>
       </c>
       <c r="H182" t="str">
-        <v>Allison Russell</v>
+        <v>Nathaniel Rateliff</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/allison-russell/451740458</v>
+        <v>https://music.apple.com/us/artist/nathaniel-rateliff/362131302</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/rainbows/1882790535</v>
+        <v>https://music.apple.com/us/album/tommys-song/1876670038</v>
       </c>
       <c r="L182" t="str">
-        <v>Rainbows - Allison Russell</v>
+        <v>Tommy’s Song - Nathaniel Rateliff</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>butterflies</v>
+        <v>Rainbows</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/butterflies/1878228436</v>
+        <v>https://music.apple.com/us/song/rainbows/1882790536</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-18</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Bloom Again - EP</v>
+        <v>Rainbows - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:48</v>
+        <v>3:25</v>
       </c>
       <c r="H183" t="str">
-        <v>runo plum</v>
+        <v>Allison Russell</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
+        <v>https://music.apple.com/us/artist/allison-russell/451740458</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/butterflies/1878228434</v>
+        <v>https://music.apple.com/us/album/rainbows/1882790535</v>
       </c>
       <c r="L183" t="str">
-        <v>butterflies - runo plum</v>
+        <v>Rainbows - Allison Russell</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>You're Right</v>
+        <v>butterflies</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/youre-right/1874975857</v>
+        <v>https://music.apple.com/us/song/butterflies/1878228436</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-18</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>You're Right - Single</v>
+        <v>Bloom Again - EP</v>
       </c>
       <c r="G184" t="str">
-        <v>3:00</v>
+        <v>2:48</v>
       </c>
       <c r="H184" t="str">
-        <v>Emma Harner</v>
+        <v>runo plum</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/emma-harner/1543609198</v>
+        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/youre-right/1874975856</v>
+        <v>https://music.apple.com/us/album/butterflies/1878228434</v>
       </c>
       <c r="L184" t="str">
-        <v>You're Right - Emma Harner</v>
+        <v>butterflies - runo plum</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Bible Belt</v>
+        <v>You're Right</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/bible-belt/1821125622</v>
+        <v>https://music.apple.com/us/song/youre-right/1874975857</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-18</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Bible Belt - Single</v>
+        <v>You're Right - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:34</v>
+        <v>3:00</v>
       </c>
       <c r="H185" t="str">
-        <v>Baby Bugs</v>
+        <v>Emma Harner</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/baby-bugs/1551794879</v>
+        <v>https://music.apple.com/us/artist/emma-harner/1543609198</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/bible-belt/1821125621</v>
+        <v>https://music.apple.com/us/album/youre-right/1874975856</v>
       </c>
       <c r="L185" t="str">
-        <v>Bible Belt - Baby Bugs</v>
+        <v>You're Right - Emma Harner</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Daze</v>
+        <v>Bible Belt</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/daze/1862607801</v>
+        <v>https://music.apple.com/us/song/bible-belt/1821125622</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-18</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Daze - Single</v>
+        <v>Bible Belt - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:22</v>
+        <v>3:34</v>
       </c>
       <c r="H186" t="str">
-        <v>Olympia Vitalis</v>
+        <v>Baby Bugs</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
+        <v>https://music.apple.com/us/artist/baby-bugs/1551794879</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/daze/1862607800</v>
+        <v>https://music.apple.com/us/album/bible-belt/1821125621</v>
       </c>
       <c r="L186" t="str">
-        <v>Daze - Olympia Vitalis</v>
+        <v>Bible Belt - Baby Bugs</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Passionfruit</v>
+        <v>Daze</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/passionfruit/1878215125</v>
+        <v>https://music.apple.com/us/song/daze/1862607801</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-18</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Passionfruit - Single</v>
+        <v>Daze - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:57</v>
+        <v>3:22</v>
       </c>
       <c r="H187" t="str">
-        <v>Anish Kumar</v>
+        <v>Olympia Vitalis</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/passionfruit/1878215124</v>
+        <v>https://music.apple.com/us/album/daze/1862607800</v>
       </c>
       <c r="L187" t="str">
-        <v>Passionfruit - Anish Kumar</v>
+        <v>Daze - Olympia Vitalis</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Madan</v>
+        <v>Passionfruit</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/madan/1879822223</v>
+        <v>https://music.apple.com/us/song/passionfruit/1878215125</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-18</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Madan - Single</v>
+        <v>Passionfruit - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>2:56</v>
+        <v>3:57</v>
       </c>
       <c r="H188" t="str">
-        <v>Jonas Blue</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/jonas-blue/405728790</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/madan/1879822222</v>
+        <v>https://music.apple.com/us/album/passionfruit/1878215124</v>
       </c>
       <c r="L188" t="str">
-        <v>Madan - Jonas Blue</v>
+        <v>Passionfruit - Anish Kumar</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Bad Bitch</v>
+        <v>Madan</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/bad-bitch/1882818210</v>
+        <v>https://music.apple.com/us/song/madan/1879822223</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-18</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Bad Bitch - Single</v>
+        <v>Madan - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>2:28</v>
+        <v>2:56</v>
       </c>
       <c r="H189" t="str">
-        <v>41</v>
+        <v>Jonas Blue</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/41/1688992229</v>
+        <v>https://music.apple.com/us/artist/jonas-blue/405728790</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/bad-bitch/1882818208</v>
+        <v>https://music.apple.com/us/album/madan/1879822222</v>
       </c>
       <c r="L189" t="str">
-        <v>Bad Bitch - 41</v>
+        <v>Madan - Jonas Blue</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Shame</v>
+        <v>Bad Bitch</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/shame/1874080307</v>
+        <v>https://music.apple.com/us/song/bad-bitch/1882818210</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-18</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Devotion [Deluxe]</v>
+        <v>Bad Bitch - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:36</v>
+        <v>2:28</v>
       </c>
       <c r="H190" t="str">
-        <v>Sunday (1994)</v>
+        <v>41</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/sunday-1994/1728938785</v>
+        <v>https://music.apple.com/us/artist/41/1688992229</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/shame/1874080202</v>
+        <v>https://music.apple.com/us/album/bad-bitch/1882818208</v>
       </c>
       <c r="L190" t="str">
-        <v>Shame - Sunday (1994)</v>
+        <v>Bad Bitch - 41</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>teach you to love me</v>
+        <v>Shame</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/teach-you-to-love-me/1883146005</v>
+        <v>https://music.apple.com/us/song/shame/1874080307</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-18</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>teach you to love me - Single</v>
+        <v>Devotion [Deluxe]</v>
       </c>
       <c r="G191" t="str">
-        <v>3:09</v>
+        <v>3:36</v>
       </c>
       <c r="H191" t="str">
-        <v>Hailey Picardi</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/sunday-1994/1728938785</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/teach-you-to-love-me/1883146002</v>
+        <v>https://music.apple.com/us/album/shame/1874080202</v>
       </c>
       <c r="L191" t="str">
-        <v>teach you to love me - Hailey Picardi</v>
+        <v>Shame - Sunday (1994)</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>The Fix</v>
+        <v>teach you to love me</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/the-fix/1882082897</v>
+        <v>https://music.apple.com/us/song/teach-you-to-love-me/1883146005</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-18</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>The Fix - Single</v>
+        <v>teach you to love me - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>2:42</v>
+        <v>3:09</v>
       </c>
       <c r="H192" t="str">
-        <v>Baby J</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/the-fix/1882082895</v>
+        <v>https://music.apple.com/us/album/teach-you-to-love-me/1883146002</v>
       </c>
       <c r="L192" t="str">
-        <v>The Fix - Baby J</v>
+        <v>teach you to love me - Hailey Picardi</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Hanging on Hope</v>
+        <v>The Fix</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/hanging-on-hope/1881749452</v>
+        <v>https://music.apple.com/us/song/the-fix/1882082897</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-18</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Hanging on Hope - Single</v>
+        <v>The Fix - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:43</v>
+        <v>2:42</v>
       </c>
       <c r="H193" t="str">
-        <v>Buffalo Traffic Jam</v>
+        <v>Baby J</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
+        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/hanging-on-hope/1881749451</v>
+        <v>https://music.apple.com/us/album/the-fix/1882082895</v>
       </c>
       <c r="L193" t="str">
-        <v>Hanging on Hope - Buffalo Traffic Jam</v>
+        <v>The Fix - Baby J</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>I Know What to Say Now</v>
+        <v>Hanging on Hope</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/i-know-what-to-say-now/1879440545</v>
+        <v>https://music.apple.com/us/song/hanging-on-hope/1881749452</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-18</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>I Know What to Say Now - Single</v>
+        <v>Hanging on Hope - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:18</v>
+        <v>3:43</v>
       </c>
       <c r="H194" t="str">
-        <v>Active Child</v>
+        <v>Buffalo Traffic Jam</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/active-child/355288617</v>
+        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/i-know-what-to-say-now/1879440351</v>
+        <v>https://music.apple.com/us/album/hanging-on-hope/1881749451</v>
       </c>
       <c r="L194" t="str">
-        <v>I Know What to Say Now - Active Child</v>
+        <v>Hanging on Hope - Buffalo Traffic Jam</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Feel Something</v>
+        <v>I Know What to Say Now</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/feel-something/1876008375</v>
+        <v>https://music.apple.com/us/song/i-know-what-to-say-now/1879440545</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-18</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Feel Something - Single</v>
+        <v>I Know What to Say Now - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:09</v>
+        <v>3:18</v>
       </c>
       <c r="H195" t="str">
-        <v>Baby Queen</v>
+        <v>Active Child</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
+        <v>https://music.apple.com/us/artist/active-child/355288617</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/feel-something/1876008371</v>
+        <v>https://music.apple.com/us/album/i-know-what-to-say-now/1879440351</v>
       </c>
       <c r="L195" t="str">
-        <v>Feel Something - Baby Queen</v>
+        <v>I Know What to Say Now - Active Child</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>You Or Me</v>
+        <v>Feel Something</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/you-or-me/1869085528</v>
+        <v>https://music.apple.com/us/song/feel-something/1876008375</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-18</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Good God / Baad Man</v>
+        <v>Feel Something - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>5:28</v>
+        <v>3:09</v>
       </c>
       <c r="H196" t="str">
-        <v>Corrosion of Conformity</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
+        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/you-or-me/1869085524</v>
+        <v>https://music.apple.com/us/album/feel-something/1876008371</v>
       </c>
       <c r="L196" t="str">
-        <v>You Or Me - Corrosion of Conformity</v>
+        <v>Feel Something - Baby Queen</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Mortercheyn</v>
+        <v>You Or Me</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/mortercheyn/1862521946</v>
+        <v>https://music.apple.com/us/song/you-or-me/1869085528</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-18</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Coronach</v>
+        <v>Good God / Baad Man</v>
       </c>
       <c r="G197" t="str">
-        <v>4:18</v>
+        <v>5:28</v>
       </c>
       <c r="H197" t="str">
-        <v>Hellripper</v>
+        <v>Corrosion of Conformity</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/hellripper/1229248568</v>
+        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/mortercheyn/1862521937</v>
+        <v>https://music.apple.com/us/album/you-or-me/1869085524</v>
       </c>
       <c r="L197" t="str">
-        <v>Mortercheyn - Hellripper</v>
+        <v>You Or Me - Corrosion of Conformity</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Rip The God</v>
+        <v>Mortercheyn</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/rip-the-god/1866957697</v>
+        <v>https://music.apple.com/us/song/mortercheyn/1862521946</v>
       </c>
       <c r="D198" t="str">
         <v>2026-03-18</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Savage Imperial Death March</v>
+        <v>Coronach</v>
       </c>
       <c r="G198" t="str">
-        <v>5:20</v>
+        <v>4:18</v>
       </c>
       <c r="H198" t="str">
-        <v>Melvins</v>
+        <v>Hellripper</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/melvins/737433</v>
+        <v>https://music.apple.com/us/artist/hellripper/1229248568</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/rip-the-god/1866957685</v>
+        <v>https://music.apple.com/us/album/mortercheyn/1862521937</v>
       </c>
       <c r="L198" t="str">
-        <v>Rip The God - Melvins</v>
+        <v>Mortercheyn - Hellripper</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Who We Are</v>
+        <v>Rip The God</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/who-we-are/1879626950</v>
+        <v>https://music.apple.com/us/song/rip-the-god/1866957697</v>
       </c>
       <c r="D199" t="str">
         <v>2026-03-18</v>
@@ -7937,68 +7937,106 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Who We Are - Single</v>
+        <v>Savage Imperial Death March</v>
       </c>
       <c r="G199" t="str">
-        <v>2:10</v>
+        <v>5:20</v>
       </c>
       <c r="H199" t="str">
-        <v>Kaleena Zanders</v>
+        <v>Melvins</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+        <v>https://music.apple.com/us/artist/melvins/737433</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/who-we-are/1879626949</v>
+        <v>https://music.apple.com/us/album/rip-the-god/1866957685</v>
       </c>
       <c r="L199" t="str">
-        <v>Who We Are - Kaleena Zanders</v>
+        <v>Rip The God - Melvins</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
+        <v>Who We Are</v>
+      </c>
+      <c r="B200" t="str">
+        <v/>
+      </c>
+      <c r="C200" t="str">
+        <v>https://music.apple.com/us/song/who-we-are/1879626950</v>
+      </c>
+      <c r="D200" t="str">
+        <v>2026-03-18</v>
+      </c>
+      <c r="E200" t="str">
+        <v/>
+      </c>
+      <c r="F200" t="str">
+        <v>Who We Are - Single</v>
+      </c>
+      <c r="G200" t="str">
+        <v>2:10</v>
+      </c>
+      <c r="H200" t="str">
+        <v>Kaleena Zanders</v>
+      </c>
+      <c r="I200" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J200" t="str">
+        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+      </c>
+      <c r="K200" t="str">
+        <v>https://music.apple.com/us/album/who-we-are/1879626949</v>
+      </c>
+      <c r="L200" t="str">
+        <v>Who We Are - Kaleena Zanders</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
         <v>Reels in 360</v>
       </c>
-      <c r="B200" t="str">
-        <v/>
-      </c>
-      <c r="C200" t="str">
+      <c r="B201" t="str">
+        <v/>
+      </c>
+      <c r="C201" t="str">
         <v>https://music.apple.com/us/song/reels-in-360/1867998408</v>
       </c>
-      <c r="D200" t="str">
-        <v>2026-03-18</v>
-      </c>
-      <c r="E200" t="str">
-        <v/>
-      </c>
-      <c r="F200" t="str">
+      <c r="D201" t="str">
+        <v>2026-03-18</v>
+      </c>
+      <c r="E201" t="str">
+        <v/>
+      </c>
+      <c r="F201" t="str">
         <v>Dying Is The Internet</v>
       </c>
-      <c r="G200" t="str">
+      <c r="G201" t="str">
         <v>4:37</v>
       </c>
-      <c r="H200" t="str">
+      <c r="H201" t="str">
         <v>Simo Cell</v>
       </c>
-      <c r="I200" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J200" t="str">
+      <c r="I201" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J201" t="str">
         <v>https://music.apple.com/us/artist/simo-cell/1001568130</v>
       </c>
-      <c r="K200" t="str">
+      <c r="K201" t="str">
         <v>https://music.apple.com/us/album/reels-in-360/1867998295</v>
       </c>
-      <c r="L200" t="str">
+      <c r="L201" t="str">
         <v>Reels in 360 - Simo Cell</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L200"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L201"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
@@ -553,7 +553,7 @@
         <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G5" t="str">
         <v>4:11</v>
@@ -591,7 +591,7 @@
         <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G6" t="str">
         <v>2:57</v>
@@ -667,7 +667,7 @@
         <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B8" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G8" t="str">
         <v>7:10</v>
@@ -705,7 +705,7 @@
         <v>Grace Enger - Give A Little (Live Performance)</v>
       </c>
       <c r="B9" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G9" t="str">
         <v>3:06</v>
@@ -743,7 +743,7 @@
         <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
       </c>
       <c r="B10" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:05</v>
@@ -781,7 +781,7 @@
         <v>Nathan Evans x Saint PHNX - Happy Place (Official Acoustic Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=lyuE94W1WIc</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G11" t="str">
         <v>3:03</v>
@@ -819,7 +819,7 @@
         <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G12" t="str">
         <v>3:12</v>
@@ -857,7 +857,7 @@
         <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B13" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G13" t="str">
         <v>9:11</v>
@@ -895,7 +895,7 @@
         <v>SIENNA SPIRO - The Visitor</v>
       </c>
       <c r="B14" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G14" t="str">
         <v>3:49</v>
@@ -933,7 +933,7 @@
         <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
       </c>
       <c r="B15" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G15" t="str">
         <v>3:28</v>
@@ -1369,7 +1369,7 @@
         <v>2:31</v>
       </c>
       <c r="H26" t="str">
-        <v>Chris Janson</v>
+        <v>Chris Janson and Official David Lee Murphy</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,7 +1381,7 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
       </c>
     </row>
     <row r="27">
@@ -2035,7 +2035,7 @@
         <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
       </c>
       <c r="B44" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G44" t="str">
         <v>3:57</v>
@@ -2263,7 +2263,7 @@
         <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B50" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G50" t="str">
         <v>3:13</v>
@@ -2301,7 +2301,7 @@
         <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B51" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G51" t="str">
         <v>4:12</v>
@@ -2415,7 +2415,7 @@
         <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G54" t="str">
         <v>3:48</v>
@@ -2567,7 +2567,7 @@
         <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
       </c>
       <c r="B58" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G58" t="str">
         <v>4:56</v>
@@ -2605,7 +2605,7 @@
         <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
       </c>
       <c r="B59" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=366CV87TguE</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G59" t="str">
         <v>2:54</v>
@@ -2643,7 +2643,7 @@
         <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G60" t="str">
         <v>2:46</v>
@@ -3251,7 +3251,7 @@
         <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
       </c>
       <c r="B76" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G76" t="str">
         <v>4:43</v>
@@ -3327,7 +3327,7 @@
         <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
         <v>4:37</v>
@@ -3365,7 +3365,7 @@
         <v>Cannons - These Nights (Live at The Fonda)</v>
       </c>
       <c r="B79" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
         <v>4:52</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -515,19 +515,19 @@
         <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=033viNHogN4</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:38</v>
@@ -559,7 +559,7 @@
         <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=lyuE94W1WIc</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1313,19 +1313,19 @@
         <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G25" t="str">
         <v>2:42</v>
@@ -1351,19 +1351,19 @@
         <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
       </c>
       <c r="B26" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>2:31</v>
@@ -1389,19 +1389,19 @@
         <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G27" t="str">
         <v>3:14</v>
@@ -1427,19 +1427,19 @@
         <v>Allison Russell - Rainbows (Official Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G28" t="str">
         <v>3:22</v>
@@ -1465,19 +1465,19 @@
         <v>We Three - Love Who You Love (Official Audio)</v>
       </c>
       <c r="B29" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G29" t="str">
         <v>3:43</v>
@@ -1503,19 +1503,19 @@
         <v>paris jackson - zombies in love</v>
       </c>
       <c r="B30" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G30" t="str">
         <v>2:54</v>
@@ -1541,19 +1541,19 @@
         <v>Kane Brown - Woman (Official Music Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>2:46</v>
@@ -1579,19 +1579,19 @@
         <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G32" t="str">
         <v>3:37</v>
@@ -1617,19 +1617,19 @@
         <v>Malcolm Todd - Breathe (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G33" t="str">
         <v>2:57</v>
@@ -1655,19 +1655,19 @@
         <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay</v>
       </c>
       <c r="B34" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G34" t="str">
         <v>3:38</v>
@@ -1693,19 +1693,19 @@
         <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
       </c>
       <c r="B35" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>4:29</v>
@@ -1731,19 +1731,19 @@
         <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
       </c>
       <c r="B36" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>4:28</v>
@@ -1769,19 +1769,19 @@
         <v>aron! - Wonderful Thing (Piano)</v>
       </c>
       <c r="B37" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G37" t="str">
         <v>3:26</v>
@@ -1807,19 +1807,19 @@
         <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
       </c>
       <c r="B38" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G38" t="str">
         <v>3:51</v>
@@ -1845,19 +1845,19 @@
         <v>Sunday (1994) - The Fairground</v>
       </c>
       <c r="B39" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G39" t="str">
         <v>2:49</v>
@@ -1883,19 +1883,19 @@
         <v>Owen Riegling - In The Feeling (Visualizer)</v>
       </c>
       <c r="B40" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>4:16</v>
@@ -1921,19 +1921,19 @@
         <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G41" t="str">
         <v>4:16</v>
@@ -1959,19 +1959,19 @@
         <v>Maverick Sabre - 8 Stages</v>
       </c>
       <c r="B42" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G42" t="str">
         <v>3:25</v>
@@ -1997,19 +1997,19 @@
         <v>Amanda Jordan - What Else Is New</v>
       </c>
       <c r="B43" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G43" t="str">
         <v>2:50</v>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2225,19 +2225,19 @@
         <v>Natalie Jane - sabotage (Lyric Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G49" t="str">
         <v>2:57</v>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2377,19 +2377,19 @@
         <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
       </c>
       <c r="B53" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G53" t="str">
         <v>3:34</v>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2453,19 +2453,19 @@
         <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E55" t="str">
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G55" t="str">
         <v>4:58</v>
@@ -2491,19 +2491,19 @@
         <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E56" t="str">
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G56" t="str">
         <v>2:33</v>
@@ -2529,19 +2529,19 @@
         <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B57" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E57" t="str">
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G57" t="str">
         <v>5:01</v>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=366CV87TguE</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3213,19 +3213,19 @@
         <v>Bazzi - moment (Official Music Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G75" t="str">
         <v>2:43</v>
@@ -3257,7 +3257,7 @@
         <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/distance/1882713727</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/porch-light/1872239892</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/dry-spell/1883177258</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/the-visitor/1882146993</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/i-aint-no-cowboy/1862634799</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/cant-sit-still/1878782917</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245797</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/blow-my-mind/1852752616</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/sata/1874015489</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/una-aventura/1882069505</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/riptides/1878362645</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/home-feat-hikaru-utada/1845190340</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/dirty-wedding-dress/1872842320</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/fastest-gun-alive/1874700373</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/imposible/1880775726</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/trade-places/1878823464</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/motion-party/1882152039</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/woman/1882549709</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/sunburn/1880836041</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/que-te-cost%C3%B3/1882108997</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/oooshxt/1879612533</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/cruel-world/1859630041</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/star/1876633306</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/get-go/1862570884</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/thunderwave/1861531685</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/club-song/1882478246</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/better-man/1880496044</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/sabotage/1882209853</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/2000s-pop-punk-rnb/1878820143</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/naked/1883802157</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/catharina/1880130477</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/through-the-pain-feat-pozer/1877868063</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/trying-times/1862353792</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/595/1880470541</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/when-did-you-stop-loving-me/1879593803</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/call-me/1882521075</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/mi-amor/1872454951</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/boba/1880372256</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/video-shoot/1882892621</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/talk-to-me-nuh/1882510363</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/just-believe/1884083105</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/knife-in-the-heart/1857952500</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/the-way-we-touch/1875315428</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/dangerous/1867202642</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/when-i-wake-up/1878237800</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/breathe/1882808152</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/minty/1870867418</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/earth/1870867498</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/drink-the-water/1883172887</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/a-rainy-night-in-soho/1878459216</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/if-i-dont-leave-im-gonna-stay/1880111466</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/muchacho-alegre/1880256976</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/real-slow/1869618394</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/mountain-girl/1870722299</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/like-a-spark/1876952751</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/cheesecake/1882526540</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/always-let-you-down/1871578121</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/freakin-out/1879596115</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/name-in-vein/1880069474</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/st-catherines-wheel/1868804170</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/undefeated-champion/1840517120</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/pull-up/1854381591</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/ranjha/1882965642</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/zombies-in-love/1880178176</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/days-of-us/1868438268</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/life-of-a-man/1882845328</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/ya-no/1882115676</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/do-you-really-love-her/1879639011</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/relieve-you/1879589717</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/safety/1878181748</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/starlet/1873450846</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/physical/1883210753</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/im-dying-to-feel-alive-again/1880883509</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/regalito/1880846653</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/cruel-streak/1858689493</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/die-young/1870715300</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/island-girl/1884461360</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/girly-things/1876032954</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/looking-lovely-feat-robin-thicke/1878437828</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/tommys-song/1876670040</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/rainbows/1882790536</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/butterflies/1878228436</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/youre-right/1874975857</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/bible-belt/1821125622</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/daze/1862607801</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/passionfruit/1878215125</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/madan/1879822223</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/bad-bitch/1882818210</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/shame/1874080307</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/teach-you-to-love-me/1883146005</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/the-fix/1882082897</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/hanging-on-hope/1881749452</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -7779,7 +7779,7 @@
         <v>https://music.apple.com/us/song/i-know-what-to-say-now/1879440545</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -7817,7 +7817,7 @@
         <v>https://music.apple.com/us/song/feel-something/1876008375</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -7855,7 +7855,7 @@
         <v>https://music.apple.com/us/song/you-or-me/1869085528</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -7893,7 +7893,7 @@
         <v>https://music.apple.com/us/song/mortercheyn/1862521946</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E198" t="str">
         <v/>
@@ -7931,7 +7931,7 @@
         <v>https://music.apple.com/us/song/rip-the-god/1866957697</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E199" t="str">
         <v/>
@@ -7969,7 +7969,7 @@
         <v>https://music.apple.com/us/song/who-we-are/1879626950</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E200" t="str">
         <v/>
@@ -8007,7 +8007,7 @@
         <v>https://music.apple.com/us/song/reels-in-360/1867998408</v>
       </c>
       <c r="D201" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E201" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
@@ -477,7 +477,7 @@
         <v>Nick Carter - Love Life Tragedy</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:31</v>
@@ -1275,7 +1275,7 @@
         <v>Bishop Briggs - River (10 Years Later)</v>
       </c>
       <c r="B24" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G24" t="str">
         <v>3:46</v>
@@ -2795,7 +2795,7 @@
         <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
       </c>
       <c r="B64" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G64" t="str">
         <v>2:41</v>
@@ -2833,7 +2833,7 @@
         <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G65" t="str">
         <v>2:29</v>
@@ -2871,7 +2871,7 @@
         <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
       </c>
       <c r="B66" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G66" t="str">
         <v>2:43</v>
@@ -2909,7 +2909,7 @@
         <v>Matt Hansen - SAME TIME (Official Live Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G67" t="str">
         <v>3:46</v>
@@ -2947,7 +2947,7 @@
         <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G68" t="str">
         <v>4:01</v>
@@ -2985,7 +2985,7 @@
         <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G69" t="str">
         <v>3:23</v>
@@ -3023,7 +3023,7 @@
         <v>almost monday - leaving is easy (official video)</v>
       </c>
       <c r="B70" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G70" t="str">
         <v>3:39</v>
@@ -3061,7 +3061,7 @@
         <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G71" t="str">
         <v>3:04</v>
@@ -3099,7 +3099,7 @@
         <v>vaultboy - DELETED (Official Lyric Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G72" t="str">
         <v>3:25</v>
@@ -3137,7 +3137,7 @@
         <v>The Warning - Kerosene (Official Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G73" t="str">
         <v>3:49</v>
@@ -3175,7 +3175,7 @@
         <v>aron! - Wonderful Thing (City View Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G74" t="str">
         <v>2:14</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
@@ -1199,7 +1199,7 @@
         <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G22" t="str">
         <v>2:39</v>
@@ -1237,7 +1237,7 @@
         <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
       </c>
       <c r="B23" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>5:08</v>
@@ -2757,7 +2757,7 @@
         <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G63" t="str">
         <v>3:16</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:17</v>
@@ -1123,7 +1123,7 @@
         <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>2:50</v>
@@ -1161,7 +1161,7 @@
         <v>Rick Astley - Waiting On You (Official Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G21" t="str">
         <v>3:51</v>
@@ -2073,7 +2073,7 @@
         <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G45" t="str">
         <v>3:58</v>
@@ -2111,7 +2111,7 @@
         <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
       </c>
       <c r="B46" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G46" t="str">
         <v>3:25</v>
@@ -2149,7 +2149,7 @@
         <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B47" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G47" t="str">
         <v>4:09</v>
@@ -2187,7 +2187,7 @@
         <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G48" t="str">
         <v>2:08</v>
@@ -2719,7 +2719,7 @@
         <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
       </c>
       <c r="B62" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G62" t="str">
         <v>3:21</v>
@@ -3289,7 +3289,7 @@
         <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
         <v>2:44</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L201"/>
+  <dimension ref="A1:L202"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -591,7 +591,7 @@
         <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
       </c>
       <c r="B6" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G6" t="str">
         <v>2:57</v>
@@ -629,7 +629,7 @@
         <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B7" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:47</v>
@@ -667,7 +667,7 @@
         <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B8" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G8" t="str">
         <v>7:10</v>
@@ -743,7 +743,7 @@
         <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
       </c>
       <c r="B10" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:05</v>
@@ -781,7 +781,7 @@
         <v>Nathan Evans x Saint PHNX - Happy Place (Official Acoustic Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=lyuE94W1WIc</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G11" t="str">
         <v>3:03</v>
@@ -819,7 +819,7 @@
         <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G12" t="str">
         <v>3:12</v>
@@ -857,7 +857,7 @@
         <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B13" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G13" t="str">
         <v>9:11</v>
@@ -895,7 +895,7 @@
         <v>SIENNA SPIRO - The Visitor</v>
       </c>
       <c r="B14" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G14" t="str">
         <v>3:49</v>
@@ -933,7 +933,7 @@
         <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
       </c>
       <c r="B15" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G15" t="str">
         <v>3:28</v>
@@ -971,7 +971,7 @@
         <v>Martin Garrix - Catharina (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G16" t="str">
         <v>3:31</v>
@@ -1009,7 +1009,7 @@
         <v>Baby Queen - Feel Something (Official Visualiser)</v>
       </c>
       <c r="B17" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>3:11</v>
@@ -1047,7 +1047,7 @@
         <v>HAUSER - Hungarian Dance No. 5</v>
       </c>
       <c r="B18" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G18" t="str">
         <v>2:27</v>
@@ -1085,7 +1085,7 @@
         <v>Holly Humberstone - Cruel World</v>
       </c>
       <c r="B19" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G19" t="str">
         <v>3:34</v>
@@ -2301,7 +2301,7 @@
         <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B51" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G51" t="str">
         <v>4:12</v>
@@ -2339,7 +2339,7 @@
         <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
       </c>
       <c r="B52" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G52" t="str">
         <v>3:57</v>
@@ -2415,7 +2415,7 @@
         <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G54" t="str">
         <v>3:48</v>
@@ -2567,7 +2567,7 @@
         <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
       </c>
       <c r="B58" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G58" t="str">
         <v>4:56</v>
@@ -2605,7 +2605,7 @@
         <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
       </c>
       <c r="B59" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=366CV87TguE</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G59" t="str">
         <v>2:54</v>
@@ -2643,7 +2643,7 @@
         <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G60" t="str">
         <v>2:46</v>
@@ -2681,7 +2681,7 @@
         <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G61" t="str">
         <v>2:56</v>
@@ -4236,13 +4236,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Distance</v>
+        <v>Pongo</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/distance/1882713727</v>
+        <v>https://music.apple.com/us/song/pongo/1882157609</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-19</v>
@@ -4251,25 +4251,25 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Distance - Single</v>
+        <v>Pongo - Single</v>
       </c>
       <c r="G102" t="str">
-        <v>3:14</v>
+        <v>3:09</v>
       </c>
       <c r="H102" t="str">
-        <v>Finn Askew</v>
+        <v>Rvssian</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/finn-askew/1292169978</v>
+        <v>https://music.apple.com/us/artist/rvssian/628716915</v>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/distance/1882713721</v>
+        <v>https://music.apple.com/us/album/pongo/1882157603</v>
       </c>
       <c r="L102" t="str">
-        <v>Distance - Finn Askew</v>
+        <v>Pongo - Rvssian</v>
       </c>
     </row>
     <row r="103">
@@ -4350,13 +4350,13 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Ocean In The Desert</v>
+        <v>Distance</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
+        <v>https://music.apple.com/us/song/distance/1882713727</v>
       </c>
       <c r="D105" t="str">
         <v>2026-03-19</v>
@@ -4365,25 +4365,25 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Ocean In The Desert - Single</v>
+        <v>Distance - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>3:44</v>
+        <v>3:14</v>
       </c>
       <c r="H105" t="str">
-        <v>Dionne Warwick</v>
+        <v>Finn Askew</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/dionne-warwick/16198</v>
+        <v>https://music.apple.com/us/artist/finn-askew/1292169978</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/ocean-in-the-desert/1878421568</v>
+        <v>https://music.apple.com/us/album/distance/1882713721</v>
       </c>
       <c r="L105" t="str">
-        <v>Ocean In The Desert - Dionne Warwick</v>
+        <v>Distance - Finn Askew</v>
       </c>
     </row>
     <row r="106">
@@ -4654,13 +4654,13 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Riptides</v>
+        <v>Ocean In The Desert</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/riptides/1878362645</v>
+        <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
       </c>
       <c r="D113" t="str">
         <v>2026-03-19</v>
@@ -4669,25 +4669,25 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>I Built You a Tower</v>
+        <v>Ocean In The Desert - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>3:17</v>
+        <v>3:44</v>
       </c>
       <c r="H113" t="str">
-        <v>Death Cab for Cutie</v>
+        <v>Dionne Warwick</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
+        <v>https://music.apple.com/us/artist/dionne-warwick/16198</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/riptides/1878362451</v>
+        <v>https://music.apple.com/us/album/ocean-in-the-desert/1878421568</v>
       </c>
       <c r="L113" t="str">
-        <v>Riptides - Death Cab for Cutie</v>
+        <v>Ocean In The Desert - Dionne Warwick</v>
       </c>
     </row>
     <row r="114">
@@ -4768,13 +4768,13 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Fastest Gun Alive</v>
+        <v>Riptides</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/fastest-gun-alive/1874700373</v>
+        <v>https://music.apple.com/us/song/riptides/1878362645</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-19</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Age of the Ram</v>
+        <v>I Built You a Tower</v>
       </c>
       <c r="G116" t="str">
-        <v>3:07</v>
+        <v>3:17</v>
       </c>
       <c r="H116" t="str">
-        <v>Charley Crockett</v>
+        <v>Death Cab for Cutie</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
+        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/fastest-gun-alive/1874700242</v>
+        <v>https://music.apple.com/us/album/riptides/1878362451</v>
       </c>
       <c r="L116" t="str">
-        <v>Fastest Gun Alive - Charley Crockett</v>
+        <v>Riptides - Death Cab for Cutie</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>IMPOSIBLE</v>
+        <v>Fastest Gun Alive</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/imposible/1880775726</v>
+        <v>https://music.apple.com/us/song/fastest-gun-alive/1874700373</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-19</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>IMPOSIBLE - Single</v>
+        <v>Age of the Ram</v>
       </c>
       <c r="G117" t="str">
-        <v>3:13</v>
+        <v>3:07</v>
       </c>
       <c r="H117" t="str">
-        <v>Grupo Frontera</v>
+        <v>Charley Crockett</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
+        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/imposible/1880775721</v>
+        <v>https://music.apple.com/us/album/fastest-gun-alive/1874700242</v>
       </c>
       <c r="L117" t="str">
-        <v>IMPOSIBLE - Grupo Frontera</v>
+        <v>Fastest Gun Alive - Charley Crockett</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Trade Places</v>
+        <v>IMPOSIBLE</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/trade-places/1878823464</v>
+        <v>https://music.apple.com/us/song/imposible/1880775726</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-19</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Monica</v>
+        <v>IMPOSIBLE - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>3:02</v>
+        <v>3:13</v>
       </c>
       <c r="H118" t="str">
-        <v>Jack Harlow</v>
+        <v>Grupo Frontera</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/jack-harlow/1047679432</v>
+        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/trade-places/1878823462</v>
+        <v>https://music.apple.com/us/album/imposible/1880775721</v>
       </c>
       <c r="L118" t="str">
-        <v>Trade Places - Jack Harlow</v>
+        <v>IMPOSIBLE - Grupo Frontera</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Motion Party</v>
+        <v>Trade Places</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/motion-party/1882152039</v>
+        <v>https://music.apple.com/us/song/trade-places/1878823464</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-19</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Motion Party - Single</v>
+        <v>Monica</v>
       </c>
       <c r="G119" t="str">
-        <v>1:35</v>
+        <v>3:02</v>
       </c>
       <c r="H119" t="str">
-        <v>Bossman Dlow</v>
+        <v>Jack Harlow</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
+        <v>https://music.apple.com/us/artist/jack-harlow/1047679432</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/motion-party/1882151996</v>
+        <v>https://music.apple.com/us/album/trade-places/1878823462</v>
       </c>
       <c r="L119" t="str">
-        <v>Motion Party - Bossman Dlow</v>
+        <v>Trade Places - Jack Harlow</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Woman</v>
+        <v>Motion Party</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/woman/1882549709</v>
+        <v>https://music.apple.com/us/song/motion-party/1882152039</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-19</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Woman - Single</v>
+        <v>Motion Party - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>2:46</v>
+        <v>1:35</v>
       </c>
       <c r="H120" t="str">
-        <v>Kane Brown</v>
+        <v>Bossman Dlow</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/kane-brown/930928857</v>
+        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/woman/1882549705</v>
+        <v>https://music.apple.com/us/album/motion-party/1882151996</v>
       </c>
       <c r="L120" t="str">
-        <v>Woman - Kane Brown</v>
+        <v>Motion Party - Bossman Dlow</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Sunburn</v>
+        <v>Woman</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/sunburn/1880836041</v>
+        <v>https://music.apple.com/us/song/woman/1882549709</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-19</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Sunburn - Single</v>
+        <v>Woman - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:05</v>
+        <v>2:46</v>
       </c>
       <c r="H121" t="str">
-        <v>Tucker Wetmore</v>
+        <v>Kane Brown</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/tucker-wetmore/1486724646</v>
+        <v>https://music.apple.com/us/artist/kane-brown/930928857</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/sunburn/1880835818</v>
+        <v>https://music.apple.com/us/album/woman/1882549705</v>
       </c>
       <c r="L121" t="str">
-        <v>Sunburn - Tucker Wetmore</v>
+        <v>Woman - Kane Brown</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Que Te Costó</v>
+        <v>Sunburn</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/que-te-cost%C3%B3/1882108997</v>
+        <v>https://music.apple.com/us/song/sunburn/1880836041</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-19</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Metamorfosis</v>
+        <v>Sunburn - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>2:54</v>
+        <v>3:05</v>
       </c>
       <c r="H122" t="str">
-        <v>Yahritza Y Su Esencia</v>
+        <v>Tucker Wetmore</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
+        <v>https://music.apple.com/us/artist/tucker-wetmore/1486724646</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/que-te-cost%C3%B3/1882108989</v>
+        <v>https://music.apple.com/us/album/sunburn/1880835818</v>
       </c>
       <c r="L122" t="str">
-        <v>Que Te Costó - Yahritza Y Su Esencia</v>
+        <v>Sunburn - Tucker Wetmore</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>oooshxt!</v>
+        <v>Que Te Costó</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/oooshxt/1879612533</v>
+        <v>https://music.apple.com/us/song/que-te-cost%C3%B3/1882108997</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-19</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>oooshxt! - Single</v>
+        <v>Metamorfosis</v>
       </c>
       <c r="G123" t="str">
-        <v>2:15</v>
+        <v>2:54</v>
       </c>
       <c r="H123" t="str">
-        <v>Samara Cyn</v>
+        <v>Yahritza Y Su Esencia</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
+        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/oooshxt/1879612532</v>
+        <v>https://music.apple.com/us/album/que-te-cost%C3%B3/1882108989</v>
       </c>
       <c r="L123" t="str">
-        <v>oooshxt! - Samara Cyn</v>
+        <v>Que Te Costó - Yahritza Y Su Esencia</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Cruel World</v>
+        <v>oooshxt!</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/cruel-world/1859630041</v>
+        <v>https://music.apple.com/us/song/oooshxt/1879612533</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-19</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Cruel World</v>
+        <v>oooshxt! - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>3:26</v>
+        <v>2:15</v>
       </c>
       <c r="H124" t="str">
-        <v>Holly Humberstone</v>
+        <v>Samara Cyn</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/cruel-world/1859629846</v>
+        <v>https://music.apple.com/us/album/oooshxt/1879612532</v>
       </c>
       <c r="L124" t="str">
-        <v>Cruel World - Holly Humberstone</v>
+        <v>oooshxt! - Samara Cyn</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Star</v>
+        <v>Cruel World</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/star/1876633306</v>
+        <v>https://music.apple.com/us/song/cruel-world/1859630041</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-19</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Star - Single</v>
+        <v>Cruel World</v>
       </c>
       <c r="G125" t="str">
-        <v>3:25</v>
+        <v>3:26</v>
       </c>
       <c r="H125" t="str">
-        <v>Iceage</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/star/1876633303</v>
+        <v>https://music.apple.com/us/album/cruel-world/1859629846</v>
       </c>
       <c r="L125" t="str">
-        <v>Star - Iceage</v>
+        <v>Cruel World - Holly Humberstone</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Get Go</v>
+        <v>Star</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/get-go/1862570884</v>
+        <v>https://music.apple.com/us/song/star/1876633306</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-19</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Ambiguous Desire</v>
+        <v>Star - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>3:22</v>
+        <v>3:25</v>
       </c>
       <c r="H126" t="str">
-        <v>Arlo Parks</v>
+        <v>Iceage</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
+        <v>https://music.apple.com/us/artist/iceage/406846711</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/get-go/1862570378</v>
+        <v>https://music.apple.com/us/album/star/1876633303</v>
       </c>
       <c r="L126" t="str">
-        <v>Get Go - Arlo Parks</v>
+        <v>Star - Iceage</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>ThunderWave</v>
+        <v>Get Go</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/thunderwave/1861531685</v>
+        <v>https://music.apple.com/us/song/get-go/1862570884</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-19</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Distracted</v>
+        <v>Ambiguous Desire</v>
       </c>
       <c r="G127" t="str">
-        <v>3:14</v>
+        <v>3:22</v>
       </c>
       <c r="H127" t="str">
-        <v>Thundercat</v>
+        <v>Arlo Parks</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
+        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/thunderwave/1861531667</v>
+        <v>https://music.apple.com/us/album/get-go/1862570378</v>
       </c>
       <c r="L127" t="str">
-        <v>ThunderWave - Thundercat</v>
+        <v>Get Go - Arlo Parks</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Club Song</v>
+        <v>ThunderWave</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/club-song/1882478246</v>
+        <v>https://music.apple.com/us/song/thunderwave/1861531685</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-19</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Club Song - Single</v>
+        <v>Distracted</v>
       </c>
       <c r="G128" t="str">
-        <v>2:27</v>
+        <v>3:14</v>
       </c>
       <c r="H128" t="str">
-        <v>The Pussycat Dolls</v>
+        <v>Thundercat</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/the-pussycat-dolls/23331509</v>
+        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/club-song/1882478243</v>
+        <v>https://music.apple.com/us/album/thunderwave/1861531667</v>
       </c>
       <c r="L128" t="str">
-        <v>Club Song - The Pussycat Dolls</v>
+        <v>ThunderWave - Thundercat</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Better Man</v>
+        <v>Club Song</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/better-man/1880496044</v>
+        <v>https://music.apple.com/us/song/club-song/1882478246</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-19</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Better Man - Single</v>
+        <v>Club Song - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>2:53</v>
+        <v>2:27</v>
       </c>
       <c r="H129" t="str">
-        <v>jxdn</v>
+        <v>The Pussycat Dolls</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/jxdn/1513237359</v>
+        <v>https://music.apple.com/us/artist/the-pussycat-dolls/23331509</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/better-man/1880496042</v>
+        <v>https://music.apple.com/us/album/club-song/1882478243</v>
       </c>
       <c r="L129" t="str">
-        <v>Better Man - jxdn</v>
+        <v>Club Song - The Pussycat Dolls</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>sabotage</v>
+        <v>Better Man</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/sabotage/1882209853</v>
+        <v>https://music.apple.com/us/song/better-man/1880496044</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-19</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>sabotage - Single</v>
+        <v>Better Man - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>2:58</v>
+        <v>2:53</v>
       </c>
       <c r="H130" t="str">
-        <v>Natalie Jane</v>
+        <v>jxdn</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/natalie-jane/1504380197</v>
+        <v>https://music.apple.com/us/artist/jxdn/1513237359</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/sabotage/1882209670</v>
+        <v>https://music.apple.com/us/album/better-man/1880496042</v>
       </c>
       <c r="L130" t="str">
-        <v>sabotage - Natalie Jane</v>
+        <v>Better Man - jxdn</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>2000s Pop Punk Rnb</v>
+        <v>sabotage</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/2000s-pop-punk-rnb/1878820143</v>
+        <v>https://music.apple.com/us/song/sabotage/1882209853</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-19</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Still Loiteringgg / 2000s Pop Punk Rnb - Single</v>
+        <v>sabotage - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>2:56</v>
+        <v>2:58</v>
       </c>
       <c r="H131" t="str">
-        <v>WHATMORE</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/whatmore/1797119133</v>
+        <v>https://music.apple.com/us/artist/natalie-jane/1504380197</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/2000s-pop-punk-rnb/1878820131</v>
+        <v>https://music.apple.com/us/album/sabotage/1882209670</v>
       </c>
       <c r="L131" t="str">
-        <v>2000s Pop Punk Rnb - WHATMORE</v>
+        <v>sabotage - Natalie Jane</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Naked</v>
+        <v>2000s Pop Punk Rnb</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/naked/1883802157</v>
+        <v>https://music.apple.com/us/song/2000s-pop-punk-rnb/1878820143</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-19</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Naked - Single</v>
+        <v>Still Loiteringgg / 2000s Pop Punk Rnb - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>3:39</v>
+        <v>2:56</v>
       </c>
       <c r="H132" t="str">
-        <v>Kenya Grace</v>
+        <v>WHATMORE</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
+        <v>https://music.apple.com/us/artist/whatmore/1797119133</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/naked/1883801913</v>
+        <v>https://music.apple.com/us/album/2000s-pop-punk-rnb/1878820131</v>
       </c>
       <c r="L132" t="str">
-        <v>Naked - Kenya Grace</v>
+        <v>2000s Pop Punk Rnb - WHATMORE</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Catharina</v>
+        <v>Naked</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/catharina/1880130477</v>
+        <v>https://music.apple.com/us/song/naked/1883802157</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-19</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Catharina - Single</v>
+        <v>Naked - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>3:27</v>
+        <v>3:39</v>
       </c>
       <c r="H133" t="str">
-        <v>Martin Garrix</v>
+        <v>Kenya Grace</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
+        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/catharina/1880130476</v>
+        <v>https://music.apple.com/us/album/naked/1883801913</v>
       </c>
       <c r="L133" t="str">
-        <v>Catharina - Martin Garrix</v>
+        <v>Naked - Kenya Grace</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Through The Pain (feat. Pozer)</v>
+        <v>Catharina</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/through-the-pain-feat-pozer/1877868063</v>
+        <v>https://music.apple.com/us/song/catharina/1880130477</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-19</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Through The Pain (feat. Pozer) - Single</v>
+        <v>Catharina - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>3:00</v>
+        <v>3:27</v>
       </c>
       <c r="H134" t="str">
-        <v>Chase &amp; Status</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/chase-status/121546679</v>
+        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/through-the-pain-feat-pozer/1877868059</v>
+        <v>https://music.apple.com/us/album/catharina/1880130476</v>
       </c>
       <c r="L134" t="str">
-        <v>Through The Pain (feat. Pozer) - Chase &amp; Status</v>
+        <v>Catharina - Martin Garrix</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Trying Times</v>
+        <v>Through The Pain (feat. Pozer)</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/trying-times/1862353792</v>
+        <v>https://music.apple.com/us/song/through-the-pain-feat-pozer/1877868063</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-19</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Trying Times</v>
+        <v>Through The Pain (feat. Pozer) - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>4:33</v>
+        <v>3:00</v>
       </c>
       <c r="H135" t="str">
-        <v>James Blake</v>
+        <v>Chase &amp; Status</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/chase-status/121546679</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/trying-times/1862353780</v>
+        <v>https://music.apple.com/us/album/through-the-pain-feat-pozer/1877868059</v>
       </c>
       <c r="L135" t="str">
-        <v>Trying Times - James Blake</v>
+        <v>Through The Pain (feat. Pozer) - Chase &amp; Status</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>595</v>
+        <v>Trying Times</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/595/1880470541</v>
+        <v>https://music.apple.com/us/song/trying-times/1862353792</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-19</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Be Sweet To Me</v>
+        <v>Trying Times</v>
       </c>
       <c r="G136" t="str">
-        <v>2:29</v>
+        <v>4:33</v>
       </c>
       <c r="H136" t="str">
-        <v>Violet Grohl</v>
+        <v>James Blake</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/595/1880470537</v>
+        <v>https://music.apple.com/us/album/trying-times/1862353780</v>
       </c>
       <c r="L136" t="str">
-        <v>595 - Violet Grohl</v>
+        <v>Trying Times - James Blake</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>When Did You Stop Loving Me?</v>
+        <v>595</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/when-did-you-stop-loving-me/1879593803</v>
+        <v>https://music.apple.com/us/song/595/1880470541</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-19</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Soft 2</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G137" t="str">
-        <v>3:50</v>
+        <v>2:29</v>
       </c>
       <c r="H137" t="str">
-        <v>LANY</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/lany/867853783</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/when-did-you-stop-loving-me/1879593289</v>
+        <v>https://music.apple.com/us/album/595/1880470537</v>
       </c>
       <c r="L137" t="str">
-        <v>When Did You Stop Loving Me? - LANY</v>
+        <v>595 - Violet Grohl</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>CALL ME</v>
+        <v>When Did You Stop Loving Me?</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/call-me/1882521075</v>
+        <v>https://music.apple.com/us/song/when-did-you-stop-loving-me/1879593803</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-19</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>CALL ME - Single</v>
+        <v>Soft 2</v>
       </c>
       <c r="G138" t="str">
-        <v>2:10</v>
+        <v>3:50</v>
       </c>
       <c r="H138" t="str">
-        <v>ALTÉGO</v>
+        <v>LANY</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/alt%C3%A9go/1606418899</v>
+        <v>https://music.apple.com/us/artist/lany/867853783</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/call-me/1882521073</v>
+        <v>https://music.apple.com/us/album/when-did-you-stop-loving-me/1879593289</v>
       </c>
       <c r="L138" t="str">
-        <v>CALL ME - ALTÉGO</v>
+        <v>When Did You Stop Loving Me? - LANY</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Mi Amor</v>
+        <v>CALL ME</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/mi-amor/1872454951</v>
+        <v>https://music.apple.com/us/song/call-me/1882521075</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-19</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Free (Deluxe)</v>
+        <v>CALL ME - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>2:00</v>
+        <v>2:10</v>
       </c>
       <c r="H139" t="str">
-        <v>Nasty C</v>
+        <v>ALTÉGO</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
+        <v>https://music.apple.com/us/artist/alt%C3%A9go/1606418899</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/mi-amor/1872454582</v>
+        <v>https://music.apple.com/us/album/call-me/1882521073</v>
       </c>
       <c r="L139" t="str">
-        <v>Mi Amor - Nasty C</v>
+        <v>CALL ME - ALTÉGO</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>BOBA</v>
+        <v>Mi Amor</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/boba/1880372256</v>
+        <v>https://music.apple.com/us/song/mi-amor/1872454951</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-19</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>BOBA - Single</v>
+        <v>Free (Deluxe)</v>
       </c>
       <c r="G140" t="str">
-        <v>3:00</v>
+        <v>2:00</v>
       </c>
       <c r="H140" t="str">
-        <v>SOFI TUKKER</v>
+        <v>Nasty C</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
+        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/boba/1880372250</v>
+        <v>https://music.apple.com/us/album/mi-amor/1872454582</v>
       </c>
       <c r="L140" t="str">
-        <v>BOBA - SOFI TUKKER</v>
+        <v>Mi Amor - Nasty C</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Video Shoot</v>
+        <v>BOBA</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/video-shoot/1882892621</v>
+        <v>https://music.apple.com/us/song/boba/1880372256</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-19</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Skeletor</v>
+        <v>BOBA - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>2:38</v>
+        <v>3:00</v>
       </c>
       <c r="H141" t="str">
-        <v>Chief Keef</v>
+        <v>SOFI TUKKER</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
+        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/video-shoot/1882892614</v>
+        <v>https://music.apple.com/us/album/boba/1880372250</v>
       </c>
       <c r="L141" t="str">
-        <v>Video Shoot - Chief Keef</v>
+        <v>BOBA - SOFI TUKKER</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Talk To Me Nuh</v>
+        <v>Video Shoot</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/talk-to-me-nuh/1882510363</v>
+        <v>https://music.apple.com/us/song/video-shoot/1882892621</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-19</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Talk To Me Nuh - Single</v>
+        <v>Skeletor</v>
       </c>
       <c r="G142" t="str">
-        <v>2:06</v>
+        <v>2:38</v>
       </c>
       <c r="H142" t="str">
-        <v>Shenseea</v>
+        <v>Chief Keef</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/shenseea/1132311326</v>
+        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/talk-to-me-nuh/1882510361</v>
+        <v>https://music.apple.com/us/album/video-shoot/1882892614</v>
       </c>
       <c r="L142" t="str">
-        <v>Talk To Me Nuh - Shenseea</v>
+        <v>Video Shoot - Chief Keef</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Just Believe</v>
+        <v>Talk To Me Nuh</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/just-believe/1884083105</v>
+        <v>https://music.apple.com/us/song/talk-to-me-nuh/1882510363</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-19</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Just Believe - Single</v>
+        <v>Talk To Me Nuh - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>2:41</v>
+        <v>2:06</v>
       </c>
       <c r="H143" t="str">
-        <v>Bailey Zimmerman</v>
+        <v>Shenseea</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
+        <v>https://music.apple.com/us/artist/shenseea/1132311326</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/just-believe/1884083104</v>
+        <v>https://music.apple.com/us/album/talk-to-me-nuh/1882510361</v>
       </c>
       <c r="L143" t="str">
-        <v>Just Believe - Bailey Zimmerman</v>
+        <v>Talk To Me Nuh - Shenseea</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Knife In The Heart</v>
+        <v>Just Believe</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/knife-in-the-heart/1857952500</v>
+        <v>https://music.apple.com/us/song/just-believe/1884083105</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-19</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>The Afterparty</v>
+        <v>Just Believe - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>2:57</v>
+        <v>2:41</v>
       </c>
       <c r="H144" t="str">
-        <v>Lykke Li</v>
+        <v>Bailey Zimmerman</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
+        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/knife-in-the-heart/1857952252</v>
+        <v>https://music.apple.com/us/album/just-believe/1884083104</v>
       </c>
       <c r="L144" t="str">
-        <v>Knife In The Heart - Lykke Li</v>
+        <v>Just Believe - Bailey Zimmerman</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>The Way We Touch</v>
+        <v>Knife In The Heart</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/the-way-we-touch/1875315428</v>
+        <v>https://music.apple.com/us/song/knife-in-the-heart/1857952500</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-19</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>The Way We Touch - Single</v>
+        <v>The Afterparty</v>
       </c>
       <c r="G145" t="str">
-        <v>3:09</v>
+        <v>2:57</v>
       </c>
       <c r="H145" t="str">
-        <v>Charlotte Cardin</v>
+        <v>Lykke Li</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-cardin/784665014</v>
+        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/the-way-we-touch/1875315210</v>
+        <v>https://music.apple.com/us/album/knife-in-the-heart/1857952252</v>
       </c>
       <c r="L145" t="str">
-        <v>The Way We Touch - Charlotte Cardin</v>
+        <v>Knife In The Heart - Lykke Li</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>DANGEROUS</v>
+        <v>The Way We Touch</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/dangerous/1867202642</v>
+        <v>https://music.apple.com/us/song/the-way-we-touch/1875315428</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-19</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>NIGHTS AFTER VAMP</v>
+        <v>The Way We Touch - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>4:06</v>
+        <v>3:09</v>
       </c>
       <c r="H146" t="str">
-        <v>Magnolia Park</v>
+        <v>Charlotte Cardin</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
+        <v>https://music.apple.com/us/artist/charlotte-cardin/784665014</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/dangerous/1867202638</v>
+        <v>https://music.apple.com/us/album/the-way-we-touch/1875315210</v>
       </c>
       <c r="L146" t="str">
-        <v>DANGEROUS - Magnolia Park</v>
+        <v>The Way We Touch - Charlotte Cardin</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>When I Wake Up</v>
+        <v>DANGEROUS</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/when-i-wake-up/1878237800</v>
+        <v>https://music.apple.com/us/song/dangerous/1867202642</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-19</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Dear God</v>
+        <v>NIGHTS AFTER VAMP</v>
       </c>
       <c r="G147" t="str">
-        <v>3:33</v>
+        <v>4:06</v>
       </c>
       <c r="H147" t="str">
-        <v>The Pretty Reckless</v>
+        <v>Magnolia Park</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
+        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/when-i-wake-up/1878237662</v>
+        <v>https://music.apple.com/us/album/dangerous/1867202638</v>
       </c>
       <c r="L147" t="str">
-        <v>When I Wake Up - The Pretty Reckless</v>
+        <v>DANGEROUS - Magnolia Park</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Breathe</v>
+        <v>When I Wake Up</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/breathe/1882808152</v>
+        <v>https://music.apple.com/us/song/when-i-wake-up/1878237800</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-19</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Breathe - Single</v>
+        <v>Dear God</v>
       </c>
       <c r="G148" t="str">
-        <v>2:56</v>
+        <v>3:33</v>
       </c>
       <c r="H148" t="str">
-        <v>Malcolm Todd</v>
+        <v>The Pretty Reckless</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
+        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/breathe/1882807987</v>
+        <v>https://music.apple.com/us/album/when-i-wake-up/1878237662</v>
       </c>
       <c r="L148" t="str">
-        <v>Breathe - Malcolm Todd</v>
+        <v>When I Wake Up - The Pretty Reckless</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Minty</v>
+        <v>Breathe</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/minty/1870867418</v>
+        <v>https://music.apple.com/us/song/breathe/1882808152</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-19</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>Breathe - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>1:47</v>
+        <v>2:56</v>
       </c>
       <c r="H149" t="str">
-        <v>MIKE</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/mike/1253023714</v>
+        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/minty/1870867411</v>
+        <v>https://music.apple.com/us/album/breathe/1882807987</v>
       </c>
       <c r="L149" t="str">
-        <v>Minty - MIKE</v>
+        <v>Breathe - Malcolm Todd</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Earth</v>
+        <v>Minty</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/earth/1870867498</v>
+        <v>https://music.apple.com/us/song/minty/1870867418</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-19</v>
@@ -6078,33 +6078,33 @@
         <v>POMPEII // UTILITY</v>
       </c>
       <c r="G150" t="str">
-        <v>1:37</v>
+        <v>1:47</v>
       </c>
       <c r="H150" t="str">
-        <v>Earl Sweatshirt</v>
+        <v>MIKE</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
+        <v>https://music.apple.com/us/artist/mike/1253023714</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/earth/1870867411</v>
+        <v>https://music.apple.com/us/album/minty/1870867411</v>
       </c>
       <c r="L150" t="str">
-        <v>Earth - Earl Sweatshirt</v>
+        <v>Minty - MIKE</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Drink The Water</v>
+        <v>Earth</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/drink-the-water/1883172887</v>
+        <v>https://music.apple.com/us/song/earth/1870867498</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-19</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G151" t="str">
-        <v>3:42</v>
+        <v>1:37</v>
       </c>
       <c r="H151" t="str">
-        <v>Jack Johnson</v>
+        <v>Earl Sweatshirt</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
+        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/drink-the-water/1883172879</v>
+        <v>https://music.apple.com/us/album/earth/1870867411</v>
       </c>
       <c r="L151" t="str">
-        <v>Drink The Water - Jack Johnson</v>
+        <v>Earth - Earl Sweatshirt</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>A Rainy Night in Soho</v>
+        <v>Drink The Water</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/a-rainy-night-in-soho/1878459216</v>
+        <v>https://music.apple.com/us/song/drink-the-water/1883172887</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-19</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>A Rainy Night in Soho - Single</v>
+        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
       </c>
       <c r="G152" t="str">
-        <v>4:32</v>
+        <v>3:42</v>
       </c>
       <c r="H152" t="str">
-        <v>Bruce Springsteen</v>
+        <v>Jack Johnson</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/bruce-springsteen/178834</v>
+        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/a-rainy-night-in-soho/1878459215</v>
+        <v>https://music.apple.com/us/album/drink-the-water/1883172879</v>
       </c>
       <c r="L152" t="str">
-        <v>A Rainy Night in Soho - Bruce Springsteen</v>
+        <v>Drink The Water - Jack Johnson</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>If I Don't Leave I'm Gonna Stay</v>
+        <v>A Rainy Night in Soho</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/if-i-dont-leave-im-gonna-stay/1880111466</v>
+        <v>https://music.apple.com/us/song/a-rainy-night-in-soho/1878459216</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-19</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>If I Don't Leave I'm Gonna Stay - Single</v>
+        <v>A Rainy Night in Soho - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>3:32</v>
+        <v>4:32</v>
       </c>
       <c r="H153" t="str">
-        <v>Carly Pearce</v>
+        <v>Bruce Springsteen</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/bruce-springsteen/178834</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/if-i-dont-leave-im-gonna-stay/1880111464</v>
+        <v>https://music.apple.com/us/album/a-rainy-night-in-soho/1878459215</v>
       </c>
       <c r="L153" t="str">
-        <v>If I Don't Leave I'm Gonna Stay - Carly Pearce</v>
+        <v>A Rainy Night in Soho - Bruce Springsteen</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Muchacho Alegre</v>
+        <v>If I Don't Leave I'm Gonna Stay</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/muchacho-alegre/1880256976</v>
+        <v>https://music.apple.com/us/song/if-i-dont-leave-im-gonna-stay/1880111466</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-19</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Muchacho Alegre - Single</v>
+        <v>If I Don't Leave I'm Gonna Stay - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>3:08</v>
+        <v>3:32</v>
       </c>
       <c r="H154" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/muchacho-alegre/1880256973</v>
+        <v>https://music.apple.com/us/album/if-i-dont-leave-im-gonna-stay/1880111464</v>
       </c>
       <c r="L154" t="str">
-        <v>Muchacho Alegre - Luis R Conriquez</v>
+        <v>If I Don't Leave I'm Gonna Stay - Carly Pearce</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Real Slow</v>
+        <v>Muchacho Alegre</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/real-slow/1869618394</v>
+        <v>https://music.apple.com/us/song/muchacho-alegre/1880256976</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-19</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Work of Heart</v>
+        <v>Muchacho Alegre - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:22</v>
+        <v>3:08</v>
       </c>
       <c r="H155" t="str">
-        <v>Flatland Cavalry</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/real-slow/1869617637</v>
+        <v>https://music.apple.com/us/album/muchacho-alegre/1880256973</v>
       </c>
       <c r="L155" t="str">
-        <v>Real Slow - Flatland Cavalry</v>
+        <v>Muchacho Alegre - Luis R Conriquez</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Mountain Girl</v>
+        <v>Real Slow</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/mountain-girl/1870722299</v>
+        <v>https://music.apple.com/us/song/real-slow/1869618394</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-19</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>As Is</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G156" t="str">
-        <v>2:42</v>
+        <v>3:22</v>
       </c>
       <c r="H156" t="str">
-        <v>Josiah and the Bonnevilles</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/josiah-and-the-bonnevilles/1101954493</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/mountain-girl/1870722288</v>
+        <v>https://music.apple.com/us/album/real-slow/1869617637</v>
       </c>
       <c r="L156" t="str">
-        <v>Mountain Girl - Josiah and the Bonnevilles</v>
+        <v>Real Slow - Flatland Cavalry</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Like a Spark</v>
+        <v>Mountain Girl</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/like-a-spark/1876952751</v>
+        <v>https://music.apple.com/us/song/mountain-girl/1870722299</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-19</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>American Stories</v>
+        <v>As Is</v>
       </c>
       <c r="G157" t="str">
-        <v>3:31</v>
+        <v>2:42</v>
       </c>
       <c r="H157" t="str">
-        <v>Rostam</v>
+        <v>Josiah and the Bonnevilles</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
+        <v>https://music.apple.com/us/artist/josiah-and-the-bonnevilles/1101954493</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/like-a-spark/1876952750</v>
+        <v>https://music.apple.com/us/album/mountain-girl/1870722288</v>
       </c>
       <c r="L157" t="str">
-        <v>Like a Spark - Rostam</v>
+        <v>Mountain Girl - Josiah and the Bonnevilles</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Cheesecake</v>
+        <v>Like a Spark</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/cheesecake/1882526540</v>
+        <v>https://music.apple.com/us/song/like-a-spark/1876952751</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-19</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>So Much To Tell You (Deluxe)</v>
+        <v>American Stories</v>
       </c>
       <c r="G158" t="str">
-        <v>3:29</v>
+        <v>3:31</v>
       </c>
       <c r="H158" t="str">
-        <v>Ax and the Hatchetmen</v>
+        <v>Rostam</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/ax-and-the-hatchetmen/1471855465</v>
+        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/cheesecake/1882525852</v>
+        <v>https://music.apple.com/us/album/like-a-spark/1876952750</v>
       </c>
       <c r="L158" t="str">
-        <v>Cheesecake - Ax and the Hatchetmen</v>
+        <v>Like a Spark - Rostam</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>ALWAYS LET YOU DOWN</v>
+        <v>Cheesecake</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/always-let-you-down/1871578121</v>
+        <v>https://music.apple.com/us/song/cheesecake/1882526540</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-19</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>KINDA HARD</v>
+        <v>So Much To Tell You (Deluxe)</v>
       </c>
       <c r="G159" t="str">
-        <v>3:04</v>
+        <v>3:29</v>
       </c>
       <c r="H159" t="str">
-        <v>Bilmuri</v>
+        <v>Ax and the Hatchetmen</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
+        <v>https://music.apple.com/us/artist/ax-and-the-hatchetmen/1471855465</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/always-let-you-down/1871578103</v>
+        <v>https://music.apple.com/us/album/cheesecake/1882525852</v>
       </c>
       <c r="L159" t="str">
-        <v>ALWAYS LET YOU DOWN - Bilmuri</v>
+        <v>Cheesecake - Ax and the Hatchetmen</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Freakin’ Out</v>
+        <v>ALWAYS LET YOU DOWN</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/freakin-out/1879596115</v>
+        <v>https://music.apple.com/us/song/always-let-you-down/1871578121</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-19</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Freakin’ Out - Single</v>
+        <v>KINDA HARD</v>
       </c>
       <c r="G160" t="str">
-        <v>3:37</v>
+        <v>3:04</v>
       </c>
       <c r="H160" t="str">
-        <v>Dexter and The Moonrocks</v>
+        <v>Bilmuri</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
+        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/freakin-out/1879596114</v>
+        <v>https://music.apple.com/us/album/always-let-you-down/1871578103</v>
       </c>
       <c r="L160" t="str">
-        <v>Freakin’ Out - Dexter and The Moonrocks</v>
+        <v>ALWAYS LET YOU DOWN - Bilmuri</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Name in Vein</v>
+        <v>Freakin’ Out</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/name-in-vein/1880069474</v>
+        <v>https://music.apple.com/us/song/freakin-out/1879596115</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-19</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Name in Vein - Single</v>
+        <v>Freakin’ Out - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:03</v>
+        <v>3:37</v>
       </c>
       <c r="H161" t="str">
-        <v>VOILÀ</v>
+        <v>Dexter and The Moonrocks</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/name-in-vein/1880069473</v>
+        <v>https://music.apple.com/us/album/freakin-out/1879596114</v>
       </c>
       <c r="L161" t="str">
-        <v>Name in Vein - VOILÀ</v>
+        <v>Freakin’ Out - Dexter and The Moonrocks</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>St. Catherine's Wheel</v>
+        <v>Name in Vein</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/st-catherines-wheel/1868804170</v>
+        <v>https://music.apple.com/us/song/name-in-vein/1880069474</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-19</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Into Oblivion</v>
+        <v>Name in Vein - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>4:05</v>
+        <v>3:03</v>
       </c>
       <c r="H162" t="str">
-        <v>Lamb of God</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
+        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/st-catherines-wheel/1868804163</v>
+        <v>https://music.apple.com/us/album/name-in-vein/1880069473</v>
       </c>
       <c r="L162" t="str">
-        <v>St. Catherine's Wheel - Lamb of God</v>
+        <v>Name in Vein - VOILÀ</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Undefeated Champion</v>
+        <v>St. Catherine's Wheel</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/undefeated-champion/1840517120</v>
+        <v>https://music.apple.com/us/song/st-catherines-wheel/1868804170</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-19</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Sweat</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G163" t="str">
-        <v>3:34</v>
+        <v>4:05</v>
       </c>
       <c r="H163" t="str">
-        <v>Melanie C</v>
+        <v>Lamb of God</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
+        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/undefeated-champion/1840516706</v>
+        <v>https://music.apple.com/us/album/st-catherines-wheel/1868804163</v>
       </c>
       <c r="L163" t="str">
-        <v>Undefeated Champion - Melanie C</v>
+        <v>St. Catherine's Wheel - Lamb of God</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Pull Up</v>
+        <v>Undefeated Champion</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/pull-up/1854381591</v>
+        <v>https://music.apple.com/us/song/undefeated-champion/1840517120</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-19</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Pull Up - Single</v>
+        <v>Sweat</v>
       </c>
       <c r="G164" t="str">
-        <v>2:35</v>
+        <v>3:34</v>
       </c>
       <c r="H164" t="str">
-        <v>Collect 200</v>
+        <v>Melanie C</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/collect-200/1804375505</v>
+        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/pull-up/1854381590</v>
+        <v>https://music.apple.com/us/album/undefeated-champion/1840516706</v>
       </c>
       <c r="L164" t="str">
-        <v>Pull Up - Collect 200</v>
+        <v>Undefeated Champion - Melanie C</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Ranjha</v>
+        <v>Pull Up</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/ranjha/1882965642</v>
+        <v>https://music.apple.com/us/song/pull-up/1854381591</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-19</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Ranjha - Single</v>
+        <v>Pull Up - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:04</v>
+        <v>2:35</v>
       </c>
       <c r="H165" t="str">
-        <v>Diljit Dosanjh</v>
+        <v>Collect 200</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/diljit-dosanjh/423087540</v>
+        <v>https://music.apple.com/us/artist/collect-200/1804375505</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/ranjha/1882965641</v>
+        <v>https://music.apple.com/us/album/pull-up/1854381590</v>
       </c>
       <c r="L165" t="str">
-        <v>Ranjha - Diljit Dosanjh</v>
+        <v>Pull Up - Collect 200</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>zombies in love</v>
+        <v>Ranjha</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/zombies-in-love/1880178176</v>
+        <v>https://music.apple.com/us/song/ranjha/1882965642</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-19</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>zombies in love - Single</v>
+        <v>Ranjha - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>2:53</v>
+        <v>3:04</v>
       </c>
       <c r="H166" t="str">
-        <v>paris jackson</v>
+        <v>Diljit Dosanjh</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
+        <v>https://music.apple.com/us/artist/diljit-dosanjh/423087540</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/zombies-in-love/1880178173</v>
+        <v>https://music.apple.com/us/album/ranjha/1882965641</v>
       </c>
       <c r="L166" t="str">
-        <v>zombies in love - paris jackson</v>
+        <v>Ranjha - Diljit Dosanjh</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Days Of Us</v>
+        <v>zombies in love</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/days-of-us/1868438268</v>
+        <v>https://music.apple.com/us/song/zombies-in-love/1880178176</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-19</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Full Circle</v>
+        <v>zombies in love - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>4:39</v>
+        <v>2:53</v>
       </c>
       <c r="H167" t="str">
-        <v>Tom Misch</v>
+        <v>paris jackson</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
+        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/days-of-us/1868437787</v>
+        <v>https://music.apple.com/us/album/zombies-in-love/1880178173</v>
       </c>
       <c r="L167" t="str">
-        <v>Days Of Us - Tom Misch</v>
+        <v>zombies in love - paris jackson</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Life Of A Man</v>
+        <v>Days Of Us</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/life-of-a-man/1882845328</v>
+        <v>https://music.apple.com/us/song/days-of-us/1868438268</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-19</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Life Of A Man - Single</v>
+        <v>Full Circle</v>
       </c>
       <c r="G168" t="str">
-        <v>3:15</v>
+        <v>4:39</v>
       </c>
       <c r="H168" t="str">
-        <v>1Ski OG</v>
+        <v>Tom Misch</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/life-of-a-man/1882845327</v>
+        <v>https://music.apple.com/us/album/days-of-us/1868437787</v>
       </c>
       <c r="L168" t="str">
-        <v>Life Of A Man - 1Ski OG</v>
+        <v>Days Of Us - Tom Misch</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Ya No</v>
+        <v>Life Of A Man</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/ya-no/1882115676</v>
+        <v>https://music.apple.com/us/song/life-of-a-man/1882845328</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-19</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Ya No - Single</v>
+        <v>Life Of A Man - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:40</v>
+        <v>3:15</v>
       </c>
       <c r="H169" t="str">
-        <v>Marca MP</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/ya-no/1882115675</v>
+        <v>https://music.apple.com/us/album/life-of-a-man/1882845327</v>
       </c>
       <c r="L169" t="str">
-        <v>Ya No - Marca MP</v>
+        <v>Life Of A Man - 1Ski OG</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Do You Really Love Her</v>
+        <v>Ya No</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/do-you-really-love-her/1879639011</v>
+        <v>https://music.apple.com/us/song/ya-no/1882115676</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-19</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Do You Really Love Her - Single</v>
+        <v>Ya No - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:48</v>
+        <v>3:40</v>
       </c>
       <c r="H170" t="str">
-        <v>Spacey Jane</v>
+        <v>Marca MP</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
+        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/do-you-really-love-her/1879639009</v>
+        <v>https://music.apple.com/us/album/ya-no/1882115675</v>
       </c>
       <c r="L170" t="str">
-        <v>Do You Really Love Her - Spacey Jane</v>
+        <v>Ya No - Marca MP</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Relieve You</v>
+        <v>Do You Really Love Her</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/relieve-you/1879589717</v>
+        <v>https://music.apple.com/us/song/do-you-really-love-her/1879639011</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-19</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Relieve You - Single</v>
+        <v>Do You Really Love Her - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:19</v>
+        <v>3:48</v>
       </c>
       <c r="H171" t="str">
-        <v>4Fargo</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/4fargo/1381605295</v>
+        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/relieve-you/1879589716</v>
+        <v>https://music.apple.com/us/album/do-you-really-love-her/1879639009</v>
       </c>
       <c r="L171" t="str">
-        <v>Relieve You - 4Fargo</v>
+        <v>Do You Really Love Her - Spacey Jane</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Safety</v>
+        <v>Relieve You</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/safety/1878181748</v>
+        <v>https://music.apple.com/us/song/relieve-you/1879589717</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-19</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Safety - Single</v>
+        <v>Relieve You - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:18</v>
+        <v>2:19</v>
       </c>
       <c r="H172" t="str">
-        <v>Lekan</v>
+        <v>4Fargo</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/lekan/1540259198</v>
+        <v>https://music.apple.com/us/artist/4fargo/1381605295</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/safety/1878181738</v>
+        <v>https://music.apple.com/us/album/relieve-you/1879589716</v>
       </c>
       <c r="L172" t="str">
-        <v>Safety - Lekan</v>
+        <v>Relieve You - 4Fargo</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Starlet</v>
+        <v>Safety</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/starlet/1873450846</v>
+        <v>https://music.apple.com/us/song/safety/1878181748</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-19</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>LK99</v>
+        <v>Safety - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:56</v>
+        <v>3:18</v>
       </c>
       <c r="H173" t="str">
-        <v>Leven Kali</v>
+        <v>Lekan</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/leven-kali/1166360470</v>
+        <v>https://music.apple.com/us/artist/lekan/1540259198</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/starlet/1873450570</v>
+        <v>https://music.apple.com/us/album/safety/1878181738</v>
       </c>
       <c r="L173" t="str">
-        <v>Starlet - Leven Kali</v>
+        <v>Safety - Lekan</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Physical</v>
+        <v>Starlet</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/physical/1883210753</v>
+        <v>https://music.apple.com/us/song/starlet/1873450846</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-19</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Physical - Single</v>
+        <v>LK99</v>
       </c>
       <c r="G174" t="str">
-        <v>3:52</v>
+        <v>2:56</v>
       </c>
       <c r="H174" t="str">
-        <v>Jacquees</v>
+        <v>Leven Kali</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/jacquees/386779763</v>
+        <v>https://music.apple.com/us/artist/leven-kali/1166360470</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/physical/1883210752</v>
+        <v>https://music.apple.com/us/album/starlet/1873450570</v>
       </c>
       <c r="L174" t="str">
-        <v>Physical - Jacquees</v>
+        <v>Starlet - Leven Kali</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>i'm dying to feel alive again</v>
+        <v>Physical</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/im-dying-to-feel-alive-again/1880883509</v>
+        <v>https://music.apple.com/us/song/physical/1883210753</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-19</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>i'm dying to feel alive again - Single</v>
+        <v>Physical - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>4:29</v>
+        <v>3:52</v>
       </c>
       <c r="H175" t="str">
-        <v>Casper Sage</v>
+        <v>Jacquees</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
+        <v>https://music.apple.com/us/artist/jacquees/386779763</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/im-dying-to-feel-alive-again/1880883507</v>
+        <v>https://music.apple.com/us/album/physical/1883210752</v>
       </c>
       <c r="L175" t="str">
-        <v>i'm dying to feel alive again - Casper Sage</v>
+        <v>Physical - Jacquees</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Regalito</v>
+        <v>i'm dying to feel alive again</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/regalito/1880846653</v>
+        <v>https://music.apple.com/us/song/im-dying-to-feel-alive-again/1880883509</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-19</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>TRESCENDER</v>
+        <v>i'm dying to feel alive again - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:41</v>
+        <v>4:29</v>
       </c>
       <c r="H176" t="str">
-        <v>Piso 21</v>
+        <v>Casper Sage</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/piso-21/403121923</v>
+        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/regalito/1880845994</v>
+        <v>https://music.apple.com/us/album/im-dying-to-feel-alive-again/1880883507</v>
       </c>
       <c r="L176" t="str">
-        <v>Regalito - Piso 21</v>
+        <v>i'm dying to feel alive again - Casper Sage</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Cruel Streak</v>
+        <v>Regalito</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/cruel-streak/1858689493</v>
+        <v>https://music.apple.com/us/song/regalito/1880846653</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-19</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>A Pound of Feathers</v>
+        <v>TRESCENDER</v>
       </c>
       <c r="G177" t="str">
-        <v>4:09</v>
+        <v>2:41</v>
       </c>
       <c r="H177" t="str">
-        <v>The Black Crowes</v>
+        <v>Piso 21</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
+        <v>https://music.apple.com/us/artist/piso-21/403121923</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/cruel-streak/1858689485</v>
+        <v>https://music.apple.com/us/album/regalito/1880845994</v>
       </c>
       <c r="L177" t="str">
-        <v>Cruel Streak - The Black Crowes</v>
+        <v>Regalito - Piso 21</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Die Young</v>
+        <v>Cruel Streak</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/die-young/1870715300</v>
+        <v>https://music.apple.com/us/song/cruel-streak/1858689493</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-19</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Little Wide Open</v>
+        <v>A Pound of Feathers</v>
       </c>
       <c r="G178" t="str">
-        <v>3:52</v>
+        <v>4:09</v>
       </c>
       <c r="H178" t="str">
-        <v>Kevin Morby</v>
+        <v>The Black Crowes</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/kevin-morby/708517315</v>
+        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/die-young/1870715298</v>
+        <v>https://music.apple.com/us/album/cruel-streak/1858689485</v>
       </c>
       <c r="L178" t="str">
-        <v>Die Young - Kevin Morby</v>
+        <v>Cruel Streak - The Black Crowes</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Island Girl</v>
+        <v>Die Young</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/island-girl/1884461360</v>
+        <v>https://music.apple.com/us/song/die-young/1870715300</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-19</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Island Girl - Single</v>
+        <v>Little Wide Open</v>
       </c>
       <c r="G179" t="str">
-        <v>3:27</v>
+        <v>3:52</v>
       </c>
       <c r="H179" t="str">
-        <v>Pia Mia</v>
+        <v>Kevin Morby</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/pia-mia/483071062</v>
+        <v>https://music.apple.com/us/artist/kevin-morby/708517315</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/island-girl/1884461354</v>
+        <v>https://music.apple.com/us/album/die-young/1870715298</v>
       </c>
       <c r="L179" t="str">
-        <v>Island Girl - Pia Mia</v>
+        <v>Die Young - Kevin Morby</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>GIRLY THINGS</v>
+        <v>Island Girl</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/girly-things/1876032954</v>
+        <v>https://music.apple.com/us/song/island-girl/1884461360</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-19</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>GIRLY THINGS - Single</v>
+        <v>Island Girl - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:20</v>
+        <v>3:27</v>
       </c>
       <c r="H180" t="str">
-        <v>Claudia Valentina</v>
+        <v>Pia Mia</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/claudia-valentina/1434841711</v>
+        <v>https://music.apple.com/us/artist/pia-mia/483071062</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/girly-things/1876032953</v>
+        <v>https://music.apple.com/us/album/island-girl/1884461354</v>
       </c>
       <c r="L180" t="str">
-        <v>GIRLY THINGS - Claudia Valentina</v>
+        <v>Island Girl - Pia Mia</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Looking Lovely (feat. Robin Thicke)</v>
+        <v>GIRLY THINGS</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/looking-lovely-feat-robin-thicke/1878437828</v>
+        <v>https://music.apple.com/us/song/girly-things/1876032954</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-19</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Looking Lovely (feat. Robin Thicke) - Single</v>
+        <v>GIRLY THINGS - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:22</v>
+        <v>2:20</v>
       </c>
       <c r="H181" t="str">
-        <v>Shaggy</v>
+        <v>Claudia Valentina</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/shaggy/68616</v>
+        <v>https://music.apple.com/us/artist/claudia-valentina/1434841711</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/looking-lovely-feat-robin-thicke/1878437504</v>
+        <v>https://music.apple.com/us/album/girly-things/1876032953</v>
       </c>
       <c r="L181" t="str">
-        <v>Looking Lovely (feat. Robin Thicke) - Shaggy</v>
+        <v>GIRLY THINGS - Claudia Valentina</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Tommy’s Song</v>
+        <v>Looking Lovely (feat. Robin Thicke)</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/tommys-song/1876670040</v>
+        <v>https://music.apple.com/us/song/looking-lovely-feat-robin-thicke/1878437828</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-19</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Lovers - Single</v>
+        <v>Looking Lovely (feat. Robin Thicke) - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:44</v>
+        <v>3:22</v>
       </c>
       <c r="H182" t="str">
-        <v>Nathaniel Rateliff</v>
+        <v>Shaggy</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/nathaniel-rateliff/362131302</v>
+        <v>https://music.apple.com/us/artist/shaggy/68616</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/tommys-song/1876670038</v>
+        <v>https://music.apple.com/us/album/looking-lovely-feat-robin-thicke/1878437504</v>
       </c>
       <c r="L182" t="str">
-        <v>Tommy’s Song - Nathaniel Rateliff</v>
+        <v>Looking Lovely (feat. Robin Thicke) - Shaggy</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Rainbows</v>
+        <v>Tommy’s Song</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/rainbows/1882790536</v>
+        <v>https://music.apple.com/us/song/tommys-song/1876670040</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-19</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Rainbows - Single</v>
+        <v>Lovers - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:25</v>
+        <v>3:44</v>
       </c>
       <c r="H183" t="str">
-        <v>Allison Russell</v>
+        <v>Nathaniel Rateliff</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/allison-russell/451740458</v>
+        <v>https://music.apple.com/us/artist/nathaniel-rateliff/362131302</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/rainbows/1882790535</v>
+        <v>https://music.apple.com/us/album/tommys-song/1876670038</v>
       </c>
       <c r="L183" t="str">
-        <v>Rainbows - Allison Russell</v>
+        <v>Tommy’s Song - Nathaniel Rateliff</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>butterflies</v>
+        <v>Rainbows</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/butterflies/1878228436</v>
+        <v>https://music.apple.com/us/song/rainbows/1882790536</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-19</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Bloom Again - EP</v>
+        <v>Rainbows - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:48</v>
+        <v>3:25</v>
       </c>
       <c r="H184" t="str">
-        <v>runo plum</v>
+        <v>Allison Russell</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
+        <v>https://music.apple.com/us/artist/allison-russell/451740458</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/butterflies/1878228434</v>
+        <v>https://music.apple.com/us/album/rainbows/1882790535</v>
       </c>
       <c r="L184" t="str">
-        <v>butterflies - runo plum</v>
+        <v>Rainbows - Allison Russell</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>You're Right</v>
+        <v>butterflies</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/youre-right/1874975857</v>
+        <v>https://music.apple.com/us/song/butterflies/1878228436</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-19</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>You're Right - Single</v>
+        <v>Bloom Again - EP</v>
       </c>
       <c r="G185" t="str">
-        <v>3:00</v>
+        <v>2:48</v>
       </c>
       <c r="H185" t="str">
-        <v>Emma Harner</v>
+        <v>runo plum</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/emma-harner/1543609198</v>
+        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/youre-right/1874975856</v>
+        <v>https://music.apple.com/us/album/butterflies/1878228434</v>
       </c>
       <c r="L185" t="str">
-        <v>You're Right - Emma Harner</v>
+        <v>butterflies - runo plum</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Bible Belt</v>
+        <v>You're Right</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/bible-belt/1821125622</v>
+        <v>https://music.apple.com/us/song/youre-right/1874975857</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-19</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Bible Belt - Single</v>
+        <v>You're Right - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:34</v>
+        <v>3:00</v>
       </c>
       <c r="H186" t="str">
-        <v>Baby Bugs</v>
+        <v>Emma Harner</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/baby-bugs/1551794879</v>
+        <v>https://music.apple.com/us/artist/emma-harner/1543609198</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/bible-belt/1821125621</v>
+        <v>https://music.apple.com/us/album/youre-right/1874975856</v>
       </c>
       <c r="L186" t="str">
-        <v>Bible Belt - Baby Bugs</v>
+        <v>You're Right - Emma Harner</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Daze</v>
+        <v>Bible Belt</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/daze/1862607801</v>
+        <v>https://music.apple.com/us/song/bible-belt/1821125622</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-19</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Daze - Single</v>
+        <v>Bible Belt - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:22</v>
+        <v>3:34</v>
       </c>
       <c r="H187" t="str">
-        <v>Olympia Vitalis</v>
+        <v>Baby Bugs</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
+        <v>https://music.apple.com/us/artist/baby-bugs/1551794879</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/daze/1862607800</v>
+        <v>https://music.apple.com/us/album/bible-belt/1821125621</v>
       </c>
       <c r="L187" t="str">
-        <v>Daze - Olympia Vitalis</v>
+        <v>Bible Belt - Baby Bugs</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Passionfruit</v>
+        <v>Daze</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/passionfruit/1878215125</v>
+        <v>https://music.apple.com/us/song/daze/1862607801</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-19</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Passionfruit - Single</v>
+        <v>Daze - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:57</v>
+        <v>3:22</v>
       </c>
       <c r="H188" t="str">
-        <v>Anish Kumar</v>
+        <v>Olympia Vitalis</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/passionfruit/1878215124</v>
+        <v>https://music.apple.com/us/album/daze/1862607800</v>
       </c>
       <c r="L188" t="str">
-        <v>Passionfruit - Anish Kumar</v>
+        <v>Daze - Olympia Vitalis</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Madan</v>
+        <v>Passionfruit</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/madan/1879822223</v>
+        <v>https://music.apple.com/us/song/passionfruit/1878215125</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-19</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Madan - Single</v>
+        <v>Passionfruit - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>2:56</v>
+        <v>3:57</v>
       </c>
       <c r="H189" t="str">
-        <v>Jonas Blue</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/jonas-blue/405728790</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/madan/1879822222</v>
+        <v>https://music.apple.com/us/album/passionfruit/1878215124</v>
       </c>
       <c r="L189" t="str">
-        <v>Madan - Jonas Blue</v>
+        <v>Passionfruit - Anish Kumar</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Bad Bitch</v>
+        <v>Madan</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/bad-bitch/1882818210</v>
+        <v>https://music.apple.com/us/song/madan/1879822223</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-19</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Bad Bitch - Single</v>
+        <v>Madan - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>2:28</v>
+        <v>2:56</v>
       </c>
       <c r="H190" t="str">
-        <v>41</v>
+        <v>Jonas Blue</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/41/1688992229</v>
+        <v>https://music.apple.com/us/artist/jonas-blue/405728790</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/bad-bitch/1882818208</v>
+        <v>https://music.apple.com/us/album/madan/1879822222</v>
       </c>
       <c r="L190" t="str">
-        <v>Bad Bitch - 41</v>
+        <v>Madan - Jonas Blue</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Shame</v>
+        <v>Bad Bitch</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/shame/1874080307</v>
+        <v>https://music.apple.com/us/song/bad-bitch/1882818210</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-19</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Devotion [Deluxe]</v>
+        <v>Bad Bitch - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>3:36</v>
+        <v>2:28</v>
       </c>
       <c r="H191" t="str">
-        <v>Sunday (1994)</v>
+        <v>41</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/sunday-1994/1728938785</v>
+        <v>https://music.apple.com/us/artist/41/1688992229</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/shame/1874080202</v>
+        <v>https://music.apple.com/us/album/bad-bitch/1882818208</v>
       </c>
       <c r="L191" t="str">
-        <v>Shame - Sunday (1994)</v>
+        <v>Bad Bitch - 41</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>teach you to love me</v>
+        <v>Shame</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/teach-you-to-love-me/1883146005</v>
+        <v>https://music.apple.com/us/song/shame/1874080307</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-19</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>teach you to love me - Single</v>
+        <v>Devotion [Deluxe]</v>
       </c>
       <c r="G192" t="str">
-        <v>3:09</v>
+        <v>3:36</v>
       </c>
       <c r="H192" t="str">
-        <v>Hailey Picardi</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/sunday-1994/1728938785</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/teach-you-to-love-me/1883146002</v>
+        <v>https://music.apple.com/us/album/shame/1874080202</v>
       </c>
       <c r="L192" t="str">
-        <v>teach you to love me - Hailey Picardi</v>
+        <v>Shame - Sunday (1994)</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>The Fix</v>
+        <v>teach you to love me</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/the-fix/1882082897</v>
+        <v>https://music.apple.com/us/song/teach-you-to-love-me/1883146005</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-19</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>The Fix - Single</v>
+        <v>teach you to love me - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>2:42</v>
+        <v>3:09</v>
       </c>
       <c r="H193" t="str">
-        <v>Baby J</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/the-fix/1882082895</v>
+        <v>https://music.apple.com/us/album/teach-you-to-love-me/1883146002</v>
       </c>
       <c r="L193" t="str">
-        <v>The Fix - Baby J</v>
+        <v>teach you to love me - Hailey Picardi</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Hanging on Hope</v>
+        <v>The Fix</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/hanging-on-hope/1881749452</v>
+        <v>https://music.apple.com/us/song/the-fix/1882082897</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-19</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Hanging on Hope - Single</v>
+        <v>The Fix - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:43</v>
+        <v>2:42</v>
       </c>
       <c r="H194" t="str">
-        <v>Buffalo Traffic Jam</v>
+        <v>Baby J</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
+        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/hanging-on-hope/1881749451</v>
+        <v>https://music.apple.com/us/album/the-fix/1882082895</v>
       </c>
       <c r="L194" t="str">
-        <v>Hanging on Hope - Buffalo Traffic Jam</v>
+        <v>The Fix - Baby J</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>I Know What to Say Now</v>
+        <v>Hanging on Hope</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/i-know-what-to-say-now/1879440545</v>
+        <v>https://music.apple.com/us/song/hanging-on-hope/1881749452</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-19</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>I Know What to Say Now - Single</v>
+        <v>Hanging on Hope - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:18</v>
+        <v>3:43</v>
       </c>
       <c r="H195" t="str">
-        <v>Active Child</v>
+        <v>Buffalo Traffic Jam</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/active-child/355288617</v>
+        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/i-know-what-to-say-now/1879440351</v>
+        <v>https://music.apple.com/us/album/hanging-on-hope/1881749451</v>
       </c>
       <c r="L195" t="str">
-        <v>I Know What to Say Now - Active Child</v>
+        <v>Hanging on Hope - Buffalo Traffic Jam</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Feel Something</v>
+        <v>I Know What to Say Now</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/feel-something/1876008375</v>
+        <v>https://music.apple.com/us/song/i-know-what-to-say-now/1879440545</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-19</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Feel Something - Single</v>
+        <v>I Know What to Say Now - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>3:09</v>
+        <v>3:18</v>
       </c>
       <c r="H196" t="str">
-        <v>Baby Queen</v>
+        <v>Active Child</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
+        <v>https://music.apple.com/us/artist/active-child/355288617</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/feel-something/1876008371</v>
+        <v>https://music.apple.com/us/album/i-know-what-to-say-now/1879440351</v>
       </c>
       <c r="L196" t="str">
-        <v>Feel Something - Baby Queen</v>
+        <v>I Know What to Say Now - Active Child</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>You Or Me</v>
+        <v>Feel Something</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/you-or-me/1869085528</v>
+        <v>https://music.apple.com/us/song/feel-something/1876008375</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-19</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Good God / Baad Man</v>
+        <v>Feel Something - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>5:28</v>
+        <v>3:09</v>
       </c>
       <c r="H197" t="str">
-        <v>Corrosion of Conformity</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
+        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/you-or-me/1869085524</v>
+        <v>https://music.apple.com/us/album/feel-something/1876008371</v>
       </c>
       <c r="L197" t="str">
-        <v>You Or Me - Corrosion of Conformity</v>
+        <v>Feel Something - Baby Queen</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Mortercheyn</v>
+        <v>You Or Me</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/mortercheyn/1862521946</v>
+        <v>https://music.apple.com/us/song/you-or-me/1869085528</v>
       </c>
       <c r="D198" t="str">
         <v>2026-03-19</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Coronach</v>
+        <v>Good God / Baad Man</v>
       </c>
       <c r="G198" t="str">
-        <v>4:18</v>
+        <v>5:28</v>
       </c>
       <c r="H198" t="str">
-        <v>Hellripper</v>
+        <v>Corrosion of Conformity</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/hellripper/1229248568</v>
+        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/mortercheyn/1862521937</v>
+        <v>https://music.apple.com/us/album/you-or-me/1869085524</v>
       </c>
       <c r="L198" t="str">
-        <v>Mortercheyn - Hellripper</v>
+        <v>You Or Me - Corrosion of Conformity</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Rip The God</v>
+        <v>Mortercheyn</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/rip-the-god/1866957697</v>
+        <v>https://music.apple.com/us/song/mortercheyn/1862521946</v>
       </c>
       <c r="D199" t="str">
         <v>2026-03-19</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Savage Imperial Death March</v>
+        <v>Coronach</v>
       </c>
       <c r="G199" t="str">
-        <v>5:20</v>
+        <v>4:18</v>
       </c>
       <c r="H199" t="str">
-        <v>Melvins</v>
+        <v>Hellripper</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/melvins/737433</v>
+        <v>https://music.apple.com/us/artist/hellripper/1229248568</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/rip-the-god/1866957685</v>
+        <v>https://music.apple.com/us/album/mortercheyn/1862521937</v>
       </c>
       <c r="L199" t="str">
-        <v>Rip The God - Melvins</v>
+        <v>Mortercheyn - Hellripper</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Who We Are</v>
+        <v>Rip The God</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/who-we-are/1879626950</v>
+        <v>https://music.apple.com/us/song/rip-the-god/1866957697</v>
       </c>
       <c r="D200" t="str">
         <v>2026-03-19</v>
@@ -7975,68 +7975,106 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Who We Are - Single</v>
+        <v>Savage Imperial Death March</v>
       </c>
       <c r="G200" t="str">
-        <v>2:10</v>
+        <v>5:20</v>
       </c>
       <c r="H200" t="str">
-        <v>Kaleena Zanders</v>
+        <v>Melvins</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+        <v>https://music.apple.com/us/artist/melvins/737433</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/who-we-are/1879626949</v>
+        <v>https://music.apple.com/us/album/rip-the-god/1866957685</v>
       </c>
       <c r="L200" t="str">
-        <v>Who We Are - Kaleena Zanders</v>
+        <v>Rip The God - Melvins</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
+        <v>Who We Are</v>
+      </c>
+      <c r="B201" t="str">
+        <v/>
+      </c>
+      <c r="C201" t="str">
+        <v>https://music.apple.com/us/song/who-we-are/1879626950</v>
+      </c>
+      <c r="D201" t="str">
+        <v>2026-03-19</v>
+      </c>
+      <c r="E201" t="str">
+        <v/>
+      </c>
+      <c r="F201" t="str">
+        <v>Who We Are - Single</v>
+      </c>
+      <c r="G201" t="str">
+        <v>2:10</v>
+      </c>
+      <c r="H201" t="str">
+        <v>Kaleena Zanders</v>
+      </c>
+      <c r="I201" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J201" t="str">
+        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+      </c>
+      <c r="K201" t="str">
+        <v>https://music.apple.com/us/album/who-we-are/1879626949</v>
+      </c>
+      <c r="L201" t="str">
+        <v>Who We Are - Kaleena Zanders</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
         <v>Reels in 360</v>
       </c>
-      <c r="B201" t="str">
-        <v/>
-      </c>
-      <c r="C201" t="str">
+      <c r="B202" t="str">
+        <v/>
+      </c>
+      <c r="C202" t="str">
         <v>https://music.apple.com/us/song/reels-in-360/1867998408</v>
       </c>
-      <c r="D201" t="str">
-        <v>2026-03-19</v>
-      </c>
-      <c r="E201" t="str">
-        <v/>
-      </c>
-      <c r="F201" t="str">
+      <c r="D202" t="str">
+        <v>2026-03-19</v>
+      </c>
+      <c r="E202" t="str">
+        <v/>
+      </c>
+      <c r="F202" t="str">
         <v>Dying Is The Internet</v>
       </c>
-      <c r="G201" t="str">
+      <c r="G202" t="str">
         <v>4:37</v>
       </c>
-      <c r="H201" t="str">
+      <c r="H202" t="str">
         <v>Simo Cell</v>
       </c>
-      <c r="I201" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J201" t="str">
+      <c r="I202" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J202" t="str">
         <v>https://music.apple.com/us/artist/simo-cell/1001568130</v>
       </c>
-      <c r="K201" t="str">
+      <c r="K202" t="str">
         <v>https://music.apple.com/us/album/reels-in-360/1867998295</v>
       </c>
-      <c r="L201" t="str">
+      <c r="L202" t="str">
         <v>Reels in 360 - Simo Cell</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L201"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L202"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
@@ -553,7 +553,7 @@
         <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
       </c>
       <c r="B5" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G5" t="str">
         <v>4:11</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
@@ -705,7 +705,7 @@
         <v>Grace Enger - Give A Little (Live Performance)</v>
       </c>
       <c r="B9" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G9" t="str">
         <v>3:06</v>
@@ -1997,7 +1997,7 @@
         <v>Amanda Jordan - What Else Is New</v>
       </c>
       <c r="B43" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G43" t="str">
         <v>2:50</v>
@@ -2035,7 +2035,7 @@
         <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
       </c>
       <c r="B44" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G44" t="str">
         <v>3:57</v>
@@ -2263,7 +2263,7 @@
         <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B50" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G50" t="str">
         <v>3:13</v>
@@ -2453,7 +2453,7 @@
         <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G55" t="str">
         <v>4:58</v>
@@ -2491,7 +2491,7 @@
         <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G56" t="str">
         <v>2:33</v>
@@ -2529,7 +2529,7 @@
         <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B57" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G57" t="str">
         <v>5:01</v>
@@ -3213,7 +3213,7 @@
         <v>Bazzi - moment (Official Music Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
         <v>2:43</v>
@@ -3251,7 +3251,7 @@
         <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
       </c>
       <c r="B76" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
         <v>4:43</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L202"/>
+  <dimension ref="A1:L201"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -445,7 +445,7 @@
         <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -477,19 +477,19 @@
         <v>Nick Carter - Love Life Tragedy</v>
       </c>
       <c r="B3" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:31</v>
@@ -515,19 +515,19 @@
         <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=033viNHogN4</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:38</v>
@@ -559,7 +559,7 @@
         <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -778,16 +778,16 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Nathan Evans x Saint PHNX - Happy Place (Official Acoustic Video)</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
       </c>
       <c r="B11" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=lyuE94W1WIc</v>
+        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -796,10 +796,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:03</v>
+        <v>3:12</v>
       </c>
       <c r="H11" t="str">
-        <v>NathanEvanss</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,21 +811,21 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Nathan Evans x Saint PHNX - Happy Place (Official Acoustic Video) - NathanEvanss</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B12" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
+        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -834,10 +834,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>3:12</v>
+        <v>9:11</v>
       </c>
       <c r="H12" t="str">
-        <v>Freya Ridings</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,21 +849,21 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
+        <v>SIENNA SPIRO - The Visitor</v>
       </c>
       <c r="B13" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
+        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -872,10 +872,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>9:11</v>
+        <v>3:49</v>
       </c>
       <c r="H13" t="str">
-        <v>David Gilmour</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,21 +887,21 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>SIENNA SPIRO - The Visitor</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
       </c>
       <c r="B14" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
+        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -910,10 +910,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:49</v>
+        <v>3:28</v>
       </c>
       <c r="H14" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Jonas Brothers and Demi Lovato</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,21 +925,21 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
+        <v>Martin Garrix - Catharina (Official Video)</v>
       </c>
       <c r="B15" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
+        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -948,10 +948,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:28</v>
+        <v>3:31</v>
       </c>
       <c r="H15" t="str">
-        <v>Jonas Brothers and Demi Lovato</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,21 +963,21 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
+        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Martin Garrix - Catharina (Official Video)</v>
+        <v>Baby Queen - Feel Something (Official Visualiser)</v>
       </c>
       <c r="B16" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
+        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -986,10 +986,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:31</v>
+        <v>3:11</v>
       </c>
       <c r="H16" t="str">
-        <v>Martin Garrix</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,21 +1001,21 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
+        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser)</v>
+        <v>HAUSER - Hungarian Dance No. 5</v>
       </c>
       <c r="B17" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
+        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1024,10 +1024,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:11</v>
+        <v>2:27</v>
       </c>
       <c r="H17" t="str">
-        <v>Baby Queen</v>
+        <v>HAUSER</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,21 +1039,21 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
+        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>HAUSER - Hungarian Dance No. 5</v>
+        <v>Holly Humberstone - Cruel World</v>
       </c>
       <c r="B18" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
+        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1062,10 +1062,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>2:27</v>
+        <v>3:34</v>
       </c>
       <c r="H18" t="str">
-        <v>HAUSER</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,21 +1077,21 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
+        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Holly Humberstone - Cruel World</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
       </c>
       <c r="B19" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
+        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1100,10 +1100,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:34</v>
+        <v>2:50</v>
       </c>
       <c r="H19" t="str">
-        <v>Holly Humberstone</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,33 +1115,33 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
+        <v>Rick Astley - Waiting On You (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
+        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>2:50</v>
+        <v>3:51</v>
       </c>
       <c r="H20" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,33 +1153,33 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
+        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Rick Astley - Waiting On You (Official Video)</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
+        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:51</v>
+        <v>2:39</v>
       </c>
       <c r="H21" t="str">
-        <v>Rick Astley</v>
+        <v>Alan Walker and Emyrson Flora</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,33 +1191,33 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
       </c>
       <c r="B22" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
+        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>2:39</v>
+        <v>5:08</v>
       </c>
       <c r="H22" t="str">
-        <v>Alan Walker and Emyrson Flora</v>
+        <v>Jessie J</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,33 +1229,33 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
+        <v>Bishop Briggs - River (10 Years Later)</v>
       </c>
       <c r="B23" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
+        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>5:08</v>
+        <v>3:46</v>
       </c>
       <c r="H23" t="str">
-        <v>Jessie J</v>
+        <v>Bishop Briggs</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,33 +1267,33 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
+        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Bishop Briggs - River (10 Years Later)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
+        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:46</v>
+        <v>2:42</v>
       </c>
       <c r="H24" t="str">
-        <v>Bishop Briggs</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,33 +1305,33 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
       </c>
       <c r="B25" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
+        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>2:42</v>
+        <v>2:31</v>
       </c>
       <c r="H25" t="str">
-        <v>Dean Lewis</v>
+        <v>Chris Janson and Official David Lee Murphy</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,33 +1343,33 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
+        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>2:31</v>
+        <v>3:14</v>
       </c>
       <c r="H26" t="str">
-        <v>Chris Janson and Official David Lee Murphy</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,33 +1381,33 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
+        <v>Allison Russell - Rainbows (Official Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
+        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:14</v>
+        <v>3:22</v>
       </c>
       <c r="H27" t="str">
-        <v>Luke Combs</v>
+        <v>Allison Russell</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,33 +1419,33 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
+        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Allison Russell - Rainbows (Official Video)</v>
+        <v>We Three - Love Who You Love (Official Audio)</v>
       </c>
       <c r="B28" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
+        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:22</v>
+        <v>3:43</v>
       </c>
       <c r="H28" t="str">
-        <v>Allison Russell</v>
+        <v>We Three</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,33 +1457,33 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
+        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>We Three - Love Who You Love (Official Audio)</v>
+        <v>paris jackson - zombies in love</v>
       </c>
       <c r="B29" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
+        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:43</v>
+        <v>2:54</v>
       </c>
       <c r="H29" t="str">
-        <v>We Three</v>
+        <v>paris jackson</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,33 +1495,33 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
+        <v>paris jackson - zombies in love - paris jackson</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>paris jackson - zombies in love</v>
+        <v>Kane Brown - Woman (Official Music Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
+        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:54</v>
+        <v>2:46</v>
       </c>
       <c r="H30" t="str">
-        <v>paris jackson</v>
+        <v>Kane Brown</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,33 +1533,33 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>paris jackson - zombies in love - paris jackson</v>
+        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Kane Brown - Woman (Official Music Video)</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
+        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>2:46</v>
+        <v>3:37</v>
       </c>
       <c r="H31" t="str">
-        <v>Kane Brown</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,33 +1571,33 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
+        <v>Malcolm Todd - Breathe (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
+        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:37</v>
+        <v>2:57</v>
       </c>
       <c r="H32" t="str">
-        <v>Lainey Wilson</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,33 +1609,33 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
+        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Malcolm Todd - Breathe (Official Video)</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay</v>
       </c>
       <c r="B33" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
+        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>2:57</v>
+        <v>3:38</v>
       </c>
       <c r="H33" t="str">
-        <v>Malcolm Todd</v>
+        <v>Carly Pearce and Riley Green</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,33 +1647,33 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay - Carly Pearce and Riley Green</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
       </c>
       <c r="B34" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
+        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:38</v>
+        <v>4:29</v>
       </c>
       <c r="H34" t="str">
-        <v>Carly Pearce and Riley Green</v>
+        <v>Kungs</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,33 +1685,33 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay - Carly Pearce and Riley Green</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
       </c>
       <c r="B35" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
+        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>4:29</v>
+        <v>4:28</v>
       </c>
       <c r="H35" t="str">
-        <v>Kungs</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,33 +1723,33 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
+        <v>aron! - Wonderful Thing (Piano)</v>
       </c>
       <c r="B36" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
+        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>4:28</v>
+        <v>3:26</v>
       </c>
       <c r="H36" t="str">
-        <v>Sunday (1994)</v>
+        <v>aron!</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,33 +1761,33 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
+        <v>aron! - Wonderful Thing (Piano) - aron!</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>aron! - Wonderful Thing (Piano)</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
       </c>
       <c r="B37" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
+        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:26</v>
+        <v>3:51</v>
       </c>
       <c r="H37" t="str">
-        <v>aron!</v>
+        <v>Colinstoughmusic</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,33 +1799,33 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>aron! - Wonderful Thing (Piano) - aron!</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
+        <v>Sunday (1994) - The Fairground</v>
       </c>
       <c r="B38" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
+        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>3:51</v>
+        <v>2:49</v>
       </c>
       <c r="H38" t="str">
-        <v>Colinstoughmusic</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,33 +1837,33 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
+        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Sunday (1994) - The Fairground</v>
+        <v>Owen Riegling - In The Feeling (Visualizer)</v>
       </c>
       <c r="B39" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
+        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>2:49</v>
+        <v>4:16</v>
       </c>
       <c r="H39" t="str">
-        <v>Sunday (1994)</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,33 +1875,33 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
+        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer)</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
+        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>4:16</v>
       </c>
       <c r="H40" t="str">
-        <v>Owen Riegling</v>
+        <v>LANY</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,33 +1913,33 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
+        <v>Maverick Sabre - 8 Stages</v>
       </c>
       <c r="B41" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
+        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>4:16</v>
+        <v>3:25</v>
       </c>
       <c r="H41" t="str">
-        <v>LANY</v>
+        <v>Maverick Sabre</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,33 +1951,33 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
+        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Maverick Sabre - 8 Stages</v>
+        <v>Amanda Jordan - What Else Is New</v>
       </c>
       <c r="B42" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
+        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:25</v>
+        <v>2:50</v>
       </c>
       <c r="H42" t="str">
-        <v>Maverick Sabre</v>
+        <v>Amanda Jordan</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,21 +1989,21 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
+        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Amanda Jordan - What Else Is New</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
       </c>
       <c r="B43" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
+        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2012,10 +2012,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>2:50</v>
+        <v>3:57</v>
       </c>
       <c r="H43" t="str">
-        <v>Amanda Jordan</v>
+        <v>Beabadoobee</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,21 +2027,21 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
       </c>
       <c r="B44" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
+        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2050,10 +2050,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:57</v>
+        <v>3:58</v>
       </c>
       <c r="H44" t="str">
-        <v>Beabadoobee</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,21 +2065,21 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
       </c>
       <c r="B45" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
+        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2088,10 +2088,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:58</v>
+        <v>3:25</v>
       </c>
       <c r="H45" t="str">
-        <v>Spacey Jane</v>
+        <v>Spotify and Zara Larsson</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,33 +2103,33 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B46" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
+        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:25</v>
+        <v>4:09</v>
       </c>
       <c r="H46" t="str">
-        <v>Spotify and Zara Larsson</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,21 +2141,21 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
       </c>
       <c r="B47" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
+        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2164,10 +2164,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>4:09</v>
+        <v>2:08</v>
       </c>
       <c r="H47" t="str">
-        <v>Mei Semones</v>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,33 +2179,33 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
+        <v>Natalie Jane - sabotage (Lyric Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
+        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>2:08</v>
+        <v>2:57</v>
       </c>
       <c r="H48" t="str">
-        <v>The Lemon Twigs</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,33 +2217,33 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
+        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video)</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B49" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
+        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>2:57</v>
+        <v>3:13</v>
       </c>
       <c r="H49" t="str">
-        <v>Natalie Jane</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,21 +2255,21 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B50" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
+        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2278,10 +2278,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:13</v>
+        <v>4:12</v>
       </c>
       <c r="H50" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,21 +2293,21 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
       </c>
       <c r="B51" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
+        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2316,10 +2316,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>4:12</v>
+        <v>3:57</v>
       </c>
       <c r="H51" t="str">
-        <v>David Gilmour</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,33 +2331,33 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
       </c>
       <c r="B52" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
+        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:57</v>
+        <v>3:34</v>
       </c>
       <c r="H52" t="str">
-        <v>Far Caspian</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,33 +2369,33 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
+        <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>9 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
+        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>9 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:34</v>
+        <v>3:48</v>
       </c>
       <c r="H53" t="str">
-        <v>Celine Dion</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,21 +2407,21 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
+        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Harry Styles - American Girls (Official Video)</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B54" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
+        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2430,10 +2430,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:48</v>
+        <v>4:58</v>
       </c>
       <c r="H54" t="str">
-        <v>Harry Styles</v>
+        <v>Warner Records and Morrissey</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,21 +2445,21 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
+        <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B55" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
+        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2468,10 +2468,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>4:58</v>
+        <v>2:33</v>
       </c>
       <c r="H55" t="str">
-        <v>Warner Records and Morrissey</v>
+        <v>Ellise</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,21 +2483,21 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
+        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Ellise - Littlepill (Official Music Video)</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B56" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
+        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2506,10 +2506,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>2:33</v>
+        <v>5:01</v>
       </c>
       <c r="H56" t="str">
-        <v>Ellise</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,21 +2521,21 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
       </c>
       <c r="B57" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
+        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2544,10 +2544,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>5:01</v>
+        <v>4:56</v>
       </c>
       <c r="H57" t="str">
-        <v>The Doobie Brothers</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,21 +2559,21 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
       </c>
       <c r="B58" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
+        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2582,10 +2582,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>4:56</v>
+        <v>2:54</v>
       </c>
       <c r="H58" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,21 +2597,21 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
       </c>
       <c r="B59" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
+        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2620,10 +2620,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>2:54</v>
+        <v>2:46</v>
       </c>
       <c r="H59" t="str">
-        <v>Bebe Rexha</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,21 +2635,21 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
       </c>
       <c r="B60" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
+        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2658,10 +2658,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>2:46</v>
+        <v>2:56</v>
       </c>
       <c r="H60" t="str">
-        <v>NathanEvanss</v>
+        <v>R3HAB</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,33 +2673,33 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
       </c>
       <c r="B61" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
+        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
-        <v>2:56</v>
+        <v>3:21</v>
       </c>
       <c r="H61" t="str">
-        <v>R3HAB</v>
+        <v>War Child UK and Depeche Mode</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,33 +2711,33 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
+        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:21</v>
+        <v>3:16</v>
       </c>
       <c r="H62" t="str">
-        <v>War Child UK and Depeche Mode</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,33 +2749,33 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
       </c>
       <c r="B63" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
+        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:16</v>
+        <v>2:41</v>
       </c>
       <c r="H63" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,33 +2787,33 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
+        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:41</v>
+        <v>2:29</v>
       </c>
       <c r="H64" t="str">
-        <v>Johnny Orlando</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,33 +2825,33 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
       </c>
       <c r="B65" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
+        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
-        <v>2:29</v>
+        <v>2:43</v>
       </c>
       <c r="H65" t="str">
-        <v>Russell Dickerson</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,33 +2863,33 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
+        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
-        <v>2:43</v>
+        <v>3:46</v>
       </c>
       <c r="H66" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,33 +2901,33 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
+        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:46</v>
+        <v>4:01</v>
       </c>
       <c r="H67" t="str">
-        <v>Matt Hansen</v>
+        <v>Mike Posner</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,33 +2939,33 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
+        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>4:01</v>
+        <v>3:23</v>
       </c>
       <c r="H68" t="str">
-        <v>Mike Posner</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,33 +2977,33 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
+        <v>almost monday - leaving is easy (official video)</v>
       </c>
       <c r="B69" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
+        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:23</v>
+        <v>3:39</v>
       </c>
       <c r="H69" t="str">
-        <v>Katelyn Tarver</v>
+        <v>almost monday</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,33 +3015,33 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
+        <v>almost monday - leaving is easy (official video) - almost monday</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>almost monday - leaving is easy (official video)</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
+        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E70" t="str">
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:39</v>
+        <v>3:04</v>
       </c>
       <c r="H70" t="str">
-        <v>almost monday</v>
+        <v>Anne Wilson and Cole Swindell</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,33 +3053,33 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>almost monday - leaving is easy (official video) - almost monday</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
+        <v>vaultboy - DELETED (Official Lyric Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
+        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E71" t="str">
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:04</v>
+        <v>3:25</v>
       </c>
       <c r="H71" t="str">
-        <v>Anne Wilson and Cole Swindell</v>
+        <v>vaultboy</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,33 +3091,33 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
+        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video)</v>
+        <v>The Warning - Kerosene (Official Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
+        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:25</v>
+        <v>3:49</v>
       </c>
       <c r="H72" t="str">
-        <v>vaultboy</v>
+        <v>The Warning</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,33 +3129,33 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
+        <v>The Warning - Kerosene (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>The Warning - Kerosene (Official Video)</v>
+        <v>aron! - Wonderful Thing (City View Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
+        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:49</v>
+        <v>2:14</v>
       </c>
       <c r="H73" t="str">
-        <v>The Warning</v>
+        <v>aron!</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,33 +3167,33 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>The Warning - Kerosene (Official Video) - The Warning</v>
+        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>aron! - Wonderful Thing (City View Video)</v>
+        <v>Bazzi - moment (Official Music Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
+        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>2:14</v>
+        <v>2:43</v>
       </c>
       <c r="H74" t="str">
-        <v>aron!</v>
+        <v>Bazzi</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,21 +3205,21 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
+        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Bazzi - moment (Official Music Video)</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
+        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>2:43</v>
+        <v>4:43</v>
       </c>
       <c r="H75" t="str">
-        <v>Bazzi</v>
+        <v>Sting</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,21 +3243,21 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
+        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>4:43</v>
+        <v>2:44</v>
       </c>
       <c r="H76" t="str">
-        <v>Sting</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,21 +3281,21 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
+        <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
+        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>2:44</v>
+        <v>4:37</v>
       </c>
       <c r="H77" t="str">
-        <v>Dean Lewis</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,21 +3319,21 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
+        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Jessie Ware - Ride (Official Video)</v>
+        <v>Cannons - These Nights (Live at The Fonda)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
+        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>4:37</v>
+        <v>4:52</v>
       </c>
       <c r="H78" t="str">
-        <v>Jessie Ware</v>
+        <v>Cannons</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,21 +3357,21 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
+        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Cannons - These Nights (Live at The Fonda)</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
+        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3380,10 +3380,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>4:52</v>
+        <v>2:13</v>
       </c>
       <c r="H79" t="str">
-        <v>Cannons</v>
+        <v>Kim Petras</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,21 +3395,21 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
+        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>2:13</v>
+        <v>3:19</v>
       </c>
       <c r="H80" t="str">
-        <v>Kim Petras</v>
+        <v>Vanessa Carlton</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,21 +3433,21 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
+        <v>Kiana Ledé - Jury [Official Visualizer]</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
+        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:19</v>
+        <v>2:31</v>
       </c>
       <c r="H81" t="str">
-        <v>Vanessa Carlton</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,21 +3471,21 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
+        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer]</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
+        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>2:31</v>
+        <v>2:43</v>
       </c>
       <c r="H82" t="str">
-        <v>Kiana Ledé</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,21 +3509,21 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
+        <v>Maya Hawke - Devil You Know (Official Audio)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
+        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>2:43</v>
+        <v>3:10</v>
       </c>
       <c r="H83" t="str">
-        <v>Ringo Starr</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,21 +3547,21 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
+        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio)</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
+        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:10</v>
+        <v>3:55</v>
       </c>
       <c r="H84" t="str">
-        <v>Maya Hawke</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,21 +3585,21 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
+        <v>Demi Lovato - Really Don't Care (Live)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
+        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:55</v>
+        <v>3:52</v>
       </c>
       <c r="H85" t="str">
-        <v>Armin van Buuren</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,21 +3623,21 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Demi Lovato - Really Don't Care (Live)</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
+        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:52</v>
+        <v>2:53</v>
       </c>
       <c r="H86" t="str">
-        <v>Demi Lovato</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,21 +3661,21 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
+        <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
+        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:53</v>
+        <v>4:30</v>
       </c>
       <c r="H87" t="str">
-        <v>Peter Gabriel</v>
+        <v>Jessie J</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,21 +3699,21 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video)</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
+        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>4:30</v>
+        <v>5:18</v>
       </c>
       <c r="H88" t="str">
-        <v>Jessie J</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,21 +3737,21 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
+        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3760,10 +3760,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>5:18</v>
+        <v>7:20</v>
       </c>
       <c r="H89" t="str">
-        <v>Harry Styles</v>
+        <v>Mark Ronson and BRITs</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,21 +3775,21 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
+        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3798,10 +3798,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>7:20</v>
+        <v>3:01</v>
       </c>
       <c r="H90" t="str">
-        <v>Mark Ronson and BRITs</v>
+        <v>BRITs</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,21 +3813,21 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
+        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3836,10 +3836,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:01</v>
+        <v>3:31</v>
       </c>
       <c r="H91" t="str">
-        <v>BRITs</v>
+        <v>Olivia Dean and BRITs</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,21 +3851,21 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
+        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3874,10 +3874,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:31</v>
+        <v>3:00</v>
       </c>
       <c r="H92" t="str">
-        <v>Olivia Dean and BRITs</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,21 +3889,21 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
+        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3912,10 +3912,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:00</v>
+        <v>3:11</v>
       </c>
       <c r="H93" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,21 +3927,21 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
+        <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
+        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3950,10 +3950,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:11</v>
+        <v>3:32</v>
       </c>
       <c r="H94" t="str">
-        <v>The Kiffness</v>
+        <v>Lauv</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,21 +3965,21 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
+        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Lauv - “insecure” (Official Audio)</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
+        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -3988,10 +3988,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:32</v>
+        <v>5:03</v>
       </c>
       <c r="H95" t="str">
-        <v>Lauv</v>
+        <v>RAYE</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,21 +4003,21 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
+        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4026,10 +4026,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>5:03</v>
+        <v>4:50</v>
       </c>
       <c r="H96" t="str">
-        <v>RAYE</v>
+        <v>Armik</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,21 +4041,21 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
+        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4064,10 +4064,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>4:50</v>
+        <v>4:53</v>
       </c>
       <c r="H97" t="str">
-        <v>Armik</v>
+        <v>Scorpions</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,21 +4079,21 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
+        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4102,10 +4102,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>4:53</v>
+        <v>3:04</v>
       </c>
       <c r="H98" t="str">
-        <v>Scorpions</v>
+        <v>Cat Music and 3 more</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,21 +4117,21 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
+        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4140,10 +4140,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:04</v>
+        <v>4:32</v>
       </c>
       <c r="H99" t="str">
-        <v>Cat Music and 3 more</v>
+        <v>MercyMe and 3 more</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,21 +4155,21 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
+        <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
+        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4178,10 +4178,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>4:32</v>
+        <v>3:47</v>
       </c>
       <c r="H100" t="str">
-        <v>MercyMe and 3 more</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,21 +4193,21 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
+        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video)</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
+        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4216,10 +4216,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:47</v>
+        <v>3:40</v>
       </c>
       <c r="H101" t="str">
-        <v>Girl Tones</v>
+        <v>Jessie Ware and empik</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,539 +4231,539 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Pongo</v>
+        <v>SWIM</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/pongo/1882157609</v>
+        <v>https://music.apple.com/us/song/swim/1868862384</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E102" t="str">
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Pongo - Single</v>
+        <v>ARIRANG</v>
       </c>
       <c r="G102" t="str">
-        <v>3:09</v>
+        <v>2:39</v>
       </c>
       <c r="H102" t="str">
-        <v>Rvssian</v>
+        <v>BTS</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/rvssian/628716915</v>
+        <v>https://music.apple.com/us/artist/bts/883131348</v>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/pongo/1882157603</v>
+        <v>https://music.apple.com/us/album/swim/1868862375</v>
       </c>
       <c r="L102" t="str">
-        <v>Pongo - Rvssian</v>
+        <v>SWIM - BTS</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Porch Light</v>
+        <v>Click Clack Symphony. (feat. Hans Zimmer)</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/porch-light/1872239892</v>
+        <v>https://music.apple.com/us/song/click-clack-symphony-feat-hans-zimmer/1871085694</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E103" t="str">
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>The Great Divide</v>
+        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
       </c>
       <c r="G103" t="str">
-        <v>4:22</v>
+        <v>5:01</v>
       </c>
       <c r="H103" t="str">
-        <v>Noah Kahan</v>
+        <v>RAYE</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
+        <v>https://music.apple.com/us/artist/raye/261686</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/porch-light/1872239868</v>
+        <v>https://music.apple.com/us/album/click-clack-symphony-feat-hans-zimmer/1871085677</v>
       </c>
       <c r="L103" t="str">
-        <v>Porch Light - Noah Kahan</v>
+        <v>Click Clack Symphony. (feat. Hans Zimmer) - RAYE</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Dry Spell</v>
+        <v>Loving Life Again</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/dry-spell/1883177258</v>
+        <v>https://music.apple.com/us/song/loving-life-again/1869436847</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E104" t="str">
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Middle of Nowhere</v>
+        <v>Dandelion</v>
       </c>
       <c r="G104" t="str">
-        <v>3:17</v>
+        <v>3:46</v>
       </c>
       <c r="H104" t="str">
-        <v>Kacey Musgraves</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/dry-spell/1883176984</v>
+        <v>https://music.apple.com/us/album/loving-life-again/1869436835</v>
       </c>
       <c r="L104" t="str">
-        <v>Dry Spell - Kacey Musgraves</v>
+        <v>Loving Life Again - Ella Langley</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Distance</v>
+        <v>Rethink Some Things</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/distance/1882713727</v>
+        <v>https://music.apple.com/us/song/rethink-some-things/1862634795</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E105" t="str">
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Distance - Single</v>
+        <v>The Way I Am</v>
       </c>
       <c r="G105" t="str">
-        <v>3:14</v>
+        <v>2:45</v>
       </c>
       <c r="H105" t="str">
-        <v>Finn Askew</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/finn-askew/1292169978</v>
+        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/distance/1882713721</v>
+        <v>https://music.apple.com/us/album/rethink-some-things/1862634688</v>
       </c>
       <c r="L105" t="str">
-        <v>Distance - Finn Askew</v>
+        <v>Rethink Some Things - Luke Combs</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>The Visitor</v>
+        <v>TRANKAITO</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/the-visitor/1882146993</v>
+        <v>https://music.apple.com/us/song/trankaito/1886206698</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E106" t="str">
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>The Visitor - Single</v>
+        <v>EL GREEN PRINT: La Saga (Disc 1) — FEID VS FERXXO</v>
       </c>
       <c r="G106" t="str">
-        <v>3:48</v>
+        <v>2:42</v>
       </c>
       <c r="H106" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Feid</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
+        <v>https://music.apple.com/us/artist/feid/194502100</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/the-visitor/1882146992</v>
+        <v>https://music.apple.com/us/album/trankaito/1886206566</v>
       </c>
       <c r="L106" t="str">
-        <v>The Visitor - SIENNA SPIRO</v>
+        <v>TRANKAITO - Feid</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>I Ain't No Cowboy</v>
+        <v>Leak It</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/i-aint-no-cowboy/1862634799</v>
+        <v>https://music.apple.com/us/song/leak-it/1881685399</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E107" t="str">
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>The Way I Am</v>
+        <v>Leak It - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>3:13</v>
+        <v>3:03</v>
       </c>
       <c r="H107" t="str">
-        <v>Luke Combs</v>
+        <v>FLO</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
+        <v>https://music.apple.com/us/artist/flo/1615611716</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/i-aint-no-cowboy/1862634688</v>
+        <v>https://music.apple.com/us/album/leak-it/1881685398</v>
       </c>
       <c r="L107" t="str">
-        <v>I Ain't No Cowboy - Luke Combs</v>
+        <v>Leak It - FLO</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Can't Sit Still</v>
+        <v>LUVAGIRL</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/cant-sit-still/1878782917</v>
+        <v>https://music.apple.com/us/song/luvagirl/1882867562</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E108" t="str">
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Can't Sit Still - Single</v>
+        <v>LUVAGIRL - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>3:35</v>
+        <v>2:40</v>
       </c>
       <c r="H108" t="str">
-        <v>Lainey Wilson</v>
+        <v>Coco Jones</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
+        <v>https://music.apple.com/us/artist/coco-jones/401400095</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/cant-sit-still/1878782913</v>
+        <v>https://music.apple.com/us/album/luvagirl/1882867560</v>
       </c>
       <c r="L108" t="str">
-        <v>Can't Sit Still - Lainey Wilson</v>
+        <v>LUVAGIRL - Coco Jones</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>All I Did Was Dream of You (feat. The Marías)</v>
+        <v>D33P3R</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245797</v>
+        <v>https://music.apple.com/us/song/d33p3r/1876874356</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E109" t="str">
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>All I Did Was Dream of You (feat. The Marías) - Single</v>
+        <v>R3SET</v>
       </c>
       <c r="G109" t="str">
-        <v>3:43</v>
+        <v>3:25</v>
       </c>
       <c r="H109" t="str">
-        <v>beabadoobee</v>
+        <v>Mike WiLL Made-It</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/beabadoobee/1307650474</v>
+        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245651</v>
+        <v>https://music.apple.com/us/album/d33p3r/1876874349</v>
       </c>
       <c r="L109" t="str">
-        <v>All I Did Was Dream of You (feat. The Marías) - beabadoobee</v>
+        <v>D33P3R - Mike WiLL Made-It</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Blow My Mind</v>
+        <v>Let King Tonka Talk</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/blow-my-mind/1852752616</v>
+        <v>https://music.apple.com/us/song/let-king-tonka-talk/1886559004</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E110" t="str">
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Sexistential</v>
+        <v>Let King Tonka Talk - Single</v>
       </c>
       <c r="G110" t="str">
-        <v>2:57</v>
+        <v>3:01</v>
       </c>
       <c r="H110" t="str">
-        <v>Robyn</v>
+        <v>Yeat</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/blow-my-mind/1852752613</v>
+        <v>https://music.apple.com/us/album/let-king-tonka-talk/1886559003</v>
       </c>
       <c r="L110" t="str">
-        <v>Blow My Mind - Robyn</v>
+        <v>Let King Tonka Talk - Yeat</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>SATA</v>
+        <v>Don't Hate Me</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/sata/1874015489</v>
+        <v>https://music.apple.com/us/song/dont-hate-me/1886125791</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E111" t="str">
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>CTRL ESCAPE</v>
+        <v>Don't Hate Me - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>3:02</v>
+        <v>3:09</v>
       </c>
       <c r="H111" t="str">
-        <v>John Summit</v>
+        <v>Miles Caton</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/miles-caton/1674606130</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/sata/1874015470</v>
+        <v>https://music.apple.com/us/album/dont-hate-me/1886125790</v>
       </c>
       <c r="L111" t="str">
-        <v>SATA - John Summit</v>
+        <v>Don't Hate Me - Miles Caton</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Una Aventura</v>
+        <v>Pongo</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/una-aventura/1882069505</v>
+        <v>https://music.apple.com/us/song/pongo/1882157609</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E112" t="str">
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Una Aventura - Single</v>
+        <v>Pongo - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>3:00</v>
+        <v>3:09</v>
       </c>
       <c r="H112" t="str">
-        <v>Ozuna</v>
+        <v>Rvssian</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/ozuna/283578837</v>
+        <v>https://music.apple.com/us/artist/rvssian/628716915</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/una-aventura/1882068957</v>
+        <v>https://music.apple.com/us/album/pongo/1882157603</v>
       </c>
       <c r="L112" t="str">
-        <v>Una Aventura - Ozuna</v>
+        <v>Pongo - Rvssian</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Ocean In The Desert</v>
+        <v>BOTERO</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
+        <v>https://music.apple.com/us/song/botero/1884672859</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E113" t="str">
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Ocean In The Desert - Single</v>
+        <v>BOTERO - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>3:44</v>
+        <v>4:14</v>
       </c>
       <c r="H113" t="str">
-        <v>Dionne Warwick</v>
+        <v>Maluma</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/dionne-warwick/16198</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/ocean-in-the-desert/1878421568</v>
+        <v>https://music.apple.com/us/album/botero/1884672851</v>
       </c>
       <c r="L113" t="str">
-        <v>Ocean In The Desert - Dionne Warwick</v>
+        <v>BOTERO - Maluma</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Home (feat. Hikaru Utada)</v>
+        <v>Distance</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/home-feat-hikaru-utada/1845190340</v>
+        <v>https://music.apple.com/us/song/distance/1882713727</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E114" t="str">
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Whatever's Clever!</v>
+        <v>Distance - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>3:44</v>
+        <v>3:14</v>
       </c>
       <c r="H114" t="str">
-        <v>Charlie Puth</v>
+        <v>Finn Askew</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v>https://music.apple.com/us/artist/finn-askew/1292169978</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/home-feat-hikaru-utada/1845189970</v>
+        <v>https://music.apple.com/us/album/distance/1882713721</v>
       </c>
       <c r="L114" t="str">
-        <v>Home (feat. Hikaru Utada) - Charlie Puth</v>
+        <v>Distance - Finn Askew</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>dirty wedding dress</v>
+        <v>Ocean In The Desert</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/dirty-wedding-dress/1872842320</v>
+        <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E115" t="str">
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>everyone for ten minutes</v>
+        <v>Ocean In The Desert - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>4:49</v>
+        <v>3:44</v>
       </c>
       <c r="H115" t="str">
-        <v>Bleachers</v>
+        <v>Dionne Warwick</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/dionne-warwick/16198</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/dirty-wedding-dress/1872842313</v>
+        <v>https://music.apple.com/us/album/ocean-in-the-desert/1878421568</v>
       </c>
       <c r="L115" t="str">
-        <v>dirty wedding dress - Bleachers</v>
+        <v>Ocean In The Desert - Dionne Warwick</v>
       </c>
     </row>
     <row r="116">
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/riptides/1878362645</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4806,3275 +4806,3237 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Fastest Gun Alive</v>
+        <v>2.0</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/fastest-gun-alive/1874700373</v>
+        <v>https://music.apple.com/us/song/2-0/1868862380</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E117" t="str">
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Age of the Ram</v>
+        <v>ARIRANG</v>
       </c>
       <c r="G117" t="str">
-        <v>3:07</v>
+        <v>2:49</v>
       </c>
       <c r="H117" t="str">
-        <v>Charley Crockett</v>
+        <v>BTS</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
+        <v>https://music.apple.com/us/artist/bts/883131348</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/fastest-gun-alive/1874700242</v>
+        <v>https://music.apple.com/us/album/2-0/1868862375</v>
       </c>
       <c r="L117" t="str">
-        <v>Fastest Gun Alive - Charley Crockett</v>
+        <v>2.0 - BTS</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>IMPOSIBLE</v>
+        <v>6IXER PARTY</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/imposible/1880775726</v>
+        <v>https://music.apple.com/us/song/6ixer-party/1880492403</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E118" t="str">
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>IMPOSIBLE - Single</v>
+        <v>6WA</v>
       </c>
       <c r="G118" t="str">
-        <v>3:13</v>
+        <v>3:08</v>
       </c>
       <c r="H118" t="str">
-        <v>Grupo Frontera</v>
+        <v>BigXthaPlug</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
+        <v>https://music.apple.com/us/artist/bigxthaplug/1482508209</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/imposible/1880775721</v>
+        <v>https://music.apple.com/us/album/6ixer-party/1880492397</v>
       </c>
       <c r="L118" t="str">
-        <v>IMPOSIBLE - Grupo Frontera</v>
+        <v>6IXER PARTY - BigXthaPlug</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Trade Places</v>
+        <v>Highest</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/trade-places/1878823464</v>
+        <v>https://music.apple.com/us/song/highest/1882162060</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E119" t="str">
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Monica</v>
+        <v>Detour</v>
       </c>
       <c r="G119" t="str">
-        <v>3:02</v>
+        <v>2:56</v>
       </c>
       <c r="H119" t="str">
-        <v>Jack Harlow</v>
+        <v>Samara Cyn</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/jack-harlow/1047679432</v>
+        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/trade-places/1878823462</v>
+        <v>https://music.apple.com/us/album/highest/1882161774</v>
       </c>
       <c r="L119" t="str">
-        <v>Trade Places - Jack Harlow</v>
+        <v>Highest - Samara Cyn</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Motion Party</v>
+        <v>Better Than Yours (feat. YoungBoy Never Broke Again)</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/motion-party/1882152039</v>
+        <v>https://music.apple.com/us/song/better-than-yours-feat-youngboy-never-broke-again/1885598075</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E120" t="str">
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Motion Party - Single</v>
+        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>1:35</v>
+        <v>2:40</v>
       </c>
       <c r="H120" t="str">
-        <v>Bossman Dlow</v>
+        <v>Coi Leray</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
+        <v>https://music.apple.com/us/artist/coi-leray/1358539712</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/motion-party/1882151996</v>
+        <v>https://music.apple.com/us/album/better-than-yours-feat-youngboy-never-broke-again/1885597834</v>
       </c>
       <c r="L120" t="str">
-        <v>Motion Party - Bossman Dlow</v>
+        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Coi Leray</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Woman</v>
+        <v>So What</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/woman/1882549709</v>
+        <v>https://music.apple.com/us/song/so-what/1870703328</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E121" t="str">
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Woman - Single</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G121" t="str">
-        <v>2:46</v>
+        <v>4:31</v>
       </c>
       <c r="H121" t="str">
-        <v>Kane Brown</v>
+        <v>MUNA</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/kane-brown/930928857</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/woman/1882549705</v>
+        <v>https://music.apple.com/us/album/so-what/1870702692</v>
       </c>
       <c r="L121" t="str">
-        <v>Woman - Kane Brown</v>
+        <v>So What - MUNA</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Sunburn</v>
+        <v>Girl of Your Dreams (Live at Apple Music Radio)</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/sunburn/1880836041</v>
+        <v>https://music.apple.com/us/song/girl-of-your-dreams-live-at-apple-music-radio/1886190880</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E122" t="str">
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Sunburn - Single</v>
+        <v>Live at Apple Music Radio</v>
       </c>
       <c r="G122" t="str">
-        <v>3:05</v>
+        <v>3:12</v>
       </c>
       <c r="H122" t="str">
-        <v>Tucker Wetmore</v>
+        <v>Eli</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/tucker-wetmore/1486724646</v>
+        <v>https://music.apple.com/us/artist/eli/1802895652</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/sunburn/1880835818</v>
+        <v>https://music.apple.com/us/album/girl-of-your-dreams-live-at-apple-music-radio/1886190879</v>
       </c>
       <c r="L122" t="str">
-        <v>Sunburn - Tucker Wetmore</v>
+        <v>Girl of Your Dreams (Live at Apple Music Radio) - Eli</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Que Te Costó</v>
+        <v>Running To Pain</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/que-te-cost%C3%B3/1882108997</v>
+        <v>https://music.apple.com/us/song/running-to-pain/1876521161</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E123" t="str">
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Metamorfosis</v>
+        <v>So Help Me God</v>
       </c>
       <c r="G123" t="str">
-        <v>2:54</v>
+        <v>4:06</v>
       </c>
       <c r="H123" t="str">
-        <v>Yahritza Y Su Esencia</v>
+        <v>Kelsey Lu</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
+        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/que-te-cost%C3%B3/1882108989</v>
+        <v>https://music.apple.com/us/album/running-to-pain/1876521144</v>
       </c>
       <c r="L123" t="str">
-        <v>Que Te Costó - Yahritza Y Su Esencia</v>
+        <v>Running To Pain - Kelsey Lu</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>oooshxt!</v>
+        <v>Pinterest (Spanish)</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/oooshxt/1879612533</v>
+        <v>https://music.apple.com/us/song/pinterest-spanish/1885472606</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E124" t="str">
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>oooshxt! - Single</v>
+        <v>Pinterest (Spanish) - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>2:15</v>
+        <v>2:14</v>
       </c>
       <c r="H124" t="str">
-        <v>Samara Cyn</v>
+        <v>Anitta</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
+        <v>https://music.apple.com/us/artist/anitta/597214610</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/oooshxt/1879612532</v>
+        <v>https://music.apple.com/us/album/pinterest-spanish/1885472605</v>
       </c>
       <c r="L124" t="str">
-        <v>oooshxt! - Samara Cyn</v>
+        <v>Pinterest (Spanish) - Anitta</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Cruel World</v>
+        <v>Business &amp; Personal (Intro)</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/cruel-world/1859630041</v>
+        <v>https://music.apple.com/us/song/business-personal-intro/1886539096</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E125" t="str">
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Cruel World</v>
+        <v>Big Mama</v>
       </c>
       <c r="G125" t="str">
-        <v>3:26</v>
+        <v>4:20</v>
       </c>
       <c r="H125" t="str">
-        <v>Holly Humberstone</v>
+        <v>Latto</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/latto/419799506</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/cruel-world/1859629846</v>
+        <v>https://music.apple.com/us/album/business-personal-intro/1886538932</v>
       </c>
       <c r="L125" t="str">
-        <v>Cruel World - Holly Humberstone</v>
+        <v>Business &amp; Personal (Intro) - Latto</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Star</v>
+        <v>Bird Flu</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/star/1876633306</v>
+        <v>https://music.apple.com/us/song/bird-flu/1884792159</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E126" t="str">
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Star - Single</v>
+        <v>Love is the New Gangsta</v>
       </c>
       <c r="G126" t="str">
-        <v>3:25</v>
+        <v>2:58</v>
       </c>
       <c r="H126" t="str">
-        <v>Iceage</v>
+        <v>6LACK</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/star/1876633303</v>
+        <v>https://music.apple.com/us/album/bird-flu/1884792154</v>
       </c>
       <c r="L126" t="str">
-        <v>Star - Iceage</v>
+        <v>Bird Flu - 6LACK</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Get Go</v>
+        <v>Lighter</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/get-go/1862570884</v>
+        <v>https://music.apple.com/us/song/lighter/1884704638</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E127" t="str">
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Ambiguous Desire</v>
+        <v>Lighter (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:22</v>
+        <v>2:59</v>
       </c>
       <c r="H127" t="str">
-        <v>Arlo Parks</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/get-go/1862570378</v>
+        <v>https://music.apple.com/us/album/lighter/1884704631</v>
       </c>
       <c r="L127" t="str">
-        <v>Get Go - Arlo Parks</v>
+        <v>Lighter - Jelly Roll</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>ThunderWave</v>
+        <v>Wide Awake</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/thunderwave/1861531685</v>
+        <v>https://music.apple.com/us/song/wide-awake/1881700925</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E128" t="str">
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Distracted</v>
+        <v>Wide Awake - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>3:14</v>
+        <v>4:16</v>
       </c>
       <c r="H128" t="str">
-        <v>Thundercat</v>
+        <v>Chris Stussy</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
+        <v>https://music.apple.com/us/artist/chris-stussy/746159191</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/thunderwave/1861531667</v>
+        <v>https://music.apple.com/us/album/wide-awake/1881700618</v>
       </c>
       <c r="L128" t="str">
-        <v>ThunderWave - Thundercat</v>
+        <v>Wide Awake - Chris Stussy</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Club Song</v>
+        <v>Don’t Make Me Love U</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/club-song/1882478246</v>
+        <v>https://music.apple.com/us/song/dont-make-me-love-u/1885895137</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E129" t="str">
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Club Song - Single</v>
+        <v>Don’t Make Me Love U - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>2:27</v>
+        <v>3:25</v>
       </c>
       <c r="H129" t="str">
-        <v>The Pussycat Dolls</v>
+        <v>Lizzo</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/the-pussycat-dolls/23331509</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/club-song/1882478243</v>
+        <v>https://music.apple.com/us/album/dont-make-me-love-u/1885895026</v>
       </c>
       <c r="L129" t="str">
-        <v>Club Song - The Pussycat Dolls</v>
+        <v>Don’t Make Me Love U - Lizzo</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Better Man</v>
+        <v>Dinner Party</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/better-man/1880496044</v>
+        <v>https://music.apple.com/us/song/dinner-party/1884418570</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E130" t="str">
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Better Man - Single</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G130" t="str">
-        <v>2:53</v>
+        <v>2:34</v>
       </c>
       <c r="H130" t="str">
-        <v>jxdn</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/jxdn/1513237359</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/better-man/1880496042</v>
+        <v>https://music.apple.com/us/album/dinner-party/1884418567</v>
       </c>
       <c r="L130" t="str">
-        <v>Better Man - jxdn</v>
+        <v>Dinner Party - Niall Horan</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>sabotage</v>
+        <v>NORMAL</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/sabotage/1882209853</v>
+        <v>https://music.apple.com/us/song/normal/1868862387</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E131" t="str">
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>sabotage - Single</v>
+        <v>ARIRANG</v>
       </c>
       <c r="G131" t="str">
-        <v>2:58</v>
+        <v>3:01</v>
       </c>
       <c r="H131" t="str">
-        <v>Natalie Jane</v>
+        <v>BTS</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/natalie-jane/1504380197</v>
+        <v>https://music.apple.com/us/artist/bts/883131348</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/sabotage/1882209670</v>
+        <v>https://music.apple.com/us/album/normal/1868862375</v>
       </c>
       <c r="L131" t="str">
-        <v>sabotage - Natalie Jane</v>
+        <v>NORMAL - BTS</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>2000s Pop Punk Rnb</v>
+        <v>Die Living</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/2000s-pop-punk-rnb/1878820143</v>
+        <v>https://music.apple.com/us/song/die-living/1884752889</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E132" t="str">
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Still Loiteringgg / 2000s Pop Punk Rnb - Single</v>
+        <v>Die Living - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>2:56</v>
+        <v>2:50</v>
       </c>
       <c r="H132" t="str">
-        <v>WHATMORE</v>
+        <v>ILLENIUM</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/whatmore/1797119133</v>
+        <v>https://music.apple.com/us/artist/illenium/645420096</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/2000s-pop-punk-rnb/1878820131</v>
+        <v>https://music.apple.com/us/album/die-living/1884752887</v>
       </c>
       <c r="L132" t="str">
-        <v>2000s Pop Punk Rnb - WHATMORE</v>
+        <v>Die Living - ILLENIUM</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Naked</v>
+        <v>Heaven On Earth</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/naked/1883802157</v>
+        <v>https://music.apple.com/us/song/heaven-on-earth/1882808097</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E133" t="str">
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Naked - Single</v>
+        <v>Heaven On Earth - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>3:39</v>
+        <v>2:59</v>
       </c>
       <c r="H133" t="str">
-        <v>Kenya Grace</v>
+        <v>Pentatonix</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
+        <v>https://music.apple.com/us/artist/pentatonix/466047278</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/naked/1883801913</v>
+        <v>https://music.apple.com/us/album/heaven-on-earth/1882808095</v>
       </c>
       <c r="L133" t="str">
-        <v>Naked - Kenya Grace</v>
+        <v>Heaven On Earth - Pentatonix</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Catharina</v>
+        <v>an apple a day</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/catharina/1880130477</v>
+        <v>https://music.apple.com/us/song/an-apple-a-day/1885590382</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E134" t="str">
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Catharina - Single</v>
+        <v>an apple a day - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>3:27</v>
+        <v>5:16</v>
       </c>
       <c r="H134" t="str">
-        <v>Martin Garrix</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/catharina/1880130476</v>
+        <v>https://music.apple.com/us/album/an-apple-a-day/1885590042</v>
       </c>
       <c r="L134" t="str">
-        <v>Catharina - Martin Garrix</v>
+        <v>an apple a day - horsegiirL</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Through The Pain (feat. Pozer)</v>
+        <v>OUT LATE.</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/through-the-pain-feat-pozer/1877868063</v>
+        <v>https://music.apple.com/us/song/out-late/1884478039</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E135" t="str">
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Through The Pain (feat. Pozer) - Single</v>
+        <v>OUT LATE. - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:00</v>
+        <v>2:09</v>
       </c>
       <c r="H135" t="str">
-        <v>Chase &amp; Status</v>
+        <v>Loud Luxury</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/chase-status/121546679</v>
+        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/through-the-pain-feat-pozer/1877868059</v>
+        <v>https://music.apple.com/us/album/out-late/1884478038</v>
       </c>
       <c r="L135" t="str">
-        <v>Through The Pain (feat. Pozer) - Chase &amp; Status</v>
+        <v>OUT LATE. - Loud Luxury</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Trying Times</v>
+        <v>Be With You</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/trying-times/1862353792</v>
+        <v>https://music.apple.com/us/song/be-with-you/1885607727</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E136" t="str">
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Trying Times</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G136" t="str">
-        <v>4:33</v>
+        <v>3:35</v>
       </c>
       <c r="H136" t="str">
-        <v>James Blake</v>
+        <v>Muse</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/trying-times/1862353780</v>
+        <v>https://music.apple.com/us/album/be-with-you/1885607338</v>
       </c>
       <c r="L136" t="str">
-        <v>Trying Times - James Blake</v>
+        <v>Be With You - Muse</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>595</v>
+        <v>Caught In The Echo</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/595/1880470541</v>
+        <v>https://music.apple.com/us/song/caught-in-the-echo/1877913491</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E137" t="str">
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Be Sweet To Me</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="G137" t="str">
-        <v>2:29</v>
+        <v>4:02</v>
       </c>
       <c r="H137" t="str">
-        <v>Violet Grohl</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/595/1880470537</v>
+        <v>https://music.apple.com/us/album/caught-in-the-echo/1877913489</v>
       </c>
       <c r="L137" t="str">
-        <v>595 - Violet Grohl</v>
+        <v>Caught In The Echo - Foo Fighters</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>When Did You Stop Loving Me?</v>
+        <v>Little by Little</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/when-did-you-stop-loving-me/1879593803</v>
+        <v>https://music.apple.com/us/song/little-by-little/1879889876</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E138" t="str">
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Soft 2</v>
+        <v>Little by Little - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>3:50</v>
+        <v>2:34</v>
       </c>
       <c r="H138" t="str">
-        <v>LANY</v>
+        <v>Mon Rovîa</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/lany/867853783</v>
+        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/when-did-you-stop-loving-me/1879593289</v>
+        <v>https://music.apple.com/us/album/little-by-little/1879889873</v>
       </c>
       <c r="L138" t="str">
-        <v>When Did You Stop Loving Me? - LANY</v>
+        <v>Little by Little - Mon Rovîa</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>CALL ME</v>
+        <v>Montgomery County</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/call-me/1882521075</v>
+        <v>https://music.apple.com/us/song/montgomery-county/1862624758</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E139" t="str">
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>CALL ME - Single</v>
+        <v>Parker McCollum (The Deluxe Edition)</v>
       </c>
       <c r="G139" t="str">
-        <v>2:10</v>
+        <v>3:28</v>
       </c>
       <c r="H139" t="str">
-        <v>ALTÉGO</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/alt%C3%A9go/1606418899</v>
+        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/call-me/1882521073</v>
+        <v>https://music.apple.com/us/album/montgomery-county/1862624506</v>
       </c>
       <c r="L139" t="str">
-        <v>CALL ME - ALTÉGO</v>
+        <v>Montgomery County - Parker McCollum</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Mi Amor</v>
+        <v>Dive Into Me</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/mi-amor/1872454951</v>
+        <v>https://music.apple.com/us/song/dive-into-me/1879790158</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E140" t="str">
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Free (Deluxe)</v>
+        <v>Dive Into Me - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>2:00</v>
+        <v>2:46</v>
       </c>
       <c r="H140" t="str">
-        <v>Nasty C</v>
+        <v>Alok</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
+        <v>https://music.apple.com/us/artist/alok/324709167</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/mi-amor/1872454582</v>
+        <v>https://music.apple.com/us/album/dive-into-me/1879789970</v>
       </c>
       <c r="L140" t="str">
-        <v>Mi Amor - Nasty C</v>
+        <v>Dive Into Me - Alok</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>BOBA</v>
+        <v>more than just a little bit</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/boba/1880372256</v>
+        <v>https://music.apple.com/us/song/more-than-just-a-little-bit/1878764653</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E141" t="str">
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>BOBA - Single</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G141" t="str">
-        <v>3:00</v>
+        <v>2:40</v>
       </c>
       <c r="H141" t="str">
-        <v>SOFI TUKKER</v>
+        <v>Artemas</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/boba/1880372250</v>
+        <v>https://music.apple.com/us/album/more-than-just-a-little-bit/1878764647</v>
       </c>
       <c r="L141" t="str">
-        <v>BOBA - SOFI TUKKER</v>
+        <v>more than just a little bit - Artemas</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Video Shoot</v>
+        <v>WORSHIP</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/video-shoot/1882892621</v>
+        <v>https://music.apple.com/us/song/worship/1882144650</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E142" t="str">
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Skeletor</v>
+        <v>WORSHIP - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>2:38</v>
+        <v>2:43</v>
       </c>
       <c r="H142" t="str">
-        <v>Chief Keef</v>
+        <v>Asake</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
+        <v>https://music.apple.com/us/artist/asake/1436064480</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/video-shoot/1882892614</v>
+        <v>https://music.apple.com/us/album/worship/1882144646</v>
       </c>
       <c r="L142" t="str">
-        <v>Video Shoot - Chief Keef</v>
+        <v>WORSHIP - Asake</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Talk To Me Nuh</v>
+        <v>Honest</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/talk-to-me-nuh/1882510363</v>
+        <v>https://music.apple.com/us/song/honest/1884124206</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E143" t="str">
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Talk To Me Nuh - Single</v>
+        <v>Honest - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>2:06</v>
+        <v>3:22</v>
       </c>
       <c r="H143" t="str">
-        <v>Shenseea</v>
+        <v>Ebony Riley</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/shenseea/1132311326</v>
+        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/talk-to-me-nuh/1882510361</v>
+        <v>https://music.apple.com/us/album/honest/1884124203</v>
       </c>
       <c r="L143" t="str">
-        <v>Talk To Me Nuh - Shenseea</v>
+        <v>Honest - Ebony Riley</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Just Believe</v>
+        <v>6ft Under</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/just-believe/1884083105</v>
+        <v>https://music.apple.com/us/song/6ft-under/1880796117</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E144" t="str">
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Just Believe - Single</v>
+        <v>6ft Under - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>2:41</v>
+        <v>3:30</v>
       </c>
       <c r="H144" t="str">
-        <v>Bailey Zimmerman</v>
+        <v>KELS</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
+        <v>https://music.apple.com/us/artist/kels/1536970454</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/just-believe/1884083104</v>
+        <v>https://music.apple.com/us/album/6ft-under/1880796111</v>
       </c>
       <c r="L144" t="str">
-        <v>Just Believe - Bailey Zimmerman</v>
+        <v>6ft Under - KELS</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Knife In The Heart</v>
+        <v>Maybe Again</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/knife-in-the-heart/1857952500</v>
+        <v>https://music.apple.com/us/song/maybe-again/1875112466</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E145" t="str">
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>The Afterparty</v>
+        <v>When The City Sleeps</v>
       </c>
       <c r="G145" t="str">
-        <v>2:57</v>
+        <v>3:29</v>
       </c>
       <c r="H145" t="str">
-        <v>Lykke Li</v>
+        <v>Alex Isley</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
+        <v>https://music.apple.com/us/artist/alex-isley/566610959</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/knife-in-the-heart/1857952252</v>
+        <v>https://music.apple.com/us/album/maybe-again/1875112024</v>
       </c>
       <c r="L145" t="str">
-        <v>Knife In The Heart - Lykke Li</v>
+        <v>Maybe Again - Alex Isley</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>The Way We Touch</v>
+        <v>Trigger Happy</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/the-way-we-touch/1875315428</v>
+        <v>https://music.apple.com/us/song/trigger-happy/1883215750</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E146" t="str">
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>The Way We Touch - Single</v>
+        <v>Attachment Theory</v>
       </c>
       <c r="G146" t="str">
-        <v>3:09</v>
+        <v>3:01</v>
       </c>
       <c r="H146" t="str">
-        <v>Charlotte Cardin</v>
+        <v>Aubrie Sellers</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-cardin/784665014</v>
+        <v>https://music.apple.com/us/artist/aubrie-sellers/1039090991</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/the-way-we-touch/1875315210</v>
+        <v>https://music.apple.com/us/album/trigger-happy/1883215748</v>
       </c>
       <c r="L146" t="str">
-        <v>The Way We Touch - Charlotte Cardin</v>
+        <v>Trigger Happy - Aubrie Sellers</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>DANGEROUS</v>
+        <v>REAL ONES NEVER DIE</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/dangerous/1867202642</v>
+        <v>https://music.apple.com/us/song/real-ones-never-die/1886092613</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E147" t="str">
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>NIGHTS AFTER VAMP</v>
+        <v>HAVE U BN 2 HEAVEN @ NITE? - EP</v>
       </c>
       <c r="G147" t="str">
-        <v>4:06</v>
+        <v>3:01</v>
       </c>
       <c r="H147" t="str">
-        <v>Magnolia Park</v>
+        <v>Kid Cudi</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
+        <v>https://music.apple.com/us/artist/kid-cudi/273058501</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/dangerous/1867202638</v>
+        <v>https://music.apple.com/us/album/real-ones-never-die/1886092612</v>
       </c>
       <c r="L147" t="str">
-        <v>DANGEROUS - Magnolia Park</v>
+        <v>REAL ONES NEVER DIE - Kid Cudi</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>When I Wake Up</v>
+        <v>DON'T EVEN CALL</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/when-i-wake-up/1878237800</v>
+        <v>https://music.apple.com/us/song/dont-even-call/1885914732</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E148" t="str">
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Dear God</v>
+        <v>SAME DIFFERENCE</v>
       </c>
       <c r="G148" t="str">
-        <v>3:33</v>
+        <v>3:30</v>
       </c>
       <c r="H148" t="str">
-        <v>The Pretty Reckless</v>
+        <v>Swae Lee</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
+        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/when-i-wake-up/1878237662</v>
+        <v>https://music.apple.com/us/album/dont-even-call/1885914714</v>
       </c>
       <c r="L148" t="str">
-        <v>When I Wake Up - The Pretty Reckless</v>
+        <v>DON'T EVEN CALL - Swae Lee</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Breathe</v>
+        <v>Runnin' On E</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/breathe/1882808152</v>
+        <v>https://music.apple.com/us/song/runnin-on-e/1884646318</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E149" t="str">
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Breathe - Single</v>
+        <v>Runnin' On E - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>2:56</v>
+        <v>2:27</v>
       </c>
       <c r="H149" t="str">
-        <v>Malcolm Todd</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
+        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/breathe/1882807987</v>
+        <v>https://music.apple.com/us/album/runnin-on-e/1884646317</v>
       </c>
       <c r="L149" t="str">
-        <v>Breathe - Malcolm Todd</v>
+        <v>Runnin' On E - Wyatt Flores</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Minty</v>
+        <v>FREESTYLE</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/minty/1870867418</v>
+        <v>https://music.apple.com/us/song/freestyle/1884623617</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E150" t="str">
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>LINAJE</v>
       </c>
       <c r="G150" t="str">
-        <v>1:47</v>
+        <v>5:36</v>
       </c>
       <c r="H150" t="str">
-        <v>MIKE</v>
+        <v>Hermanos Espinoza</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/mike/1253023714</v>
+        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/minty/1870867411</v>
+        <v>https://music.apple.com/us/album/freestyle/1884623413</v>
       </c>
       <c r="L150" t="str">
-        <v>Minty - MIKE</v>
+        <v>FREESTYLE - Hermanos Espinoza</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Earth</v>
+        <v>Orcasitas</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/earth/1870867498</v>
+        <v>https://music.apple.com/us/song/orcasitas/1882386609</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E151" t="str">
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>Alma De Cántaro</v>
       </c>
       <c r="G151" t="str">
-        <v>1:37</v>
+        <v>3:23</v>
       </c>
       <c r="H151" t="str">
-        <v>Earl Sweatshirt</v>
+        <v>marquitos</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
+        <v>https://music.apple.com/us/artist/marquitos/1778532119</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/earth/1870867411</v>
+        <v>https://music.apple.com/us/album/orcasitas/1882386365</v>
       </c>
       <c r="L151" t="str">
-        <v>Earth - Earl Sweatshirt</v>
+        <v>Orcasitas - marquitos</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Drink The Water</v>
+        <v>Vida Loca</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/drink-the-water/1883172887</v>
+        <v>https://music.apple.com/us/song/vida-loca/1885698516</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E152" t="str">
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
+        <v>FREE SPIRITS</v>
       </c>
       <c r="G152" t="str">
-        <v>3:42</v>
+        <v>2:35</v>
       </c>
       <c r="H152" t="str">
-        <v>Jack Johnson</v>
+        <v>CA7RIEL &amp; Paco Amoroso</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
+        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/drink-the-water/1883172879</v>
+        <v>https://music.apple.com/us/album/vida-loca/1885698497</v>
       </c>
       <c r="L152" t="str">
-        <v>Drink The Water - Jack Johnson</v>
+        <v>Vida Loca - CA7RIEL &amp; Paco Amoroso</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>A Rainy Night in Soho</v>
+        <v>Honest</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/a-rainy-night-in-soho/1878459216</v>
+        <v>https://music.apple.com/us/song/honest/1867616799</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E153" t="str">
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>A Rainy Night in Soho - Single</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G153" t="str">
-        <v>4:32</v>
+        <v>3:39</v>
       </c>
       <c r="H153" t="str">
-        <v>Bruce Springsteen</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/bruce-springsteen/178834</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/a-rainy-night-in-soho/1878459215</v>
+        <v>https://music.apple.com/us/album/honest/1867616617</v>
       </c>
       <c r="L153" t="str">
-        <v>A Rainy Night in Soho - Bruce Springsteen</v>
+        <v>Honest - Dermot Kennedy</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>If I Don't Leave I'm Gonna Stay</v>
+        <v>Ruleta Rusa</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/if-i-dont-leave-im-gonna-stay/1880111466</v>
+        <v>https://music.apple.com/us/song/ruleta-rusa/1868792929</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E154" t="str">
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>If I Don't Leave I'm Gonna Stay - Single</v>
+        <v>K de Karma (Apple Music Edition)</v>
       </c>
       <c r="G154" t="str">
-        <v>3:32</v>
+        <v>3:01</v>
       </c>
       <c r="H154" t="str">
-        <v>Carly Pearce</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/if-i-dont-leave-im-gonna-stay/1880111464</v>
+        <v>https://music.apple.com/us/album/ruleta-rusa/1868792704</v>
       </c>
       <c r="L154" t="str">
-        <v>If I Don't Leave I'm Gonna Stay - Carly Pearce</v>
+        <v>Ruleta Rusa - Kenia Os</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Muchacho Alegre</v>
+        <v>Where There's Smoke, There's Fire</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/muchacho-alegre/1880256976</v>
+        <v>https://music.apple.com/us/song/where-theres-smoke-theres-fire/1873477949</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E155" t="str">
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Muchacho Alegre - Single</v>
+        <v>Peaches!</v>
       </c>
       <c r="G155" t="str">
-        <v>3:08</v>
+        <v>5:00</v>
       </c>
       <c r="H155" t="str">
-        <v>Luis R Conriquez</v>
+        <v>The Black Keys</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/muchacho-alegre/1880256973</v>
+        <v>https://music.apple.com/us/album/where-theres-smoke-theres-fire/1873477948</v>
       </c>
       <c r="L155" t="str">
-        <v>Muchacho Alegre - Luis R Conriquez</v>
+        <v>Where There's Smoke, There's Fire - The Black Keys</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Real Slow</v>
+        <v>Light as a Feather</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/real-slow/1869618394</v>
+        <v>https://music.apple.com/us/song/light-as-a-feather/1870989894</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E156" t="str">
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Work of Heart</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G156" t="str">
-        <v>3:22</v>
+        <v>3:36</v>
       </c>
       <c r="H156" t="str">
-        <v>Flatland Cavalry</v>
+        <v>Cannons</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/real-slow/1869617637</v>
+        <v>https://music.apple.com/us/album/light-as-a-feather/1870989672</v>
       </c>
       <c r="L156" t="str">
-        <v>Real Slow - Flatland Cavalry</v>
+        <v>Light as a Feather - Cannons</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Mountain Girl</v>
+        <v>Loving One</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/mountain-girl/1870722299</v>
+        <v>https://music.apple.com/us/song/loving-one/1882487874</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E157" t="str">
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>As Is</v>
+        <v>Loving One - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>2:42</v>
+        <v>3:39</v>
       </c>
       <c r="H157" t="str">
-        <v>Josiah and the Bonnevilles</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/josiah-and-the-bonnevilles/1101954493</v>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/mountain-girl/1870722288</v>
+        <v>https://music.apple.com/us/album/loving-one/1882487871</v>
       </c>
       <c r="L157" t="str">
-        <v>Mountain Girl - Josiah and the Bonnevilles</v>
+        <v>Loving One - People I’ve Met</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Like a Spark</v>
+        <v>Both Can Be True</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/like-a-spark/1876952751</v>
+        <v>https://music.apple.com/us/song/both-can-be-true/1879642452</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E158" t="str">
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>American Stories</v>
+        <v>Both Can Be True - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:31</v>
+        <v>3:05</v>
       </c>
       <c r="H158" t="str">
-        <v>Rostam</v>
+        <v>Trousdale</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/like-a-spark/1876952750</v>
+        <v>https://music.apple.com/us/album/both-can-be-true/1879642449</v>
       </c>
       <c r="L158" t="str">
-        <v>Like a Spark - Rostam</v>
+        <v>Both Can Be True - Trousdale</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Cheesecake</v>
+        <v>Buffalo 66</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/cheesecake/1882526540</v>
+        <v>https://music.apple.com/us/song/buffalo-66/1878795630</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E159" t="str">
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>So Much To Tell You (Deluxe)</v>
+        <v>Jesus loves a primadonna</v>
       </c>
       <c r="G159" t="str">
-        <v>3:29</v>
+        <v>4:27</v>
       </c>
       <c r="H159" t="str">
-        <v>Ax and the Hatchetmen</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/ax-and-the-hatchetmen/1471855465</v>
+        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/cheesecake/1882525852</v>
+        <v>https://music.apple.com/us/album/buffalo-66/1878795618</v>
       </c>
       <c r="L159" t="str">
-        <v>Cheesecake - Ax and the Hatchetmen</v>
+        <v>Buffalo 66 - Nessa Barrett</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>ALWAYS LET YOU DOWN</v>
+        <v>brb</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/always-let-you-down/1871578121</v>
+        <v>https://music.apple.com/us/song/brb/1884716531</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E160" t="str">
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>KINDA HARD</v>
+        <v>brb - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:04</v>
+        <v>2:36</v>
       </c>
       <c r="H160" t="str">
-        <v>Bilmuri</v>
+        <v>The Two Lips</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
+        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/always-let-you-down/1871578103</v>
+        <v>https://music.apple.com/us/album/brb/1884716521</v>
       </c>
       <c r="L160" t="str">
-        <v>ALWAYS LET YOU DOWN - Bilmuri</v>
+        <v>brb - The Two Lips</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Freakin’ Out</v>
+        <v>Euphoria</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/freakin-out/1879596115</v>
+        <v>https://music.apple.com/us/song/euphoria/1859028065</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E161" t="str">
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Freakin’ Out - Single</v>
+        <v>Euphoria - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:37</v>
+        <v>3:32</v>
       </c>
       <c r="H161" t="str">
-        <v>Dexter and The Moonrocks</v>
+        <v>Talia Rae</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
+        <v>https://music.apple.com/us/artist/talia-rae/480784264</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/freakin-out/1879596114</v>
+        <v>https://music.apple.com/us/album/euphoria/1859027872</v>
       </c>
       <c r="L161" t="str">
-        <v>Freakin’ Out - Dexter and The Moonrocks</v>
+        <v>Euphoria - Talia Rae</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Name in Vein</v>
+        <v>if i'm lucky</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/name-in-vein/1880069474</v>
+        <v>https://music.apple.com/us/song/if-im-lucky/1878512865</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E162" t="str">
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Name in Vein - Single</v>
+        <v>better late than not at all - EP</v>
       </c>
       <c r="G162" t="str">
-        <v>3:03</v>
+        <v>2:57</v>
       </c>
       <c r="H162" t="str">
-        <v>VOILÀ</v>
+        <v>Chelsea Jordan</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/name-in-vein/1880069473</v>
+        <v>https://music.apple.com/us/album/if-im-lucky/1878512860</v>
       </c>
       <c r="L162" t="str">
-        <v>Name in Vein - VOILÀ</v>
+        <v>if i'm lucky - Chelsea Jordan</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>St. Catherine's Wheel</v>
+        <v>Gracie</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/st-catherines-wheel/1868804170</v>
+        <v>https://music.apple.com/us/song/gracie/1863525497</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E163" t="str">
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Into Oblivion</v>
+        <v>F.I.G</v>
       </c>
       <c r="G163" t="str">
-        <v>4:05</v>
+        <v>2:54</v>
       </c>
       <c r="H163" t="str">
-        <v>Lamb of God</v>
+        <v>Naomi Scott</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
+        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/st-catherines-wheel/1868804163</v>
+        <v>https://music.apple.com/us/album/gracie/1863525485</v>
       </c>
       <c r="L163" t="str">
-        <v>St. Catherine's Wheel - Lamb of God</v>
+        <v>Gracie - Naomi Scott</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Undefeated Champion</v>
+        <v>Something's Not Right Here</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/undefeated-champion/1840517120</v>
+        <v>https://music.apple.com/us/song/somethings-not-right-here/1882090886</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E164" t="str">
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Sweat</v>
+        <v>Dreaming Out Loud (Deluxe Edition)</v>
       </c>
       <c r="G164" t="str">
-        <v>3:34</v>
+        <v>3:02</v>
       </c>
       <c r="H164" t="str">
-        <v>Melanie C</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
+        <v>https://music.apple.com/us/artist/onerepublic/260414340</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/undefeated-champion/1840516706</v>
+        <v>https://music.apple.com/us/album/somethings-not-right-here/1882090709</v>
       </c>
       <c r="L164" t="str">
-        <v>Undefeated Champion - Melanie C</v>
+        <v>Something's Not Right Here - OneRepublic</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Pull Up</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/pull-up/1854381591</v>
+        <v>https://music.apple.com/us/song/dream-chaser/1884219678</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E165" t="str">
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Pull Up - Single</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="G165" t="str">
-        <v>2:35</v>
+        <v>3:14</v>
       </c>
       <c r="H165" t="str">
-        <v>Collect 200</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/collect-200/1804375505</v>
+        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/pull-up/1854381590</v>
+        <v>https://music.apple.com/us/album/dream-chaser/1884219677</v>
       </c>
       <c r="L165" t="str">
-        <v>Pull Up - Collect 200</v>
+        <v>Dream Chaser - Willie Nelson</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Ranjha</v>
+        <v>Trouble</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/ranjha/1882965642</v>
+        <v>https://music.apple.com/us/song/trouble/1876369964</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E166" t="str">
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Ranjha - Single</v>
+        <v>Girlfriend</v>
       </c>
       <c r="G166" t="str">
-        <v>3:04</v>
+        <v>3:17</v>
       </c>
       <c r="H166" t="str">
-        <v>Diljit Dosanjh</v>
+        <v>Grace Ives</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/diljit-dosanjh/423087540</v>
+        <v>https://music.apple.com/us/artist/grace-ives/1390289298</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/ranjha/1882965641</v>
+        <v>https://music.apple.com/us/album/trouble/1876369944</v>
       </c>
       <c r="L166" t="str">
-        <v>Ranjha - Diljit Dosanjh</v>
+        <v>Trouble - Grace Ives</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>zombies in love</v>
+        <v>judas</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/zombies-in-love/1880178176</v>
+        <v>https://music.apple.com/us/song/judas/1882829414</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E167" t="str">
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>zombies in love - Single</v>
+        <v>judas - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>2:53</v>
+        <v>3:31</v>
       </c>
       <c r="H167" t="str">
-        <v>paris jackson</v>
+        <v>Josiah Queen</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
+        <v>https://music.apple.com/us/artist/josiah-queen/1498117530</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/zombies-in-love/1880178173</v>
+        <v>https://music.apple.com/us/album/judas/1882829413</v>
       </c>
       <c r="L167" t="str">
-        <v>zombies in love - paris jackson</v>
+        <v>judas - Josiah Queen</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Days Of Us</v>
+        <v>JINX</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/days-of-us/1868438268</v>
+        <v>https://music.apple.com/us/song/jinx/1880173550</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E168" t="str">
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Full Circle</v>
+        <v>JINX - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>4:39</v>
+        <v>2:54</v>
       </c>
       <c r="H168" t="str">
-        <v>Tom Misch</v>
+        <v>Zacari</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
+        <v>https://music.apple.com/us/artist/zacari/1027112445</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/days-of-us/1868437787</v>
+        <v>https://music.apple.com/us/album/jinx/1880173549</v>
       </c>
       <c r="L168" t="str">
-        <v>Days Of Us - Tom Misch</v>
+        <v>JINX - Zacari</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Life Of A Man</v>
+        <v>se fue</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/life-of-a-man/1882845328</v>
+        <v>https://music.apple.com/us/song/se-fue/1876355980</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E169" t="str">
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Life Of A Man - Single</v>
+        <v>Náufrago</v>
       </c>
       <c r="G169" t="str">
-        <v>3:15</v>
+        <v>2:51</v>
       </c>
       <c r="H169" t="str">
-        <v>1Ski OG</v>
+        <v>Eddy</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/eddy/1779584924</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/life-of-a-man/1882845327</v>
+        <v>https://music.apple.com/us/album/se-fue/1876355962</v>
       </c>
       <c r="L169" t="str">
-        <v>Life Of A Man - 1Ski OG</v>
+        <v>se fue - Eddy</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Ya No</v>
+        <v>The Blade</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/ya-no/1882115676</v>
+        <v>https://music.apple.com/us/song/the-blade/1884066958</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E170" t="str">
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Ya No - Single</v>
+        <v>The Blade - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:40</v>
+        <v>3:15</v>
       </c>
       <c r="H170" t="str">
-        <v>Marca MP</v>
+        <v>Kingfishr</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
+        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/ya-no/1882115675</v>
+        <v>https://music.apple.com/us/album/the-blade/1884066685</v>
       </c>
       <c r="L170" t="str">
-        <v>Ya No - Marca MP</v>
+        <v>The Blade - Kingfishr</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Do You Really Love Her</v>
+        <v>Metric Rules</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/do-you-really-love-her/1879639011</v>
+        <v>https://music.apple.com/us/song/metric-rules/1885609351</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E171" t="str">
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Do You Really Love Her - Single</v>
+        <v>When Lagos Sleeps - EP</v>
       </c>
       <c r="G171" t="str">
-        <v>3:48</v>
+        <v>3:13</v>
       </c>
       <c r="H171" t="str">
-        <v>Spacey Jane</v>
+        <v>SPINALL</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
+        <v>https://music.apple.com/us/artist/spinall/813737832</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/do-you-really-love-her/1879639009</v>
+        <v>https://music.apple.com/us/album/metric-rules/1885609347</v>
       </c>
       <c r="L171" t="str">
-        <v>Do You Really Love Her - Spacey Jane</v>
+        <v>Metric Rules - SPINALL</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Relieve You</v>
+        <v>FIGURE IT OUT</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/relieve-you/1879589717</v>
+        <v>https://music.apple.com/us/song/figure-it-out/1882873714</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E172" t="str">
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Relieve You - Single</v>
+        <v>FIGURE IT OUT - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>2:19</v>
+        <v>2:15</v>
       </c>
       <c r="H172" t="str">
-        <v>4Fargo</v>
+        <v>ZEP</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/4fargo/1381605295</v>
+        <v>https://music.apple.com/us/artist/zep/1582892045</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/relieve-you/1879589716</v>
+        <v>https://music.apple.com/us/album/figure-it-out/1882873713</v>
       </c>
       <c r="L172" t="str">
-        <v>Relieve You - 4Fargo</v>
+        <v>FIGURE IT OUT - ZEP</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Safety</v>
+        <v>Coasting (Piano Session)</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/safety/1878181748</v>
+        <v>https://music.apple.com/us/song/coasting-piano-session/1880328049</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E173" t="str">
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Safety - Single</v>
+        <v>Coasting (Piano Session) - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:18</v>
+        <v>3:23</v>
       </c>
       <c r="H173" t="str">
-        <v>Lekan</v>
+        <v>Hutch</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/lekan/1540259198</v>
+        <v>https://music.apple.com/us/artist/hutch/1852060852</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/safety/1878181738</v>
+        <v>https://music.apple.com/us/album/coasting-piano-session/1880328048</v>
       </c>
       <c r="L173" t="str">
-        <v>Safety - Lekan</v>
+        <v>Coasting (Piano Session) - Hutch</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Starlet</v>
+        <v>Still Sincere (feat. PinkPantheress) [MK Dub]</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/starlet/1873450846</v>
+        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress-mk-dub/1882054680</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E174" t="str">
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>LK99</v>
+        <v>Still Sincere (MK Dub) [feat. PinkPantheress] - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:56</v>
+        <v>5:15</v>
       </c>
       <c r="H174" t="str">
-        <v>Leven Kali</v>
+        <v>MJ Cole</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/leven-kali/1166360470</v>
+        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/starlet/1873450570</v>
+        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress-mk-dub/1882054676</v>
       </c>
       <c r="L174" t="str">
-        <v>Starlet - Leven Kali</v>
+        <v>Still Sincere (feat. PinkPantheress) [MK Dub] - MJ Cole</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Physical</v>
+        <v>Cyclone</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/physical/1883210753</v>
+        <v>https://music.apple.com/us/song/cyclone/1843578165</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E175" t="str">
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Physical - Single</v>
+        <v>Loss</v>
       </c>
       <c r="G175" t="str">
-        <v>3:52</v>
+        <v>5:33</v>
       </c>
       <c r="H175" t="str">
-        <v>Jacquees</v>
+        <v>Gaerea</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/jacquees/386779763</v>
+        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/physical/1883210752</v>
+        <v>https://music.apple.com/us/album/cyclone/1843578156</v>
       </c>
       <c r="L175" t="str">
-        <v>Physical - Jacquees</v>
+        <v>Cyclone - Gaerea</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>i'm dying to feel alive again</v>
+        <v>Checkmate</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/im-dying-to-feel-alive-again/1880883509</v>
+        <v>https://music.apple.com/us/song/checkmate/1882117113</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E176" t="str">
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>i'm dying to feel alive again - Single</v>
+        <v>Checkmate - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>4:29</v>
+        <v>4:23</v>
       </c>
       <c r="H176" t="str">
-        <v>Casper Sage</v>
+        <v>Blue Medusa</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
+        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/im-dying-to-feel-alive-again/1880883507</v>
+        <v>https://music.apple.com/us/album/checkmate/1882117111</v>
       </c>
       <c r="L176" t="str">
-        <v>i'm dying to feel alive again - Casper Sage</v>
+        <v>Checkmate - Blue Medusa</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Regalito</v>
+        <v>DAVE</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/regalito/1880846653</v>
+        <v>https://music.apple.com/us/song/dave/1881700152</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E177" t="str">
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>TRESCENDER</v>
+        <v>DAVE - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:41</v>
+        <v>2:01</v>
       </c>
       <c r="H177" t="str">
-        <v>Piso 21</v>
+        <v>Hulvey</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/piso-21/403121923</v>
+        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/regalito/1880845994</v>
+        <v>https://music.apple.com/us/album/dave/1881700151</v>
       </c>
       <c r="L177" t="str">
-        <v>Regalito - Piso 21</v>
+        <v>DAVE - Hulvey</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Cruel Streak</v>
+        <v>Change</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/cruel-streak/1858689493</v>
+        <v>https://music.apple.com/us/song/change/1880857720</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E178" t="str">
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>A Pound of Feathers</v>
+        <v>Change - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>4:09</v>
+        <v>2:38</v>
       </c>
       <c r="H178" t="str">
-        <v>The Black Crowes</v>
+        <v>Stephen Stanley</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
+        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/cruel-streak/1858689485</v>
+        <v>https://music.apple.com/us/album/change/1880857716</v>
       </c>
       <c r="L178" t="str">
-        <v>Cruel Streak - The Black Crowes</v>
+        <v>Change - Stephen Stanley</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Die Young</v>
+        <v>Te Entiendo</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/die-young/1870715300</v>
+        <v>https://music.apple.com/us/song/te-entiendo/1882386240</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E179" t="str">
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Little Wide Open</v>
+        <v>Te Entiendo - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:52</v>
+        <v>3:05</v>
       </c>
       <c r="H179" t="str">
-        <v>Kevin Morby</v>
+        <v>Maisak</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/kevin-morby/708517315</v>
+        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/die-young/1870715298</v>
+        <v>https://music.apple.com/us/album/te-entiendo/1882386238</v>
       </c>
       <c r="L179" t="str">
-        <v>Die Young - Kevin Morby</v>
+        <v>Te Entiendo - Maisak</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Island Girl</v>
+        <v>CHEVROLET 90</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/island-girl/1884461360</v>
+        <v>https://music.apple.com/us/song/chevrolet-90/1879599158</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E180" t="str">
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Island Girl - Single</v>
+        <v>V</v>
       </c>
       <c r="G180" t="str">
-        <v>3:27</v>
+        <v>2:01</v>
       </c>
       <c r="H180" t="str">
-        <v>Pia Mia</v>
+        <v>Rey Quinto</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/pia-mia/483071062</v>
+        <v>https://music.apple.com/us/artist/rey-quinto/1715073363</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/island-girl/1884461354</v>
+        <v>https://music.apple.com/us/album/chevrolet-90/1879599141</v>
       </c>
       <c r="L180" t="str">
-        <v>Island Girl - Pia Mia</v>
+        <v>CHEVROLET 90 - Rey Quinto</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>GIRLY THINGS</v>
+        <v>Tirabalas</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/girly-things/1876032954</v>
+        <v>https://music.apple.com/us/song/tirabalas/1877963582</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E181" t="str">
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>GIRLY THINGS - Single</v>
+        <v>ESSENCE #10 (Deluxe)</v>
       </c>
       <c r="G181" t="str">
-        <v>2:20</v>
+        <v>3:53</v>
       </c>
       <c r="H181" t="str">
-        <v>Claudia Valentina</v>
+        <v>Hans el Oso</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/claudia-valentina/1434841711</v>
+        <v>https://music.apple.com/us/artist/hans-el-oso/1619227662</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/girly-things/1876032953</v>
+        <v>https://music.apple.com/us/album/tirabalas/1877963565</v>
       </c>
       <c r="L181" t="str">
-        <v>GIRLY THINGS - Claudia Valentina</v>
+        <v>Tirabalas - Hans el Oso</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Looking Lovely (feat. Robin Thicke)</v>
+        <v>punchbowl</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/looking-lovely-feat-robin-thicke/1878437828</v>
+        <v>https://music.apple.com/us/song/punchbowl/1883156074</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E182" t="str">
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Looking Lovely (feat. Robin Thicke) - Single</v>
+        <v>punchbowl - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:22</v>
+        <v>2:34</v>
       </c>
       <c r="H182" t="str">
-        <v>Shaggy</v>
+        <v>Julio Caesar</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/shaggy/68616</v>
+        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/looking-lovely-feat-robin-thicke/1878437504</v>
+        <v>https://music.apple.com/us/album/punchbowl/1883156073</v>
       </c>
       <c r="L182" t="str">
-        <v>Looking Lovely (feat. Robin Thicke) - Shaggy</v>
+        <v>punchbowl - Julio Caesar</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Tommy’s Song</v>
+        <v>Wild Ride</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/tommys-song/1876670040</v>
+        <v>https://music.apple.com/us/song/wild-ride/1884728581</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E183" t="str">
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Lovers - Single</v>
+        <v>Wild Ride - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:44</v>
+        <v>3:41</v>
       </c>
       <c r="H183" t="str">
-        <v>Nathaniel Rateliff</v>
+        <v>Durand Bernarr</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/nathaniel-rateliff/362131302</v>
+        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/tommys-song/1876670038</v>
+        <v>https://music.apple.com/us/album/wild-ride/1884728580</v>
       </c>
       <c r="L183" t="str">
-        <v>Tommy’s Song - Nathaniel Rateliff</v>
+        <v>Wild Ride - Durand Bernarr</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Rainbows</v>
+        <v>Lamb Chop</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/rainbows/1882790536</v>
+        <v>https://music.apple.com/us/song/lamb-chop/1881677466</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E184" t="str">
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Rainbows - Single</v>
+        <v>Lamb Chop - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:25</v>
+        <v>2:03</v>
       </c>
       <c r="H184" t="str">
-        <v>Allison Russell</v>
+        <v>Chuckyy</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/allison-russell/451740458</v>
+        <v>https://music.apple.com/us/artist/chuckyy/1703210537</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/rainbows/1882790535</v>
+        <v>https://music.apple.com/us/album/lamb-chop/1881677465</v>
       </c>
       <c r="L184" t="str">
-        <v>Rainbows - Allison Russell</v>
+        <v>Lamb Chop - Chuckyy</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>butterflies</v>
+        <v>Free Nick</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/butterflies/1878228436</v>
+        <v>https://music.apple.com/us/song/free-nick/1881667330</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E185" t="str">
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Bloom Again - EP</v>
+        <v>Free Nick - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:48</v>
+        <v>2:05</v>
       </c>
       <c r="H185" t="str">
-        <v>runo plum</v>
+        <v>Raq baby</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
+        <v>https://music.apple.com/us/artist/raq-baby/1712935965</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/butterflies/1878228434</v>
+        <v>https://music.apple.com/us/album/free-nick/1881667216</v>
       </c>
       <c r="L185" t="str">
-        <v>butterflies - runo plum</v>
+        <v>Free Nick - Raq baby</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>You're Right</v>
+        <v>Make Me Brand New</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/youre-right/1874975857</v>
+        <v>https://music.apple.com/us/song/make-me-brand-new/1878525836</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E186" t="str">
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>You're Right - Single</v>
+        <v>Make Me Brand New - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:00</v>
+        <v>3:06</v>
       </c>
       <c r="H186" t="str">
-        <v>Emma Harner</v>
+        <v>Dante’ Pride</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/emma-harner/1543609198</v>
+        <v>https://music.apple.com/us/artist/dante-pride/1175536450</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/youre-right/1874975856</v>
+        <v>https://music.apple.com/us/album/make-me-brand-new/1878525833</v>
       </c>
       <c r="L186" t="str">
-        <v>You're Right - Emma Harner</v>
+        <v>Make Me Brand New - Dante’ Pride</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Bible Belt</v>
+        <v>Define You</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/bible-belt/1821125622</v>
+        <v>https://music.apple.com/us/song/define-you/1877189744</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E187" t="str">
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Bible Belt - Single</v>
+        <v>Define You - Single</v>
       </c>
       <c r="G187" t="str">
         <v>3:34</v>
       </c>
       <c r="H187" t="str">
-        <v>Baby Bugs</v>
+        <v>Luca Fogale</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/baby-bugs/1551794879</v>
+        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/bible-belt/1821125621</v>
+        <v>https://music.apple.com/us/album/define-you/1877189743</v>
       </c>
       <c r="L187" t="str">
-        <v>Bible Belt - Baby Bugs</v>
+        <v>Define You - Luca Fogale</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Daze</v>
+        <v>If You Change</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/daze/1862607801</v>
+        <v>https://music.apple.com/us/song/if-you-change/1880416153</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E188" t="str">
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Daze - Single</v>
+        <v>Roses</v>
       </c>
       <c r="G188" t="str">
-        <v>3:22</v>
+        <v>4:41</v>
       </c>
       <c r="H188" t="str">
-        <v>Olympia Vitalis</v>
+        <v>Widowspeak</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
+        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/daze/1862607800</v>
+        <v>https://music.apple.com/us/album/if-you-change/1880416141</v>
       </c>
       <c r="L188" t="str">
-        <v>Daze - Olympia Vitalis</v>
+        <v>If You Change - Widowspeak</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Passionfruit</v>
+        <v>What I See</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/passionfruit/1878215125</v>
+        <v>https://music.apple.com/us/song/what-i-see/1882879437</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E189" t="str">
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Passionfruit - Single</v>
+        <v>SYNY 3 Act II - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:57</v>
+        <v>2:32</v>
       </c>
       <c r="H189" t="str">
-        <v>Anish Kumar</v>
+        <v>See You Next Year</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/see-you-next-year/1624754980</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/passionfruit/1878215124</v>
+        <v>https://music.apple.com/us/album/what-i-see/1882879433</v>
       </c>
       <c r="L189" t="str">
-        <v>Passionfruit - Anish Kumar</v>
+        <v>What I See - See You Next Year</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Madan</v>
+        <v>Witching Hour</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/madan/1879822223</v>
+        <v>https://music.apple.com/us/song/witching-hour/1870760652</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E190" t="str">
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Madan - Single</v>
+        <v>Butterfly</v>
       </c>
       <c r="G190" t="str">
-        <v>2:56</v>
+        <v>3:47</v>
       </c>
       <c r="H190" t="str">
-        <v>Jonas Blue</v>
+        <v>Witch Post</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/jonas-blue/405728790</v>
+        <v>https://music.apple.com/us/artist/witch-post/1774955367</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/madan/1879822222</v>
+        <v>https://music.apple.com/us/album/witching-hour/1870760649</v>
       </c>
       <c r="L190" t="str">
-        <v>Madan - Jonas Blue</v>
+        <v>Witching Hour - Witch Post</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Bad Bitch</v>
+        <v>Actin' Tough</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/bad-bitch/1882818210</v>
+        <v>https://music.apple.com/us/song/actin-tough/1881996627</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E191" t="str">
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Bad Bitch - Single</v>
+        <v>Actin' Tough - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>2:28</v>
+        <v>3:07</v>
       </c>
       <c r="H191" t="str">
-        <v>41</v>
+        <v>Dean Turnley</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/41/1688992229</v>
+        <v>https://music.apple.com/us/artist/dean-turnley/1561296990</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/bad-bitch/1882818208</v>
+        <v>https://music.apple.com/us/album/actin-tough/1881996384</v>
       </c>
       <c r="L191" t="str">
-        <v>Bad Bitch - 41</v>
+        <v>Actin' Tough - Dean Turnley</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Shame</v>
+        <v>Coração - A COLORS SHOW</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/shame/1874080307</v>
+        <v>https://music.apple.com/us/song/cora%C3%A7%C3%A3o-a-colors-show/1880127530</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E192" t="str">
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Devotion [Deluxe]</v>
+        <v>Coração - A COLORS SHOW - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>3:36</v>
+        <v>2:52</v>
       </c>
       <c r="H192" t="str">
-        <v>Sunday (1994)</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/sunday-1994/1728938785</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/shame/1874080202</v>
+        <v>https://music.apple.com/us/album/cora%C3%A7%C3%A3o-a-colors-show/1880127529</v>
       </c>
       <c r="L192" t="str">
-        <v>Shame - Sunday (1994)</v>
+        <v>Coração - A COLORS SHOW - Anais Cardot</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>teach you to love me</v>
+        <v>Rewind It</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/teach-you-to-love-me/1883146005</v>
+        <v>https://music.apple.com/us/song/rewind-it/1884966852</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E193" t="str">
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>teach you to love me - Single</v>
+        <v>Rewind It - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:09</v>
+        <v>1:34</v>
       </c>
       <c r="H193" t="str">
-        <v>Hailey Picardi</v>
+        <v>Nino Paid</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/nino-paid/1636385121</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/teach-you-to-love-me/1883146002</v>
+        <v>https://music.apple.com/us/album/rewind-it/1884966848</v>
       </c>
       <c r="L193" t="str">
-        <v>teach you to love me - Hailey Picardi</v>
+        <v>Rewind It - Nino Paid</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>The Fix</v>
+        <v>Turn It Up</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/the-fix/1882082897</v>
+        <v>https://music.apple.com/us/song/turn-it-up/1885664396</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E194" t="str">
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>The Fix - Single</v>
+        <v>Turn It Up - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>2:42</v>
+        <v>2:33</v>
       </c>
       <c r="H194" t="str">
-        <v>Baby J</v>
+        <v>slayr</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
+        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/the-fix/1882082895</v>
+        <v>https://music.apple.com/us/album/turn-it-up/1885664393</v>
       </c>
       <c r="L194" t="str">
-        <v>The Fix - Baby J</v>
+        <v>Turn It Up - slayr</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Hanging on Hope</v>
+        <v>Down</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/hanging-on-hope/1881749452</v>
+        <v>https://music.apple.com/us/song/down/1884531560</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E195" t="str">
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Hanging on Hope - Single</v>
+        <v>Down - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:43</v>
+        <v>2:08</v>
       </c>
       <c r="H195" t="str">
-        <v>Buffalo Traffic Jam</v>
+        <v>MexikoDro</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
+        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/hanging-on-hope/1881749451</v>
+        <v>https://music.apple.com/us/album/down/1884531558</v>
       </c>
       <c r="L195" t="str">
-        <v>Hanging on Hope - Buffalo Traffic Jam</v>
+        <v>Down - MexikoDro</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>I Know What to Say Now</v>
+        <v>Make It Out</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/i-know-what-to-say-now/1879440545</v>
+        <v>https://music.apple.com/us/song/make-it-out/1883117489</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E196" t="str">
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>I Know What to Say Now - Single</v>
+        <v>Make It Out - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>3:18</v>
+        <v>2:17</v>
       </c>
       <c r="H196" t="str">
-        <v>Active Child</v>
+        <v>Trueblood</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/active-child/355288617</v>
+        <v>https://music.apple.com/us/artist/trueblood/1688100658</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/i-know-what-to-say-now/1879440351</v>
+        <v>https://music.apple.com/us/album/make-it-out/1883117392</v>
       </c>
       <c r="L196" t="str">
-        <v>I Know What to Say Now - Active Child</v>
+        <v>Make It Out - Trueblood</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Feel Something</v>
+        <v>better than boston</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/feel-something/1876008375</v>
+        <v>https://music.apple.com/us/song/better-than-boston/1885587018</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E197" t="str">
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Feel Something - Single</v>
+        <v>better than boston - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>3:09</v>
+        <v>3:02</v>
       </c>
       <c r="H197" t="str">
-        <v>Baby Queen</v>
+        <v>Tom Siletto</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
+        <v>https://music.apple.com/us/artist/tom-siletto/1530304047</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/feel-something/1876008371</v>
+        <v>https://music.apple.com/us/album/better-than-boston/1885587016</v>
       </c>
       <c r="L197" t="str">
-        <v>Feel Something - Baby Queen</v>
+        <v>better than boston - Tom Siletto</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>You Or Me</v>
+        <v>So Much Beauty (Around Us)</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/you-or-me/1869085528</v>
+        <v>https://music.apple.com/us/song/so-much-beauty-around-us/1880038915</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E198" t="str">
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Good God / Baad Man</v>
+        <v>So Much Beauty (Around Us) - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>5:28</v>
+        <v>2:34</v>
       </c>
       <c r="H198" t="str">
-        <v>Corrosion of Conformity</v>
+        <v>Lost Frequencies</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
+        <v>https://music.apple.com/us/artist/lost-frequencies/877792512</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/you-or-me/1869085524</v>
+        <v>https://music.apple.com/us/album/so-much-beauty-around-us/1880038907</v>
       </c>
       <c r="L198" t="str">
-        <v>You Or Me - Corrosion of Conformity</v>
+        <v>So Much Beauty (Around Us) - Lost Frequencies</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Mortercheyn</v>
+        <v>All I Need</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/mortercheyn/1862521946</v>
+        <v>https://music.apple.com/us/song/all-i-need/1878185372</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E199" t="str">
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Coronach</v>
+        <v>All I Need - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>4:18</v>
+        <v>3:06</v>
       </c>
       <c r="H199" t="str">
-        <v>Hellripper</v>
+        <v>GRiZ</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/hellripper/1229248568</v>
+        <v>https://music.apple.com/us/artist/griz/980722716</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/mortercheyn/1862521937</v>
+        <v>https://music.apple.com/us/album/all-i-need/1878185371</v>
       </c>
       <c r="L199" t="str">
-        <v>Mortercheyn - Hellripper</v>
+        <v>All I Need - GRiZ</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Rip The God</v>
+        <v>Weeping Tones</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/rip-the-god/1866957697</v>
+        <v>https://music.apple.com/us/song/weeping-tones/1863532922</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E200" t="str">
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Savage Imperial Death March</v>
+        <v>Peace In Place</v>
       </c>
       <c r="G200" t="str">
-        <v>5:20</v>
+        <v>2:59</v>
       </c>
       <c r="H200" t="str">
-        <v>Melvins</v>
+        <v>Poison the Well</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/melvins/737433</v>
+        <v>https://music.apple.com/us/artist/poison-the-well/1710155</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/rip-the-god/1866957685</v>
+        <v>https://music.apple.com/us/album/weeping-tones/1863532634</v>
       </c>
       <c r="L200" t="str">
-        <v>Rip The God - Melvins</v>
+        <v>Weeping Tones - Poison the Well</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Who We Are</v>
+        <v>Promise You This</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/who-we-are/1879626950</v>
+        <v>https://music.apple.com/us/song/promise-you-this/1862225614</v>
       </c>
       <c r="D201" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E201" t="str">
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>Who We Are - Single</v>
+        <v>Goliath</v>
       </c>
       <c r="G201" t="str">
-        <v>2:10</v>
+        <v>5:19</v>
       </c>
       <c r="H201" t="str">
-        <v>Kaleena Zanders</v>
+        <v>Exodus</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/who-we-are/1879626949</v>
+        <v>https://music.apple.com/us/album/promise-you-this/1862225385</v>
       </c>
       <c r="L201" t="str">
-        <v>Who We Are - Kaleena Zanders</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="str">
-        <v>Reels in 360</v>
-      </c>
-      <c r="B202" t="str">
-        <v/>
-      </c>
-      <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/reels-in-360/1867998408</v>
-      </c>
-      <c r="D202" t="str">
-        <v>2026-03-19</v>
-      </c>
-      <c r="E202" t="str">
-        <v/>
-      </c>
-      <c r="F202" t="str">
-        <v>Dying Is The Internet</v>
-      </c>
-      <c r="G202" t="str">
-        <v>4:37</v>
-      </c>
-      <c r="H202" t="str">
-        <v>Simo Cell</v>
-      </c>
-      <c r="I202" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/simo-cell/1001568130</v>
-      </c>
-      <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/reels-in-360/1867998295</v>
-      </c>
-      <c r="L202" t="str">
-        <v>Reels in 360 - Simo Cell</v>
+        <v>Promise You This - Exodus</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L202"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L201"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:17</v>
@@ -2035,7 +2035,7 @@
         <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G44" t="str">
         <v>3:58</v>
@@ -2073,7 +2073,7 @@
         <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
       </c>
       <c r="B45" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G45" t="str">
         <v>3:25</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
@@ -1085,7 +1085,7 @@
         <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G19" t="str">
         <v>2:50</v>
@@ -2111,7 +2111,7 @@
         <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B46" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G46" t="str">
         <v>4:09</v>
@@ -2149,7 +2149,7 @@
         <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G47" t="str">
         <v>2:08</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
@@ -1009,7 +1009,7 @@
         <v>HAUSER - Hungarian Dance No. 5</v>
       </c>
       <c r="B17" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>2:27</v>
@@ -1047,7 +1047,7 @@
         <v>Holly Humberstone - Cruel World</v>
       </c>
       <c r="B18" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G18" t="str">
         <v>3:34</v>
@@ -2643,7 +2643,7 @@
         <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
         <v>2:56</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
@@ -629,7 +629,7 @@
         <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B7" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:47</v>
@@ -895,7 +895,7 @@
         <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
       </c>
       <c r="B14" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G14" t="str">
         <v>3:28</v>
@@ -933,7 +933,7 @@
         <v>Martin Garrix - Catharina (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G15" t="str">
         <v>3:31</v>
@@ -971,7 +971,7 @@
         <v>Baby Queen - Feel Something (Official Visualiser)</v>
       </c>
       <c r="B16" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G16" t="str">
         <v>3:11</v>
@@ -2301,7 +2301,7 @@
         <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
       </c>
       <c r="B51" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G51" t="str">
         <v>3:57</v>
@@ -4125,7 +4125,7 @@
         <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B99" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
         <v>4:32</v>
@@ -4163,7 +4163,7 @@
         <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v>3:47</v>
@@ -4201,7 +4201,7 @@
         <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
       </c>
       <c r="B101" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v>3:40</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L201"/>
+  <dimension ref="A1:L204"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -553,7 +553,7 @@
         <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
       </c>
       <c r="B5" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G5" t="str">
         <v>4:11</v>
@@ -591,7 +591,7 @@
         <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
       </c>
       <c r="B6" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G6" t="str">
         <v>2:57</v>
@@ -667,7 +667,7 @@
         <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B8" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G8" t="str">
         <v>7:10</v>
@@ -705,7 +705,7 @@
         <v>Grace Enger - Give A Little (Live Performance)</v>
       </c>
       <c r="B9" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G9" t="str">
         <v>3:06</v>
@@ -743,7 +743,7 @@
         <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
       </c>
       <c r="B10" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:05</v>
@@ -781,7 +781,7 @@
         <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G11" t="str">
         <v>3:12</v>
@@ -819,7 +819,7 @@
         <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B12" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G12" t="str">
         <v>9:11</v>
@@ -857,7 +857,7 @@
         <v>SIENNA SPIRO - The Visitor</v>
       </c>
       <c r="B13" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G13" t="str">
         <v>3:49</v>
@@ -1614,7 +1614,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
         <v>7 days ago</v>
@@ -1647,7 +1647,7 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay - Carly Pearce and Riley Green</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
       </c>
     </row>
     <row r="34">
@@ -1959,7 +1959,7 @@
         <v>Amanda Jordan - What Else Is New</v>
       </c>
       <c r="B42" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G42" t="str">
         <v>2:50</v>
@@ -1997,7 +1997,7 @@
         <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
       </c>
       <c r="B43" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G43" t="str">
         <v>3:57</v>
@@ -2225,7 +2225,7 @@
         <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B49" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G49" t="str">
         <v>3:13</v>
@@ -2263,7 +2263,7 @@
         <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B50" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G50" t="str">
         <v>4:12</v>
@@ -2377,7 +2377,7 @@
         <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G53" t="str">
         <v>3:48</v>
@@ -2453,7 +2453,7 @@
         <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G55" t="str">
         <v>2:33</v>
@@ -2491,7 +2491,7 @@
         <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B56" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G56" t="str">
         <v>5:01</v>
@@ -2529,7 +2529,7 @@
         <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
       </c>
       <c r="B57" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G57" t="str">
         <v>4:56</v>
@@ -2567,7 +2567,7 @@
         <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
       </c>
       <c r="B58" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=366CV87TguE</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G58" t="str">
         <v>2:54</v>
@@ -2605,7 +2605,7 @@
         <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G59" t="str">
         <v>2:46</v>
@@ -3973,7 +3973,7 @@
         <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B95" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G95" t="str">
         <v>5:03</v>
@@ -4011,7 +4011,7 @@
         <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B96" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G96" t="str">
         <v>4:50</v>
@@ -4049,7 +4049,7 @@
         <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B97" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
         <v>4:53</v>
@@ -4087,7 +4087,7 @@
         <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B98" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v>3:04</v>
@@ -5566,13 +5566,13 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Caught In The Echo</v>
+        <v>First Red Rays</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/caught-in-the-echo/1877913491</v>
+        <v>https://music.apple.com/us/song/first-red-rays/1882105294</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-20</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Your Favorite Toy</v>
+        <v>An Undying Love for a Burning World</v>
       </c>
       <c r="G137" t="str">
-        <v>4:02</v>
+        <v>8:27</v>
       </c>
       <c r="H137" t="str">
-        <v>Foo Fighters</v>
+        <v>Neurosis</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
+        <v>https://music.apple.com/us/artist/neurosis/18870036</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/caught-in-the-echo/1877913489</v>
+        <v>https://music.apple.com/us/album/first-red-rays/1882105289</v>
       </c>
       <c r="L137" t="str">
-        <v>Caught In The Echo - Foo Fighters</v>
+        <v>First Red Rays - Neurosis</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Little by Little</v>
+        <v>Caught In The Echo</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/little-by-little/1879889876</v>
+        <v>https://music.apple.com/us/song/caught-in-the-echo/1877913491</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-20</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Little by Little - Single</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="G138" t="str">
-        <v>2:34</v>
+        <v>4:02</v>
       </c>
       <c r="H138" t="str">
-        <v>Mon Rovîa</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
+        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/little-by-little/1879889873</v>
+        <v>https://music.apple.com/us/album/caught-in-the-echo/1877913489</v>
       </c>
       <c r="L138" t="str">
-        <v>Little by Little - Mon Rovîa</v>
+        <v>Caught In The Echo - Foo Fighters</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Montgomery County</v>
+        <v>Little by Little</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/montgomery-county/1862624758</v>
+        <v>https://music.apple.com/us/song/little-by-little/1879889876</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-20</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Parker McCollum (The Deluxe Edition)</v>
+        <v>Little by Little - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:28</v>
+        <v>2:34</v>
       </c>
       <c r="H139" t="str">
-        <v>Parker McCollum</v>
+        <v>Mon Rovîa</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
+        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/montgomery-county/1862624506</v>
+        <v>https://music.apple.com/us/album/little-by-little/1879889873</v>
       </c>
       <c r="L139" t="str">
-        <v>Montgomery County - Parker McCollum</v>
+        <v>Little by Little - Mon Rovîa</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Dive Into Me</v>
+        <v>Montgomery County</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/dive-into-me/1879790158</v>
+        <v>https://music.apple.com/us/song/montgomery-county/1862624758</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-20</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Dive Into Me - Single</v>
+        <v>Parker McCollum (The Deluxe Edition)</v>
       </c>
       <c r="G140" t="str">
-        <v>2:46</v>
+        <v>3:28</v>
       </c>
       <c r="H140" t="str">
-        <v>Alok</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/alok/324709167</v>
+        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/dive-into-me/1879789970</v>
+        <v>https://music.apple.com/us/album/montgomery-county/1862624506</v>
       </c>
       <c r="L140" t="str">
-        <v>Dive Into Me - Alok</v>
+        <v>Montgomery County - Parker McCollum</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>more than just a little bit</v>
+        <v>Dive Into Me</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/more-than-just-a-little-bit/1878764653</v>
+        <v>https://music.apple.com/us/song/dive-into-me/1879790158</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-20</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>getting up to no good</v>
+        <v>Dive Into Me - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>2:40</v>
+        <v>2:46</v>
       </c>
       <c r="H141" t="str">
-        <v>Artemas</v>
+        <v>Alok</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/alok/324709167</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/more-than-just-a-little-bit/1878764647</v>
+        <v>https://music.apple.com/us/album/dive-into-me/1879789970</v>
       </c>
       <c r="L141" t="str">
-        <v>more than just a little bit - Artemas</v>
+        <v>Dive Into Me - Alok</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>WORSHIP</v>
+        <v>more than just a little bit</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/worship/1882144650</v>
+        <v>https://music.apple.com/us/song/more-than-just-a-little-bit/1878764653</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-20</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>WORSHIP - Single</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G142" t="str">
-        <v>2:43</v>
+        <v>2:40</v>
       </c>
       <c r="H142" t="str">
-        <v>Asake</v>
+        <v>Artemas</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/asake/1436064480</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/worship/1882144646</v>
+        <v>https://music.apple.com/us/album/more-than-just-a-little-bit/1878764647</v>
       </c>
       <c r="L142" t="str">
-        <v>WORSHIP - Asake</v>
+        <v>more than just a little bit - Artemas</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Honest</v>
+        <v>WORSHIP</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/honest/1884124206</v>
+        <v>https://music.apple.com/us/song/worship/1882144650</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-20</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Honest - Single</v>
+        <v>WORSHIP - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>3:22</v>
+        <v>2:43</v>
       </c>
       <c r="H143" t="str">
-        <v>Ebony Riley</v>
+        <v>Asake</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
+        <v>https://music.apple.com/us/artist/asake/1436064480</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/honest/1884124203</v>
+        <v>https://music.apple.com/us/album/worship/1882144646</v>
       </c>
       <c r="L143" t="str">
-        <v>Honest - Ebony Riley</v>
+        <v>WORSHIP - Asake</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>6ft Under</v>
+        <v>Honest</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/6ft-under/1880796117</v>
+        <v>https://music.apple.com/us/song/honest/1884124206</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-20</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>6ft Under - Single</v>
+        <v>Honest - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>3:30</v>
+        <v>3:22</v>
       </c>
       <c r="H144" t="str">
-        <v>KELS</v>
+        <v>Ebony Riley</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/kels/1536970454</v>
+        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/6ft-under/1880796111</v>
+        <v>https://music.apple.com/us/album/honest/1884124203</v>
       </c>
       <c r="L144" t="str">
-        <v>6ft Under - KELS</v>
+        <v>Honest - Ebony Riley</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Maybe Again</v>
+        <v>6ft Under</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/maybe-again/1875112466</v>
+        <v>https://music.apple.com/us/song/6ft-under/1880796117</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-20</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>When The City Sleeps</v>
+        <v>6ft Under - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:29</v>
+        <v>3:30</v>
       </c>
       <c r="H145" t="str">
-        <v>Alex Isley</v>
+        <v>KELS</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/alex-isley/566610959</v>
+        <v>https://music.apple.com/us/artist/kels/1536970454</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/maybe-again/1875112024</v>
+        <v>https://music.apple.com/us/album/6ft-under/1880796111</v>
       </c>
       <c r="L145" t="str">
-        <v>Maybe Again - Alex Isley</v>
+        <v>6ft Under - KELS</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Trigger Happy</v>
+        <v>Maybe Again</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/trigger-happy/1883215750</v>
+        <v>https://music.apple.com/us/song/maybe-again/1875112466</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-20</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Attachment Theory</v>
+        <v>When The City Sleeps</v>
       </c>
       <c r="G146" t="str">
-        <v>3:01</v>
+        <v>3:29</v>
       </c>
       <c r="H146" t="str">
-        <v>Aubrie Sellers</v>
+        <v>Alex Isley</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/aubrie-sellers/1039090991</v>
+        <v>https://music.apple.com/us/artist/alex-isley/566610959</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/trigger-happy/1883215748</v>
+        <v>https://music.apple.com/us/album/maybe-again/1875112024</v>
       </c>
       <c r="L146" t="str">
-        <v>Trigger Happy - Aubrie Sellers</v>
+        <v>Maybe Again - Alex Isley</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>REAL ONES NEVER DIE</v>
+        <v>Trigger Happy</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/real-ones-never-die/1886092613</v>
+        <v>https://music.apple.com/us/song/trigger-happy/1883215750</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-20</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>HAVE U BN 2 HEAVEN @ NITE? - EP</v>
+        <v>Attachment Theory</v>
       </c>
       <c r="G147" t="str">
         <v>3:01</v>
       </c>
       <c r="H147" t="str">
-        <v>Kid Cudi</v>
+        <v>Aubrie Sellers</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/kid-cudi/273058501</v>
+        <v>https://music.apple.com/us/artist/aubrie-sellers/1039090991</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/real-ones-never-die/1886092612</v>
+        <v>https://music.apple.com/us/album/trigger-happy/1883215748</v>
       </c>
       <c r="L147" t="str">
-        <v>REAL ONES NEVER DIE - Kid Cudi</v>
+        <v>Trigger Happy - Aubrie Sellers</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>DON'T EVEN CALL</v>
+        <v>REAL ONES NEVER DIE</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/dont-even-call/1885914732</v>
+        <v>https://music.apple.com/us/song/real-ones-never-die/1886092613</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-20</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>SAME DIFFERENCE</v>
+        <v>HAVE U BN 2 HEAVEN @ NITE? - EP</v>
       </c>
       <c r="G148" t="str">
-        <v>3:30</v>
+        <v>3:01</v>
       </c>
       <c r="H148" t="str">
-        <v>Swae Lee</v>
+        <v>Kid Cudi</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
+        <v>https://music.apple.com/us/artist/kid-cudi/273058501</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/dont-even-call/1885914714</v>
+        <v>https://music.apple.com/us/album/real-ones-never-die/1886092612</v>
       </c>
       <c r="L148" t="str">
-        <v>DON'T EVEN CALL - Swae Lee</v>
+        <v>REAL ONES NEVER DIE - Kid Cudi</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Runnin' On E</v>
+        <v>DON'T EVEN CALL</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/runnin-on-e/1884646318</v>
+        <v>https://music.apple.com/us/song/dont-even-call/1885914732</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-20</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Runnin' On E - Single</v>
+        <v>SAME DIFFERENCE</v>
       </c>
       <c r="G149" t="str">
-        <v>2:27</v>
+        <v>3:30</v>
       </c>
       <c r="H149" t="str">
-        <v>Wyatt Flores</v>
+        <v>Swae Lee</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
+        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/runnin-on-e/1884646317</v>
+        <v>https://music.apple.com/us/album/dont-even-call/1885914714</v>
       </c>
       <c r="L149" t="str">
-        <v>Runnin' On E - Wyatt Flores</v>
+        <v>DON'T EVEN CALL - Swae Lee</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>FREESTYLE</v>
+        <v>Runnin' On E</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/freestyle/1884623617</v>
+        <v>https://music.apple.com/us/song/runnin-on-e/1884646318</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-20</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>LINAJE</v>
+        <v>Runnin' On E - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>5:36</v>
+        <v>2:27</v>
       </c>
       <c r="H150" t="str">
-        <v>Hermanos Espinoza</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
+        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/freestyle/1884623413</v>
+        <v>https://music.apple.com/us/album/runnin-on-e/1884646317</v>
       </c>
       <c r="L150" t="str">
-        <v>FREESTYLE - Hermanos Espinoza</v>
+        <v>Runnin' On E - Wyatt Flores</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Orcasitas</v>
+        <v>FREESTYLE</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/orcasitas/1882386609</v>
+        <v>https://music.apple.com/us/song/freestyle/1884623617</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-20</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Alma De Cántaro</v>
+        <v>LINAJE</v>
       </c>
       <c r="G151" t="str">
-        <v>3:23</v>
+        <v>5:36</v>
       </c>
       <c r="H151" t="str">
-        <v>marquitos</v>
+        <v>Hermanos Espinoza</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/marquitos/1778532119</v>
+        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/orcasitas/1882386365</v>
+        <v>https://music.apple.com/us/album/freestyle/1884623413</v>
       </c>
       <c r="L151" t="str">
-        <v>Orcasitas - marquitos</v>
+        <v>FREESTYLE - Hermanos Espinoza</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Vida Loca</v>
+        <v>Orcasitas</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/vida-loca/1885698516</v>
+        <v>https://music.apple.com/us/song/orcasitas/1882386609</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-20</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>FREE SPIRITS</v>
+        <v>Alma De Cántaro</v>
       </c>
       <c r="G152" t="str">
-        <v>2:35</v>
+        <v>3:23</v>
       </c>
       <c r="H152" t="str">
-        <v>CA7RIEL &amp; Paco Amoroso</v>
+        <v>marquitos</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
+        <v>https://music.apple.com/us/artist/marquitos/1778532119</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/vida-loca/1885698497</v>
+        <v>https://music.apple.com/us/album/orcasitas/1882386365</v>
       </c>
       <c r="L152" t="str">
-        <v>Vida Loca - CA7RIEL &amp; Paco Amoroso</v>
+        <v>Orcasitas - marquitos</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Honest</v>
+        <v>Vida Loca</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/honest/1867616799</v>
+        <v>https://music.apple.com/us/song/vida-loca/1885698516</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-20</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>The Weight of the Woods</v>
+        <v>FREE SPIRITS</v>
       </c>
       <c r="G153" t="str">
-        <v>3:39</v>
+        <v>2:35</v>
       </c>
       <c r="H153" t="str">
-        <v>Dermot Kennedy</v>
+        <v>CA7RIEL &amp; Paco Amoroso</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/honest/1867616617</v>
+        <v>https://music.apple.com/us/album/vida-loca/1885698497</v>
       </c>
       <c r="L153" t="str">
-        <v>Honest - Dermot Kennedy</v>
+        <v>Vida Loca - CA7RIEL &amp; Paco Amoroso</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Ruleta Rusa</v>
+        <v>Honest</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/ruleta-rusa/1868792929</v>
+        <v>https://music.apple.com/us/song/honest/1867616799</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-20</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>K de Karma (Apple Music Edition)</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G154" t="str">
-        <v>3:01</v>
+        <v>3:39</v>
       </c>
       <c r="H154" t="str">
-        <v>Kenia Os</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/ruleta-rusa/1868792704</v>
+        <v>https://music.apple.com/us/album/honest/1867616617</v>
       </c>
       <c r="L154" t="str">
-        <v>Ruleta Rusa - Kenia Os</v>
+        <v>Honest - Dermot Kennedy</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Where There's Smoke, There's Fire</v>
+        <v>Ruleta Rusa</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/where-theres-smoke-theres-fire/1873477949</v>
+        <v>https://music.apple.com/us/song/ruleta-rusa/1868792929</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-20</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Peaches!</v>
+        <v>K de Karma (Apple Music Edition)</v>
       </c>
       <c r="G155" t="str">
-        <v>5:00</v>
+        <v>3:01</v>
       </c>
       <c r="H155" t="str">
-        <v>The Black Keys</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
+        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/where-theres-smoke-theres-fire/1873477948</v>
+        <v>https://music.apple.com/us/album/ruleta-rusa/1868792704</v>
       </c>
       <c r="L155" t="str">
-        <v>Where There's Smoke, There's Fire - The Black Keys</v>
+        <v>Ruleta Rusa - Kenia Os</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Light as a Feather</v>
+        <v>Where There's Smoke, There's Fire</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/light-as-a-feather/1870989894</v>
+        <v>https://music.apple.com/us/song/where-theres-smoke-theres-fire/1873477949</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-20</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Everything Glows</v>
+        <v>Peaches!</v>
       </c>
       <c r="G156" t="str">
-        <v>3:36</v>
+        <v>5:00</v>
       </c>
       <c r="H156" t="str">
-        <v>Cannons</v>
+        <v>The Black Keys</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/light-as-a-feather/1870989672</v>
+        <v>https://music.apple.com/us/album/where-theres-smoke-theres-fire/1873477948</v>
       </c>
       <c r="L156" t="str">
-        <v>Light as a Feather - Cannons</v>
+        <v>Where There's Smoke, There's Fire - The Black Keys</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Loving One</v>
+        <v>Light as a Feather</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/loving-one/1882487874</v>
+        <v>https://music.apple.com/us/song/light-as-a-feather/1870989894</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-20</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Loving One - Single</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G157" t="str">
-        <v>3:39</v>
+        <v>3:36</v>
       </c>
       <c r="H157" t="str">
-        <v>People I’ve Met</v>
+        <v>Cannons</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/loving-one/1882487871</v>
+        <v>https://music.apple.com/us/album/light-as-a-feather/1870989672</v>
       </c>
       <c r="L157" t="str">
-        <v>Loving One - People I’ve Met</v>
+        <v>Light as a Feather - Cannons</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Both Can Be True</v>
+        <v>Loving One</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/both-can-be-true/1879642452</v>
+        <v>https://music.apple.com/us/song/loving-one/1882487874</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-20</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Both Can Be True - Single</v>
+        <v>Loving One - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:05</v>
+        <v>3:39</v>
       </c>
       <c r="H158" t="str">
-        <v>Trousdale</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/both-can-be-true/1879642449</v>
+        <v>https://music.apple.com/us/album/loving-one/1882487871</v>
       </c>
       <c r="L158" t="str">
-        <v>Both Can Be True - Trousdale</v>
+        <v>Loving One - People I’ve Met</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Buffalo 66</v>
+        <v>Both Can Be True</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/buffalo-66/1878795630</v>
+        <v>https://music.apple.com/us/song/both-can-be-true/1879642452</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-20</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Jesus loves a primadonna</v>
+        <v>Both Can Be True - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>4:27</v>
+        <v>3:05</v>
       </c>
       <c r="H159" t="str">
-        <v>Nessa Barrett</v>
+        <v>Trousdale</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/buffalo-66/1878795618</v>
+        <v>https://music.apple.com/us/album/both-can-be-true/1879642449</v>
       </c>
       <c r="L159" t="str">
-        <v>Buffalo 66 - Nessa Barrett</v>
+        <v>Both Can Be True - Trousdale</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>brb</v>
+        <v>Buffalo 66</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/brb/1884716531</v>
+        <v>https://music.apple.com/us/song/buffalo-66/1878795630</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-20</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>brb - Single</v>
+        <v>Jesus loves a primadonna</v>
       </c>
       <c r="G160" t="str">
-        <v>2:36</v>
+        <v>4:27</v>
       </c>
       <c r="H160" t="str">
-        <v>The Two Lips</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
+        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/brb/1884716521</v>
+        <v>https://music.apple.com/us/album/buffalo-66/1878795618</v>
       </c>
       <c r="L160" t="str">
-        <v>brb - The Two Lips</v>
+        <v>Buffalo 66 - Nessa Barrett</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Euphoria</v>
+        <v>brb</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/euphoria/1859028065</v>
+        <v>https://music.apple.com/us/song/brb/1884716531</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-20</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Euphoria - Single</v>
+        <v>brb - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:32</v>
+        <v>2:36</v>
       </c>
       <c r="H161" t="str">
-        <v>Talia Rae</v>
+        <v>The Two Lips</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/talia-rae/480784264</v>
+        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/euphoria/1859027872</v>
+        <v>https://music.apple.com/us/album/brb/1884716521</v>
       </c>
       <c r="L161" t="str">
-        <v>Euphoria - Talia Rae</v>
+        <v>brb - The Two Lips</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>if i'm lucky</v>
+        <v>Euphoria</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/if-im-lucky/1878512865</v>
+        <v>https://music.apple.com/us/song/euphoria/1859028065</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-20</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>better late than not at all - EP</v>
+        <v>Euphoria - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>2:57</v>
+        <v>3:32</v>
       </c>
       <c r="H162" t="str">
-        <v>Chelsea Jordan</v>
+        <v>Talia Rae</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
+        <v>https://music.apple.com/us/artist/talia-rae/480784264</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/if-im-lucky/1878512860</v>
+        <v>https://music.apple.com/us/album/euphoria/1859027872</v>
       </c>
       <c r="L162" t="str">
-        <v>if i'm lucky - Chelsea Jordan</v>
+        <v>Euphoria - Talia Rae</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Gracie</v>
+        <v>if i'm lucky</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/gracie/1863525497</v>
+        <v>https://music.apple.com/us/song/if-im-lucky/1878512865</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-20</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>F.I.G</v>
+        <v>better late than not at all - EP</v>
       </c>
       <c r="G163" t="str">
-        <v>2:54</v>
+        <v>2:57</v>
       </c>
       <c r="H163" t="str">
-        <v>Naomi Scott</v>
+        <v>Chelsea Jordan</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
+        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/gracie/1863525485</v>
+        <v>https://music.apple.com/us/album/if-im-lucky/1878512860</v>
       </c>
       <c r="L163" t="str">
-        <v>Gracie - Naomi Scott</v>
+        <v>if i'm lucky - Chelsea Jordan</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Something's Not Right Here</v>
+        <v>Gracie</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/somethings-not-right-here/1882090886</v>
+        <v>https://music.apple.com/us/song/gracie/1863525497</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-20</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Dreaming Out Loud (Deluxe Edition)</v>
+        <v>F.I.G</v>
       </c>
       <c r="G164" t="str">
-        <v>3:02</v>
+        <v>2:54</v>
       </c>
       <c r="H164" t="str">
-        <v>OneRepublic</v>
+        <v>Naomi Scott</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/onerepublic/260414340</v>
+        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/somethings-not-right-here/1882090709</v>
+        <v>https://music.apple.com/us/album/gracie/1863525485</v>
       </c>
       <c r="L164" t="str">
-        <v>Something's Not Right Here - OneRepublic</v>
+        <v>Gracie - Naomi Scott</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Dream Chaser</v>
+        <v>down under</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/dream-chaser/1884219678</v>
+        <v>https://music.apple.com/us/song/down-under/1883127406</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-20</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Dream Chaser</v>
+        <v>down under - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:14</v>
+        <v>3:24</v>
       </c>
       <c r="H165" t="str">
-        <v>Willie Nelson</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/dream-chaser/1884219677</v>
+        <v>https://music.apple.com/us/album/down-under/1883127402</v>
       </c>
       <c r="L165" t="str">
-        <v>Dream Chaser - Willie Nelson</v>
+        <v>down under - Kevian Kraemer</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Trouble</v>
+        <v>Send Me A Sign</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/trouble/1876369964</v>
+        <v>https://music.apple.com/us/song/send-me-a-sign/1883251911</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-20</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Girlfriend</v>
+        <v>Send Me A Sign - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:17</v>
+        <v>3:15</v>
       </c>
       <c r="H166" t="str">
-        <v>Grace Ives</v>
+        <v>Girlfriend, Wife</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/grace-ives/1390289298</v>
+        <v>https://music.apple.com/us/artist/girlfriend-wife/1851494782</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/trouble/1876369944</v>
+        <v>https://music.apple.com/us/album/send-me-a-sign/1883251889</v>
       </c>
       <c r="L166" t="str">
-        <v>Trouble - Grace Ives</v>
+        <v>Send Me A Sign - Girlfriend, Wife</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>judas</v>
+        <v>Something's Not Right Here</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/judas/1882829414</v>
+        <v>https://music.apple.com/us/song/somethings-not-right-here/1882090886</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-20</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>judas - Single</v>
+        <v>Dreaming Out Loud (Deluxe Edition)</v>
       </c>
       <c r="G167" t="str">
-        <v>3:31</v>
+        <v>3:02</v>
       </c>
       <c r="H167" t="str">
-        <v>Josiah Queen</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/josiah-queen/1498117530</v>
+        <v>https://music.apple.com/us/artist/onerepublic/260414340</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/judas/1882829413</v>
+        <v>https://music.apple.com/us/album/somethings-not-right-here/1882090709</v>
       </c>
       <c r="L167" t="str">
-        <v>judas - Josiah Queen</v>
+        <v>Something's Not Right Here - OneRepublic</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>JINX</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/jinx/1880173550</v>
+        <v>https://music.apple.com/us/song/dream-chaser/1884219678</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-20</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>JINX - Single</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="G168" t="str">
-        <v>2:54</v>
+        <v>3:14</v>
       </c>
       <c r="H168" t="str">
-        <v>Zacari</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/zacari/1027112445</v>
+        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/jinx/1880173549</v>
+        <v>https://music.apple.com/us/album/dream-chaser/1884219677</v>
       </c>
       <c r="L168" t="str">
-        <v>JINX - Zacari</v>
+        <v>Dream Chaser - Willie Nelson</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>se fue</v>
+        <v>Trouble</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/se-fue/1876355980</v>
+        <v>https://music.apple.com/us/song/trouble/1876369964</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-20</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Náufrago</v>
+        <v>Girlfriend</v>
       </c>
       <c r="G169" t="str">
-        <v>2:51</v>
+        <v>3:17</v>
       </c>
       <c r="H169" t="str">
-        <v>Eddy</v>
+        <v>Grace Ives</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/eddy/1779584924</v>
+        <v>https://music.apple.com/us/artist/grace-ives/1390289298</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/se-fue/1876355962</v>
+        <v>https://music.apple.com/us/album/trouble/1876369944</v>
       </c>
       <c r="L169" t="str">
-        <v>se fue - Eddy</v>
+        <v>Trouble - Grace Ives</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>The Blade</v>
+        <v>judas</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/the-blade/1884066958</v>
+        <v>https://music.apple.com/us/song/judas/1882829414</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-20</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>The Blade - Single</v>
+        <v>judas - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:15</v>
+        <v>3:31</v>
       </c>
       <c r="H170" t="str">
-        <v>Kingfishr</v>
+        <v>Josiah Queen</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
+        <v>https://music.apple.com/us/artist/josiah-queen/1498117530</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/the-blade/1884066685</v>
+        <v>https://music.apple.com/us/album/judas/1882829413</v>
       </c>
       <c r="L170" t="str">
-        <v>The Blade - Kingfishr</v>
+        <v>judas - Josiah Queen</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Metric Rules</v>
+        <v>JINX</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/metric-rules/1885609351</v>
+        <v>https://music.apple.com/us/song/jinx/1880173550</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-20</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>When Lagos Sleeps - EP</v>
+        <v>JINX - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>3:13</v>
+        <v>2:54</v>
       </c>
       <c r="H171" t="str">
-        <v>SPINALL</v>
+        <v>Zacari</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/spinall/813737832</v>
+        <v>https://music.apple.com/us/artist/zacari/1027112445</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/metric-rules/1885609347</v>
+        <v>https://music.apple.com/us/album/jinx/1880173549</v>
       </c>
       <c r="L171" t="str">
-        <v>Metric Rules - SPINALL</v>
+        <v>JINX - Zacari</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>FIGURE IT OUT</v>
+        <v>se fue</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/figure-it-out/1882873714</v>
+        <v>https://music.apple.com/us/song/se-fue/1876355980</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-20</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>FIGURE IT OUT - Single</v>
+        <v>Náufrago</v>
       </c>
       <c r="G172" t="str">
-        <v>2:15</v>
+        <v>2:51</v>
       </c>
       <c r="H172" t="str">
-        <v>ZEP</v>
+        <v>Eddy</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/zep/1582892045</v>
+        <v>https://music.apple.com/us/artist/eddy/1779584924</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/figure-it-out/1882873713</v>
+        <v>https://music.apple.com/us/album/se-fue/1876355962</v>
       </c>
       <c r="L172" t="str">
-        <v>FIGURE IT OUT - ZEP</v>
+        <v>se fue - Eddy</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Coasting (Piano Session)</v>
+        <v>The Blade</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/coasting-piano-session/1880328049</v>
+        <v>https://music.apple.com/us/song/the-blade/1884066958</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-20</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Coasting (Piano Session) - Single</v>
+        <v>The Blade - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:23</v>
+        <v>3:15</v>
       </c>
       <c r="H173" t="str">
-        <v>Hutch</v>
+        <v>Kingfishr</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/hutch/1852060852</v>
+        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/coasting-piano-session/1880328048</v>
+        <v>https://music.apple.com/us/album/the-blade/1884066685</v>
       </c>
       <c r="L173" t="str">
-        <v>Coasting (Piano Session) - Hutch</v>
+        <v>The Blade - Kingfishr</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Still Sincere (feat. PinkPantheress) [MK Dub]</v>
+        <v>Metric Rules</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress-mk-dub/1882054680</v>
+        <v>https://music.apple.com/us/song/metric-rules/1885609351</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-20</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Still Sincere (MK Dub) [feat. PinkPantheress] - Single</v>
+        <v>When Lagos Sleeps - EP</v>
       </c>
       <c r="G174" t="str">
-        <v>5:15</v>
+        <v>3:13</v>
       </c>
       <c r="H174" t="str">
-        <v>MJ Cole</v>
+        <v>SPINALL</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
+        <v>https://music.apple.com/us/artist/spinall/813737832</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress-mk-dub/1882054676</v>
+        <v>https://music.apple.com/us/album/metric-rules/1885609347</v>
       </c>
       <c r="L174" t="str">
-        <v>Still Sincere (feat. PinkPantheress) [MK Dub] - MJ Cole</v>
+        <v>Metric Rules - SPINALL</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Cyclone</v>
+        <v>FIGURE IT OUT</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/cyclone/1843578165</v>
+        <v>https://music.apple.com/us/song/figure-it-out/1882873714</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-20</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Loss</v>
+        <v>FIGURE IT OUT - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>5:33</v>
+        <v>2:15</v>
       </c>
       <c r="H175" t="str">
-        <v>Gaerea</v>
+        <v>ZEP</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
+        <v>https://music.apple.com/us/artist/zep/1582892045</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/cyclone/1843578156</v>
+        <v>https://music.apple.com/us/album/figure-it-out/1882873713</v>
       </c>
       <c r="L175" t="str">
-        <v>Cyclone - Gaerea</v>
+        <v>FIGURE IT OUT - ZEP</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Checkmate</v>
+        <v>Coasting (Piano Session)</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/checkmate/1882117113</v>
+        <v>https://music.apple.com/us/song/coasting-piano-session/1880328049</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-20</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Checkmate - Single</v>
+        <v>Coasting (Piano Session) - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>4:23</v>
+        <v>3:23</v>
       </c>
       <c r="H176" t="str">
-        <v>Blue Medusa</v>
+        <v>Hutch</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
+        <v>https://music.apple.com/us/artist/hutch/1852060852</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/checkmate/1882117111</v>
+        <v>https://music.apple.com/us/album/coasting-piano-session/1880328048</v>
       </c>
       <c r="L176" t="str">
-        <v>Checkmate - Blue Medusa</v>
+        <v>Coasting (Piano Session) - Hutch</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>DAVE</v>
+        <v>Still Sincere (feat. PinkPantheress) [MK Dub]</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/dave/1881700152</v>
+        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress-mk-dub/1882054680</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-20</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>DAVE - Single</v>
+        <v>Still Sincere (MK Dub) [feat. PinkPantheress] - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:01</v>
+        <v>5:15</v>
       </c>
       <c r="H177" t="str">
-        <v>Hulvey</v>
+        <v>MJ Cole</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
+        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/dave/1881700151</v>
+        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress-mk-dub/1882054676</v>
       </c>
       <c r="L177" t="str">
-        <v>DAVE - Hulvey</v>
+        <v>Still Sincere (feat. PinkPantheress) [MK Dub] - MJ Cole</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Change</v>
+        <v>Cyclone</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/change/1880857720</v>
+        <v>https://music.apple.com/us/song/cyclone/1843578165</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-20</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Change - Single</v>
+        <v>Loss</v>
       </c>
       <c r="G178" t="str">
-        <v>2:38</v>
+        <v>5:33</v>
       </c>
       <c r="H178" t="str">
-        <v>Stephen Stanley</v>
+        <v>Gaerea</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
+        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/change/1880857716</v>
+        <v>https://music.apple.com/us/album/cyclone/1843578156</v>
       </c>
       <c r="L178" t="str">
-        <v>Change - Stephen Stanley</v>
+        <v>Cyclone - Gaerea</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Te Entiendo</v>
+        <v>Checkmate</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/te-entiendo/1882386240</v>
+        <v>https://music.apple.com/us/song/checkmate/1882117113</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-20</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Te Entiendo - Single</v>
+        <v>Checkmate - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:05</v>
+        <v>4:23</v>
       </c>
       <c r="H179" t="str">
-        <v>Maisak</v>
+        <v>Blue Medusa</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
+        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/te-entiendo/1882386238</v>
+        <v>https://music.apple.com/us/album/checkmate/1882117111</v>
       </c>
       <c r="L179" t="str">
-        <v>Te Entiendo - Maisak</v>
+        <v>Checkmate - Blue Medusa</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>CHEVROLET 90</v>
+        <v>DAVE</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/chevrolet-90/1879599158</v>
+        <v>https://music.apple.com/us/song/dave/1881700152</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-20</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>V</v>
+        <v>DAVE - Single</v>
       </c>
       <c r="G180" t="str">
         <v>2:01</v>
       </c>
       <c r="H180" t="str">
-        <v>Rey Quinto</v>
+        <v>Hulvey</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/rey-quinto/1715073363</v>
+        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/chevrolet-90/1879599141</v>
+        <v>https://music.apple.com/us/album/dave/1881700151</v>
       </c>
       <c r="L180" t="str">
-        <v>CHEVROLET 90 - Rey Quinto</v>
+        <v>DAVE - Hulvey</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Tirabalas</v>
+        <v>Change</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/tirabalas/1877963582</v>
+        <v>https://music.apple.com/us/song/change/1880857720</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-20</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>ESSENCE #10 (Deluxe)</v>
+        <v>Change - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:53</v>
+        <v>2:38</v>
       </c>
       <c r="H181" t="str">
-        <v>Hans el Oso</v>
+        <v>Stephen Stanley</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/hans-el-oso/1619227662</v>
+        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/tirabalas/1877963565</v>
+        <v>https://music.apple.com/us/album/change/1880857716</v>
       </c>
       <c r="L181" t="str">
-        <v>Tirabalas - Hans el Oso</v>
+        <v>Change - Stephen Stanley</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>punchbowl</v>
+        <v>Te Entiendo</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/punchbowl/1883156074</v>
+        <v>https://music.apple.com/us/song/te-entiendo/1882386240</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-20</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>punchbowl - Single</v>
+        <v>Te Entiendo - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:34</v>
+        <v>3:05</v>
       </c>
       <c r="H182" t="str">
-        <v>Julio Caesar</v>
+        <v>Maisak</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
+        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/punchbowl/1883156073</v>
+        <v>https://music.apple.com/us/album/te-entiendo/1882386238</v>
       </c>
       <c r="L182" t="str">
-        <v>punchbowl - Julio Caesar</v>
+        <v>Te Entiendo - Maisak</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Wild Ride</v>
+        <v>CHEVROLET 90</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/wild-ride/1884728581</v>
+        <v>https://music.apple.com/us/song/chevrolet-90/1879599158</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-20</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Wild Ride - Single</v>
+        <v>V</v>
       </c>
       <c r="G183" t="str">
-        <v>3:41</v>
+        <v>2:01</v>
       </c>
       <c r="H183" t="str">
-        <v>Durand Bernarr</v>
+        <v>Rey Quinto</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
+        <v>https://music.apple.com/us/artist/rey-quinto/1715073363</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/wild-ride/1884728580</v>
+        <v>https://music.apple.com/us/album/chevrolet-90/1879599141</v>
       </c>
       <c r="L183" t="str">
-        <v>Wild Ride - Durand Bernarr</v>
+        <v>CHEVROLET 90 - Rey Quinto</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Lamb Chop</v>
+        <v>Tirabalas</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/lamb-chop/1881677466</v>
+        <v>https://music.apple.com/us/song/tirabalas/1877963582</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-20</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Lamb Chop - Single</v>
+        <v>ESSENCE #10 (Deluxe)</v>
       </c>
       <c r="G184" t="str">
-        <v>2:03</v>
+        <v>3:53</v>
       </c>
       <c r="H184" t="str">
-        <v>Chuckyy</v>
+        <v>Hans el Oso</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/chuckyy/1703210537</v>
+        <v>https://music.apple.com/us/artist/hans-el-oso/1619227662</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/lamb-chop/1881677465</v>
+        <v>https://music.apple.com/us/album/tirabalas/1877963565</v>
       </c>
       <c r="L184" t="str">
-        <v>Lamb Chop - Chuckyy</v>
+        <v>Tirabalas - Hans el Oso</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Free Nick</v>
+        <v>punchbowl</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/free-nick/1881667330</v>
+        <v>https://music.apple.com/us/song/punchbowl/1883156074</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-20</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Free Nick - Single</v>
+        <v>punchbowl - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:05</v>
+        <v>2:34</v>
       </c>
       <c r="H185" t="str">
-        <v>Raq baby</v>
+        <v>Julio Caesar</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/raq-baby/1712935965</v>
+        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/free-nick/1881667216</v>
+        <v>https://music.apple.com/us/album/punchbowl/1883156073</v>
       </c>
       <c r="L185" t="str">
-        <v>Free Nick - Raq baby</v>
+        <v>punchbowl - Julio Caesar</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Make Me Brand New</v>
+        <v>Wild Ride</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/make-me-brand-new/1878525836</v>
+        <v>https://music.apple.com/us/song/wild-ride/1884728581</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-20</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Make Me Brand New - Single</v>
+        <v>Wild Ride - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:06</v>
+        <v>3:41</v>
       </c>
       <c r="H186" t="str">
-        <v>Dante’ Pride</v>
+        <v>Durand Bernarr</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/dante-pride/1175536450</v>
+        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/make-me-brand-new/1878525833</v>
+        <v>https://music.apple.com/us/album/wild-ride/1884728580</v>
       </c>
       <c r="L186" t="str">
-        <v>Make Me Brand New - Dante’ Pride</v>
+        <v>Wild Ride - Durand Bernarr</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Define You</v>
+        <v>Lamb Chop</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/define-you/1877189744</v>
+        <v>https://music.apple.com/us/song/lamb-chop/1881677466</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-20</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Define You - Single</v>
+        <v>Lamb Chop - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:34</v>
+        <v>2:03</v>
       </c>
       <c r="H187" t="str">
-        <v>Luca Fogale</v>
+        <v>Chuckyy</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
+        <v>https://music.apple.com/us/artist/chuckyy/1703210537</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/define-you/1877189743</v>
+        <v>https://music.apple.com/us/album/lamb-chop/1881677465</v>
       </c>
       <c r="L187" t="str">
-        <v>Define You - Luca Fogale</v>
+        <v>Lamb Chop - Chuckyy</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>If You Change</v>
+        <v>Free Nick</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/if-you-change/1880416153</v>
+        <v>https://music.apple.com/us/song/free-nick/1881667330</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-20</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Roses</v>
+        <v>Free Nick - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>4:41</v>
+        <v>2:05</v>
       </c>
       <c r="H188" t="str">
-        <v>Widowspeak</v>
+        <v>Raq baby</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
+        <v>https://music.apple.com/us/artist/raq-baby/1712935965</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/if-you-change/1880416141</v>
+        <v>https://music.apple.com/us/album/free-nick/1881667216</v>
       </c>
       <c r="L188" t="str">
-        <v>If You Change - Widowspeak</v>
+        <v>Free Nick - Raq baby</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>What I See</v>
+        <v>Make Me Brand New</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/what-i-see/1882879437</v>
+        <v>https://music.apple.com/us/song/make-me-brand-new/1878525836</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-20</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>SYNY 3 Act II - Single</v>
+        <v>Make Me Brand New - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>2:32</v>
+        <v>3:06</v>
       </c>
       <c r="H189" t="str">
-        <v>See You Next Year</v>
+        <v>Dante’ Pride</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/see-you-next-year/1624754980</v>
+        <v>https://music.apple.com/us/artist/dante-pride/1175536450</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/what-i-see/1882879433</v>
+        <v>https://music.apple.com/us/album/make-me-brand-new/1878525833</v>
       </c>
       <c r="L189" t="str">
-        <v>What I See - See You Next Year</v>
+        <v>Make Me Brand New - Dante’ Pride</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Witching Hour</v>
+        <v>Define You</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/witching-hour/1870760652</v>
+        <v>https://music.apple.com/us/song/define-you/1877189744</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-20</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Butterfly</v>
+        <v>Define You - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:47</v>
+        <v>3:34</v>
       </c>
       <c r="H190" t="str">
-        <v>Witch Post</v>
+        <v>Luca Fogale</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/witch-post/1774955367</v>
+        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/witching-hour/1870760649</v>
+        <v>https://music.apple.com/us/album/define-you/1877189743</v>
       </c>
       <c r="L190" t="str">
-        <v>Witching Hour - Witch Post</v>
+        <v>Define You - Luca Fogale</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Actin' Tough</v>
+        <v>If You Change</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/actin-tough/1881996627</v>
+        <v>https://music.apple.com/us/song/if-you-change/1880416153</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-20</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Actin' Tough - Single</v>
+        <v>Roses</v>
       </c>
       <c r="G191" t="str">
-        <v>3:07</v>
+        <v>4:41</v>
       </c>
       <c r="H191" t="str">
-        <v>Dean Turnley</v>
+        <v>Widowspeak</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/dean-turnley/1561296990</v>
+        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/actin-tough/1881996384</v>
+        <v>https://music.apple.com/us/album/if-you-change/1880416141</v>
       </c>
       <c r="L191" t="str">
-        <v>Actin' Tough - Dean Turnley</v>
+        <v>If You Change - Widowspeak</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Coração - A COLORS SHOW</v>
+        <v>What I See</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/cora%C3%A7%C3%A3o-a-colors-show/1880127530</v>
+        <v>https://music.apple.com/us/song/what-i-see/1882879437</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-20</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Coração - A COLORS SHOW - Single</v>
+        <v>SYNY 3 Act II - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>2:52</v>
+        <v>2:32</v>
       </c>
       <c r="H192" t="str">
-        <v>Anais Cardot</v>
+        <v>See You Next Year</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
+        <v>https://music.apple.com/us/artist/see-you-next-year/1624754980</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/cora%C3%A7%C3%A3o-a-colors-show/1880127529</v>
+        <v>https://music.apple.com/us/album/what-i-see/1882879433</v>
       </c>
       <c r="L192" t="str">
-        <v>Coração - A COLORS SHOW - Anais Cardot</v>
+        <v>What I See - See You Next Year</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Rewind It</v>
+        <v>Witching Hour</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/rewind-it/1884966852</v>
+        <v>https://music.apple.com/us/song/witching-hour/1870760652</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-20</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Rewind It - Single</v>
+        <v>Butterfly</v>
       </c>
       <c r="G193" t="str">
-        <v>1:34</v>
+        <v>3:47</v>
       </c>
       <c r="H193" t="str">
-        <v>Nino Paid</v>
+        <v>Witch Post</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/nino-paid/1636385121</v>
+        <v>https://music.apple.com/us/artist/witch-post/1774955367</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/rewind-it/1884966848</v>
+        <v>https://music.apple.com/us/album/witching-hour/1870760649</v>
       </c>
       <c r="L193" t="str">
-        <v>Rewind It - Nino Paid</v>
+        <v>Witching Hour - Witch Post</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Turn It Up</v>
+        <v>Actin' Tough</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/turn-it-up/1885664396</v>
+        <v>https://music.apple.com/us/song/actin-tough/1881996627</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-20</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Turn It Up - Single</v>
+        <v>Actin' Tough - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>2:33</v>
+        <v>3:07</v>
       </c>
       <c r="H194" t="str">
-        <v>slayr</v>
+        <v>Dean Turnley</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
+        <v>https://music.apple.com/us/artist/dean-turnley/1561296990</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/turn-it-up/1885664393</v>
+        <v>https://music.apple.com/us/album/actin-tough/1881996384</v>
       </c>
       <c r="L194" t="str">
-        <v>Turn It Up - slayr</v>
+        <v>Actin' Tough - Dean Turnley</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Down</v>
+        <v>Coração - A COLORS SHOW</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/down/1884531560</v>
+        <v>https://music.apple.com/us/song/cora%C3%A7%C3%A3o-a-colors-show/1880127530</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-20</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Down - Single</v>
+        <v>Coração - A COLORS SHOW - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>2:08</v>
+        <v>2:52</v>
       </c>
       <c r="H195" t="str">
-        <v>MexikoDro</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/down/1884531558</v>
+        <v>https://music.apple.com/us/album/cora%C3%A7%C3%A3o-a-colors-show/1880127529</v>
       </c>
       <c r="L195" t="str">
-        <v>Down - MexikoDro</v>
+        <v>Coração - A COLORS SHOW - Anais Cardot</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Make It Out</v>
+        <v>Rewind It</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/make-it-out/1883117489</v>
+        <v>https://music.apple.com/us/song/rewind-it/1884966852</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-20</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Make It Out - Single</v>
+        <v>Rewind It - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>2:17</v>
+        <v>1:34</v>
       </c>
       <c r="H196" t="str">
-        <v>Trueblood</v>
+        <v>Nino Paid</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/trueblood/1688100658</v>
+        <v>https://music.apple.com/us/artist/nino-paid/1636385121</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/make-it-out/1883117392</v>
+        <v>https://music.apple.com/us/album/rewind-it/1884966848</v>
       </c>
       <c r="L196" t="str">
-        <v>Make It Out - Trueblood</v>
+        <v>Rewind It - Nino Paid</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>better than boston</v>
+        <v>Turn It Up</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/better-than-boston/1885587018</v>
+        <v>https://music.apple.com/us/song/turn-it-up/1885664396</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-20</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>better than boston - Single</v>
+        <v>Turn It Up - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>3:02</v>
+        <v>2:33</v>
       </c>
       <c r="H197" t="str">
-        <v>Tom Siletto</v>
+        <v>slayr</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/tom-siletto/1530304047</v>
+        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/better-than-boston/1885587016</v>
+        <v>https://music.apple.com/us/album/turn-it-up/1885664393</v>
       </c>
       <c r="L197" t="str">
-        <v>better than boston - Tom Siletto</v>
+        <v>Turn It Up - slayr</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>So Much Beauty (Around Us)</v>
+        <v>Down</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/so-much-beauty-around-us/1880038915</v>
+        <v>https://music.apple.com/us/song/down/1884531560</v>
       </c>
       <c r="D198" t="str">
         <v>2026-03-20</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>So Much Beauty (Around Us) - Single</v>
+        <v>Down - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>2:34</v>
+        <v>2:08</v>
       </c>
       <c r="H198" t="str">
-        <v>Lost Frequencies</v>
+        <v>MexikoDro</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/lost-frequencies/877792512</v>
+        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/so-much-beauty-around-us/1880038907</v>
+        <v>https://music.apple.com/us/album/down/1884531558</v>
       </c>
       <c r="L198" t="str">
-        <v>So Much Beauty (Around Us) - Lost Frequencies</v>
+        <v>Down - MexikoDro</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>All I Need</v>
+        <v>Make It Out</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/all-i-need/1878185372</v>
+        <v>https://music.apple.com/us/song/make-it-out/1883117489</v>
       </c>
       <c r="D199" t="str">
         <v>2026-03-20</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>All I Need - Single</v>
+        <v>Make It Out - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>3:06</v>
+        <v>2:17</v>
       </c>
       <c r="H199" t="str">
-        <v>GRiZ</v>
+        <v>Trueblood</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/griz/980722716</v>
+        <v>https://music.apple.com/us/artist/trueblood/1688100658</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/all-i-need/1878185371</v>
+        <v>https://music.apple.com/us/album/make-it-out/1883117392</v>
       </c>
       <c r="L199" t="str">
-        <v>All I Need - GRiZ</v>
+        <v>Make It Out - Trueblood</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Weeping Tones</v>
+        <v>better than boston</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/weeping-tones/1863532922</v>
+        <v>https://music.apple.com/us/song/better-than-boston/1885587018</v>
       </c>
       <c r="D200" t="str">
         <v>2026-03-20</v>
@@ -7975,68 +7975,182 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Peace In Place</v>
+        <v>better than boston - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>2:59</v>
+        <v>3:02</v>
       </c>
       <c r="H200" t="str">
-        <v>Poison the Well</v>
+        <v>Tom Siletto</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/poison-the-well/1710155</v>
+        <v>https://music.apple.com/us/artist/tom-siletto/1530304047</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/weeping-tones/1863532634</v>
+        <v>https://music.apple.com/us/album/better-than-boston/1885587016</v>
       </c>
       <c r="L200" t="str">
-        <v>Weeping Tones - Poison the Well</v>
+        <v>better than boston - Tom Siletto</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
+        <v>So Much Beauty (Around Us)</v>
+      </c>
+      <c r="B201" t="str">
+        <v/>
+      </c>
+      <c r="C201" t="str">
+        <v>https://music.apple.com/us/song/so-much-beauty-around-us/1880038915</v>
+      </c>
+      <c r="D201" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="E201" t="str">
+        <v/>
+      </c>
+      <c r="F201" t="str">
+        <v>So Much Beauty (Around Us) - Single</v>
+      </c>
+      <c r="G201" t="str">
+        <v>2:34</v>
+      </c>
+      <c r="H201" t="str">
+        <v>Lost Frequencies</v>
+      </c>
+      <c r="I201" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J201" t="str">
+        <v>https://music.apple.com/us/artist/lost-frequencies/877792512</v>
+      </c>
+      <c r="K201" t="str">
+        <v>https://music.apple.com/us/album/so-much-beauty-around-us/1880038907</v>
+      </c>
+      <c r="L201" t="str">
+        <v>So Much Beauty (Around Us) - Lost Frequencies</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>All I Need</v>
+      </c>
+      <c r="B202" t="str">
+        <v/>
+      </c>
+      <c r="C202" t="str">
+        <v>https://music.apple.com/us/song/all-i-need/1878185372</v>
+      </c>
+      <c r="D202" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="E202" t="str">
+        <v/>
+      </c>
+      <c r="F202" t="str">
+        <v>All I Need - Single</v>
+      </c>
+      <c r="G202" t="str">
+        <v>3:06</v>
+      </c>
+      <c r="H202" t="str">
+        <v>GRiZ</v>
+      </c>
+      <c r="I202" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J202" t="str">
+        <v>https://music.apple.com/us/artist/griz/980722716</v>
+      </c>
+      <c r="K202" t="str">
+        <v>https://music.apple.com/us/album/all-i-need/1878185371</v>
+      </c>
+      <c r="L202" t="str">
+        <v>All I Need - GRiZ</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>Weeping Tones</v>
+      </c>
+      <c r="B203" t="str">
+        <v/>
+      </c>
+      <c r="C203" t="str">
+        <v>https://music.apple.com/us/song/weeping-tones/1863532922</v>
+      </c>
+      <c r="D203" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="E203" t="str">
+        <v/>
+      </c>
+      <c r="F203" t="str">
+        <v>Peace In Place</v>
+      </c>
+      <c r="G203" t="str">
+        <v>2:59</v>
+      </c>
+      <c r="H203" t="str">
+        <v>Poison the Well</v>
+      </c>
+      <c r="I203" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J203" t="str">
+        <v>https://music.apple.com/us/artist/poison-the-well/1710155</v>
+      </c>
+      <c r="K203" t="str">
+        <v>https://music.apple.com/us/album/weeping-tones/1863532634</v>
+      </c>
+      <c r="L203" t="str">
+        <v>Weeping Tones - Poison the Well</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
         <v>Promise You This</v>
       </c>
-      <c r="B201" t="str">
-        <v/>
-      </c>
-      <c r="C201" t="str">
+      <c r="B204" t="str">
+        <v/>
+      </c>
+      <c r="C204" t="str">
         <v>https://music.apple.com/us/song/promise-you-this/1862225614</v>
       </c>
-      <c r="D201" t="str">
-        <v>2026-03-20</v>
-      </c>
-      <c r="E201" t="str">
-        <v/>
-      </c>
-      <c r="F201" t="str">
+      <c r="D204" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="E204" t="str">
+        <v/>
+      </c>
+      <c r="F204" t="str">
         <v>Goliath</v>
       </c>
-      <c r="G201" t="str">
+      <c r="G204" t="str">
         <v>5:19</v>
       </c>
-      <c r="H201" t="str">
+      <c r="H204" t="str">
         <v>Exodus</v>
       </c>
-      <c r="I201" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J201" t="str">
+      <c r="I204" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J204" t="str">
         <v>https://music.apple.com/us/artist/exodus/1448557080</v>
       </c>
-      <c r="K201" t="str">
+      <c r="K204" t="str">
         <v>https://music.apple.com/us/album/promise-you-this/1862225385</v>
       </c>
-      <c r="L201" t="str">
+      <c r="L204" t="str">
         <v>Promise You This - Exodus</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L201"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L204"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -477,19 +477,19 @@
         <v>Nick Carter - Love Life Tragedy</v>
       </c>
       <c r="B3" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:31</v>
@@ -515,19 +515,19 @@
         <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=033viNHogN4</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:38</v>
@@ -559,7 +559,7 @@
         <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1237,19 +1237,19 @@
         <v>Bishop Briggs - River (10 Years Later)</v>
       </c>
       <c r="B23" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>3:46</v>
@@ -1275,19 +1275,19 @@
         <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G24" t="str">
         <v>2:42</v>
@@ -1313,19 +1313,19 @@
         <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
       </c>
       <c r="B25" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G25" t="str">
         <v>2:31</v>
@@ -1351,19 +1351,19 @@
         <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>3:14</v>
@@ -1389,19 +1389,19 @@
         <v>Allison Russell - Rainbows (Official Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G27" t="str">
         <v>3:22</v>
@@ -1427,19 +1427,19 @@
         <v>We Three - Love Who You Love (Official Audio)</v>
       </c>
       <c r="B28" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G28" t="str">
         <v>3:43</v>
@@ -1465,19 +1465,19 @@
         <v>paris jackson - zombies in love</v>
       </c>
       <c r="B29" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G29" t="str">
         <v>2:54</v>
@@ -1503,19 +1503,19 @@
         <v>Kane Brown - Woman (Official Music Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G30" t="str">
         <v>2:46</v>
@@ -1541,19 +1541,19 @@
         <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>3:37</v>
@@ -1579,19 +1579,19 @@
         <v>Malcolm Todd - Breathe (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G32" t="str">
         <v>2:57</v>
@@ -1617,19 +1617,19 @@
         <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G33" t="str">
         <v>3:38</v>
@@ -1655,19 +1655,19 @@
         <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
       </c>
       <c r="B34" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G34" t="str">
         <v>4:29</v>
@@ -1693,19 +1693,19 @@
         <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
       </c>
       <c r="B35" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>4:28</v>
@@ -1731,19 +1731,19 @@
         <v>aron! - Wonderful Thing (Piano)</v>
       </c>
       <c r="B36" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>3:26</v>
@@ -1769,19 +1769,19 @@
         <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
       </c>
       <c r="B37" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G37" t="str">
         <v>3:51</v>
@@ -1807,19 +1807,19 @@
         <v>Sunday (1994) - The Fairground</v>
       </c>
       <c r="B38" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G38" t="str">
         <v>2:49</v>
@@ -1845,19 +1845,19 @@
         <v>Owen Riegling - In The Feeling (Visualizer)</v>
       </c>
       <c r="B39" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G39" t="str">
         <v>4:16</v>
@@ -1883,19 +1883,19 @@
         <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>4:16</v>
@@ -1921,19 +1921,19 @@
         <v>Maverick Sabre - 8 Stages</v>
       </c>
       <c r="B41" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G41" t="str">
         <v>3:25</v>
@@ -1965,7 +1965,7 @@
         <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2187,19 +2187,19 @@
         <v>Natalie Jane - sabotage (Lyric Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G48" t="str">
         <v>2:57</v>
@@ -2231,7 +2231,7 @@
         <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2339,19 +2339,19 @@
         <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
       </c>
       <c r="B52" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G52" t="str">
         <v>3:34</v>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2415,19 +2415,19 @@
         <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E54" t="str">
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G54" t="str">
         <v>4:58</v>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=366CV87TguE</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3935,19 +3935,19 @@
         <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B94" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G94" t="str">
         <v>3:32</v>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/swim/1868862384</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/click-clack-symphony-feat-hans-zimmer/1871085694</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/loving-life-again/1869436847</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/rethink-some-things/1862634795</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/trankaito/1886206698</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/leak-it/1881685399</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/luvagirl/1882867562</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/d33p3r/1876874356</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/let-king-tonka-talk/1886559004</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/dont-hate-me/1886125791</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/pongo/1882157609</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/botero/1884672859</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/distance/1882713727</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/riptides/1878362645</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/2-0/1868862380</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/6ixer-party/1880492403</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/highest/1882162060</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/better-than-yours-feat-youngboy-never-broke-again/1885598075</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/so-what/1870703328</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/girl-of-your-dreams-live-at-apple-music-radio/1886190880</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/running-to-pain/1876521161</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/pinterest-spanish/1885472606</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/business-personal-intro/1886539096</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/bird-flu/1884792159</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/lighter/1884704638</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/wide-awake/1881700925</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/dont-make-me-love-u/1885895137</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/dinner-party/1884418570</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/normal/1868862387</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/die-living/1884752889</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/heaven-on-earth/1882808097</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/an-apple-a-day/1885590382</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/out-late/1884478039</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/be-with-you/1885607727</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/first-red-rays/1882105294</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/caught-in-the-echo/1877913491</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/little-by-little/1879889876</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/montgomery-county/1862624758</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/dive-into-me/1879790158</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/more-than-just-a-little-bit/1878764653</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/worship/1882144650</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/honest/1884124206</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/6ft-under/1880796117</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/maybe-again/1875112466</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/trigger-happy/1883215750</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/real-ones-never-die/1886092613</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/dont-even-call/1885914732</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/runnin-on-e/1884646318</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/freestyle/1884623617</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/orcasitas/1882386609</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/vida-loca/1885698516</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/honest/1867616799</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/ruleta-rusa/1868792929</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/where-theres-smoke-theres-fire/1873477949</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/light-as-a-feather/1870989894</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/loving-one/1882487874</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/both-can-be-true/1879642452</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/buffalo-66/1878795630</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/brb/1884716531</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/euphoria/1859028065</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/if-im-lucky/1878512865</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/gracie/1863525497</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/down-under/1883127406</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/send-me-a-sign/1883251911</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/somethings-not-right-here/1882090886</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/dream-chaser/1884219678</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/trouble/1876369964</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/judas/1882829414</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/jinx/1880173550</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/se-fue/1876355980</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/the-blade/1884066958</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/metric-rules/1885609351</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/figure-it-out/1882873714</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/coasting-piano-session/1880328049</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress-mk-dub/1882054680</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/cyclone/1843578165</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/checkmate/1882117113</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/dave/1881700152</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/change/1880857720</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/te-entiendo/1882386240</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/chevrolet-90/1879599158</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/tirabalas/1877963582</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/punchbowl/1883156074</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/wild-ride/1884728581</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/lamb-chop/1881677466</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/free-nick/1881667330</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/make-me-brand-new/1878525836</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/define-you/1877189744</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/if-you-change/1880416153</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/what-i-see/1882879437</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/witching-hour/1870760652</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/actin-tough/1881996627</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -7779,7 +7779,7 @@
         <v>https://music.apple.com/us/song/cora%C3%A7%C3%A3o-a-colors-show/1880127530</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -7817,7 +7817,7 @@
         <v>https://music.apple.com/us/song/rewind-it/1884966852</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -7855,7 +7855,7 @@
         <v>https://music.apple.com/us/song/turn-it-up/1885664396</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -7893,7 +7893,7 @@
         <v>https://music.apple.com/us/song/down/1884531560</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E198" t="str">
         <v/>
@@ -7931,7 +7931,7 @@
         <v>https://music.apple.com/us/song/make-it-out/1883117489</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E199" t="str">
         <v/>
@@ -7969,7 +7969,7 @@
         <v>https://music.apple.com/us/song/better-than-boston/1885587018</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E200" t="str">
         <v/>
@@ -8007,7 +8007,7 @@
         <v>https://music.apple.com/us/song/so-much-beauty-around-us/1880038915</v>
       </c>
       <c r="D201" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E201" t="str">
         <v/>
@@ -8045,7 +8045,7 @@
         <v>https://music.apple.com/us/song/all-i-need/1878185372</v>
       </c>
       <c r="D202" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E202" t="str">
         <v/>
@@ -8083,7 +8083,7 @@
         <v>https://music.apple.com/us/song/weeping-tones/1863532922</v>
       </c>
       <c r="D203" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E203" t="str">
         <v/>
@@ -8121,7 +8121,7 @@
         <v>https://music.apple.com/us/song/promise-you-this/1862225614</v>
       </c>
       <c r="D204" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E204" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
@@ -1161,7 +1161,7 @@
         <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G21" t="str">
         <v>2:39</v>
@@ -1199,7 +1199,7 @@
         <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
       </c>
       <c r="B22" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G22" t="str">
         <v>5:08</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
@@ -1123,7 +1123,7 @@
         <v>Rick Astley - Waiting On You (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>3:51</v>
@@ -3897,7 +3897,7 @@
         <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B93" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G93" t="str">
         <v>3:11</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:17</v>
@@ -2035,7 +2035,7 @@
         <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G44" t="str">
         <v>3:58</v>
@@ -2073,7 +2073,7 @@
         <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
       </c>
       <c r="B45" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G45" t="str">
         <v>3:25</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
@@ -1047,7 +1047,7 @@
         <v>Holly Humberstone - Cruel World</v>
       </c>
       <c r="B18" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G18" t="str">
         <v>3:34</v>
@@ -1085,7 +1085,7 @@
         <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G19" t="str">
         <v>2:50</v>
@@ -2111,7 +2111,7 @@
         <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B46" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G46" t="str">
         <v>4:09</v>
@@ -2149,7 +2149,7 @@
         <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G47" t="str">
         <v>2:08</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
@@ -553,7 +553,7 @@
         <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
       </c>
       <c r="B5" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G5" t="str">
         <v>4:11</v>
@@ -591,7 +591,7 @@
         <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
       </c>
       <c r="B6" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G6" t="str">
         <v>2:57</v>
@@ -629,7 +629,7 @@
         <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B7" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:47</v>
@@ -667,7 +667,7 @@
         <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B8" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G8" t="str">
         <v>7:10</v>
@@ -705,7 +705,7 @@
         <v>Grace Enger - Give A Little (Live Performance)</v>
       </c>
       <c r="B9" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G9" t="str">
         <v>3:06</v>
@@ -743,7 +743,7 @@
         <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
       </c>
       <c r="B10" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:05</v>
@@ -781,7 +781,7 @@
         <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G11" t="str">
         <v>3:12</v>
@@ -819,7 +819,7 @@
         <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B12" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G12" t="str">
         <v>9:11</v>
@@ -857,7 +857,7 @@
         <v>SIENNA SPIRO - The Visitor</v>
       </c>
       <c r="B13" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G13" t="str">
         <v>3:49</v>
@@ -895,7 +895,7 @@
         <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
       </c>
       <c r="B14" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G14" t="str">
         <v>3:28</v>
@@ -933,7 +933,7 @@
         <v>Martin Garrix - Catharina (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G15" t="str">
         <v>3:31</v>
@@ -971,7 +971,7 @@
         <v>Baby Queen - Feel Something (Official Visualiser)</v>
       </c>
       <c r="B16" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G16" t="str">
         <v>3:11</v>
@@ -1009,7 +1009,7 @@
         <v>HAUSER - Hungarian Dance No. 5</v>
       </c>
       <c r="B17" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>2:27</v>
@@ -1997,7 +1997,7 @@
         <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
       </c>
       <c r="B43" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G43" t="str">
         <v>3:57</v>
@@ -2225,7 +2225,7 @@
         <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B49" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G49" t="str">
         <v>3:13</v>
@@ -2263,7 +2263,7 @@
         <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B50" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G50" t="str">
         <v>4:12</v>
@@ -2301,7 +2301,7 @@
         <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
       </c>
       <c r="B51" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G51" t="str">
         <v>3:57</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week03/titles.xlsx
@@ -1959,7 +1959,7 @@
         <v>Amanda Jordan - What Else Is New</v>
       </c>
       <c r="B42" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G42" t="str">
         <v>2:50</v>
@@ -3859,7 +3859,7 @@
         <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B92" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G92" t="str">
         <v>3:00</v>
